--- a/model/wong_model.xlsx
+++ b/model/wong_model.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Inputs" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="BalanceSheet" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Tax" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Projection" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Outputs" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="175">
   <si>
     <t xml:space="preserve">Wong Family model — INPUTS</t>
   </si>
@@ -171,6 +173,57 @@
     <t xml:space="preserve">Pete, C&amp;SD HES 2024/25 top quartile</t>
   </si>
   <si>
+    <t xml:space="preserve">MODEL LEVERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio return — plan (nominal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mix 2: 40% eq @6% + 60% ladder @4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio return — status quo (nominal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unmanaged, cash-heavy. TEAM TO AGREE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency reserve target (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs 30.5 today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuity purchase cost at 2037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pete: MPF 2.31M (A) + 1.81M (C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuity income (HKMC, annual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pete: HKMC payout at 65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education — overseas annual (today)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case high end, conservative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education — years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-year degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance premiums (Lookbua, TBC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDER — reduces surplus</t>
+  </si>
+  <si>
     <t xml:space="preserve">DATES</t>
   </si>
   <si>
@@ -373,19 +426,144 @@
   </si>
   <si>
     <t xml:space="preserve">SURPLUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-by-year projection 2026-2072 — every cell driven by the Inputs tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black = formula. Change nothing here; change Inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Living exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retire spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuity inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investment return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuity purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTPUTS — the only numbers that go in the proposal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green = pulled from another tab. Quote these, not your own arithmetic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSITION TODAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parents' investable pool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual surplus (after tax, MPF, premiums)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency reserve, months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple — separate assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couple — joint assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saving from separate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio at Adrian's retirement (2037, nominal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio at Carmen 89 (2066)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio at Carmen 95 (2072)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio at 2037 in TODAY money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirement need at 2037 (today money)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funded ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total education cost (nominal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money lasts to 89? (deterministic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money lasts to 95? (deterministic)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,8 +628,15 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,13 +646,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -512,7 +703,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -585,6 +776,38 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,7 +837,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -837,7 +1060,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -1185,8 +1408,8 @@
       <c r="A35" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="9" t="n">
-        <v>2026</v>
+      <c r="B35" s="6" t="n">
+        <v>0.048</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>51</v>
@@ -1196,55 +1419,151 @@
       <c r="A36" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="9" t="n">
-        <v>2037</v>
+      <c r="B36" s="6" t="n">
+        <v>0.042</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>2039</v>
+        <v>12</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="9" t="n">
-        <v>2028</v>
+        <v>56</v>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>4120000</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>2066</v>
+        <v>58</v>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>268000</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>2039</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>2066</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="9" t="n">
         <v>2072</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>59</v>
+      <c r="D49" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1272,18 +1591,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>620000</v>
@@ -1291,7 +1610,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>1480000</v>
@@ -1299,7 +1618,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>400000</v>
@@ -1307,7 +1626,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">SUM(B4:B6)</f>
@@ -1316,13 +1635,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>1000000</v>
@@ -1330,7 +1649,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>1350000</v>
@@ -1338,7 +1657,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>900000</v>
@@ -1346,7 +1665,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>700000</v>
@@ -1354,7 +1673,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>450000</v>
@@ -1362,7 +1681,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>800000</v>
@@ -1370,7 +1689,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>1050000</v>
@@ -1378,7 +1697,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>620000</v>
@@ -1386,7 +1705,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>180000</v>
@@ -1394,7 +1713,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>500000</v>
@@ -1402,7 +1721,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>420000</v>
@@ -1410,7 +1729,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">SUM(B9:B19)</f>
@@ -1419,13 +1738,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>11500000</v>
@@ -1433,7 +1752,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>5000000</v>
@@ -1441,7 +1760,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>220000</v>
@@ -1449,7 +1768,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B25" s="11" t="n">
         <f aca="false">SUM(B22:B24)</f>
@@ -1458,13 +1777,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>1800000</v>
@@ -1472,7 +1791,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>900000</v>
@@ -1480,7 +1799,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>85000</v>
@@ -1488,7 +1807,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B30" s="11" t="n">
         <f aca="false">SUM(B27:B29)</f>
@@ -1497,7 +1816,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B32" s="12" t="n">
         <f aca="false">B7+B20+B25</f>
@@ -1506,7 +1825,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B33" s="12" t="n">
         <f aca="false">B32-B30</f>
@@ -1515,7 +1834,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B35" s="13" t="n">
         <f aca="false">B33-24405000</f>
@@ -1524,7 +1843,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B37" s="12" t="n">
         <f aca="false">B7+B20-B17-B18</f>
@@ -1556,17 +1875,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B4" s="14" t="n">
         <f aca="false">BalanceSheet!B27*Inputs!$B$25</f>
@@ -1576,21 +1895,21 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15"/>
       <c r="B6" s="15" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">Inputs!$B$27+Inputs!$B$28</f>
@@ -1611,7 +1930,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">-Inputs!$B$22</f>
@@ -1632,7 +1951,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">-$B$4/2</f>
@@ -1652,7 +1971,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">SUM(B7:B9)</f>
@@ -1673,7 +1992,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">-(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)</f>
@@ -1694,7 +2013,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">MAX(B10+B11,0)</f>
@@ -1715,7 +2034,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">IF(B12&gt;200000,Inputs!$B$24+(B12-200000)*Inputs!$B$23,IF(B12&gt;150000,9000+(B12-150000)*0.14,IF(B12&gt;100000,4000+(B12-100000)*0.1,IF(B12&gt;50000,1000+(B12-50000)*0.06,B12*0.02))))</f>
@@ -1736,7 +2055,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B15" s="17" t="n">
         <f aca="false">B13+C13</f>
@@ -1745,7 +2064,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">D13</f>
@@ -1754,7 +2073,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B17" s="12" t="n">
         <f aca="false">B16-B15</f>
@@ -1763,7 +2082,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B19" s="13" t="n">
         <f aca="false">B15-181770</f>
@@ -1772,7 +2091,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">B16-199770</f>
@@ -1781,12 +2100,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B23" s="14" t="n">
         <f aca="false">D7</f>
@@ -1795,7 +2114,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B24" s="14" t="n">
         <f aca="false">-B15</f>
@@ -1804,7 +2123,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">D8</f>
@@ -1813,7 +2132,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B26" s="14" t="n">
         <f aca="false">-Inputs!$B$31</f>
@@ -1822,11 +2141,3917 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B27" s="17" t="n">
         <f aca="false">SUM(B23:B26)</f>
         <v>718230</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:S50"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="4" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <f aca="false">$A4-1972</f>
+        <v>54</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <f aca="false">$A4-1977</f>
+        <v>49</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <f aca="false">IF($A4&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A4-Inputs!$B$44),0)</f>
+        <v>1200000</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <f aca="false">IF($A4&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A4-Inputs!$B$44),0)</f>
+        <v>720000</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A4-Inputs!$B$44)</f>
+        <v>395000</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A4-Inputs!$B$44)</f>
+        <v>145000</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <f aca="false">IF(D4=0,0,IF(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)&gt;200000,Inputs!$B$24+(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)-200000)*Inputs!$B$23,IF(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)&gt;150000,9000+(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)-150000)*0.14,IF(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)&gt;100000,4000+(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)-100000)*0.1,IF(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)&gt;50000,1000+(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0)-50000)*0.06,MAX(MAX(D4-Inputs!$B$22-Tax!$B$4/2-F4,0),0)*0.02)))))</f>
+        <v>110435</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <f aca="false">IF(E4=0,0,IF(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)&gt;200000,Inputs!$B$24+(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)-200000)*Inputs!$B$23,IF(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)&gt;150000,9000+(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)-150000)*0.14,IF(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)&gt;100000,4000+(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)-100000)*0.1,IF(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)&gt;50000,1000+(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0)-50000)*0.06,MAX(MAX(E4-Inputs!$B$22-Tax!$B$4/2-G4,0),0)*0.02)))))</f>
+        <v>71335</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <f aca="false">IF(D4&gt;0,Inputs!$B$22,0)+IF(E4&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <f aca="false">IF($A4&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A4-Inputs!$B$44),0)</f>
+        <v>984000</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <f aca="false">IF(AND($A4&gt;=Inputs!$B$47,$A4&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A4-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="16" t="n">
+        <f aca="false">IF($A4&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A4-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <f aca="false">IF($A4&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="16" t="n">
+        <f aca="false">D4+E4-H4-I4-J4-K4-L4-M4+N4-Inputs!$B$42</f>
+        <v>718230</v>
+      </c>
+      <c r="P4" s="16" t="n">
+        <f aca="false">BalanceSheet!$B$37</f>
+        <v>9790000</v>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <f aca="false">P4*Inputs!$B$35</f>
+        <v>469920</v>
+      </c>
+      <c r="R4" s="16" t="n">
+        <f aca="false">IF($A4=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <f aca="false">MAX(P4+Q4+O4+R4,0)</f>
+        <v>10978150</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <f aca="false">$A5-1972</f>
+        <v>55</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <f aca="false">$A5-1977</f>
+        <v>50</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">IF($A5&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A5-Inputs!$B$44),0)</f>
+        <v>1236000</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <f aca="false">IF($A5&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A5-Inputs!$B$44),0)</f>
+        <v>741600</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A5-Inputs!$B$44)</f>
+        <v>404875</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A5-Inputs!$B$44)</f>
+        <v>148625</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <f aca="false">IF(D5=0,0,IF(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)&gt;200000,Inputs!$B$24+(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)-200000)*Inputs!$B$23,IF(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)&gt;150000,9000+(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)-150000)*0.14,IF(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)&gt;100000,4000+(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)-100000)*0.1,IF(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)&gt;50000,1000+(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0)-50000)*0.06,MAX(MAX(D5-Inputs!$B$22-Tax!$B$4/2-F5,0),0)*0.02)))))</f>
+        <v>114876.25</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <f aca="false">IF(E5=0,0,IF(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)&gt;200000,Inputs!$B$24+(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)-200000)*Inputs!$B$23,IF(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)&gt;150000,9000+(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)-150000)*0.14,IF(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)&gt;100000,4000+(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)-100000)*0.1,IF(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)&gt;50000,1000+(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0)-50000)*0.06,MAX(MAX(E5-Inputs!$B$22-Tax!$B$4/2-G5,0),0)*0.02)))))</f>
+        <v>74390.75</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <f aca="false">IF(D5&gt;0,Inputs!$B$22,0)+IF(E5&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <f aca="false">IF($A5&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A5-Inputs!$B$44),0)</f>
+        <v>1008600</v>
+      </c>
+      <c r="L5" s="16" t="n">
+        <f aca="false">IF(AND($A5&gt;=Inputs!$B$47,$A5&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A5-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <f aca="false">IF($A5&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A5-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <f aca="false">IF($A5&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <f aca="false">D5+E5-H5-I5-J5-K5-L5-M5+N5-Inputs!$B$42</f>
+        <v>743733</v>
+      </c>
+      <c r="P5" s="16" t="n">
+        <f aca="false">S4</f>
+        <v>10978150</v>
+      </c>
+      <c r="Q5" s="16" t="n">
+        <f aca="false">P5*Inputs!$B$35</f>
+        <v>526951.2</v>
+      </c>
+      <c r="R5" s="16" t="n">
+        <f aca="false">IF($A5=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="16" t="n">
+        <f aca="false">MAX(P5+Q5+O5+R5,0)</f>
+        <v>12248834.2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <f aca="false">$A6-1972</f>
+        <v>56</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <f aca="false">$A6-1977</f>
+        <v>51</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">IF($A6&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A6-Inputs!$B$44),0)</f>
+        <v>1273080</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <f aca="false">IF($A6&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A6-Inputs!$B$44),0)</f>
+        <v>763848</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A6-Inputs!$B$44)</f>
+        <v>414996.875</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A6-Inputs!$B$44)</f>
+        <v>152340.625</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <f aca="false">IF(D6=0,0,IF(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)&gt;200000,Inputs!$B$24+(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)-200000)*Inputs!$B$23,IF(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)&gt;150000,9000+(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)-150000)*0.14,IF(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)&gt;100000,4000+(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)-100000)*0.1,IF(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)&gt;50000,1000+(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0)-50000)*0.06,MAX(MAX(D6-Inputs!$B$22-Tax!$B$4/2-F6,0),0)*0.02)))))</f>
+        <v>119459.13125</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <f aca="false">IF(E6=0,0,IF(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)&gt;200000,Inputs!$B$24+(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)-200000)*Inputs!$B$23,IF(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)&gt;150000,9000+(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)-150000)*0.14,IF(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)&gt;100000,4000+(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)-100000)*0.1,IF(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)&gt;50000,1000+(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0)-50000)*0.06,MAX(MAX(E6-Inputs!$B$22-Tax!$B$4/2-G6,0),0)*0.02)))))</f>
+        <v>77541.25375</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <f aca="false">IF(D6&gt;0,Inputs!$B$22,0)+IF(E6&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <f aca="false">IF($A6&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A6-Inputs!$B$44),0)</f>
+        <v>1033815</v>
+      </c>
+      <c r="L6" s="16" t="n">
+        <f aca="false">IF(AND($A6&gt;=Inputs!$B$47,$A6&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A6-Inputs!$B$44),0)</f>
+        <v>661500</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <f aca="false">IF($A6&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A6-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <f aca="false">IF($A6&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="16" t="n">
+        <f aca="false">D6+E6-H6-I6-J6-K6-L6-M6+N6-Inputs!$B$42</f>
+        <v>108612.615</v>
+      </c>
+      <c r="P6" s="16" t="n">
+        <f aca="false">S5</f>
+        <v>12248834.2</v>
+      </c>
+      <c r="Q6" s="16" t="n">
+        <f aca="false">P6*Inputs!$B$35</f>
+        <v>587944.0416</v>
+      </c>
+      <c r="R6" s="16" t="n">
+        <f aca="false">IF($A6=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="16" t="n">
+        <f aca="false">MAX(P6+Q6+O6+R6,0)</f>
+        <v>12945390.8566</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <f aca="false">$A7-1972</f>
+        <v>57</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <f aca="false">$A7-1977</f>
+        <v>52</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">IF($A7&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A7-Inputs!$B$44),0)</f>
+        <v>1311272.4</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">IF($A7&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A7-Inputs!$B$44),0)</f>
+        <v>786763.44</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A7-Inputs!$B$44)</f>
+        <v>425371.796875</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A7-Inputs!$B$44)</f>
+        <v>156149.140625</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <f aca="false">IF(D7=0,0,IF(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)&gt;200000,Inputs!$B$24+(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)-200000)*Inputs!$B$23,IF(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)&gt;150000,9000+(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)-150000)*0.14,IF(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)&gt;100000,4000+(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)-100000)*0.1,IF(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)&gt;50000,1000+(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0)-50000)*0.06,MAX(MAX(D7-Inputs!$B$22-Tax!$B$4/2-F7,0),0)*0.02)))))</f>
+        <v>124188.10253125</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <f aca="false">IF(E7=0,0,IF(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)&gt;200000,Inputs!$B$24+(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)-200000)*Inputs!$B$23,IF(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)&gt;150000,9000+(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)-150000)*0.14,IF(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)&gt;100000,4000+(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)-100000)*0.1,IF(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)&gt;50000,1000+(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0)-50000)*0.06,MAX(MAX(E7-Inputs!$B$22-Tax!$B$4/2-G7,0),0)*0.02)))))</f>
+        <v>80789.43089375</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <f aca="false">IF(D7&gt;0,Inputs!$B$22,0)+IF(E7&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <f aca="false">IF($A7&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A7-Inputs!$B$44),0)</f>
+        <v>1059660.375</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <f aca="false">IF(AND($A7&gt;=Inputs!$B$47,$A7&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A7-Inputs!$B$44),0)</f>
+        <v>694575</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <f aca="false">IF($A7&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A7-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <f aca="false">IF($A7&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <f aca="false">D7+E7-H7-I7-J7-K7-L7-M7+N7-Inputs!$B$42</f>
+        <v>102822.931575</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <f aca="false">S6</f>
+        <v>12945390.8566</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <f aca="false">P7*Inputs!$B$35</f>
+        <v>621378.7611168</v>
+      </c>
+      <c r="R7" s="16" t="n">
+        <f aca="false">IF($A7=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <f aca="false">MAX(P7+Q7+O7+R7,0)</f>
+        <v>13669592.5492918</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <f aca="false">$A8-1972</f>
+        <v>58</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">$A8-1977</f>
+        <v>53</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">IF($A8&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A8-Inputs!$B$44),0)</f>
+        <v>1350610.572</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">IF($A8&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A8-Inputs!$B$44),0)</f>
+        <v>810366.3432</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A8-Inputs!$B$44)</f>
+        <v>436006.091796875</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A8-Inputs!$B$44)</f>
+        <v>160052.869140625</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <f aca="false">IF(D8=0,0,IF(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)&gt;200000,Inputs!$B$24+(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)-200000)*Inputs!$B$23,IF(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)&gt;150000,9000+(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)-150000)*0.14,IF(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)&gt;100000,4000+(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)-100000)*0.1,IF(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)&gt;50000,1000+(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0)-50000)*0.06,MAX(MAX(D8-Inputs!$B$22-Tax!$B$4/2-F8,0),0)*0.02)))))</f>
+        <v>129067.761634531</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <f aca="false">IF(E8=0,0,IF(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)&gt;200000,Inputs!$B$24+(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)-200000)*Inputs!$B$23,IF(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)&gt;150000,9000+(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)-150000)*0.14,IF(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)&gt;100000,4000+(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)-100000)*0.1,IF(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)&gt;50000,1000+(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0)-50000)*0.06,MAX(MAX(E8-Inputs!$B$22-Tax!$B$4/2-G8,0),0)*0.02)))))</f>
+        <v>84138.2905900938</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <f aca="false">IF(D8&gt;0,Inputs!$B$22,0)+IF(E8&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <f aca="false">IF($A8&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A8-Inputs!$B$44),0)</f>
+        <v>1086151.884375</v>
+      </c>
+      <c r="L8" s="16" t="n">
+        <f aca="false">IF(AND($A8&gt;=Inputs!$B$47,$A8&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A8-Inputs!$B$44),0)</f>
+        <v>729303.75</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <f aca="false">IF($A8&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A8-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="16" t="n">
+        <f aca="false">IF($A8&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="16" t="n">
+        <f aca="false">D8+E8-H8-I8-J8-K8-L8-M8+N8-Inputs!$B$42</f>
+        <v>96315.2286003755</v>
+      </c>
+      <c r="P8" s="16" t="n">
+        <f aca="false">S7</f>
+        <v>13669592.5492918</v>
+      </c>
+      <c r="Q8" s="16" t="n">
+        <f aca="false">P8*Inputs!$B$35</f>
+        <v>656140.442366006</v>
+      </c>
+      <c r="R8" s="16" t="n">
+        <f aca="false">IF($A8=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="16" t="n">
+        <f aca="false">MAX(P8+Q8+O8+R8,0)</f>
+        <v>14422048.2202582</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <f aca="false">$A9-1972</f>
+        <v>59</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <f aca="false">$A9-1977</f>
+        <v>54</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">IF($A9&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A9-Inputs!$B$44),0)</f>
+        <v>1391128.88916</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">IF($A9&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A9-Inputs!$B$44),0)</f>
+        <v>834677.333496</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A9-Inputs!$B$44)</f>
+        <v>446906.244091797</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A9-Inputs!$B$44)</f>
+        <v>164054.190869141</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <f aca="false">IF(D9=0,0,IF(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)&gt;200000,Inputs!$B$24+(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)-200000)*Inputs!$B$23,IF(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)&gt;150000,9000+(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)-150000)*0.14,IF(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)&gt;100000,4000+(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)-100000)*0.1,IF(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)&gt;50000,1000+(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0)-50000)*0.06,MAX(MAX(D9-Inputs!$B$22-Tax!$B$4/2-F9,0),0)*0.02)))))</f>
+        <v>134102.849661595</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <f aca="false">IF(E9=0,0,IF(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)&gt;200000,Inputs!$B$24+(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)-200000)*Inputs!$B$23,IF(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)&gt;150000,9000+(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)-150000)*0.14,IF(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)&gt;100000,4000+(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)-100000)*0.1,IF(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)&gt;50000,1000+(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0)-50000)*0.06,MAX(MAX(E9-Inputs!$B$22-Tax!$B$4/2-G9,0),0)*0.02)))))</f>
+        <v>87590.9342465661</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <f aca="false">IF(D9&gt;0,Inputs!$B$22,0)+IF(E9&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <f aca="false">IF($A9&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A9-Inputs!$B$44),0)</f>
+        <v>1113305.68148437</v>
+      </c>
+      <c r="L9" s="16" t="n">
+        <f aca="false">IF(AND($A9&gt;=Inputs!$B$47,$A9&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A9-Inputs!$B$44),0)</f>
+        <v>765768.9375</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <f aca="false">IF($A9&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A9-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="16" t="n">
+        <f aca="false">IF($A9&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <f aca="false">D9+E9-H9-I9-J9-K9-L9-M9+N9-Inputs!$B$42</f>
+        <v>89037.8197634646</v>
+      </c>
+      <c r="P9" s="16" t="n">
+        <f aca="false">S8</f>
+        <v>14422048.2202582</v>
+      </c>
+      <c r="Q9" s="16" t="n">
+        <f aca="false">P9*Inputs!$B$35</f>
+        <v>692258.314572393</v>
+      </c>
+      <c r="R9" s="16" t="n">
+        <f aca="false">IF($A9=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="16" t="n">
+        <f aca="false">MAX(P9+Q9+O9+R9,0)</f>
+        <v>15203344.354594</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <f aca="false">$A10-1972</f>
+        <v>60</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <f aca="false">$A10-1977</f>
+        <v>55</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">IF($A10&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A10-Inputs!$B$44),0)</f>
+        <v>1432862.7558348</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">IF($A10&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A10-Inputs!$B$44),0)</f>
+        <v>859717.65350088</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A10-Inputs!$B$44)</f>
+        <v>458078.900194092</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A10-Inputs!$B$44)</f>
+        <v>168155.545640869</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <f aca="false">IF(D10=0,0,IF(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)&gt;200000,Inputs!$B$24+(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)-200000)*Inputs!$B$23,IF(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)&gt;150000,9000+(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)-150000)*0.14,IF(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)&gt;100000,4000+(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)-100000)*0.1,IF(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)&gt;50000,1000+(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0)-50000)*0.06,MAX(MAX(D10-Inputs!$B$22-Tax!$B$4/2-F10,0),0)*0.02)))))</f>
+        <v>139298.255458921</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <f aca="false">IF(E10=0,0,IF(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)&gt;200000,Inputs!$B$24+(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)-200000)*Inputs!$B$23,IF(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)&gt;150000,9000+(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)-150000)*0.14,IF(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)&gt;100000,4000+(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)-100000)*0.1,IF(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)&gt;50000,1000+(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0)-50000)*0.06,MAX(MAX(E10-Inputs!$B$22-Tax!$B$4/2-G10,0),0)*0.02)))))</f>
+        <v>91150.5583362019</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <f aca="false">IF(D10&gt;0,Inputs!$B$22,0)+IF(E10&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <f aca="false">IF($A10&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A10-Inputs!$B$44),0)</f>
+        <v>1141138.32352148</v>
+      </c>
+      <c r="L10" s="16" t="n">
+        <f aca="false">IF(AND($A10&gt;=Inputs!$B$47,$A10&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A10-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <f aca="false">IF($A10&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A10-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="16" t="n">
+        <f aca="false">IF($A10&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="16" t="n">
+        <f aca="false">D10+E10-H10-I10-J10-K10-L10-M10+N10-Inputs!$B$42</f>
+        <v>884993.272019075</v>
+      </c>
+      <c r="P10" s="16" t="n">
+        <f aca="false">S9</f>
+        <v>15203344.354594</v>
+      </c>
+      <c r="Q10" s="16" t="n">
+        <f aca="false">P10*Inputs!$B$35</f>
+        <v>729760.529020514</v>
+      </c>
+      <c r="R10" s="16" t="n">
+        <f aca="false">IF($A10=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="16" t="n">
+        <f aca="false">MAX(P10+Q10+O10+R10,0)</f>
+        <v>16818098.1556336</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <f aca="false">$A11-1972</f>
+        <v>61</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">$A11-1977</f>
+        <v>56</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">IF($A11&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A11-Inputs!$B$44),0)</f>
+        <v>1475848.63850984</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">IF($A11&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A11-Inputs!$B$44),0)</f>
+        <v>885509.183105907</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A11-Inputs!$B$44)</f>
+        <v>469530.872698944</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A11-Inputs!$B$44)</f>
+        <v>172359.434281891</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <f aca="false">IF(D11=0,0,IF(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)&gt;200000,Inputs!$B$24+(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)-200000)*Inputs!$B$23,IF(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)&gt;150000,9000+(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)-150000)*0.14,IF(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)&gt;100000,4000+(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)-100000)*0.1,IF(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)&gt;50000,1000+(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0)-50000)*0.06,MAX(MAX(D11-Inputs!$B$22-Tax!$B$4/2-F11,0),0)*0.02)))))</f>
+        <v>144659.020187853</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <f aca="false">IF(E11=0,0,IF(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)&gt;200000,Inputs!$B$24+(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)-200000)*Inputs!$B$23,IF(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)&gt;150000,9000+(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)-150000)*0.14,IF(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)&gt;100000,4000+(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)-100000)*0.1,IF(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)&gt;50000,1000+(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0)-50000)*0.06,MAX(MAX(E11-Inputs!$B$22-Tax!$B$4/2-G11,0),0)*0.02)))))</f>
+        <v>94820.4573000827</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <f aca="false">IF(D11&gt;0,Inputs!$B$22,0)+IF(E11&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <f aca="false">IF($A11&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A11-Inputs!$B$44),0)</f>
+        <v>1169666.78160952</v>
+      </c>
+      <c r="L11" s="16" t="n">
+        <f aca="false">IF(AND($A11&gt;=Inputs!$B$47,$A11&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A11-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <f aca="false">IF($A11&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A11-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="16" t="n">
+        <f aca="false">IF($A11&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <f aca="false">D11+E11-H11-I11-J11-K11-L11-M11+N11-Inputs!$B$42</f>
+        <v>916211.562518294</v>
+      </c>
+      <c r="P11" s="16" t="n">
+        <f aca="false">S10</f>
+        <v>16818098.1556336</v>
+      </c>
+      <c r="Q11" s="16" t="n">
+        <f aca="false">P11*Inputs!$B$35</f>
+        <v>807268.711470414</v>
+      </c>
+      <c r="R11" s="16" t="n">
+        <f aca="false">IF($A11=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="16" t="n">
+        <f aca="false">MAX(P11+Q11+O11+R11,0)</f>
+        <v>18541578.4296223</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <f aca="false">$A12-1972</f>
+        <v>62</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <f aca="false">$A12-1977</f>
+        <v>57</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">IF($A12&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A12-Inputs!$B$44),0)</f>
+        <v>1520124.09766514</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">IF($A12&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A12-Inputs!$B$44),0)</f>
+        <v>912074.458599084</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A12-Inputs!$B$44)</f>
+        <v>481269.144516417</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A12-Inputs!$B$44)</f>
+        <v>176668.420138938</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <f aca="false">IF(D12=0,0,IF(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)&gt;200000,Inputs!$B$24+(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)-200000)*Inputs!$B$23,IF(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)&gt;150000,9000+(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)-150000)*0.14,IF(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)&gt;100000,4000+(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)-100000)*0.1,IF(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)&gt;50000,1000+(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0)-50000)*0.06,MAX(MAX(D12-Inputs!$B$22-Tax!$B$4/2-F12,0),0)*0.02)))))</f>
+        <v>150190.342035283</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <f aca="false">IF(E12=0,0,IF(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)&gt;200000,Inputs!$B$24+(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)-200000)*Inputs!$B$23,IF(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)&gt;150000,9000+(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)-150000)*0.14,IF(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)&gt;100000,4000+(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)-100000)*0.1,IF(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)&gt;50000,1000+(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0)-50000)*0.06,MAX(MAX(E12-Inputs!$B$22-Tax!$B$4/2-G12,0),0)*0.02)))))</f>
+        <v>98604.0265382248</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <f aca="false">IF(D12&gt;0,Inputs!$B$22,0)+IF(E12&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <f aca="false">IF($A12&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A12-Inputs!$B$44),0)</f>
+        <v>1198908.45114976</v>
+      </c>
+      <c r="L12" s="16" t="n">
+        <f aca="false">IF(AND($A12&gt;=Inputs!$B$47,$A12&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A12-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <f aca="false">IF($A12&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A12-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="16" t="n">
+        <f aca="false">IF($A12&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="16" t="n">
+        <f aca="false">D12+E12-H12-I12-J12-K12-L12-M12+N12-Inputs!$B$42</f>
+        <v>948495.736540957</v>
+      </c>
+      <c r="P12" s="16" t="n">
+        <f aca="false">S11</f>
+        <v>18541578.4296223</v>
+      </c>
+      <c r="Q12" s="16" t="n">
+        <f aca="false">P12*Inputs!$B$35</f>
+        <v>889995.764621872</v>
+      </c>
+      <c r="R12" s="16" t="n">
+        <f aca="false">IF($A12=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <f aca="false">MAX(P12+Q12+O12+R12,0)</f>
+        <v>20380069.9307852</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <f aca="false">$A13-1972</f>
+        <v>63</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <f aca="false">$A13-1977</f>
+        <v>58</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">IF($A13&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A13-Inputs!$B$44),0)</f>
+        <v>1565727.82059509</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">IF($A13&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A13-Inputs!$B$44),0)</f>
+        <v>939436.692357056</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A13-Inputs!$B$44)</f>
+        <v>493300.873129328</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A13-Inputs!$B$44)</f>
+        <v>181085.130642411</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <f aca="false">IF(D13=0,0,IF(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)&gt;200000,Inputs!$B$24+(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)-200000)*Inputs!$B$23,IF(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)&gt;150000,9000+(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)-150000)*0.14,IF(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)&gt;100000,4000+(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)-100000)*0.1,IF(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)&gt;50000,1000+(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0)-50000)*0.06,MAX(MAX(D13-Inputs!$B$22-Tax!$B$4/2-F13,0),0)*0.02)))))</f>
+        <v>155897.58106918</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <f aca="false">IF(E13=0,0,IF(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)&gt;200000,Inputs!$B$24+(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)-200000)*Inputs!$B$23,IF(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)&gt;150000,9000+(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)-150000)*0.14,IF(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)&gt;100000,4000+(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)-100000)*0.1,IF(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)&gt;50000,1000+(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0)-50000)*0.06,MAX(MAX(E13-Inputs!$B$22-Tax!$B$4/2-G13,0),0)*0.02)))))</f>
+        <v>102504.76549149</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <f aca="false">IF(D13&gt;0,Inputs!$B$22,0)+IF(E13&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <f aca="false">IF($A13&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A13-Inputs!$B$44),0)</f>
+        <v>1228881.1624285</v>
+      </c>
+      <c r="L13" s="16" t="n">
+        <f aca="false">IF(AND($A13&gt;=Inputs!$B$47,$A13&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A13-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <f aca="false">IF($A13&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A13-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="16" t="n">
+        <f aca="false">IF($A13&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <f aca="false">D13+E13-H13-I13-J13-K13-L13-M13+N13-Inputs!$B$42</f>
+        <v>981881.003962977</v>
+      </c>
+      <c r="P13" s="16" t="n">
+        <f aca="false">S12</f>
+        <v>20380069.9307852</v>
+      </c>
+      <c r="Q13" s="16" t="n">
+        <f aca="false">P13*Inputs!$B$35</f>
+        <v>978243.356677688</v>
+      </c>
+      <c r="R13" s="16" t="n">
+        <f aca="false">IF($A13=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <f aca="false">MAX(P13+Q13+O13+R13,0)</f>
+        <v>22340194.2914258</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <f aca="false">$A14-1972</f>
+        <v>64</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <f aca="false">$A14-1977</f>
+        <v>59</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">IF($A14&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A14-Inputs!$B$44),0)</f>
+        <v>1612699.65521295</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">IF($A14&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A14-Inputs!$B$44),0)</f>
+        <v>967619.793127768</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A14-Inputs!$B$44)</f>
+        <v>505633.394957561</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A14-Inputs!$B$44)</f>
+        <v>185612.258908472</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <f aca="false">IF(D14=0,0,IF(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)&gt;200000,Inputs!$B$24+(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)-200000)*Inputs!$B$23,IF(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)&gt;150000,9000+(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)-150000)*0.14,IF(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)&gt;100000,4000+(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)-100000)*0.1,IF(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)&gt;50000,1000+(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0)-50000)*0.06,MAX(MAX(D14-Inputs!$B$22-Tax!$B$4/2-F14,0),0)*0.02)))))</f>
+        <v>161786.264243416</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <f aca="false">IF(E14=0,0,IF(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)&gt;200000,Inputs!$B$24+(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)-200000)*Inputs!$B$23,IF(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)&gt;150000,9000+(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)-150000)*0.14,IF(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)&gt;100000,4000+(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)-100000)*0.1,IF(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)&gt;50000,1000+(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0)-50000)*0.06,MAX(MAX(E14-Inputs!$B$22-Tax!$B$4/2-G14,0),0)*0.02)))))</f>
+        <v>106526.28081728</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <f aca="false">IF(D14&gt;0,Inputs!$B$22,0)+IF(E14&gt;0,Inputs!$B$22,0)</f>
+        <v>36000</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <f aca="false">IF($A14&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A14-Inputs!$B$44),0)</f>
+        <v>1259603.19148922</v>
+      </c>
+      <c r="L14" s="16" t="n">
+        <f aca="false">IF(AND($A14&gt;=Inputs!$B$47,$A14&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A14-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="16" t="n">
+        <f aca="false">IF($A14&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A14-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="16" t="n">
+        <f aca="false">IF($A14&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="16" t="n">
+        <f aca="false">D14+E14-H14-I14-J14-K14-L14-M14+N14-Inputs!$B$42</f>
+        <v>1016403.7117908</v>
+      </c>
+      <c r="P14" s="16" t="n">
+        <f aca="false">S13</f>
+        <v>22340194.2914258</v>
+      </c>
+      <c r="Q14" s="16" t="n">
+        <f aca="false">P14*Inputs!$B$35</f>
+        <v>1072329.32598844</v>
+      </c>
+      <c r="R14" s="16" t="n">
+        <f aca="false">IF($A14=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <f aca="false">MAX(P14+Q14+O14+R14,0)</f>
+        <v>24428927.3292051</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B15" s="20" t="n">
+        <f aca="false">$A15-1972</f>
+        <v>65</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <f aca="false">$A15-1977</f>
+        <v>60</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <f aca="false">IF($A15&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A15-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <f aca="false">IF($A15&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A15-Inputs!$B$44),0)</f>
+        <v>996648.386921601</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A15-Inputs!$B$44)</f>
+        <v>518274.2298315</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A15-Inputs!$B$44)</f>
+        <v>190252.565381184</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <f aca="false">IF(D15=0,0,IF(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)&gt;200000,Inputs!$B$24+(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)-200000)*Inputs!$B$23,IF(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)&gt;150000,9000+(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)-150000)*0.14,IF(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)&gt;100000,4000+(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)-100000)*0.1,IF(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)&gt;50000,1000+(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0)-50000)*0.06,MAX(MAX(D15-Inputs!$B$22-Tax!$B$4/2-F15,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <f aca="false">IF(E15=0,0,IF(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)&gt;200000,Inputs!$B$24+(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)-200000)*Inputs!$B$23,IF(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)&gt;150000,9000+(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)-150000)*0.14,IF(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)&gt;100000,4000+(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)-100000)*0.1,IF(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)&gt;50000,1000+(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0)-50000)*0.06,MAX(MAX(E15-Inputs!$B$22-Tax!$B$4/2-G15,0),0)*0.02)))))</f>
+        <v>110672.289661871</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <f aca="false">IF(D15&gt;0,Inputs!$B$22,0)+IF(E15&gt;0,Inputs!$B$22,0)</f>
+        <v>18000</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <f aca="false">IF($A15&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A15-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <f aca="false">IF(AND($A15&gt;=Inputs!$B$47,$A15&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A15-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <f aca="false">IF($A15&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A15-Inputs!$B$44),0)</f>
+        <v>1023427.59308499</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <f aca="false">IF($A15&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O15" s="21" t="n">
+        <f aca="false">D15+E15-H15-I15-J15-K15-L15-M15+N15-Inputs!$B$42</f>
+        <v>112548.504174743</v>
+      </c>
+      <c r="P15" s="21" t="n">
+        <f aca="false">S14</f>
+        <v>24428927.3292051</v>
+      </c>
+      <c r="Q15" s="21" t="n">
+        <f aca="false">P15*Inputs!$B$35</f>
+        <v>1172588.51180184</v>
+      </c>
+      <c r="R15" s="21" t="n">
+        <f aca="false">IF($A15=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>-4120000</v>
+      </c>
+      <c r="S15" s="21" t="n">
+        <f aca="false">MAX(P15+Q15+O15+R15,0)</f>
+        <v>21594064.3451817</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <f aca="false">$A16-1972</f>
+        <v>66</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <f aca="false">$A16-1977</f>
+        <v>61</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">IF($A16&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A16-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <f aca="false">IF($A16&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A16-Inputs!$B$44),0)</f>
+        <v>1026547.83852925</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A16-Inputs!$B$44)</f>
+        <v>531231.085577287</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A16-Inputs!$B$44)</f>
+        <v>195008.879515713</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <f aca="false">IF(D16=0,0,IF(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)&gt;200000,Inputs!$B$24+(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)-200000)*Inputs!$B$23,IF(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)&gt;150000,9000+(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)-150000)*0.14,IF(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)&gt;100000,4000+(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)-100000)*0.1,IF(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)&gt;50000,1000+(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0)-50000)*0.06,MAX(MAX(D16-Inputs!$B$22-Tax!$B$4/2-F16,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <f aca="false">IF(E16=0,0,IF(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)&gt;200000,Inputs!$B$24+(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)-200000)*Inputs!$B$23,IF(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)&gt;150000,9000+(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)-150000)*0.14,IF(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)&gt;100000,4000+(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)-100000)*0.1,IF(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)&gt;50000,1000+(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0)-50000)*0.06,MAX(MAX(E16-Inputs!$B$22-Tax!$B$4/2-G16,0),0)*0.02)))))</f>
+        <v>114946.623032301</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <f aca="false">IF(D16&gt;0,Inputs!$B$22,0)+IF(E16&gt;0,Inputs!$B$22,0)</f>
+        <v>18000</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <f aca="false">IF($A16&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A16-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="n">
+        <f aca="false">IF(AND($A16&gt;=Inputs!$B$47,$A16&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A16-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16" t="n">
+        <f aca="false">IF($A16&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A16-Inputs!$B$44),0)</f>
+        <v>1049013.28291211</v>
+      </c>
+      <c r="N16" s="16" t="n">
+        <f aca="false">IF($A16&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <f aca="false">D16+E16-H16-I16-J16-K16-L16-M16+N16-Inputs!$B$42</f>
+        <v>112587.932584836</v>
+      </c>
+      <c r="P16" s="16" t="n">
+        <f aca="false">S15</f>
+        <v>21594064.3451817</v>
+      </c>
+      <c r="Q16" s="16" t="n">
+        <f aca="false">P16*Inputs!$B$35</f>
+        <v>1036515.08856872</v>
+      </c>
+      <c r="R16" s="16" t="n">
+        <f aca="false">IF($A16=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="16" t="n">
+        <f aca="false">MAX(P16+Q16+O16+R16,0)</f>
+        <v>22743167.3663352</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B17" s="20" t="n">
+        <f aca="false">$A17-1972</f>
+        <v>67</v>
+      </c>
+      <c r="C17" s="20" t="n">
+        <f aca="false">$A17-1977</f>
+        <v>62</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <f aca="false">IF($A17&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A17-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <f aca="false">IF($A17&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A17-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A17-Inputs!$B$44)</f>
+        <v>544511.862716719</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A17-Inputs!$B$44)</f>
+        <v>199884.101503606</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <f aca="false">IF(D17=0,0,IF(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)&gt;200000,Inputs!$B$24+(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)-200000)*Inputs!$B$23,IF(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)&gt;150000,9000+(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)-150000)*0.14,IF(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)&gt;100000,4000+(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)-100000)*0.1,IF(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)&gt;50000,1000+(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0)-50000)*0.06,MAX(MAX(D17-Inputs!$B$22-Tax!$B$4/2-F17,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <f aca="false">IF(E17=0,0,IF(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)&gt;200000,Inputs!$B$24+(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)-200000)*Inputs!$B$23,IF(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)&gt;150000,9000+(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)-150000)*0.14,IF(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)&gt;100000,4000+(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)-100000)*0.1,IF(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)&gt;50000,1000+(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0)-50000)*0.06,MAX(MAX(E17-Inputs!$B$22-Tax!$B$4/2-G17,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <f aca="false">IF(D17&gt;0,Inputs!$B$22,0)+IF(E17&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <f aca="false">IF($A17&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A17-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="21" t="n">
+        <f aca="false">IF(AND($A17&gt;=Inputs!$B$47,$A17&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A17-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <f aca="false">IF($A17&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A17-Inputs!$B$44),0)</f>
+        <v>1075238.61498491</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <f aca="false">IF($A17&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O17" s="21" t="n">
+        <f aca="false">D17+E17-H17-I17-J17-K17-L17-M17+N17-Inputs!$B$42</f>
+        <v>-807238.614984914</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <f aca="false">S16</f>
+        <v>22743167.3663352</v>
+      </c>
+      <c r="Q17" s="21" t="n">
+        <f aca="false">P17*Inputs!$B$35</f>
+        <v>1091672.03358409</v>
+      </c>
+      <c r="R17" s="21" t="n">
+        <f aca="false">IF($A17=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="21" t="n">
+        <f aca="false">MAX(P17+Q17+O17+R17,0)</f>
+        <v>23027600.7849344</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <f aca="false">$A18-1972</f>
+        <v>68</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <f aca="false">$A18-1977</f>
+        <v>63</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">IF($A18&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A18-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">IF($A18&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A18-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A18-Inputs!$B$44)</f>
+        <v>558124.659284637</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A18-Inputs!$B$44)</f>
+        <v>204881.204041196</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <f aca="false">IF(D18=0,0,IF(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)&gt;200000,Inputs!$B$24+(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)-200000)*Inputs!$B$23,IF(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)&gt;150000,9000+(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)-150000)*0.14,IF(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)&gt;100000,4000+(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)-100000)*0.1,IF(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)&gt;50000,1000+(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0)-50000)*0.06,MAX(MAX(D18-Inputs!$B$22-Tax!$B$4/2-F18,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <f aca="false">IF(E18=0,0,IF(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)&gt;200000,Inputs!$B$24+(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)-200000)*Inputs!$B$23,IF(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)&gt;150000,9000+(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)-150000)*0.14,IF(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)&gt;100000,4000+(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)-100000)*0.1,IF(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)&gt;50000,1000+(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0)-50000)*0.06,MAX(MAX(E18-Inputs!$B$22-Tax!$B$4/2-G18,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <f aca="false">IF(D18&gt;0,Inputs!$B$22,0)+IF(E18&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="16" t="n">
+        <f aca="false">IF($A18&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A18-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="16" t="n">
+        <f aca="false">IF(AND($A18&gt;=Inputs!$B$47,$A18&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A18-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="16" t="n">
+        <f aca="false">IF($A18&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A18-Inputs!$B$44),0)</f>
+        <v>1102119.58035954</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <f aca="false">IF($A18&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <f aca="false">D18+E18-H18-I18-J18-K18-L18-M18+N18-Inputs!$B$42</f>
+        <v>-834119.580359537</v>
+      </c>
+      <c r="P18" s="16" t="n">
+        <f aca="false">S17</f>
+        <v>23027600.7849344</v>
+      </c>
+      <c r="Q18" s="16" t="n">
+        <f aca="false">P18*Inputs!$B$35</f>
+        <v>1105324.83767685</v>
+      </c>
+      <c r="R18" s="16" t="n">
+        <f aca="false">IF($A18=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <f aca="false">MAX(P18+Q18+O18+R18,0)</f>
+        <v>23298806.0422517</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <f aca="false">$A19-1972</f>
+        <v>69</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <f aca="false">$A19-1977</f>
+        <v>64</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">IF($A19&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A19-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">IF($A19&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A19-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A19-Inputs!$B$44)</f>
+        <v>572077.775766753</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A19-Inputs!$B$44)</f>
+        <v>210003.234142226</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <f aca="false">IF(D19=0,0,IF(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)&gt;200000,Inputs!$B$24+(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)-200000)*Inputs!$B$23,IF(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)&gt;150000,9000+(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)-150000)*0.14,IF(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)&gt;100000,4000+(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)-100000)*0.1,IF(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)&gt;50000,1000+(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0)-50000)*0.06,MAX(MAX(D19-Inputs!$B$22-Tax!$B$4/2-F19,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <f aca="false">IF(E19=0,0,IF(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)&gt;200000,Inputs!$B$24+(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)-200000)*Inputs!$B$23,IF(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)&gt;150000,9000+(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)-150000)*0.14,IF(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)&gt;100000,4000+(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)-100000)*0.1,IF(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)&gt;50000,1000+(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0)-50000)*0.06,MAX(MAX(E19-Inputs!$B$22-Tax!$B$4/2-G19,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <f aca="false">IF(D19&gt;0,Inputs!$B$22,0)+IF(E19&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="16" t="n">
+        <f aca="false">IF($A19&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A19-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <f aca="false">IF(AND($A19&gt;=Inputs!$B$47,$A19&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A19-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <f aca="false">IF($A19&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A19-Inputs!$B$44),0)</f>
+        <v>1129672.56986853</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <f aca="false">IF($A19&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O19" s="16" t="n">
+        <f aca="false">D19+E19-H19-I19-J19-K19-L19-M19+N19-Inputs!$B$42</f>
+        <v>-861672.569868526</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <f aca="false">S18</f>
+        <v>23298806.0422517</v>
+      </c>
+      <c r="Q19" s="16" t="n">
+        <f aca="false">P19*Inputs!$B$35</f>
+        <v>1118342.69002808</v>
+      </c>
+      <c r="R19" s="16" t="n">
+        <f aca="false">IF($A19=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <f aca="false">MAX(P19+Q19+O19+R19,0)</f>
+        <v>23555476.1624113</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <f aca="false">$A20-1972</f>
+        <v>70</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <f aca="false">$A20-1977</f>
+        <v>65</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">IF($A20&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A20-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <f aca="false">IF($A20&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A20-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A20-Inputs!$B$44)</f>
+        <v>586379.720160922</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A20-Inputs!$B$44)</f>
+        <v>215253.314995782</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <f aca="false">IF(D20=0,0,IF(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)&gt;200000,Inputs!$B$24+(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)-200000)*Inputs!$B$23,IF(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)&gt;150000,9000+(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)-150000)*0.14,IF(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)&gt;100000,4000+(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)-100000)*0.1,IF(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)&gt;50000,1000+(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0)-50000)*0.06,MAX(MAX(D20-Inputs!$B$22-Tax!$B$4/2-F20,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <f aca="false">IF(E20=0,0,IF(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)&gt;200000,Inputs!$B$24+(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)-200000)*Inputs!$B$23,IF(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)&gt;150000,9000+(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)-150000)*0.14,IF(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)&gt;100000,4000+(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)-100000)*0.1,IF(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)&gt;50000,1000+(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0)-50000)*0.06,MAX(MAX(E20-Inputs!$B$22-Tax!$B$4/2-G20,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <f aca="false">IF(D20&gt;0,Inputs!$B$22,0)+IF(E20&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <f aca="false">IF($A20&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A20-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="n">
+        <f aca="false">IF(AND($A20&gt;=Inputs!$B$47,$A20&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A20-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <f aca="false">IF($A20&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A20-Inputs!$B$44),0)</f>
+        <v>1157914.38411524</v>
+      </c>
+      <c r="N20" s="16" t="n">
+        <f aca="false">IF($A20&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O20" s="16" t="n">
+        <f aca="false">D20+E20-H20-I20-J20-K20-L20-M20+N20-Inputs!$B$42</f>
+        <v>-889914.384115238</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <f aca="false">S19</f>
+        <v>23555476.1624113</v>
+      </c>
+      <c r="Q20" s="16" t="n">
+        <f aca="false">P20*Inputs!$B$35</f>
+        <v>1130662.85579574</v>
+      </c>
+      <c r="R20" s="16" t="n">
+        <f aca="false">IF($A20=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="16" t="n">
+        <f aca="false">MAX(P20+Q20+O20+R20,0)</f>
+        <v>23796224.6340918</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <f aca="false">$A21-1972</f>
+        <v>71</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <f aca="false">$A21-1977</f>
+        <v>66</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">IF($A21&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A21-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <f aca="false">IF($A21&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A21-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A21-Inputs!$B$44)</f>
+        <v>601039.213164945</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A21-Inputs!$B$44)</f>
+        <v>220634.647870676</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <f aca="false">IF(D21=0,0,IF(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)&gt;200000,Inputs!$B$24+(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)-200000)*Inputs!$B$23,IF(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)&gt;150000,9000+(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)-150000)*0.14,IF(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)&gt;100000,4000+(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)-100000)*0.1,IF(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)&gt;50000,1000+(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0)-50000)*0.06,MAX(MAX(D21-Inputs!$B$22-Tax!$B$4/2-F21,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <f aca="false">IF(E21=0,0,IF(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)&gt;200000,Inputs!$B$24+(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)-200000)*Inputs!$B$23,IF(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)&gt;150000,9000+(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)-150000)*0.14,IF(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)&gt;100000,4000+(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)-100000)*0.1,IF(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)&gt;50000,1000+(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0)-50000)*0.06,MAX(MAX(E21-Inputs!$B$22-Tax!$B$4/2-G21,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <f aca="false">IF(D21&gt;0,Inputs!$B$22,0)+IF(E21&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="16" t="n">
+        <f aca="false">IF($A21&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A21-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="16" t="n">
+        <f aca="false">IF(AND($A21&gt;=Inputs!$B$47,$A21&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A21-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="16" t="n">
+        <f aca="false">IF($A21&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A21-Inputs!$B$44),0)</f>
+        <v>1186862.24371812</v>
+      </c>
+      <c r="N21" s="16" t="n">
+        <f aca="false">IF($A21&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O21" s="16" t="n">
+        <f aca="false">D21+E21-H21-I21-J21-K21-L21-M21+N21-Inputs!$B$42</f>
+        <v>-918862.243718119</v>
+      </c>
+      <c r="P21" s="16" t="n">
+        <f aca="false">S20</f>
+        <v>23796224.6340918</v>
+      </c>
+      <c r="Q21" s="16" t="n">
+        <f aca="false">P21*Inputs!$B$35</f>
+        <v>1142218.78243641</v>
+      </c>
+      <c r="R21" s="16" t="n">
+        <f aca="false">IF($A21=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <f aca="false">MAX(P21+Q21+O21+R21,0)</f>
+        <v>24019581.1728101</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <f aca="false">$A22-1972</f>
+        <v>72</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <f aca="false">$A22-1977</f>
+        <v>67</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">IF($A22&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A22-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <f aca="false">IF($A22&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A22-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A22-Inputs!$B$44)</f>
+        <v>616065.193494069</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A22-Inputs!$B$44)</f>
+        <v>226150.514067443</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <f aca="false">IF(D22=0,0,IF(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)&gt;200000,Inputs!$B$24+(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)-200000)*Inputs!$B$23,IF(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)&gt;150000,9000+(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)-150000)*0.14,IF(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)&gt;100000,4000+(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)-100000)*0.1,IF(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)&gt;50000,1000+(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0)-50000)*0.06,MAX(MAX(D22-Inputs!$B$22-Tax!$B$4/2-F22,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <f aca="false">IF(E22=0,0,IF(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)&gt;200000,Inputs!$B$24+(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)-200000)*Inputs!$B$23,IF(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)&gt;150000,9000+(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)-150000)*0.14,IF(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)&gt;100000,4000+(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)-100000)*0.1,IF(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)&gt;50000,1000+(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0)-50000)*0.06,MAX(MAX(E22-Inputs!$B$22-Tax!$B$4/2-G22,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <f aca="false">IF(D22&gt;0,Inputs!$B$22,0)+IF(E22&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="16" t="n">
+        <f aca="false">IF($A22&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A22-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="n">
+        <f aca="false">IF(AND($A22&gt;=Inputs!$B$47,$A22&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A22-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <f aca="false">IF($A22&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A22-Inputs!$B$44),0)</f>
+        <v>1216533.79981107</v>
+      </c>
+      <c r="N22" s="16" t="n">
+        <f aca="false">IF($A22&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O22" s="16" t="n">
+        <f aca="false">D22+E22-H22-I22-J22-K22-L22-M22+N22-Inputs!$B$42</f>
+        <v>-948533.799811072</v>
+      </c>
+      <c r="P22" s="16" t="n">
+        <f aca="false">S21</f>
+        <v>24019581.1728101</v>
+      </c>
+      <c r="Q22" s="16" t="n">
+        <f aca="false">P22*Inputs!$B$35</f>
+        <v>1152939.89629488</v>
+      </c>
+      <c r="R22" s="16" t="n">
+        <f aca="false">IF($A22=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <f aca="false">MAX(P22+Q22+O22+R22,0)</f>
+        <v>24223987.2692939</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <f aca="false">$A23-1972</f>
+        <v>73</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <f aca="false">$A23-1977</f>
+        <v>68</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">IF($A23&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A23-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <f aca="false">IF($A23&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A23-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A23-Inputs!$B$44)</f>
+        <v>631466.82333142</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A23-Inputs!$B$44)</f>
+        <v>231804.276919129</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <f aca="false">IF(D23=0,0,IF(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)&gt;200000,Inputs!$B$24+(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)-200000)*Inputs!$B$23,IF(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)&gt;150000,9000+(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)-150000)*0.14,IF(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)&gt;100000,4000+(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)-100000)*0.1,IF(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)&gt;50000,1000+(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0)-50000)*0.06,MAX(MAX(D23-Inputs!$B$22-Tax!$B$4/2-F23,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <f aca="false">IF(E23=0,0,IF(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)&gt;200000,Inputs!$B$24+(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)-200000)*Inputs!$B$23,IF(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)&gt;150000,9000+(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)-150000)*0.14,IF(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)&gt;100000,4000+(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)-100000)*0.1,IF(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)&gt;50000,1000+(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0)-50000)*0.06,MAX(MAX(E23-Inputs!$B$22-Tax!$B$4/2-G23,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="16" t="n">
+        <f aca="false">IF(D23&gt;0,Inputs!$B$22,0)+IF(E23&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="16" t="n">
+        <f aca="false">IF($A23&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A23-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="16" t="n">
+        <f aca="false">IF(AND($A23&gt;=Inputs!$B$47,$A23&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A23-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="16" t="n">
+        <f aca="false">IF($A23&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A23-Inputs!$B$44),0)</f>
+        <v>1246947.14480635</v>
+      </c>
+      <c r="N23" s="16" t="n">
+        <f aca="false">IF($A23&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O23" s="16" t="n">
+        <f aca="false">D23+E23-H23-I23-J23-K23-L23-M23+N23-Inputs!$B$42</f>
+        <v>-978947.144806349</v>
+      </c>
+      <c r="P23" s="16" t="n">
+        <f aca="false">S22</f>
+        <v>24223987.2692939</v>
+      </c>
+      <c r="Q23" s="16" t="n">
+        <f aca="false">P23*Inputs!$B$35</f>
+        <v>1162751.38892611</v>
+      </c>
+      <c r="R23" s="16" t="n">
+        <f aca="false">IF($A23=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="16" t="n">
+        <f aca="false">MAX(P23+Q23+O23+R23,0)</f>
+        <v>24407791.5134136</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <f aca="false">$A24-1972</f>
+        <v>74</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <f aca="false">$A24-1977</f>
+        <v>69</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">IF($A24&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A24-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <f aca="false">IF($A24&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A24-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A24-Inputs!$B$44)</f>
+        <v>647253.493914706</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A24-Inputs!$B$44)</f>
+        <v>237599.383842107</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <f aca="false">IF(D24=0,0,IF(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)&gt;200000,Inputs!$B$24+(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)-200000)*Inputs!$B$23,IF(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)&gt;150000,9000+(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)-150000)*0.14,IF(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)&gt;100000,4000+(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)-100000)*0.1,IF(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)&gt;50000,1000+(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0)-50000)*0.06,MAX(MAX(D24-Inputs!$B$22-Tax!$B$4/2-F24,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <f aca="false">IF(E24=0,0,IF(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)&gt;200000,Inputs!$B$24+(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)-200000)*Inputs!$B$23,IF(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)&gt;150000,9000+(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)-150000)*0.14,IF(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)&gt;100000,4000+(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)-100000)*0.1,IF(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)&gt;50000,1000+(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0)-50000)*0.06,MAX(MAX(E24-Inputs!$B$22-Tax!$B$4/2-G24,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <f aca="false">IF(D24&gt;0,Inputs!$B$22,0)+IF(E24&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="16" t="n">
+        <f aca="false">IF($A24&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A24-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="n">
+        <f aca="false">IF(AND($A24&gt;=Inputs!$B$47,$A24&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A24-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="16" t="n">
+        <f aca="false">IF($A24&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A24-Inputs!$B$44),0)</f>
+        <v>1278120.82342651</v>
+      </c>
+      <c r="N24" s="16" t="n">
+        <f aca="false">IF($A24&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <f aca="false">D24+E24-H24-I24-J24-K24-L24-M24+N24-Inputs!$B$42</f>
+        <v>-1010120.82342651</v>
+      </c>
+      <c r="P24" s="16" t="n">
+        <f aca="false">S23</f>
+        <v>24407791.5134136</v>
+      </c>
+      <c r="Q24" s="16" t="n">
+        <f aca="false">P24*Inputs!$B$35</f>
+        <v>1171573.99264385</v>
+      </c>
+      <c r="R24" s="16" t="n">
+        <f aca="false">IF($A24=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="16" t="n">
+        <f aca="false">MAX(P24+Q24+O24+R24,0)</f>
+        <v>24569244.682631</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <f aca="false">$A25-1972</f>
+        <v>75</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <f aca="false">$A25-1977</f>
+        <v>70</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <f aca="false">IF($A25&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A25-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <f aca="false">IF($A25&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A25-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A25-Inputs!$B$44)</f>
+        <v>663434.831262573</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A25-Inputs!$B$44)</f>
+        <v>243539.36843816</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <f aca="false">IF(D25=0,0,IF(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)&gt;200000,Inputs!$B$24+(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)-200000)*Inputs!$B$23,IF(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)&gt;150000,9000+(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)-150000)*0.14,IF(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)&gt;100000,4000+(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)-100000)*0.1,IF(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)&gt;50000,1000+(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0)-50000)*0.06,MAX(MAX(D25-Inputs!$B$22-Tax!$B$4/2-F25,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <f aca="false">IF(E25=0,0,IF(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)&gt;200000,Inputs!$B$24+(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)-200000)*Inputs!$B$23,IF(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)&gt;150000,9000+(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)-150000)*0.14,IF(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)&gt;100000,4000+(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)-100000)*0.1,IF(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)&gt;50000,1000+(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0)-50000)*0.06,MAX(MAX(E25-Inputs!$B$22-Tax!$B$4/2-G25,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <f aca="false">IF(D25&gt;0,Inputs!$B$22,0)+IF(E25&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="16" t="n">
+        <f aca="false">IF($A25&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A25-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="16" t="n">
+        <f aca="false">IF(AND($A25&gt;=Inputs!$B$47,$A25&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A25-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="16" t="n">
+        <f aca="false">IF($A25&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A25-Inputs!$B$44),0)</f>
+        <v>1310073.84401217</v>
+      </c>
+      <c r="N25" s="16" t="n">
+        <f aca="false">IF($A25&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O25" s="16" t="n">
+        <f aca="false">D25+E25-H25-I25-J25-K25-L25-M25+N25-Inputs!$B$42</f>
+        <v>-1042073.84401217</v>
+      </c>
+      <c r="P25" s="16" t="n">
+        <f aca="false">S24</f>
+        <v>24569244.682631</v>
+      </c>
+      <c r="Q25" s="16" t="n">
+        <f aca="false">P25*Inputs!$B$35</f>
+        <v>1179323.74476629</v>
+      </c>
+      <c r="R25" s="16" t="n">
+        <f aca="false">IF($A25=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="16" t="n">
+        <f aca="false">MAX(P25+Q25+O25+R25,0)</f>
+        <v>24706494.5833851</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <f aca="false">$A26-1972</f>
+        <v>76</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <f aca="false">$A26-1977</f>
+        <v>71</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">IF($A26&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A26-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <f aca="false">IF($A26&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A26-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A26-Inputs!$B$44)</f>
+        <v>680020.702044138</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A26-Inputs!$B$44)</f>
+        <v>249627.852649114</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <f aca="false">IF(D26=0,0,IF(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)&gt;200000,Inputs!$B$24+(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)-200000)*Inputs!$B$23,IF(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)&gt;150000,9000+(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)-150000)*0.14,IF(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)&gt;100000,4000+(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)-100000)*0.1,IF(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)&gt;50000,1000+(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0)-50000)*0.06,MAX(MAX(D26-Inputs!$B$22-Tax!$B$4/2-F26,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <f aca="false">IF(E26=0,0,IF(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)&gt;200000,Inputs!$B$24+(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)-200000)*Inputs!$B$23,IF(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)&gt;150000,9000+(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)-150000)*0.14,IF(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)&gt;100000,4000+(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)-100000)*0.1,IF(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)&gt;50000,1000+(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0)-50000)*0.06,MAX(MAX(E26-Inputs!$B$22-Tax!$B$4/2-G26,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <f aca="false">IF(D26&gt;0,Inputs!$B$22,0)+IF(E26&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="16" t="n">
+        <f aca="false">IF($A26&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A26-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="16" t="n">
+        <f aca="false">IF(AND($A26&gt;=Inputs!$B$47,$A26&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A26-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="16" t="n">
+        <f aca="false">IF($A26&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A26-Inputs!$B$44),0)</f>
+        <v>1342825.69011247</v>
+      </c>
+      <c r="N26" s="16" t="n">
+        <f aca="false">IF($A26&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O26" s="16" t="n">
+        <f aca="false">D26+E26-H26-I26-J26-K26-L26-M26+N26-Inputs!$B$42</f>
+        <v>-1074825.69011247</v>
+      </c>
+      <c r="P26" s="16" t="n">
+        <f aca="false">S25</f>
+        <v>24706494.5833851</v>
+      </c>
+      <c r="Q26" s="16" t="n">
+        <f aca="false">P26*Inputs!$B$35</f>
+        <v>1185911.74000248</v>
+      </c>
+      <c r="R26" s="16" t="n">
+        <f aca="false">IF($A26=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <f aca="false">MAX(P26+Q26+O26+R26,0)</f>
+        <v>24817580.6332751</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <f aca="false">$A27-1972</f>
+        <v>77</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <f aca="false">$A27-1977</f>
+        <v>72</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <f aca="false">IF($A27&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A27-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <f aca="false">IF($A27&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A27-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A27-Inputs!$B$44)</f>
+        <v>697021.219595241</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A27-Inputs!$B$44)</f>
+        <v>255868.548965342</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <f aca="false">IF(D27=0,0,IF(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)&gt;200000,Inputs!$B$24+(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)-200000)*Inputs!$B$23,IF(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)&gt;150000,9000+(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)-150000)*0.14,IF(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)&gt;100000,4000+(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)-100000)*0.1,IF(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)&gt;50000,1000+(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0)-50000)*0.06,MAX(MAX(D27-Inputs!$B$22-Tax!$B$4/2-F27,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <f aca="false">IF(E27=0,0,IF(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)&gt;200000,Inputs!$B$24+(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)-200000)*Inputs!$B$23,IF(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)&gt;150000,9000+(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)-150000)*0.14,IF(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)&gt;100000,4000+(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)-100000)*0.1,IF(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)&gt;50000,1000+(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0)-50000)*0.06,MAX(MAX(E27-Inputs!$B$22-Tax!$B$4/2-G27,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="16" t="n">
+        <f aca="false">IF(D27&gt;0,Inputs!$B$22,0)+IF(E27&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="16" t="n">
+        <f aca="false">IF($A27&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A27-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="16" t="n">
+        <f aca="false">IF(AND($A27&gt;=Inputs!$B$47,$A27&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A27-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="16" t="n">
+        <f aca="false">IF($A27&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A27-Inputs!$B$44),0)</f>
+        <v>1376396.33236529</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <f aca="false">IF($A27&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O27" s="16" t="n">
+        <f aca="false">D27+E27-H27-I27-J27-K27-L27-M27+N27-Inputs!$B$42</f>
+        <v>-1108396.33236529</v>
+      </c>
+      <c r="P27" s="16" t="n">
+        <f aca="false">S26</f>
+        <v>24817580.6332751</v>
+      </c>
+      <c r="Q27" s="16" t="n">
+        <f aca="false">P27*Inputs!$B$35</f>
+        <v>1191243.87039721</v>
+      </c>
+      <c r="R27" s="16" t="n">
+        <f aca="false">IF($A27=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="16" t="n">
+        <f aca="false">MAX(P27+Q27+O27+R27,0)</f>
+        <v>24900428.171307</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <f aca="false">$A28-1972</f>
+        <v>78</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <f aca="false">$A28-1977</f>
+        <v>73</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <f aca="false">IF($A28&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A28-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <f aca="false">IF($A28&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A28-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A28-Inputs!$B$44)</f>
+        <v>714446.750085122</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A28-Inputs!$B$44)</f>
+        <v>262265.262689475</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <f aca="false">IF(D28=0,0,IF(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)&gt;200000,Inputs!$B$24+(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)-200000)*Inputs!$B$23,IF(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)&gt;150000,9000+(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)-150000)*0.14,IF(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)&gt;100000,4000+(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)-100000)*0.1,IF(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)&gt;50000,1000+(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0)-50000)*0.06,MAX(MAX(D28-Inputs!$B$22-Tax!$B$4/2-F28,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <f aca="false">IF(E28=0,0,IF(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)&gt;200000,Inputs!$B$24+(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)-200000)*Inputs!$B$23,IF(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)&gt;150000,9000+(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)-150000)*0.14,IF(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)&gt;100000,4000+(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)-100000)*0.1,IF(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)&gt;50000,1000+(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0)-50000)*0.06,MAX(MAX(E28-Inputs!$B$22-Tax!$B$4/2-G28,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="16" t="n">
+        <f aca="false">IF(D28&gt;0,Inputs!$B$22,0)+IF(E28&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="16" t="n">
+        <f aca="false">IF($A28&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A28-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
+        <f aca="false">IF(AND($A28&gt;=Inputs!$B$47,$A28&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A28-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <f aca="false">IF($A28&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A28-Inputs!$B$44),0)</f>
+        <v>1410806.24067442</v>
+      </c>
+      <c r="N28" s="16" t="n">
+        <f aca="false">IF($A28&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <f aca="false">D28+E28-H28-I28-J28-K28-L28-M28+N28-Inputs!$B$42</f>
+        <v>-1142806.24067442</v>
+      </c>
+      <c r="P28" s="16" t="n">
+        <f aca="false">S27</f>
+        <v>24900428.171307</v>
+      </c>
+      <c r="Q28" s="16" t="n">
+        <f aca="false">P28*Inputs!$B$35</f>
+        <v>1195220.55222274</v>
+      </c>
+      <c r="R28" s="16" t="n">
+        <f aca="false">IF($A28=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <f aca="false">MAX(P28+Q28+O28+R28,0)</f>
+        <v>24952842.4828553</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <f aca="false">$A29-1972</f>
+        <v>79</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <f aca="false">$A29-1977</f>
+        <v>74</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">IF($A29&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A29-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <f aca="false">IF($A29&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A29-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A29-Inputs!$B$44)</f>
+        <v>732307.91883725</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A29-Inputs!$B$44)</f>
+        <v>268821.894256712</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <f aca="false">IF(D29=0,0,IF(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)&gt;200000,Inputs!$B$24+(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)-200000)*Inputs!$B$23,IF(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)&gt;150000,9000+(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)-150000)*0.14,IF(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)&gt;100000,4000+(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)-100000)*0.1,IF(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)&gt;50000,1000+(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0)-50000)*0.06,MAX(MAX(D29-Inputs!$B$22-Tax!$B$4/2-F29,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <f aca="false">IF(E29=0,0,IF(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)&gt;200000,Inputs!$B$24+(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)-200000)*Inputs!$B$23,IF(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)&gt;150000,9000+(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)-150000)*0.14,IF(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)&gt;100000,4000+(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)-100000)*0.1,IF(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)&gt;50000,1000+(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0)-50000)*0.06,MAX(MAX(E29-Inputs!$B$22-Tax!$B$4/2-G29,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="16" t="n">
+        <f aca="false">IF(D29&gt;0,Inputs!$B$22,0)+IF(E29&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <f aca="false">IF($A29&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A29-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="16" t="n">
+        <f aca="false">IF(AND($A29&gt;=Inputs!$B$47,$A29&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A29-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <f aca="false">IF($A29&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A29-Inputs!$B$44),0)</f>
+        <v>1446076.39669128</v>
+      </c>
+      <c r="N29" s="16" t="n">
+        <f aca="false">IF($A29&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <f aca="false">D29+E29-H29-I29-J29-K29-L29-M29+N29-Inputs!$B$42</f>
+        <v>-1178076.39669128</v>
+      </c>
+      <c r="P29" s="16" t="n">
+        <f aca="false">S28</f>
+        <v>24952842.4828553</v>
+      </c>
+      <c r="Q29" s="16" t="n">
+        <f aca="false">P29*Inputs!$B$35</f>
+        <v>1197736.43917706</v>
+      </c>
+      <c r="R29" s="16" t="n">
+        <f aca="false">IF($A29=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <f aca="false">MAX(P29+Q29+O29+R29,0)</f>
+        <v>24972502.5253411</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <f aca="false">$A30-1972</f>
+        <v>80</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <f aca="false">$A30-1977</f>
+        <v>75</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">IF($A30&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A30-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <f aca="false">IF($A30&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A30-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A30-Inputs!$B$44)</f>
+        <v>750615.616808181</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A30-Inputs!$B$44)</f>
+        <v>275542.44161313</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <f aca="false">IF(D30=0,0,IF(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)&gt;200000,Inputs!$B$24+(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)-200000)*Inputs!$B$23,IF(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)&gt;150000,9000+(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)-150000)*0.14,IF(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)&gt;100000,4000+(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)-100000)*0.1,IF(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)&gt;50000,1000+(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0)-50000)*0.06,MAX(MAX(D30-Inputs!$B$22-Tax!$B$4/2-F30,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <f aca="false">IF(E30=0,0,IF(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)&gt;200000,Inputs!$B$24+(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)-200000)*Inputs!$B$23,IF(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)&gt;150000,9000+(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)-150000)*0.14,IF(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)&gt;100000,4000+(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)-100000)*0.1,IF(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)&gt;50000,1000+(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0)-50000)*0.06,MAX(MAX(E30-Inputs!$B$22-Tax!$B$4/2-G30,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <f aca="false">IF(D30&gt;0,Inputs!$B$22,0)+IF(E30&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="16" t="n">
+        <f aca="false">IF($A30&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A30-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="16" t="n">
+        <f aca="false">IF(AND($A30&gt;=Inputs!$B$47,$A30&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A30-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="16" t="n">
+        <f aca="false">IF($A30&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A30-Inputs!$B$44),0)</f>
+        <v>1482228.30660856</v>
+      </c>
+      <c r="N30" s="16" t="n">
+        <f aca="false">IF($A30&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <f aca="false">D30+E30-H30-I30-J30-K30-L30-M30+N30-Inputs!$B$42</f>
+        <v>-1214228.30660856</v>
+      </c>
+      <c r="P30" s="16" t="n">
+        <f aca="false">S29</f>
+        <v>24972502.5253411</v>
+      </c>
+      <c r="Q30" s="16" t="n">
+        <f aca="false">P30*Inputs!$B$35</f>
+        <v>1198680.12121637</v>
+      </c>
+      <c r="R30" s="16" t="n">
+        <f aca="false">IF($A30=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="16" t="n">
+        <f aca="false">MAX(P30+Q30+O30+R30,0)</f>
+        <v>24956954.3399489</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="n">
+        <v>2053</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <f aca="false">$A31-1972</f>
+        <v>81</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <f aca="false">$A31-1977</f>
+        <v>76</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">IF($A31&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A31-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <f aca="false">IF($A31&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A31-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A31-Inputs!$B$44)</f>
+        <v>769381.007228386</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A31-Inputs!$B$44)</f>
+        <v>282431.002653458</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <f aca="false">IF(D31=0,0,IF(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)&gt;200000,Inputs!$B$24+(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)-200000)*Inputs!$B$23,IF(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)&gt;150000,9000+(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)-150000)*0.14,IF(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)&gt;100000,4000+(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)-100000)*0.1,IF(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)&gt;50000,1000+(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0)-50000)*0.06,MAX(MAX(D31-Inputs!$B$22-Tax!$B$4/2-F31,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <f aca="false">IF(E31=0,0,IF(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)&gt;200000,Inputs!$B$24+(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)-200000)*Inputs!$B$23,IF(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)&gt;150000,9000+(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)-150000)*0.14,IF(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)&gt;100000,4000+(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)-100000)*0.1,IF(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)&gt;50000,1000+(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0)-50000)*0.06,MAX(MAX(E31-Inputs!$B$22-Tax!$B$4/2-G31,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <f aca="false">IF(D31&gt;0,Inputs!$B$22,0)+IF(E31&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="16" t="n">
+        <f aca="false">IF($A31&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A31-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="16" t="n">
+        <f aca="false">IF(AND($A31&gt;=Inputs!$B$47,$A31&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A31-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="16" t="n">
+        <f aca="false">IF($A31&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A31-Inputs!$B$44),0)</f>
+        <v>1519284.01427377</v>
+      </c>
+      <c r="N31" s="16" t="n">
+        <f aca="false">IF($A31&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O31" s="16" t="n">
+        <f aca="false">D31+E31-H31-I31-J31-K31-L31-M31+N31-Inputs!$B$42</f>
+        <v>-1251284.01427377</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <f aca="false">S30</f>
+        <v>24956954.3399489</v>
+      </c>
+      <c r="Q31" s="16" t="n">
+        <f aca="false">P31*Inputs!$B$35</f>
+        <v>1197933.80831755</v>
+      </c>
+      <c r="R31" s="16" t="n">
+        <f aca="false">IF($A31=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <f aca="false">MAX(P31+Q31+O31+R31,0)</f>
+        <v>24903604.1339927</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="n">
+        <v>2054</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <f aca="false">$A32-1972</f>
+        <v>82</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <f aca="false">$A32-1977</f>
+        <v>77</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <f aca="false">IF($A32&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A32-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <f aca="false">IF($A32&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A32-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A32-Inputs!$B$44)</f>
+        <v>788615.532409095</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A32-Inputs!$B$44)</f>
+        <v>289491.777719794</v>
+      </c>
+      <c r="H32" s="16" t="n">
+        <f aca="false">IF(D32=0,0,IF(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)&gt;200000,Inputs!$B$24+(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)-200000)*Inputs!$B$23,IF(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)&gt;150000,9000+(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)-150000)*0.14,IF(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)&gt;100000,4000+(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)-100000)*0.1,IF(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)&gt;50000,1000+(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0)-50000)*0.06,MAX(MAX(D32-Inputs!$B$22-Tax!$B$4/2-F32,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <f aca="false">IF(E32=0,0,IF(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)&gt;200000,Inputs!$B$24+(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)-200000)*Inputs!$B$23,IF(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)&gt;150000,9000+(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)-150000)*0.14,IF(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)&gt;100000,4000+(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)-100000)*0.1,IF(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)&gt;50000,1000+(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0)-50000)*0.06,MAX(MAX(E32-Inputs!$B$22-Tax!$B$4/2-G32,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <f aca="false">IF(D32&gt;0,Inputs!$B$22,0)+IF(E32&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="16" t="n">
+        <f aca="false">IF($A32&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A32-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="n">
+        <f aca="false">IF(AND($A32&gt;=Inputs!$B$47,$A32&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A32-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="16" t="n">
+        <f aca="false">IF($A32&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A32-Inputs!$B$44),0)</f>
+        <v>1557266.11463062</v>
+      </c>
+      <c r="N32" s="16" t="n">
+        <f aca="false">IF($A32&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <f aca="false">D32+E32-H32-I32-J32-K32-L32-M32+N32-Inputs!$B$42</f>
+        <v>-1289266.11463062</v>
+      </c>
+      <c r="P32" s="16" t="n">
+        <f aca="false">S31</f>
+        <v>24903604.1339927</v>
+      </c>
+      <c r="Q32" s="16" t="n">
+        <f aca="false">P32*Inputs!$B$35</f>
+        <v>1195372.99843165</v>
+      </c>
+      <c r="R32" s="16" t="n">
+        <f aca="false">IF($A32=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="16" t="n">
+        <f aca="false">MAX(P32+Q32+O32+R32,0)</f>
+        <v>24809711.0177937</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="n">
+        <v>2055</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <f aca="false">$A33-1972</f>
+        <v>83</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <f aca="false">$A33-1977</f>
+        <v>78</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <f aca="false">IF($A33&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A33-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <f aca="false">IF($A33&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A33-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A33-Inputs!$B$44)</f>
+        <v>808330.920719323</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A33-Inputs!$B$44)</f>
+        <v>296729.072162789</v>
+      </c>
+      <c r="H33" s="16" t="n">
+        <f aca="false">IF(D33=0,0,IF(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)&gt;200000,Inputs!$B$24+(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)-200000)*Inputs!$B$23,IF(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)&gt;150000,9000+(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)-150000)*0.14,IF(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)&gt;100000,4000+(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)-100000)*0.1,IF(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)&gt;50000,1000+(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0)-50000)*0.06,MAX(MAX(D33-Inputs!$B$22-Tax!$B$4/2-F33,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <f aca="false">IF(E33=0,0,IF(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)&gt;200000,Inputs!$B$24+(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)-200000)*Inputs!$B$23,IF(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)&gt;150000,9000+(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)-150000)*0.14,IF(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)&gt;100000,4000+(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)-100000)*0.1,IF(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)&gt;50000,1000+(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0)-50000)*0.06,MAX(MAX(E33-Inputs!$B$22-Tax!$B$4/2-G33,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="16" t="n">
+        <f aca="false">IF(D33&gt;0,Inputs!$B$22,0)+IF(E33&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="16" t="n">
+        <f aca="false">IF($A33&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A33-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="16" t="n">
+        <f aca="false">IF(AND($A33&gt;=Inputs!$B$47,$A33&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A33-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="16" t="n">
+        <f aca="false">IF($A33&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A33-Inputs!$B$44),0)</f>
+        <v>1596197.76749638</v>
+      </c>
+      <c r="N33" s="16" t="n">
+        <f aca="false">IF($A33&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O33" s="16" t="n">
+        <f aca="false">D33+E33-H33-I33-J33-K33-L33-M33+N33-Inputs!$B$42</f>
+        <v>-1328197.76749638</v>
+      </c>
+      <c r="P33" s="16" t="n">
+        <f aca="false">S32</f>
+        <v>24809711.0177937</v>
+      </c>
+      <c r="Q33" s="16" t="n">
+        <f aca="false">P33*Inputs!$B$35</f>
+        <v>1190866.1288541</v>
+      </c>
+      <c r="R33" s="16" t="n">
+        <f aca="false">IF($A33=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S33" s="16" t="n">
+        <f aca="false">MAX(P33+Q33+O33+R33,0)</f>
+        <v>24672379.3791515</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <f aca="false">$A34-1972</f>
+        <v>84</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <f aca="false">$A34-1977</f>
+        <v>79</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <f aca="false">IF($A34&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A34-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <f aca="false">IF($A34&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A34-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A34-Inputs!$B$44)</f>
+        <v>828539.193737305</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A34-Inputs!$B$44)</f>
+        <v>304147.298966859</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <f aca="false">IF(D34=0,0,IF(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)&gt;200000,Inputs!$B$24+(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)-200000)*Inputs!$B$23,IF(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)&gt;150000,9000+(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)-150000)*0.14,IF(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)&gt;100000,4000+(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)-100000)*0.1,IF(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)&gt;50000,1000+(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0)-50000)*0.06,MAX(MAX(D34-Inputs!$B$22-Tax!$B$4/2-F34,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <f aca="false">IF(E34=0,0,IF(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)&gt;200000,Inputs!$B$24+(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)-200000)*Inputs!$B$23,IF(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)&gt;150000,9000+(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)-150000)*0.14,IF(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)&gt;100000,4000+(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)-100000)*0.1,IF(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)&gt;50000,1000+(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0)-50000)*0.06,MAX(MAX(E34-Inputs!$B$22-Tax!$B$4/2-G34,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <f aca="false">IF(D34&gt;0,Inputs!$B$22,0)+IF(E34&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="16" t="n">
+        <f aca="false">IF($A34&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A34-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="16" t="n">
+        <f aca="false">IF(AND($A34&gt;=Inputs!$B$47,$A34&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A34-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="16" t="n">
+        <f aca="false">IF($A34&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A34-Inputs!$B$44),0)</f>
+        <v>1636102.71168379</v>
+      </c>
+      <c r="N34" s="16" t="n">
+        <f aca="false">IF($A34&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <f aca="false">D34+E34-H34-I34-J34-K34-L34-M34+N34-Inputs!$B$42</f>
+        <v>-1368102.71168379</v>
+      </c>
+      <c r="P34" s="16" t="n">
+        <f aca="false">S33</f>
+        <v>24672379.3791515</v>
+      </c>
+      <c r="Q34" s="16" t="n">
+        <f aca="false">P34*Inputs!$B$35</f>
+        <v>1184274.21019927</v>
+      </c>
+      <c r="R34" s="16" t="n">
+        <f aca="false">IF($A34=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="16" t="n">
+        <f aca="false">MAX(P34+Q34+O34+R34,0)</f>
+        <v>24488550.8776669</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="n">
+        <v>2057</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <f aca="false">$A35-1972</f>
+        <v>85</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <f aca="false">$A35-1977</f>
+        <v>80</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <f aca="false">IF($A35&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A35-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <f aca="false">IF($A35&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A35-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A35-Inputs!$B$44)</f>
+        <v>849252.673580738</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A35-Inputs!$B$44)</f>
+        <v>311750.98144103</v>
+      </c>
+      <c r="H35" s="16" t="n">
+        <f aca="false">IF(D35=0,0,IF(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)&gt;200000,Inputs!$B$24+(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)-200000)*Inputs!$B$23,IF(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)&gt;150000,9000+(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)-150000)*0.14,IF(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)&gt;100000,4000+(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)-100000)*0.1,IF(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)&gt;50000,1000+(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0)-50000)*0.06,MAX(MAX(D35-Inputs!$B$22-Tax!$B$4/2-F35,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <f aca="false">IF(E35=0,0,IF(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)&gt;200000,Inputs!$B$24+(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)-200000)*Inputs!$B$23,IF(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)&gt;150000,9000+(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)-150000)*0.14,IF(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)&gt;100000,4000+(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)-100000)*0.1,IF(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)&gt;50000,1000+(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0)-50000)*0.06,MAX(MAX(E35-Inputs!$B$22-Tax!$B$4/2-G35,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="16" t="n">
+        <f aca="false">IF(D35&gt;0,Inputs!$B$22,0)+IF(E35&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="16" t="n">
+        <f aca="false">IF($A35&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A35-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="16" t="n">
+        <f aca="false">IF(AND($A35&gt;=Inputs!$B$47,$A35&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A35-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <f aca="false">IF($A35&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A35-Inputs!$B$44),0)</f>
+        <v>1677005.27947589</v>
+      </c>
+      <c r="N35" s="16" t="n">
+        <f aca="false">IF($A35&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O35" s="16" t="n">
+        <f aca="false">D35+E35-H35-I35-J35-K35-L35-M35+N35-Inputs!$B$42</f>
+        <v>-1409005.27947589</v>
+      </c>
+      <c r="P35" s="16" t="n">
+        <f aca="false">S34</f>
+        <v>24488550.8776669</v>
+      </c>
+      <c r="Q35" s="16" t="n">
+        <f aca="false">P35*Inputs!$B$35</f>
+        <v>1175450.44212801</v>
+      </c>
+      <c r="R35" s="16" t="n">
+        <f aca="false">IF($A35=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S35" s="16" t="n">
+        <f aca="false">MAX(P35+Q35+O35+R35,0)</f>
+        <v>24254996.0403191</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <f aca="false">$A36-1972</f>
+        <v>86</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <f aca="false">$A36-1977</f>
+        <v>81</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <f aca="false">IF($A36&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A36-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <f aca="false">IF($A36&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A36-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A36-Inputs!$B$44)</f>
+        <v>870483.990420256</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A36-Inputs!$B$44)</f>
+        <v>319544.755977056</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <f aca="false">IF(D36=0,0,IF(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)&gt;200000,Inputs!$B$24+(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)-200000)*Inputs!$B$23,IF(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)&gt;150000,9000+(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)-150000)*0.14,IF(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)&gt;100000,4000+(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)-100000)*0.1,IF(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)&gt;50000,1000+(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0)-50000)*0.06,MAX(MAX(D36-Inputs!$B$22-Tax!$B$4/2-F36,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <f aca="false">IF(E36=0,0,IF(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)&gt;200000,Inputs!$B$24+(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)-200000)*Inputs!$B$23,IF(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)&gt;150000,9000+(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)-150000)*0.14,IF(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)&gt;100000,4000+(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)-100000)*0.1,IF(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)&gt;50000,1000+(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0)-50000)*0.06,MAX(MAX(E36-Inputs!$B$22-Tax!$B$4/2-G36,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <f aca="false">IF(D36&gt;0,Inputs!$B$22,0)+IF(E36&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="16" t="n">
+        <f aca="false">IF($A36&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A36-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="16" t="n">
+        <f aca="false">IF(AND($A36&gt;=Inputs!$B$47,$A36&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A36-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="16" t="n">
+        <f aca="false">IF($A36&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A36-Inputs!$B$44),0)</f>
+        <v>1718930.41146278</v>
+      </c>
+      <c r="N36" s="16" t="n">
+        <f aca="false">IF($A36&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <f aca="false">D36+E36-H36-I36-J36-K36-L36-M36+N36-Inputs!$B$42</f>
+        <v>-1450930.41146278</v>
+      </c>
+      <c r="P36" s="16" t="n">
+        <f aca="false">S35</f>
+        <v>24254996.0403191</v>
+      </c>
+      <c r="Q36" s="16" t="n">
+        <f aca="false">P36*Inputs!$B$35</f>
+        <v>1164239.80993532</v>
+      </c>
+      <c r="R36" s="16" t="n">
+        <f aca="false">IF($A36=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="16" t="n">
+        <f aca="false">MAX(P36+Q36+O36+R36,0)</f>
+        <v>23968305.4387916</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19" t="n">
+        <v>2059</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <f aca="false">$A37-1972</f>
+        <v>87</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <f aca="false">$A37-1977</f>
+        <v>82</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <f aca="false">IF($A37&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A37-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <f aca="false">IF($A37&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A37-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A37-Inputs!$B$44)</f>
+        <v>892246.090180763</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A37-Inputs!$B$44)</f>
+        <v>327533.374876483</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <f aca="false">IF(D37=0,0,IF(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)&gt;200000,Inputs!$B$24+(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)-200000)*Inputs!$B$23,IF(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)&gt;150000,9000+(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)-150000)*0.14,IF(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)&gt;100000,4000+(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)-100000)*0.1,IF(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)&gt;50000,1000+(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0)-50000)*0.06,MAX(MAX(D37-Inputs!$B$22-Tax!$B$4/2-F37,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <f aca="false">IF(E37=0,0,IF(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)&gt;200000,Inputs!$B$24+(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)-200000)*Inputs!$B$23,IF(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)&gt;150000,9000+(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)-150000)*0.14,IF(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)&gt;100000,4000+(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)-100000)*0.1,IF(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)&gt;50000,1000+(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0)-50000)*0.06,MAX(MAX(E37-Inputs!$B$22-Tax!$B$4/2-G37,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="16" t="n">
+        <f aca="false">IF(D37&gt;0,Inputs!$B$22,0)+IF(E37&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="16" t="n">
+        <f aca="false">IF($A37&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A37-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="16" t="n">
+        <f aca="false">IF(AND($A37&gt;=Inputs!$B$47,$A37&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A37-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="16" t="n">
+        <f aca="false">IF($A37&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A37-Inputs!$B$44),0)</f>
+        <v>1761903.67174935</v>
+      </c>
+      <c r="N37" s="16" t="n">
+        <f aca="false">IF($A37&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O37" s="16" t="n">
+        <f aca="false">D37+E37-H37-I37-J37-K37-L37-M37+N37-Inputs!$B$42</f>
+        <v>-1493903.67174935</v>
+      </c>
+      <c r="P37" s="16" t="n">
+        <f aca="false">S36</f>
+        <v>23968305.4387916</v>
+      </c>
+      <c r="Q37" s="16" t="n">
+        <f aca="false">P37*Inputs!$B$35</f>
+        <v>1150478.661062</v>
+      </c>
+      <c r="R37" s="16" t="n">
+        <f aca="false">IF($A37=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S37" s="16" t="n">
+        <f aca="false">MAX(P37+Q37+O37+R37,0)</f>
+        <v>23624880.4281042</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="n">
+        <v>2060</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <f aca="false">$A38-1972</f>
+        <v>88</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <f aca="false">$A38-1977</f>
+        <v>83</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <f aca="false">IF($A38&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A38-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <f aca="false">IF($A38&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A38-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A38-Inputs!$B$44)</f>
+        <v>914552.242435282</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A38-Inputs!$B$44)</f>
+        <v>335721.709248395</v>
+      </c>
+      <c r="H38" s="16" t="n">
+        <f aca="false">IF(D38=0,0,IF(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)&gt;200000,Inputs!$B$24+(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)-200000)*Inputs!$B$23,IF(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)&gt;150000,9000+(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)-150000)*0.14,IF(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)&gt;100000,4000+(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)-100000)*0.1,IF(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)&gt;50000,1000+(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0)-50000)*0.06,MAX(MAX(D38-Inputs!$B$22-Tax!$B$4/2-F38,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="16" t="n">
+        <f aca="false">IF(E38=0,0,IF(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)&gt;200000,Inputs!$B$24+(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)-200000)*Inputs!$B$23,IF(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)&gt;150000,9000+(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)-150000)*0.14,IF(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)&gt;100000,4000+(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)-100000)*0.1,IF(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)&gt;50000,1000+(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0)-50000)*0.06,MAX(MAX(E38-Inputs!$B$22-Tax!$B$4/2-G38,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <f aca="false">IF(D38&gt;0,Inputs!$B$22,0)+IF(E38&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="16" t="n">
+        <f aca="false">IF($A38&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A38-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="n">
+        <f aca="false">IF(AND($A38&gt;=Inputs!$B$47,$A38&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A38-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <f aca="false">IF($A38&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A38-Inputs!$B$44),0)</f>
+        <v>1805951.26354309</v>
+      </c>
+      <c r="N38" s="16" t="n">
+        <f aca="false">IF($A38&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <f aca="false">D38+E38-H38-I38-J38-K38-L38-M38+N38-Inputs!$B$42</f>
+        <v>-1537951.26354309</v>
+      </c>
+      <c r="P38" s="16" t="n">
+        <f aca="false">S37</f>
+        <v>23624880.4281042</v>
+      </c>
+      <c r="Q38" s="16" t="n">
+        <f aca="false">P38*Inputs!$B$35</f>
+        <v>1133994.260549</v>
+      </c>
+      <c r="R38" s="16" t="n">
+        <f aca="false">IF($A38=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S38" s="16" t="n">
+        <f aca="false">MAX(P38+Q38+O38+R38,0)</f>
+        <v>23220923.4251102</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="n">
+        <v>2061</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <f aca="false">$A39-1972</f>
+        <v>89</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <f aca="false">$A39-1977</f>
+        <v>84</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <f aca="false">IF($A39&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A39-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <f aca="false">IF($A39&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A39-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A39-Inputs!$B$44)</f>
+        <v>937416.048496164</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A39-Inputs!$B$44)</f>
+        <v>344114.751979604</v>
+      </c>
+      <c r="H39" s="16" t="n">
+        <f aca="false">IF(D39=0,0,IF(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)&gt;200000,Inputs!$B$24+(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)-200000)*Inputs!$B$23,IF(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)&gt;150000,9000+(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)-150000)*0.14,IF(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)&gt;100000,4000+(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)-100000)*0.1,IF(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)&gt;50000,1000+(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0)-50000)*0.06,MAX(MAX(D39-Inputs!$B$22-Tax!$B$4/2-F39,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="16" t="n">
+        <f aca="false">IF(E39=0,0,IF(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)&gt;200000,Inputs!$B$24+(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)-200000)*Inputs!$B$23,IF(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)&gt;150000,9000+(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)-150000)*0.14,IF(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)&gt;100000,4000+(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)-100000)*0.1,IF(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)&gt;50000,1000+(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0)-50000)*0.06,MAX(MAX(E39-Inputs!$B$22-Tax!$B$4/2-G39,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="16" t="n">
+        <f aca="false">IF(D39&gt;0,Inputs!$B$22,0)+IF(E39&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="16" t="n">
+        <f aca="false">IF($A39&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A39-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="16" t="n">
+        <f aca="false">IF(AND($A39&gt;=Inputs!$B$47,$A39&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A39-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="16" t="n">
+        <f aca="false">IF($A39&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A39-Inputs!$B$44),0)</f>
+        <v>1851100.04513167</v>
+      </c>
+      <c r="N39" s="16" t="n">
+        <f aca="false">IF($A39&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O39" s="16" t="n">
+        <f aca="false">D39+E39-H39-I39-J39-K39-L39-M39+N39-Inputs!$B$42</f>
+        <v>-1583100.04513167</v>
+      </c>
+      <c r="P39" s="16" t="n">
+        <f aca="false">S38</f>
+        <v>23220923.4251102</v>
+      </c>
+      <c r="Q39" s="16" t="n">
+        <f aca="false">P39*Inputs!$B$35</f>
+        <v>1114604.32440529</v>
+      </c>
+      <c r="R39" s="16" t="n">
+        <f aca="false">IF($A39=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S39" s="16" t="n">
+        <f aca="false">MAX(P39+Q39+O39+R39,0)</f>
+        <v>22752427.7043838</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19" t="n">
+        <v>2062</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <f aca="false">$A40-1972</f>
+        <v>90</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <f aca="false">$A40-1977</f>
+        <v>85</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <f aca="false">IF($A40&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A40-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <f aca="false">IF($A40&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A40-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A40-Inputs!$B$44)</f>
+        <v>960851.449708568</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A40-Inputs!$B$44)</f>
+        <v>352717.620779094</v>
+      </c>
+      <c r="H40" s="16" t="n">
+        <f aca="false">IF(D40=0,0,IF(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)&gt;200000,Inputs!$B$24+(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)-200000)*Inputs!$B$23,IF(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)&gt;150000,9000+(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)-150000)*0.14,IF(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)&gt;100000,4000+(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)-100000)*0.1,IF(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)&gt;50000,1000+(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0)-50000)*0.06,MAX(MAX(D40-Inputs!$B$22-Tax!$B$4/2-F40,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="16" t="n">
+        <f aca="false">IF(E40=0,0,IF(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)&gt;200000,Inputs!$B$24+(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)-200000)*Inputs!$B$23,IF(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)&gt;150000,9000+(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)-150000)*0.14,IF(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)&gt;100000,4000+(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)-100000)*0.1,IF(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)&gt;50000,1000+(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0)-50000)*0.06,MAX(MAX(E40-Inputs!$B$22-Tax!$B$4/2-G40,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="16" t="n">
+        <f aca="false">IF(D40&gt;0,Inputs!$B$22,0)+IF(E40&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16" t="n">
+        <f aca="false">IF($A40&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A40-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="16" t="n">
+        <f aca="false">IF(AND($A40&gt;=Inputs!$B$47,$A40&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A40-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="16" t="n">
+        <f aca="false">IF($A40&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A40-Inputs!$B$44),0)</f>
+        <v>1897377.54625996</v>
+      </c>
+      <c r="N40" s="16" t="n">
+        <f aca="false">IF($A40&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <f aca="false">D40+E40-H40-I40-J40-K40-L40-M40+N40-Inputs!$B$42</f>
+        <v>-1629377.54625996</v>
+      </c>
+      <c r="P40" s="16" t="n">
+        <f aca="false">S39</f>
+        <v>22752427.7043838</v>
+      </c>
+      <c r="Q40" s="16" t="n">
+        <f aca="false">P40*Inputs!$B$35</f>
+        <v>1092116.52981042</v>
+      </c>
+      <c r="R40" s="16" t="n">
+        <f aca="false">IF($A40=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S40" s="16" t="n">
+        <f aca="false">MAX(P40+Q40+O40+R40,0)</f>
+        <v>22215166.6879342</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="19" t="n">
+        <v>2063</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <f aca="false">$A41-1972</f>
+        <v>91</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <f aca="false">$A41-1977</f>
+        <v>86</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <f aca="false">IF($A41&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A41-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <f aca="false">IF($A41&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A41-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A41-Inputs!$B$44)</f>
+        <v>984872.735951282</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A41-Inputs!$B$44)</f>
+        <v>361535.561298572</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <f aca="false">IF(D41=0,0,IF(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)&gt;200000,Inputs!$B$24+(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)-200000)*Inputs!$B$23,IF(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)&gt;150000,9000+(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)-150000)*0.14,IF(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)&gt;100000,4000+(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)-100000)*0.1,IF(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)&gt;50000,1000+(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0)-50000)*0.06,MAX(MAX(D41-Inputs!$B$22-Tax!$B$4/2-F41,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="16" t="n">
+        <f aca="false">IF(E41=0,0,IF(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)&gt;200000,Inputs!$B$24+(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)-200000)*Inputs!$B$23,IF(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)&gt;150000,9000+(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)-150000)*0.14,IF(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)&gt;100000,4000+(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)-100000)*0.1,IF(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)&gt;50000,1000+(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0)-50000)*0.06,MAX(MAX(E41-Inputs!$B$22-Tax!$B$4/2-G41,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="16" t="n">
+        <f aca="false">IF(D41&gt;0,Inputs!$B$22,0)+IF(E41&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="16" t="n">
+        <f aca="false">IF($A41&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A41-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="16" t="n">
+        <f aca="false">IF(AND($A41&gt;=Inputs!$B$47,$A41&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A41-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="16" t="n">
+        <f aca="false">IF($A41&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A41-Inputs!$B$44),0)</f>
+        <v>1944811.98491646</v>
+      </c>
+      <c r="N41" s="16" t="n">
+        <f aca="false">IF($A41&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O41" s="16" t="n">
+        <f aca="false">D41+E41-H41-I41-J41-K41-L41-M41+N41-Inputs!$B$42</f>
+        <v>-1676811.98491646</v>
+      </c>
+      <c r="P41" s="16" t="n">
+        <f aca="false">S40</f>
+        <v>22215166.6879342</v>
+      </c>
+      <c r="Q41" s="16" t="n">
+        <f aca="false">P41*Inputs!$B$35</f>
+        <v>1066328.00102084</v>
+      </c>
+      <c r="R41" s="16" t="n">
+        <f aca="false">IF($A41=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <f aca="false">MAX(P41+Q41+O41+R41,0)</f>
+        <v>21604682.7040386</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="19" t="n">
+        <v>2064</v>
+      </c>
+      <c r="B42" s="19" t="n">
+        <f aca="false">$A42-1972</f>
+        <v>92</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <f aca="false">$A42-1977</f>
+        <v>87</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <f aca="false">IF($A42&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A42-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <f aca="false">IF($A42&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A42-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A42-Inputs!$B$44)</f>
+        <v>1009494.55435006</v>
+      </c>
+      <c r="G42" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A42-Inputs!$B$44)</f>
+        <v>370573.950331036</v>
+      </c>
+      <c r="H42" s="16" t="n">
+        <f aca="false">IF(D42=0,0,IF(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)&gt;200000,Inputs!$B$24+(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)-200000)*Inputs!$B$23,IF(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)&gt;150000,9000+(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)-150000)*0.14,IF(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)&gt;100000,4000+(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)-100000)*0.1,IF(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)&gt;50000,1000+(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0)-50000)*0.06,MAX(MAX(D42-Inputs!$B$22-Tax!$B$4/2-F42,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="16" t="n">
+        <f aca="false">IF(E42=0,0,IF(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)&gt;200000,Inputs!$B$24+(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)-200000)*Inputs!$B$23,IF(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)&gt;150000,9000+(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)-150000)*0.14,IF(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)&gt;100000,4000+(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)-100000)*0.1,IF(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)&gt;50000,1000+(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0)-50000)*0.06,MAX(MAX(E42-Inputs!$B$22-Tax!$B$4/2-G42,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="16" t="n">
+        <f aca="false">IF(D42&gt;0,Inputs!$B$22,0)+IF(E42&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="16" t="n">
+        <f aca="false">IF($A42&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A42-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="16" t="n">
+        <f aca="false">IF(AND($A42&gt;=Inputs!$B$47,$A42&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A42-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="16" t="n">
+        <f aca="false">IF($A42&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A42-Inputs!$B$44),0)</f>
+        <v>1993432.28453937</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <f aca="false">IF($A42&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <f aca="false">D42+E42-H42-I42-J42-K42-L42-M42+N42-Inputs!$B$42</f>
+        <v>-1725432.28453937</v>
+      </c>
+      <c r="P42" s="16" t="n">
+        <f aca="false">S41</f>
+        <v>21604682.7040386</v>
+      </c>
+      <c r="Q42" s="16" t="n">
+        <f aca="false">P42*Inputs!$B$35</f>
+        <v>1037024.76979385</v>
+      </c>
+      <c r="R42" s="16" t="n">
+        <f aca="false">IF($A42=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <f aca="false">MAX(P42+Q42+O42+R42,0)</f>
+        <v>20916275.1892931</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="19" t="n">
+        <v>2065</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <f aca="false">$A43-1972</f>
+        <v>93</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <f aca="false">$A43-1977</f>
+        <v>88</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <f aca="false">IF($A43&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A43-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <f aca="false">IF($A43&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A43-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A43-Inputs!$B$44)</f>
+        <v>1034731.91820882</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A43-Inputs!$B$44)</f>
+        <v>379838.299089312</v>
+      </c>
+      <c r="H43" s="16" t="n">
+        <f aca="false">IF(D43=0,0,IF(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)&gt;200000,Inputs!$B$24+(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)-200000)*Inputs!$B$23,IF(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)&gt;150000,9000+(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)-150000)*0.14,IF(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)&gt;100000,4000+(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)-100000)*0.1,IF(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)&gt;50000,1000+(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0)-50000)*0.06,MAX(MAX(D43-Inputs!$B$22-Tax!$B$4/2-F43,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="16" t="n">
+        <f aca="false">IF(E43=0,0,IF(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)&gt;200000,Inputs!$B$24+(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)-200000)*Inputs!$B$23,IF(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)&gt;150000,9000+(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)-150000)*0.14,IF(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)&gt;100000,4000+(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)-100000)*0.1,IF(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)&gt;50000,1000+(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0)-50000)*0.06,MAX(MAX(E43-Inputs!$B$22-Tax!$B$4/2-G43,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="16" t="n">
+        <f aca="false">IF(D43&gt;0,Inputs!$B$22,0)+IF(E43&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="16" t="n">
+        <f aca="false">IF($A43&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A43-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="16" t="n">
+        <f aca="false">IF(AND($A43&gt;=Inputs!$B$47,$A43&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A43-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="16" t="n">
+        <f aca="false">IF($A43&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A43-Inputs!$B$44),0)</f>
+        <v>2043268.09165285</v>
+      </c>
+      <c r="N43" s="16" t="n">
+        <f aca="false">IF($A43&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O43" s="16" t="n">
+        <f aca="false">D43+E43-H43-I43-J43-K43-L43-M43+N43-Inputs!$B$42</f>
+        <v>-1775268.09165285</v>
+      </c>
+      <c r="P43" s="16" t="n">
+        <f aca="false">S42</f>
+        <v>20916275.1892931</v>
+      </c>
+      <c r="Q43" s="16" t="n">
+        <f aca="false">P43*Inputs!$B$35</f>
+        <v>1003981.20908607</v>
+      </c>
+      <c r="R43" s="16" t="n">
+        <f aca="false">IF($A43=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S43" s="16" t="n">
+        <f aca="false">MAX(P43+Q43+O43+R43,0)</f>
+        <v>20144988.3067263</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="n">
+        <v>2066</v>
+      </c>
+      <c r="B44" s="20" t="n">
+        <f aca="false">$A44-1972</f>
+        <v>94</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <f aca="false">$A44-1977</f>
+        <v>89</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <f aca="false">IF($A44&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A44-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <f aca="false">IF($A44&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A44-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A44-Inputs!$B$44)</f>
+        <v>1060600.21616404</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A44-Inputs!$B$44)</f>
+        <v>389334.256566545</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <f aca="false">IF(D44=0,0,IF(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)&gt;200000,Inputs!$B$24+(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)-200000)*Inputs!$B$23,IF(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)&gt;150000,9000+(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)-150000)*0.14,IF(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)&gt;100000,4000+(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)-100000)*0.1,IF(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)&gt;50000,1000+(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0)-50000)*0.06,MAX(MAX(D44-Inputs!$B$22-Tax!$B$4/2-F44,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="21" t="n">
+        <f aca="false">IF(E44=0,0,IF(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)&gt;200000,Inputs!$B$24+(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)-200000)*Inputs!$B$23,IF(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)&gt;150000,9000+(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)-150000)*0.14,IF(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)&gt;100000,4000+(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)-100000)*0.1,IF(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)&gt;50000,1000+(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0)-50000)*0.06,MAX(MAX(E44-Inputs!$B$22-Tax!$B$4/2-G44,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="21" t="n">
+        <f aca="false">IF(D44&gt;0,Inputs!$B$22,0)+IF(E44&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="21" t="n">
+        <f aca="false">IF($A44&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A44-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L44" s="21" t="n">
+        <f aca="false">IF(AND($A44&gt;=Inputs!$B$47,$A44&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A44-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="21" t="n">
+        <f aca="false">IF($A44&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A44-Inputs!$B$44),0)</f>
+        <v>2094349.79394417</v>
+      </c>
+      <c r="N44" s="21" t="n">
+        <f aca="false">IF($A44&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O44" s="21" t="n">
+        <f aca="false">D44+E44-H44-I44-J44-K44-L44-M44+N44-Inputs!$B$42</f>
+        <v>-1826349.79394417</v>
+      </c>
+      <c r="P44" s="21" t="n">
+        <f aca="false">S43</f>
+        <v>20144988.3067263</v>
+      </c>
+      <c r="Q44" s="21" t="n">
+        <f aca="false">P44*Inputs!$B$35</f>
+        <v>966959.438722864</v>
+      </c>
+      <c r="R44" s="21" t="n">
+        <f aca="false">IF($A44=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S44" s="21" t="n">
+        <f aca="false">MAX(P44+Q44+O44+R44,0)</f>
+        <v>19285597.951505</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="19" t="n">
+        <v>2067</v>
+      </c>
+      <c r="B45" s="19" t="n">
+        <f aca="false">$A45-1972</f>
+        <v>95</v>
+      </c>
+      <c r="C45" s="19" t="n">
+        <f aca="false">$A45-1977</f>
+        <v>90</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <f aca="false">IF($A45&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A45-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <f aca="false">IF($A45&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A45-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A45-Inputs!$B$44)</f>
+        <v>1087115.22156814</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A45-Inputs!$B$44)</f>
+        <v>399067.612980708</v>
+      </c>
+      <c r="H45" s="16" t="n">
+        <f aca="false">IF(D45=0,0,IF(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)&gt;200000,Inputs!$B$24+(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)-200000)*Inputs!$B$23,IF(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)&gt;150000,9000+(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)-150000)*0.14,IF(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)&gt;100000,4000+(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)-100000)*0.1,IF(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)&gt;50000,1000+(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0)-50000)*0.06,MAX(MAX(D45-Inputs!$B$22-Tax!$B$4/2-F45,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="16" t="n">
+        <f aca="false">IF(E45=0,0,IF(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)&gt;200000,Inputs!$B$24+(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)-200000)*Inputs!$B$23,IF(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)&gt;150000,9000+(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)-150000)*0.14,IF(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)&gt;100000,4000+(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)-100000)*0.1,IF(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)&gt;50000,1000+(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0)-50000)*0.06,MAX(MAX(E45-Inputs!$B$22-Tax!$B$4/2-G45,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <f aca="false">IF(D45&gt;0,Inputs!$B$22,0)+IF(E45&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="16" t="n">
+        <f aca="false">IF($A45&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A45-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="16" t="n">
+        <f aca="false">IF(AND($A45&gt;=Inputs!$B$47,$A45&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A45-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="16" t="n">
+        <f aca="false">IF($A45&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A45-Inputs!$B$44),0)</f>
+        <v>2146708.53879278</v>
+      </c>
+      <c r="N45" s="16" t="n">
+        <f aca="false">IF($A45&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O45" s="16" t="n">
+        <f aca="false">D45+E45-H45-I45-J45-K45-L45-M45+N45-Inputs!$B$42</f>
+        <v>-1878708.53879278</v>
+      </c>
+      <c r="P45" s="16" t="n">
+        <f aca="false">S44</f>
+        <v>19285597.951505</v>
+      </c>
+      <c r="Q45" s="16" t="n">
+        <f aca="false">P45*Inputs!$B$35</f>
+        <v>925708.701672241</v>
+      </c>
+      <c r="R45" s="16" t="n">
+        <f aca="false">IF($A45=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S45" s="16" t="n">
+        <f aca="false">MAX(P45+Q45+O45+R45,0)</f>
+        <v>18332598.1143845</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="19" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B46" s="19" t="n">
+        <f aca="false">$A46-1972</f>
+        <v>96</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <f aca="false">$A46-1977</f>
+        <v>91</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <f aca="false">IF($A46&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A46-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <f aca="false">IF($A46&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A46-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A46-Inputs!$B$44)</f>
+        <v>1114293.10210734</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A46-Inputs!$B$44)</f>
+        <v>409044.303305226</v>
+      </c>
+      <c r="H46" s="16" t="n">
+        <f aca="false">IF(D46=0,0,IF(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)&gt;200000,Inputs!$B$24+(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)-200000)*Inputs!$B$23,IF(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)&gt;150000,9000+(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)-150000)*0.14,IF(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)&gt;100000,4000+(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)-100000)*0.1,IF(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)&gt;50000,1000+(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0)-50000)*0.06,MAX(MAX(D46-Inputs!$B$22-Tax!$B$4/2-F46,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="16" t="n">
+        <f aca="false">IF(E46=0,0,IF(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)&gt;200000,Inputs!$B$24+(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)-200000)*Inputs!$B$23,IF(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)&gt;150000,9000+(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)-150000)*0.14,IF(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)&gt;100000,4000+(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)-100000)*0.1,IF(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)&gt;50000,1000+(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0)-50000)*0.06,MAX(MAX(E46-Inputs!$B$22-Tax!$B$4/2-G46,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <f aca="false">IF(D46&gt;0,Inputs!$B$22,0)+IF(E46&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="16" t="n">
+        <f aca="false">IF($A46&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A46-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="16" t="n">
+        <f aca="false">IF(AND($A46&gt;=Inputs!$B$47,$A46&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A46-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="16" t="n">
+        <f aca="false">IF($A46&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A46-Inputs!$B$44),0)</f>
+        <v>2200376.25226259</v>
+      </c>
+      <c r="N46" s="16" t="n">
+        <f aca="false">IF($A46&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <f aca="false">D46+E46-H46-I46-J46-K46-L46-M46+N46-Inputs!$B$42</f>
+        <v>-1932376.25226259</v>
+      </c>
+      <c r="P46" s="16" t="n">
+        <f aca="false">S45</f>
+        <v>18332598.1143845</v>
+      </c>
+      <c r="Q46" s="16" t="n">
+        <f aca="false">P46*Inputs!$B$35</f>
+        <v>879964.709490456</v>
+      </c>
+      <c r="R46" s="16" t="n">
+        <f aca="false">IF($A46=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <f aca="false">MAX(P46+Q46+O46+R46,0)</f>
+        <v>17280186.5716124</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="19" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <f aca="false">$A47-1972</f>
+        <v>97</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <f aca="false">$A47-1977</f>
+        <v>92</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <f aca="false">IF($A47&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A47-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <f aca="false">IF($A47&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A47-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A47-Inputs!$B$44)</f>
+        <v>1142150.42966002</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A47-Inputs!$B$44)</f>
+        <v>419270.410887857</v>
+      </c>
+      <c r="H47" s="16" t="n">
+        <f aca="false">IF(D47=0,0,IF(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)&gt;200000,Inputs!$B$24+(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)-200000)*Inputs!$B$23,IF(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)&gt;150000,9000+(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)-150000)*0.14,IF(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)&gt;100000,4000+(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)-100000)*0.1,IF(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)&gt;50000,1000+(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0)-50000)*0.06,MAX(MAX(D47-Inputs!$B$22-Tax!$B$4/2-F47,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <f aca="false">IF(E47=0,0,IF(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)&gt;200000,Inputs!$B$24+(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)-200000)*Inputs!$B$23,IF(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)&gt;150000,9000+(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)-150000)*0.14,IF(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)&gt;100000,4000+(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)-100000)*0.1,IF(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)&gt;50000,1000+(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0)-50000)*0.06,MAX(MAX(E47-Inputs!$B$22-Tax!$B$4/2-G47,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <f aca="false">IF(D47&gt;0,Inputs!$B$22,0)+IF(E47&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="16" t="n">
+        <f aca="false">IF($A47&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A47-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="16" t="n">
+        <f aca="false">IF(AND($A47&gt;=Inputs!$B$47,$A47&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A47-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="16" t="n">
+        <f aca="false">IF($A47&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A47-Inputs!$B$44),0)</f>
+        <v>2255385.65856916</v>
+      </c>
+      <c r="N47" s="16" t="n">
+        <f aca="false">IF($A47&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <f aca="false">D47+E47-H47-I47-J47-K47-L47-M47+N47-Inputs!$B$42</f>
+        <v>-1987385.65856916</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <f aca="false">S46</f>
+        <v>17280186.5716124</v>
+      </c>
+      <c r="Q47" s="16" t="n">
+        <f aca="false">P47*Inputs!$B$35</f>
+        <v>829448.955437393</v>
+      </c>
+      <c r="R47" s="16" t="n">
+        <f aca="false">IF($A47=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S47" s="16" t="n">
+        <f aca="false">MAX(P47+Q47+O47+R47,0)</f>
+        <v>16122249.8684806</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="19" t="n">
+        <v>2070</v>
+      </c>
+      <c r="B48" s="19" t="n">
+        <f aca="false">$A48-1972</f>
+        <v>98</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <f aca="false">$A48-1977</f>
+        <v>93</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <f aca="false">IF($A48&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A48-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <f aca="false">IF($A48&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A48-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A48-Inputs!$B$44)</f>
+        <v>1170704.19040152</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A48-Inputs!$B$44)</f>
+        <v>429752.171160053</v>
+      </c>
+      <c r="H48" s="16" t="n">
+        <f aca="false">IF(D48=0,0,IF(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)&gt;200000,Inputs!$B$24+(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)-200000)*Inputs!$B$23,IF(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)&gt;150000,9000+(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)-150000)*0.14,IF(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)&gt;100000,4000+(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)-100000)*0.1,IF(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)&gt;50000,1000+(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0)-50000)*0.06,MAX(MAX(D48-Inputs!$B$22-Tax!$B$4/2-F48,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <f aca="false">IF(E48=0,0,IF(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)&gt;200000,Inputs!$B$24+(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)-200000)*Inputs!$B$23,IF(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)&gt;150000,9000+(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)-150000)*0.14,IF(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)&gt;100000,4000+(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)-100000)*0.1,IF(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)&gt;50000,1000+(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0)-50000)*0.06,MAX(MAX(E48-Inputs!$B$22-Tax!$B$4/2-G48,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <f aca="false">IF(D48&gt;0,Inputs!$B$22,0)+IF(E48&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="16" t="n">
+        <f aca="false">IF($A48&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A48-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="16" t="n">
+        <f aca="false">IF(AND($A48&gt;=Inputs!$B$47,$A48&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A48-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="16" t="n">
+        <f aca="false">IF($A48&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A48-Inputs!$B$44),0)</f>
+        <v>2311770.30003339</v>
+      </c>
+      <c r="N48" s="16" t="n">
+        <f aca="false">IF($A48&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O48" s="16" t="n">
+        <f aca="false">D48+E48-H48-I48-J48-K48-L48-M48+N48-Inputs!$B$42</f>
+        <v>-2043770.30003339</v>
+      </c>
+      <c r="P48" s="16" t="n">
+        <f aca="false">S47</f>
+        <v>16122249.8684806</v>
+      </c>
+      <c r="Q48" s="16" t="n">
+        <f aca="false">P48*Inputs!$B$35</f>
+        <v>773867.993687068</v>
+      </c>
+      <c r="R48" s="16" t="n">
+        <f aca="false">IF($A48=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S48" s="16" t="n">
+        <f aca="false">MAX(P48+Q48+O48+R48,0)</f>
+        <v>14852347.5621343</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="19" t="n">
+        <v>2071</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <f aca="false">$A49-1972</f>
+        <v>99</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <f aca="false">$A49-1977</f>
+        <v>94</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <f aca="false">IF($A49&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A49-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <f aca="false">IF($A49&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A49-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A49-Inputs!$B$44)</f>
+        <v>1199971.79516156</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A49-Inputs!$B$44)</f>
+        <v>440495.975439054</v>
+      </c>
+      <c r="H49" s="16" t="n">
+        <f aca="false">IF(D49=0,0,IF(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)&gt;200000,Inputs!$B$24+(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)-200000)*Inputs!$B$23,IF(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)&gt;150000,9000+(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)-150000)*0.14,IF(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)&gt;100000,4000+(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)-100000)*0.1,IF(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)&gt;50000,1000+(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0)-50000)*0.06,MAX(MAX(D49-Inputs!$B$22-Tax!$B$4/2-F49,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="16" t="n">
+        <f aca="false">IF(E49=0,0,IF(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)&gt;200000,Inputs!$B$24+(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)-200000)*Inputs!$B$23,IF(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)&gt;150000,9000+(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)-150000)*0.14,IF(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)&gt;100000,4000+(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)-100000)*0.1,IF(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)&gt;50000,1000+(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0)-50000)*0.06,MAX(MAX(E49-Inputs!$B$22-Tax!$B$4/2-G49,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="16" t="n">
+        <f aca="false">IF(D49&gt;0,Inputs!$B$22,0)+IF(E49&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="16" t="n">
+        <f aca="false">IF($A49&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A49-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="16" t="n">
+        <f aca="false">IF(AND($A49&gt;=Inputs!$B$47,$A49&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A49-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="16" t="n">
+        <f aca="false">IF($A49&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A49-Inputs!$B$44),0)</f>
+        <v>2369564.55753422</v>
+      </c>
+      <c r="N49" s="16" t="n">
+        <f aca="false">IF($A49&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <f aca="false">D49+E49-H49-I49-J49-K49-L49-M49+N49-Inputs!$B$42</f>
+        <v>-2101564.55753422</v>
+      </c>
+      <c r="P49" s="16" t="n">
+        <f aca="false">S48</f>
+        <v>14852347.5621343</v>
+      </c>
+      <c r="Q49" s="16" t="n">
+        <f aca="false">P49*Inputs!$B$35</f>
+        <v>712912.682982445</v>
+      </c>
+      <c r="R49" s="16" t="n">
+        <f aca="false">IF($A49=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S49" s="16" t="n">
+        <f aca="false">MAX(P49+Q49+O49+R49,0)</f>
+        <v>13463695.6875825</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="n">
+        <v>2072</v>
+      </c>
+      <c r="B50" s="20" t="n">
+        <f aca="false">$A50-1972</f>
+        <v>100</v>
+      </c>
+      <c r="C50" s="20" t="n">
+        <f aca="false">$A50-1977</f>
+        <v>95</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <f aca="false">IF($A50&lt;Inputs!$B$45,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A50-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <f aca="false">IF($A50&lt;Inputs!$B$46,Inputs!$B$29*(1+Inputs!$B$7)^($A50-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <f aca="false">(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A50-Inputs!$B$44)</f>
+        <v>1229971.0900406</v>
+      </c>
+      <c r="G50" s="21" t="n">
+        <f aca="false">Inputs!$B$18*(1+Inputs!$B$5)^($A50-Inputs!$B$44)</f>
+        <v>451508.374825031</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <f aca="false">IF(D50=0,0,IF(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)&gt;200000,Inputs!$B$24+(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)-200000)*Inputs!$B$23,IF(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)&gt;150000,9000+(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)-150000)*0.14,IF(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)&gt;100000,4000+(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)-100000)*0.1,IF(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)&gt;50000,1000+(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0)-50000)*0.06,MAX(MAX(D50-Inputs!$B$22-Tax!$B$4/2-F50,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="21" t="n">
+        <f aca="false">IF(E50=0,0,IF(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)&gt;200000,Inputs!$B$24+(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)-200000)*Inputs!$B$23,IF(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)&gt;150000,9000+(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)-150000)*0.14,IF(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)&gt;100000,4000+(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)-100000)*0.1,IF(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)&gt;50000,1000+(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0)-50000)*0.06,MAX(MAX(E50-Inputs!$B$22-Tax!$B$4/2-G50,0),0)*0.02)))))</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="21" t="n">
+        <f aca="false">IF(D50&gt;0,Inputs!$B$22,0)+IF(E50&gt;0,Inputs!$B$22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="21" t="n">
+        <f aca="false">IF($A50&lt;Inputs!$B$45,Inputs!$B$31*(1+Inputs!$B$5)^($A50-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="21" t="n">
+        <f aca="false">IF(AND($A50&gt;=Inputs!$B$47,$A50&lt;Inputs!$B$47+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A50-Inputs!$B$44),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="21" t="n">
+        <f aca="false">IF($A50&gt;=Inputs!$B$45,Inputs!$B$32*(1+Inputs!$B$5)^($A50-Inputs!$B$44),0)</f>
+        <v>2428803.67147258</v>
+      </c>
+      <c r="N50" s="21" t="n">
+        <f aca="false">IF($A50&gt;=Inputs!$B$45,Inputs!$B$39,0)</f>
+        <v>268000</v>
+      </c>
+      <c r="O50" s="21" t="n">
+        <f aca="false">D50+E50-H50-I50-J50-K50-L50-M50+N50-Inputs!$B$42</f>
+        <v>-2160803.67147258</v>
+      </c>
+      <c r="P50" s="21" t="n">
+        <f aca="false">S49</f>
+        <v>13463695.6875825</v>
+      </c>
+      <c r="Q50" s="21" t="n">
+        <f aca="false">P50*Inputs!$B$35</f>
+        <v>646257.393003959</v>
+      </c>
+      <c r="R50" s="21" t="n">
+        <f aca="false">IF($A50=Inputs!$B$45,-Inputs!$B$38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S50" s="21" t="n">
+        <f aca="false">MAX(P50+Q50+O50+R50,0)</f>
+        <v>11949149.4091139</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="22" t="n">
+        <f aca="false">BalanceSheet!B33</f>
+        <v>24405000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="22" t="n">
+        <f aca="false">BalanceSheet!$B$37</f>
+        <v>9790000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="22" t="n">
+        <f aca="false">Tax!B27-Inputs!$B$42</f>
+        <v>718230</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <f aca="false">BalanceSheet!B7/(Inputs!$B$31/12)</f>
+        <v>30.4878048780488</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <f aca="false">Tax!B15</f>
+        <v>181770</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="22" t="n">
+        <f aca="false">Tax!B16</f>
+        <v>199770</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <f aca="false">Tax!B17</f>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" s="22" t="n">
+        <f aca="false">INDEX(Projection!S:S,MATCH(Inputs!$B$45,Projection!A:A,0))</f>
+        <v>21594064.3451817</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="22" t="n">
+        <f aca="false">INDEX(Projection!S:S,MATCH(Inputs!$B$48,Projection!A:A,0))</f>
+        <v>19285597.951505</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="22" t="n">
+        <f aca="false">INDEX(Projection!S:S,MATCH(Inputs!$B$49,Projection!A:A,0))</f>
+        <v>11949149.4091139</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="22" t="n">
+        <f aca="false">INDEX(Projection!S:S,MATCH(Inputs!$B$45,Projection!A:A,0))/(1+Inputs!$B$5)^(Inputs!$B$45-Inputs!$B$44)</f>
+        <v>16457803.4665546</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="22" t="n">
+        <f aca="false">780000*(1-(1+0.02)^-29)/0.02</f>
+        <v>17038620.0363791</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <f aca="false">B17/B18</f>
+        <v>0.965911759955651</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="22" t="n">
+        <f aca="false">SUM(Projection!L4:L50)</f>
+        <v>2851147.6875</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="25" t="str">
+        <f aca="false">IF(INDEX(Projection!S:S,MATCH(Inputs!$B$48,Projection!A:A,0))&gt;0,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="25" t="str">
+        <f aca="false">IF(INDEX(Projection!S:S,MATCH(Inputs!$B$49,Projection!A:A,0))&gt;0,"YES","NO")</f>
+        <v>YES</v>
       </c>
     </row>
   </sheetData>

--- a/model/wong_model.xlsx
+++ b/model/wong_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\finplan\finplan\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829D77D0-424C-4B59-BA32-4D6F4BEE0E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECFA40C-1A85-43A1-8458-488055C4C821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="266">
   <si>
     <t>Wong Family model — INPUTS</t>
   </si>
@@ -281,6 +281,18 @@
   </si>
   <si>
     <t>~ both parents' Flexi median at 65. TEAM TO AGREE</t>
+  </si>
+  <si>
+    <t>Medical plan review: switch to Standard (year)</t>
+  </si>
+  <si>
+    <t>Adrian 75, Carmen 70: the tier review in the plan</t>
+  </si>
+  <si>
+    <t>Guardrails: lowest discretionary share</t>
+  </si>
+  <si>
+    <t>Guyton-Klinger cuts stop at half of discretionary spending</t>
   </si>
   <si>
     <t>BACKSTOPS (values; switch on to include in base)</t>
@@ -1255,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1773,41 +1785,41 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="9">
+        <v>2047</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B52" s="6">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B53" s="9">
-        <v>0</v>
-      </c>
-      <c r="D53" s="7" t="s">
+      <c r="A53" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B54" s="8">
-        <v>3000000</v>
+      <c r="B54" s="6">
+        <v>0.7</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>87</v>
@@ -1818,7 +1830,7 @@
         <v>88</v>
       </c>
       <c r="B55" s="9">
-        <v>2039</v>
+        <v>0</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>89</v>
@@ -1828,8 +1840,8 @@
       <c r="A56" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B56" s="9">
-        <v>0</v>
+      <c r="B56" s="8">
+        <v>3000000</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>91</v>
@@ -1839,8 +1851,8 @@
       <c r="A57" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="8">
-        <v>230000</v>
+      <c r="B57" s="9">
+        <v>2039</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>93</v>
@@ -1851,7 +1863,7 @@
         <v>94</v>
       </c>
       <c r="B58" s="9">
-        <v>2037</v>
+        <v>0</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>95</v>
@@ -1861,104 +1873,104 @@
       <c r="A59" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B59" s="9">
-        <v>0</v>
+      <c r="B59" s="8">
+        <v>230000</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
+      <c r="B60" s="9">
+        <v>2037</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B61" s="6">
-        <v>0.04</v>
+        <v>100</v>
+      </c>
+      <c r="B61" s="9">
+        <v>0</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B62" s="6">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="A62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B63" s="6">
-        <v>3.5000000000000003E-2</v>
+        <v>0.04</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="B64" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B65" s="8">
-        <v>11500000</v>
+        <v>106</v>
+      </c>
+      <c r="B65" s="6">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B66" s="6">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="A66" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B67" s="6">
-        <v>0.04</v>
+        <v>109</v>
+      </c>
+      <c r="B67" s="8">
+        <v>11500000</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B68" s="6">
-        <v>1.2500000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1966,7 +1978,7 @@
         <v>111</v>
       </c>
       <c r="B69" s="6">
-        <v>1.9599999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>112</v>
@@ -1976,8 +1988,8 @@
       <c r="A70" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B70" s="8">
-        <v>8000000</v>
+      <c r="B70" s="6">
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>114</v>
@@ -1988,40 +2000,40 @@
         <v>115</v>
       </c>
       <c r="B71" s="6">
-        <v>0.5</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B72" s="8">
-        <v>7000000</v>
+        <v>8000000</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="B73" s="6">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B74" s="6">
-        <v>0.02</v>
+      <c r="B74" s="8">
+        <v>7000000</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>121</v>
@@ -2031,8 +2043,8 @@
       <c r="A75" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B75" s="8">
-        <v>200000</v>
+      <c r="B75" s="6">
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>123</v>
@@ -2042,74 +2054,74 @@
       <c r="A76" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="9">
-        <v>2037</v>
+      <c r="B76" s="6">
+        <v>0.02</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
+      <c r="B77" s="8">
+        <v>200000</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B78" s="9">
-        <v>2026</v>
+        <v>2037</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B79" s="9">
-        <v>2037</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="A79" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B80" s="9">
-        <v>2039</v>
+        <v>2026</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="9">
-        <v>2028</v>
+        <v>2037</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B82" s="9">
-        <v>2056</v>
+        <v>2039</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2117,7 +2129,7 @@
         <v>135</v>
       </c>
       <c r="B83" s="9">
-        <v>2066</v>
+        <v>2028</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>136</v>
@@ -2128,10 +2140,32 @@
         <v>137</v>
       </c>
       <c r="B84" s="9">
-        <v>2072</v>
+        <v>2056</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B85" s="9">
+        <v>2066</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B86" s="9">
+        <v>2072</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2150,18 +2184,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B4" s="8">
         <v>620000</v>
@@ -2169,7 +2203,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B5" s="8">
         <v>1480000</v>
@@ -2177,7 +2211,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B6" s="8">
         <v>400000</v>
@@ -2185,7 +2219,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B7" s="11">
         <f>SUM(B4:B6)</f>
@@ -2194,13 +2228,13 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B9" s="8">
         <v>1000000</v>
@@ -2208,7 +2242,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B10" s="8">
         <v>1350000</v>
@@ -2216,7 +2250,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B11" s="8">
         <v>900000</v>
@@ -2224,7 +2258,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" s="8">
         <v>700000</v>
@@ -2232,7 +2266,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B13" s="8">
         <v>450000</v>
@@ -2240,7 +2274,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B14" s="8">
         <v>800000</v>
@@ -2248,7 +2282,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B15" s="8">
         <v>1050000</v>
@@ -2256,7 +2290,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B16" s="8">
         <v>620000</v>
@@ -2264,7 +2298,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B17" s="8">
         <v>180000</v>
@@ -2272,7 +2306,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B18" s="8">
         <v>500000</v>
@@ -2280,7 +2314,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B19" s="8">
         <v>420000</v>
@@ -2288,7 +2322,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B20" s="11">
         <f>SUM(B9:B19)</f>
@@ -2297,13 +2331,13 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B21" s="4"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B22" s="8">
         <v>11500000</v>
@@ -2311,7 +2345,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B23" s="8">
         <v>5000000</v>
@@ -2319,7 +2353,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B24" s="8">
         <v>220000</v>
@@ -2327,7 +2361,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B25" s="11">
         <f>SUM(B22:B24)</f>
@@ -2336,13 +2370,13 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B27" s="8">
         <v>1800000</v>
@@ -2350,7 +2384,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B28" s="8">
         <v>900000</v>
@@ -2358,7 +2392,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B29" s="8">
         <v>85000</v>
@@ -2366,7 +2400,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B30" s="11">
         <f>SUM(B27:B29)</f>
@@ -2375,7 +2409,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B32" s="12">
         <f>B7+B20+B25</f>
@@ -2384,7 +2418,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B33" s="12">
         <f>B32-B30</f>
@@ -2393,7 +2427,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B35" s="13">
         <f>B33-24405000</f>
@@ -2402,7 +2436,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B37" s="12">
         <f>B7+B20-B17-B18</f>
@@ -2425,17 +2459,17 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B4" s="14">
         <f>BalanceSheet!B27*Inputs!$B$25</f>
@@ -2445,21 +2479,21 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B7" s="16">
         <f>Inputs!$B$27+Inputs!$B$28</f>
@@ -2480,7 +2514,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B8" s="16">
         <f>-Inputs!$B$22</f>
@@ -2501,7 +2535,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B9" s="16">
         <f>-$B$4/2</f>
@@ -2521,7 +2555,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B10" s="16">
         <f>SUM(B7:B9)</f>
@@ -2542,7 +2576,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B11" s="16">
         <f>-(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)</f>
@@ -2563,7 +2597,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B12" s="16">
         <f>MAX(B10+B11,0)</f>
@@ -2584,7 +2618,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B13" s="11">
         <f>IF(B12&gt;200000,Inputs!$B$24+(B12-200000)*Inputs!$B$23,IF(B12&gt;150000,9000+(B12-150000)*0.14,IF(B12&gt;100000,4000+(B12-100000)*0.1,IF(B12&gt;50000,1000+(B12-50000)*0.06,B12*0.02))))</f>
@@ -2605,7 +2639,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B15" s="17">
         <f>B13+C13</f>
@@ -2614,7 +2648,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B16" s="12">
         <f>D13</f>
@@ -2623,7 +2657,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B17" s="12">
         <f>B16-B15</f>
@@ -2632,7 +2666,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B19" s="13">
         <f>B15-181770</f>
@@ -2641,7 +2675,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B20" s="13">
         <f>B16-199770</f>
@@ -2650,12 +2684,12 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B23" s="14">
         <f>D7</f>
@@ -2664,7 +2698,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B24" s="14">
         <f>-B15</f>
@@ -2673,7 +2707,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B25" s="14">
         <f>D8</f>
@@ -2682,7 +2716,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B26" s="14">
         <f>-Inputs!$B$31</f>
@@ -2691,7 +2725,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B27" s="17">
         <f>SUM(B23:B26)</f>
@@ -2714,29 +2748,29 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2839,7 +2873,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B12" s="18">
         <f>(B11/B10)^(1/5)-1</f>
@@ -2856,16 +2890,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3652,34 +3686,34 @@
     </row>
     <row r="62" spans="1:10" ht="39" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3695,18 +3729,18 @@
         <v>49</v>
       </c>
       <c r="D63" s="18">
-        <f>IF($A63=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A63&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A63-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A63=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A63&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A63-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0</v>
       </c>
       <c r="E63" s="21">
         <v>1</v>
       </c>
       <c r="F63" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$79,$A63&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B63,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$81,$A63&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B63,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G63" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C63,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C63,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H63" s="14">
@@ -3714,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A63-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A63-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J63" s="14">
@@ -3735,7 +3769,7 @@
         <v>50</v>
       </c>
       <c r="D64" s="18">
-        <f>IF($A64=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A64&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A64-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A64=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A64&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A64-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.1</v>
       </c>
       <c r="E64" s="21">
@@ -3743,11 +3777,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F64" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$79,$A64&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B64,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$81,$A64&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B64,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G64" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C64,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C64,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H64" s="14">
@@ -3755,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A64-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A64-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J64" s="14">
@@ -3776,7 +3810,7 @@
         <v>51</v>
       </c>
       <c r="D65" s="18">
-        <f>IF($A65=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A65&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A65-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A65=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A65&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A65-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>9.555555555555556E-2</v>
       </c>
       <c r="E65" s="21">
@@ -3784,11 +3818,11 @@
         <v>1.2051111111111112</v>
       </c>
       <c r="F65" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$79,$A65&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B65,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$81,$A65&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B65,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G65" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C65,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C65,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H65" s="14">
@@ -3796,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A65-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A65-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J65" s="14">
@@ -3817,7 +3851,7 @@
         <v>52</v>
       </c>
       <c r="D66" s="18">
-        <f>IF($A66=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A66&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A66-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A66=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A66&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A66-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>9.1111111111111115E-2</v>
       </c>
       <c r="E66" s="21">
@@ -3825,11 +3859,11 @@
         <v>1.3149101234567904</v>
       </c>
       <c r="F66" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$79,$A66&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B66,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$81,$A66&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B66,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G66" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C66,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C66,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H66" s="14">
@@ -3837,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A66-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A66-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J66" s="14">
@@ -3858,7 +3892,7 @@
         <v>53</v>
       </c>
       <c r="D67" s="18">
-        <f>IF($A67=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A67&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A67-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A67=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A67&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A67-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>8.666666666666667E-2</v>
       </c>
       <c r="E67" s="21">
@@ -3866,11 +3900,11 @@
         <v>1.4288690008230456</v>
       </c>
       <c r="F67" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$79,$A67&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B67,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$81,$A67&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B67,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G67" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C67,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C67,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H67" s="14">
@@ -3878,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A67-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A67-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J67" s="14">
@@ -3899,7 +3933,7 @@
         <v>54</v>
       </c>
       <c r="D68" s="18">
-        <f>IF($A68=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A68&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A68-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A68=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A68&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A68-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>8.2222222222222224E-2</v>
       </c>
       <c r="E68" s="21">
@@ -3907,11 +3941,11 @@
         <v>1.5463537853351625</v>
       </c>
       <c r="F68" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$79,$A68&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B68,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$81,$A68&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B68,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G68" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C68,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C68,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H68" s="14">
@@ -3919,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A68-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A68-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J68" s="14">
@@ -3940,7 +3974,7 @@
         <v>55</v>
       </c>
       <c r="D69" s="18">
-        <f>IF($A69=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A69&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A69-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A69=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A69&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A69-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="E69" s="21">
@@ -3948,11 +3982,11 @@
         <v>1.6666257464167862</v>
       </c>
       <c r="F69" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$79,$A69&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B69,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$81,$A69&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B69,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G69" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C69,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C69,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H69" s="14">
@@ -3960,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A69-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A69-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J69" s="14">
@@ -3981,7 +4015,7 @@
         <v>56</v>
       </c>
       <c r="D70" s="18">
-        <f>IF($A70=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A70&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A70-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A70=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A70&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A70-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>7.3333333333333334E-2</v>
       </c>
       <c r="E70" s="21">
@@ -3989,11 +4023,11 @@
         <v>1.7888449678206837</v>
       </c>
       <c r="F70" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$79,$A70&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B70,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$81,$A70&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B70,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G70" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C70,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C70,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H70" s="14">
@@ -4001,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A70-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A70-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J70" s="14">
@@ -4022,7 +4056,7 @@
         <v>57</v>
       </c>
       <c r="D71" s="18">
-        <f>IF($A71=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A71&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A71-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A71=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A71&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A71-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>6.8888888888888888E-2</v>
       </c>
       <c r="E71" s="21">
@@ -4030,11 +4064,11 @@
         <v>1.912076510048331</v>
       </c>
       <c r="F71" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$79,$A71&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B71,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$81,$A71&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B71,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G71" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C71,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C71,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H71" s="14">
@@ -4042,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A71-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A71-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J71" s="14">
@@ -4063,7 +4097,7 @@
         <v>58</v>
       </c>
       <c r="D72" s="18">
-        <f>IF($A72=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A72&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A72-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A72=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A72&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A72-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>6.4444444444444443E-2</v>
       </c>
       <c r="E72" s="21">
@@ -4071,11 +4105,11 @@
         <v>2.0352992184736682</v>
       </c>
       <c r="F72" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$79,$A72&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B72,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$81,$A72&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B72,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G72" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C72,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C72,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H72" s="14">
@@ -4083,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A72-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A72-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J72" s="14">
@@ -4104,7 +4138,7 @@
         <v>59</v>
       </c>
       <c r="D73" s="18">
-        <f>IF($A73=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A73&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A73-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A73=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A73&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A73-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E73" s="21">
@@ -4112,11 +4146,11 @@
         <v>2.1574171715820882</v>
       </c>
       <c r="F73" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$79,$A73&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B73,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$81,$A73&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B73,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G73" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C73,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C73,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H73" s="14">
@@ -4124,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A73-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A73-Inputs!$B$80))</f>
         <v>0</v>
       </c>
       <c r="J73" s="14">
@@ -4145,7 +4179,7 @@
         <v>60</v>
       </c>
       <c r="D74" s="18">
-        <f>IF($A74=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A74&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A74-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A74=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A74&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A74-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E74" s="21">
@@ -4153,11 +4187,11 @@
         <v>2.2868622018770135</v>
       </c>
       <c r="F74" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$79,$A74&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B74,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$81,$A74&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B74,$A$15:$A$60,0))))</f>
         <v>32542</v>
       </c>
       <c r="G74" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C74,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C74,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H74" s="14">
@@ -4165,7 +4199,7 @@
         <v>74419.06977348178</v>
       </c>
       <c r="I74" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A74-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A74-Inputs!$B$80))</f>
         <v>85285.63275708229</v>
       </c>
       <c r="J74" s="14">
@@ -4186,7 +4220,7 @@
         <v>61</v>
       </c>
       <c r="D75" s="18">
-        <f>IF($A75=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A75&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A75-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A75=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A75&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A75-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E75" s="21">
@@ -4194,11 +4228,11 @@
         <v>2.4240739339896344</v>
       </c>
       <c r="F75" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$79,$A75&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B75,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$81,$A75&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B75,$A$15:$A$60,0))))</f>
         <v>34265.509148780548</v>
       </c>
       <c r="G75" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C75,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C75,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H75" s="14">
@@ -4206,7 +4240,7 @@
         <v>83062.127562442271</v>
       </c>
       <c r="I75" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A75-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A75-Inputs!$B$80))</f>
         <v>87417.773576009335</v>
       </c>
       <c r="J75" s="14">
@@ -4227,7 +4261,7 @@
         <v>62</v>
       </c>
       <c r="D76" s="18">
-        <f>IF($A76=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A76&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A76-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A76=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A76&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A76-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E76" s="21">
@@ -4235,11 +4269,11 @@
         <v>2.5695183700290127</v>
       </c>
       <c r="F76" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$79,$A76&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B76,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$81,$A76&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B76,$A$15:$A$60,0))))</f>
         <v>36080.299834833859</v>
       </c>
       <c r="G76" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C76,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C76,$A$15:$A$60,0))))</f>
         <v>25895</v>
       </c>
       <c r="H76" s="14">
@@ -4247,7 +4281,7 @@
         <v>159246.67141366165</v>
       </c>
       <c r="I76" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A76-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A76-Inputs!$B$80))</f>
         <v>89603.217915409565</v>
       </c>
       <c r="J76" s="14">
@@ -4268,7 +4302,7 @@
         <v>63</v>
       </c>
       <c r="D77" s="18">
-        <f>IF($A77=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A77&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A77-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A77=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A77&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A77-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E77" s="21">
@@ -4276,11 +4310,11 @@
         <v>2.7236894722307534</v>
       </c>
       <c r="F77" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$79,$A77&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B77,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$81,$A77&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B77,$A$15:$A$60,0))))</f>
         <v>37991.206566321816</v>
       </c>
       <c r="G77" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C77,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C77,$A$15:$A$60,0))))</f>
         <v>27671.650037838353</v>
       </c>
       <c r="H77" s="14">
@@ -4288,7 +4322,7 @@
         <v>178845.23124934867</v>
       </c>
       <c r="I77" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A77-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A77-Inputs!$B$80))</f>
         <v>91843.298363294802</v>
       </c>
       <c r="J77" s="14">
@@ -4309,7 +4343,7 @@
         <v>64</v>
       </c>
       <c r="D78" s="18">
-        <f>IF($A78=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A78&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A78-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A78=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A78&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A78-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E78" s="21">
@@ -4317,11 +4351,11 @@
         <v>2.8871108405645987</v>
       </c>
       <c r="F78" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$79,$A78&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B78,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$81,$A78&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B78,$A$15:$A$60,0))))</f>
         <v>40003.319899560935</v>
       </c>
       <c r="G78" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C78,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C78,$A$15:$A$60,0))))</f>
         <v>29570.19562914074</v>
       </c>
       <c r="H78" s="14">
@@ -4329,7 +4363,7 @@
         <v>200866.45089910406</v>
       </c>
       <c r="I78" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A78-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A78-Inputs!$B$80))</f>
         <v>94139.380822377178</v>
       </c>
       <c r="J78" s="14">
@@ -4350,7 +4384,7 @@
         <v>65</v>
       </c>
       <c r="D79" s="18">
-        <f>IF($A79=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A79&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A79-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A79=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A79&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A79-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E79" s="21">
@@ -4358,11 +4392,11 @@
         <v>3.0603374909984749</v>
       </c>
       <c r="F79" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$79,$A79&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B79,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$81,$A79&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B79,$A$15:$A$60,0))))</f>
         <v>42122</v>
       </c>
       <c r="G79" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C79,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C79,$A$15:$A$60,0))))</f>
         <v>31599</v>
       </c>
       <c r="H79" s="14">
@@ -4370,7 +4404,7 @@
         <v>225611.14017389857</v>
       </c>
       <c r="I79" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A79-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A79-Inputs!$B$80))</f>
         <v>96492.86534293661</v>
       </c>
       <c r="J79" s="14">
@@ -4391,7 +4425,7 @@
         <v>66</v>
       </c>
       <c r="D80" s="18">
-        <f>IF($A80=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A80&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A80-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A80=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A80&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A80-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E80" s="21">
@@ -4399,11 +4433,11 @@
         <v>3.2439577404583835</v>
       </c>
       <c r="F80" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$79,$A80&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B80,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$81,$A80&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B80,$A$15:$A$60,0))))</f>
         <v>44249.053788011741</v>
       </c>
       <c r="G80" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C80,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C80,$A$15:$A$60,0))))</f>
         <v>33286.969247733367</v>
       </c>
       <c r="H80" s="14">
@@ -4411,7 +4445,7 @@
         <v>251523.58209116486</v>
       </c>
       <c r="I80" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A80-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A80-Inputs!$B$80))</f>
         <v>98905.186976509998</v>
       </c>
       <c r="J80" s="14">
@@ -4432,7 +4466,7 @@
         <v>67</v>
       </c>
       <c r="D81" s="18">
-        <f>IF($A81=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A81&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A81-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A81=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A81&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A81-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E81" s="21">
@@ -4440,11 +4474,11 @@
         <v>3.4385952048858868</v>
       </c>
       <c r="F81" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$79,$A81&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B81,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$81,$A81&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B81,$A$15:$A$60,0))))</f>
         <v>46483.518378385568</v>
       </c>
       <c r="G81" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C81,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C81,$A$15:$A$60,0))))</f>
         <v>35065.107177427992</v>
       </c>
       <c r="H81" s="14">
@@ -4452,7 +4486,7 @@
         <v>280412.71280125517</v>
       </c>
       <c r="I81" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A81-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A81-Inputs!$B$80))</f>
         <v>101377.81665092276</v>
       </c>
       <c r="J81" s="14">
@@ -4473,7 +4507,7 @@
         <v>68</v>
       </c>
       <c r="D82" s="18">
-        <f>IF($A82=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A82&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A82-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A82=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A82&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A82-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E82" s="21">
@@ -4481,11 +4515,11 @@
         <v>3.6449109171790401</v>
       </c>
       <c r="F82" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$79,$A82&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B82,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$81,$A82&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B82,$A$15:$A$60,0))))</f>
         <v>48830.817743250918</v>
       </c>
       <c r="G82" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C82,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C82,$A$15:$A$60,0))))</f>
         <v>36938.230459303144</v>
       </c>
       <c r="H82" s="14">
@@ -4493,7 +4527,7 @@
         <v>312620.5401495446</v>
       </c>
       <c r="I82" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A82-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A82-Inputs!$B$80))</f>
         <v>103912.26206719583</v>
       </c>
       <c r="J82" s="14">
@@ -4514,7 +4548,7 @@
         <v>69</v>
       </c>
       <c r="D83" s="18">
-        <f>IF($A83=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A83&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A83-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A83=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A83&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A83-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E83" s="21">
@@ -4522,11 +4556,11 @@
         <v>3.8636055722097828</v>
       </c>
       <c r="F83" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$79,$A83&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B83,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$81,$A83&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B83,$A$15:$A$60,0))))</f>
         <v>51296.649751524339</v>
       </c>
       <c r="G83" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C83,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C83,$A$15:$A$60,0))))</f>
         <v>38911.413062581472</v>
       </c>
       <c r="H83" s="14">
@@ -4534,7 +4568,7 @@
         <v>348528.3741468293</v>
       </c>
       <c r="I83" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A83-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A83-Inputs!$B$80))</f>
         <v>106510.06861887571</v>
       </c>
       <c r="J83" s="14">
@@ -4555,7 +4589,7 @@
         <v>70</v>
       </c>
       <c r="D84" s="18">
-        <f>IF($A84=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A84&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A84-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A84=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A84&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A84-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E84" s="21">
@@ -4563,11 +4597,11 @@
         <v>4.09542190654237</v>
       </c>
       <c r="F84" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$79,$A84&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B84,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$81,$A84&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B84,$A$15:$A$60,0))))</f>
         <v>53887</v>
       </c>
       <c r="G84" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C84,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C84,$A$15:$A$60,0))))</f>
         <v>40990</v>
       </c>
       <c r="H84" s="14">
@@ -4575,7 +4609,7 @@
         <v>388561.34422702045</v>
       </c>
       <c r="I84" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A84-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A84-Inputs!$B$80))</f>
         <v>109172.82033434759</v>
       </c>
       <c r="J84" s="14">
@@ -4596,7 +4630,7 @@
         <v>71</v>
       </c>
       <c r="D85" s="18">
-        <f>IF($A85=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A85&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A85-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A85=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A85&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A85-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E85" s="21">
@@ -4604,11 +4638,11 @@
         <v>4.3411472209349125</v>
       </c>
       <c r="F85" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$79,$A85&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B85,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$81,$A85&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B85,$A$15:$A$60,0))))</f>
         <v>55710.710648470209</v>
       </c>
       <c r="G85" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C85,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C85,$A$15:$A$60,0))))</f>
         <v>43188.72312279437</v>
       </c>
       <c r="H85" s="14">
@@ -4616,7 +4650,7 @@
         <v>429337.00206816167</v>
       </c>
       <c r="I85" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A85-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A85-Inputs!$B$80))</f>
         <v>111902.14084270629</v>
       </c>
       <c r="J85" s="14">
@@ -4637,7 +4671,7 @@
         <v>72</v>
       </c>
       <c r="D86" s="18">
-        <f>IF($A86=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A86&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A86-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A86=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A86&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A86-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E86" s="21">
@@ -4645,11 +4679,11 @@
         <v>4.6016160541910072</v>
       </c>
       <c r="F86" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$79,$A86&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B86,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$81,$A86&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B86,$A$15:$A$60,0))))</f>
         <v>57596.141573247209</v>
       </c>
       <c r="G86" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C86,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C86,$A$15:$A$60,0))))</f>
         <v>45505.38680110743</v>
       </c>
       <c r="H86" s="14">
@@ -4657,7 +4691,7 @@
         <v>474433.64817905996</v>
       </c>
       <c r="I86" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A86-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A86-Inputs!$B$80))</f>
         <v>114699.69436377395</v>
       </c>
       <c r="J86" s="14">
@@ -4678,7 +4712,7 @@
         <v>73</v>
       </c>
       <c r="D87" s="18">
-        <f>IF($A87=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A87&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A87-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A87=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A87&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A87-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E87" s="21">
@@ -4686,11 +4720,11 @@
         <v>4.8777130174424679</v>
       </c>
       <c r="F87" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$79,$A87&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B87,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$81,$A87&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B87,$A$15:$A$60,0))))</f>
         <v>59545.381588425793</v>
       </c>
       <c r="G87" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C87,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C87,$A$15:$A$60,0))))</f>
         <v>47946.317422510139</v>
       </c>
       <c r="H87" s="14">
@@ -4698,7 +4732,7 @@
         <v>524313.65953264979</v>
       </c>
       <c r="I87" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A87-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A87-Inputs!$B$80))</f>
         <v>117567.18672286828</v>
       </c>
       <c r="J87" s="14">
@@ -4719,7 +4753,7 @@
         <v>74</v>
       </c>
       <c r="D88" s="18">
-        <f>IF($A88=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A88&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A88-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A88=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A88&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A88-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E88" s="21">
@@ -4727,11 +4761,11 @@
         <v>5.1703757984890162</v>
       </c>
       <c r="F88" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$79,$A88&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B88,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$81,$A88&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B88,$A$15:$A$60,0))))</f>
         <v>61560.590200336541</v>
       </c>
       <c r="G88" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C88,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C88,$A$15:$A$60,0))))</f>
         <v>50518.180725015911</v>
       </c>
       <c r="H88" s="14">
@@ -4739,7 +4773,7 @@
         <v>579489.36471683672</v>
       </c>
       <c r="I88" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A88-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A88-Inputs!$B$80))</f>
         <v>120506.36639093996</v>
       </c>
       <c r="J88" s="14">
@@ -4760,7 +4794,7 @@
         <v>75</v>
       </c>
       <c r="D89" s="18">
-        <f>IF($A89=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A89&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A89-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A89=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A89&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A89-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E89" s="21">
@@ -4768,11 +4802,11 @@
         <v>5.4805983463983576</v>
       </c>
       <c r="F89" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$79,$A89&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B89,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$81,$A89&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B89,$A$15:$A$60,0))))</f>
         <v>63644</v>
       </c>
       <c r="G89" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C89,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C89,$A$15:$A$60,0))))</f>
         <v>53228</v>
       </c>
       <c r="H89" s="14">
@@ -4780,7 +4814,7 @@
         <v>640528.4899402688</v>
       </c>
       <c r="I89" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A89-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A89-Inputs!$B$80))</f>
         <v>123519.02555071346</v>
       </c>
       <c r="J89" s="14">
@@ -4801,7 +4835,7 @@
         <v>76</v>
       </c>
       <c r="D90" s="18">
-        <f>IF($A90=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A90&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A90-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A90=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A90&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A90-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E90" s="21">
@@ -4809,11 +4843,11 @@
         <v>5.8094342471822591</v>
       </c>
       <c r="F90" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$79,$A90&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B90,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$81,$A90&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B90,$A$15:$A$60,0))))</f>
         <v>65797.919136549404</v>
       </c>
       <c r="G90" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C90,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C90,$A$15:$A$60,0))))</f>
         <v>55012.997845753707</v>
       </c>
       <c r="H90" s="14">
@@ -4821,7 +4855,7 @@
         <v>701843.0785504845</v>
       </c>
       <c r="I90" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A90-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A90-Inputs!$B$80))</f>
         <v>126607.00118948129</v>
       </c>
       <c r="J90" s="14">
@@ -4842,7 +4876,7 @@
         <v>77</v>
       </c>
       <c r="D91" s="18">
-        <f>IF($A91=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A91&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A91-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A91=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A91&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A91-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E91" s="21">
@@ -4850,11 +4884,11 @@
         <v>6.1580003020131953</v>
       </c>
       <c r="F91" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$79,$A91&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B91,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$81,$A91&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B91,$A$15:$A$60,0))))</f>
         <v>68024.733874361991</v>
       </c>
       <c r="G91" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C91,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C91,$A$15:$A$60,0))))</f>
         <v>56857.855489157992</v>
       </c>
       <c r="H91" s="14">
@@ -4862,7 +4896,7 @@
         <v>769027.02301674581</v>
       </c>
       <c r="I91" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A91-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A91-Inputs!$B$80))</f>
         <v>129772.17621921831</v>
       </c>
       <c r="J91" s="14">
@@ -4883,7 +4917,7 @@
         <v>78</v>
       </c>
       <c r="D92" s="18">
-        <f>IF($A92=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A92&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A92-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A92=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A92&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A92-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E92" s="21">
@@ -4891,11 +4925,11 @@
         <v>6.5274803201339875</v>
       </c>
       <c r="F92" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$79,$A92&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B92,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$81,$A92&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B92,$A$15:$A$60,0))))</f>
         <v>70326.911236731874</v>
       </c>
       <c r="G92" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C92,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C92,$A$15:$A$60,0))))</f>
         <v>58764.580325002338</v>
       </c>
       <c r="H92" s="14">
@@ -4903,7 +4937,7 @@
         <v>842642.17066596274</v>
       </c>
       <c r="I92" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A92-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A92-Inputs!$B$80))</f>
         <v>133016.48062469877</v>
       </c>
       <c r="J92" s="14">
@@ -4924,7 +4958,7 @@
         <v>79</v>
       </c>
       <c r="D93" s="18">
-        <f>IF($A93=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A93&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A93-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A93=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A93&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A93-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E93" s="21">
@@ -4932,11 +4966,11 @@
         <v>6.9191291393420267</v>
       </c>
       <c r="F93" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$79,$A93&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B93,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$81,$A93&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B93,$A$15:$A$60,0))))</f>
         <v>72707.001739013445</v>
       </c>
       <c r="G93" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C93,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C93,$A$15:$A$60,0))))</f>
         <v>60735.247065942247</v>
       </c>
       <c r="H93" s="14">
@@ -4944,7 +4978,7 @@
         <v>923304.15212569758</v>
       </c>
       <c r="I93" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A93-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A93-Inputs!$B$80))</f>
         <v>136341.89264031622</v>
       </c>
       <c r="J93" s="14">
@@ -4965,7 +4999,7 @@
         <v>80</v>
       </c>
       <c r="D94" s="18">
-        <f>IF($A94=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A94&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A94-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A94=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A94&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A94-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E94" s="21">
@@ -4973,11 +5007,11 @@
         <v>7.3342768877025488</v>
       </c>
       <c r="F94" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$79,$A94&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B94,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$81,$A94&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B94,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G94" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C94,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C94,$A$15:$A$60,0))))</f>
         <v>62772</v>
       </c>
       <c r="H94" s="14">
@@ -4985,7 +5019,7 @@
         <v>460387.22879486438</v>
       </c>
       <c r="I94" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A94-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A94-Inputs!$B$80))</f>
         <v>139750.43995632418</v>
       </c>
       <c r="J94" s="14">
@@ -5006,7 +5040,7 @@
         <v>81</v>
       </c>
       <c r="D95" s="18">
-        <f>IF($A95=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A95&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A95-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A95=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A95&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A95-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E95" s="21">
@@ -5014,11 +5048,11 @@
         <v>7.7743335009647021</v>
       </c>
       <c r="F95" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$79,$A95&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B95,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$81,$A95&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B95,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G95" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C95,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C95,$A$15:$A$60,0))))</f>
         <v>64877.055323770415</v>
       </c>
       <c r="H95" s="14">
@@ -5026,7 +5060,7 @@
         <v>504375.86464752874</v>
       </c>
       <c r="I95" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A95-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A95-Inputs!$B$80))</f>
         <v>143244.20095523223</v>
       </c>
       <c r="J95" s="14">
@@ -5047,7 +5081,7 @@
         <v>82</v>
       </c>
       <c r="D96" s="18">
-        <f>IF($A96=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A96&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A96-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A96=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A96&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A96-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E96" s="21">
@@ -5055,11 +5089,11 @@
         <v>8.2407935110225843</v>
       </c>
       <c r="F96" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$79,$A96&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B96,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$81,$A96&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B96,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G96" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C96,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C96,$A$15:$A$60,0))))</f>
         <v>67052.703553870626</v>
       </c>
       <c r="H96" s="14">
@@ -5067,7 +5101,7 @@
         <v>552567.48434325808</v>
       </c>
       <c r="I96" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A96-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A96-Inputs!$B$80))</f>
         <v>146825.30597911304</v>
       </c>
       <c r="J96" s="14">
@@ -5088,7 +5122,7 @@
         <v>83</v>
       </c>
       <c r="D97" s="18">
-        <f>IF($A97=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A97&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A97-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A97=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A97&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A97-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E97" s="21">
@@ -5096,11 +5130,11 @@
         <v>8.7352411216839396</v>
       </c>
       <c r="F97" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$79,$A97&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B97,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$81,$A97&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B97,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G97" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C97,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C97,$A$15:$A$60,0))))</f>
         <v>69301.312019257661</v>
       </c>
       <c r="H97" s="14">
@@ -5108,7 +5142,7 @@
         <v>605363.67053726898</v>
       </c>
       <c r="I97" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A97-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A97-Inputs!$B$80))</f>
         <v>150495.93862859087</v>
       </c>
       <c r="J97" s="14">
@@ -5129,7 +5163,7 @@
         <v>84</v>
       </c>
       <c r="D98" s="18">
-        <f>IF($A98=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A98&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A98-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A98=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A98&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A98-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E98" s="21">
@@ -5137,11 +5171,11 @@
         <v>9.2593555889849757</v>
       </c>
       <c r="F98" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$79,$A98&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B98,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$81,$A98&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B98,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G98" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C98,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C98,$A$15:$A$60,0))))</f>
         <v>71625.327437125714</v>
       </c>
       <c r="H98" s="14">
@@ -5149,7 +5183,7 @@
         <v>663204.37591782887</v>
       </c>
       <c r="I98" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A98-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A98-Inputs!$B$80))</f>
         <v>154258.33709430561</v>
       </c>
       <c r="J98" s="14">
@@ -5170,7 +5204,7 @@
         <v>85</v>
       </c>
       <c r="D99" s="18">
-        <f>IF($A99=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A99&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A99-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A99=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A99&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A99-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E99" s="21">
@@ -5178,11 +5212,11 @@
         <v>9.8149169243240753</v>
       </c>
       <c r="F99" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$79,$A99&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B99,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$81,$A99&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B99,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G99" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C99,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C99,$A$15:$A$60,0))))</f>
         <v>74027.278575186006</v>
       </c>
       <c r="H99" s="14">
@@ -5190,7 +5224,7 @@
         <v>726571.58934924612</v>
       </c>
       <c r="I99" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A99-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A99-Inputs!$B$80))</f>
         <v>158114.79552166327</v>
       </c>
       <c r="J99" s="14">
@@ -5211,7 +5245,7 @@
         <v>86</v>
       </c>
       <c r="D100" s="18">
-        <f>IF($A100=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A100&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A100-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A100=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A100&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A100-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E100" s="21">
@@ -5219,11 +5253,11 @@
         <v>10.40381193978352</v>
       </c>
       <c r="F100" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$79,$A100&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B100,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$81,$A100&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B100,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G100" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C100,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C100,$A$15:$A$60,0))))</f>
         <v>76509.779003226067</v>
       </c>
       <c r="H100" s="14">
@@ -5231,7 +5265,7 @@
         <v>795993.35230396176</v>
       </c>
       <c r="I100" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A100-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A100-Inputs!$B$80))</f>
         <v>162067.66540970482</v>
       </c>
       <c r="J100" s="14">
@@ -5252,7 +5286,7 @@
         <v>87</v>
       </c>
       <c r="D101" s="18">
-        <f>IF($A101=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A101&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A101-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A101=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A101&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A101-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E101" s="21">
@@ -5260,11 +5294,11 @@
         <v>11.028040656170532</v>
       </c>
       <c r="F101" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$79,$A101&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B101,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$81,$A101&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B101,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G101" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C101,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C101,$A$15:$A$60,0))))</f>
         <v>79075.529936942359</v>
       </c>
       <c r="H101" s="14">
@@ -5272,7 +5306,7 @@
         <v>872048.15905283031</v>
       </c>
       <c r="I101" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A101-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A101-Inputs!$B$80))</f>
         <v>166119.35704494742</v>
       </c>
       <c r="J101" s="14">
@@ -5293,7 +5327,7 @@
         <v>88</v>
       </c>
       <c r="D102" s="18">
-        <f>IF($A102=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A102&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A102-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A102=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A102&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A102-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E102" s="21">
@@ -5301,11 +5335,11 @@
         <v>11.689723095540764</v>
       </c>
       <c r="F102" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$79,$A102&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B102,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$81,$A102&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B102,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G102" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C102,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C102,$A$15:$A$60,0))))</f>
         <v>81727.323177140657</v>
       </c>
       <c r="H102" s="14">
@@ -5313,7 +5347,7 @@
         <v>955369.77728054509</v>
       </c>
       <c r="I102" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A102-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A102-Inputs!$B$80))</f>
         <v>170272.3409710711</v>
       </c>
       <c r="J102" s="14">
@@ -5334,7 +5368,7 @@
         <v>89</v>
       </c>
       <c r="D103" s="18">
-        <f>IF($A103=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A103&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A103-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A103=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A103&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A103-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E103" s="21">
@@ -5342,11 +5376,11 @@
         <v>12.39110648127321</v>
       </c>
       <c r="F103" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$79,$A103&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B103,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$81,$A103&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B103,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G103" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C103,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C103,$A$15:$A$60,0))))</f>
         <v>84468.044147502369</v>
       </c>
       <c r="H103" s="14">
@@ -5354,7 +5388,7 @@
         <v>1046652.5292965883</v>
       </c>
       <c r="I103" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A103-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A103-Inputs!$B$80))</f>
         <v>174529.14949534787</v>
       </c>
       <c r="J103" s="14">
@@ -5375,7 +5409,7 @@
         <v>90</v>
       </c>
       <c r="D104" s="18">
-        <f>IF($A104=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A104&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A104-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A104=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A104&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A104-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E104" s="21">
@@ -5383,11 +5417,11 @@
         <v>13.134572870149604</v>
       </c>
       <c r="F104" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$79,$A104&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B104,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$81,$A104&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B104,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G104" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C104,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C104,$A$15:$A$60,0))))</f>
         <v>87300.675034222149</v>
       </c>
       <c r="H104" s="14">
@@ -5395,7 +5429,7 @@
         <v>1146657.0778502412</v>
       </c>
       <c r="I104" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A104-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A104-Inputs!$B$80))</f>
         <v>178892.37823273157</v>
       </c>
       <c r="J104" s="14">
@@ -5416,7 +5450,7 @@
         <v>91</v>
       </c>
       <c r="D105" s="18">
-        <f>IF($A105=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A105&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A105-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A105=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A105&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A105-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E105" s="21">
@@ -5424,11 +5458,11 @@
         <v>13.922647242358581</v>
       </c>
       <c r="F105" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$79,$A105&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B105,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$81,$A105&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B105,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G105" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C105,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C105,$A$15:$A$60,0))))</f>
         <v>90228.298030933103</v>
       </c>
       <c r="H105" s="14">
@@ -5436,7 +5470,7 @@
         <v>1256216.7647630789</v>
       </c>
       <c r="I105" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A105-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A105-Inputs!$B$80))</f>
         <v>183364.68768854984</v>
       </c>
       <c r="J105" s="14">
@@ -5457,7 +5491,7 @@
         <v>92</v>
       </c>
       <c r="D106" s="18">
-        <f>IF($A106=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A106&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A106-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A106=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A106&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A106-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E106" s="21">
@@ -5465,11 +5499,11 @@
         <v>14.758006076900097</v>
       </c>
       <c r="F106" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$79,$A106&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B106,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$81,$A106&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B106,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G106" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C106,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C106,$A$15:$A$60,0))))</f>
         <v>93254.098692450338</v>
       </c>
       <c r="H106" s="14">
@@ -5477,7 +5511,7 @@
         <v>1376244.5551990236</v>
       </c>
       <c r="I106" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A106-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A106-Inputs!$B$80))</f>
         <v>187948.80488076361</v>
       </c>
       <c r="J106" s="14">
@@ -5498,7 +5532,7 @@
         <v>93</v>
       </c>
       <c r="D107" s="18">
-        <f>IF($A107=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A107&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A107-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A107=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A107&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A107-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E107" s="21">
@@ -5506,11 +5540,11 @@
         <v>15.643486441514103</v>
       </c>
       <c r="F107" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$79,$A107&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B107,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$81,$A107&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B107,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G107" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C107,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C107,$A$15:$A$60,0))))</f>
         <v>96381.369400982076</v>
       </c>
       <c r="H107" s="14">
@@ -5518,7 +5552,7 @@
         <v>1507740.6454388252</v>
       </c>
       <c r="I107" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A107-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A107-Inputs!$B$80))</f>
         <v>192647.52500278264</v>
       </c>
       <c r="J107" s="14">
@@ -5539,7 +5573,7 @@
         <v>94</v>
       </c>
       <c r="D108" s="18">
-        <f>IF($A108=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A108&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A108-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A108=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A108&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A108-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E108" s="21">
@@ -5547,11 +5581,11 @@
         <v>16.58209562800495</v>
       </c>
       <c r="F108" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$79,$A108&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B108,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$81,$A108&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B108,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G108" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C108,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C108,$A$15:$A$60,0))))</f>
         <v>99613.512948580057</v>
       </c>
       <c r="H108" s="14">
@@ -5559,7 +5593,7 @@
         <v>1651800.7975548638</v>
       </c>
       <c r="I108" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A108-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A108-Inputs!$B$80))</f>
         <v>197463.71312785221</v>
       </c>
       <c r="J108" s="14">
@@ -5580,7 +5614,7 @@
         <v>95</v>
       </c>
       <c r="D109" s="18">
-        <f>IF($A109=Inputs!$B$78,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A109&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A109-(Inputs!$B$78+1))/(Inputs!$B$47-(Inputs!$B$78+1)))))</f>
+        <f>IF($A109=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A109&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A109-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E109" s="21">
@@ -5588,11 +5622,11 @@
         <v>17.577021365685248</v>
       </c>
       <c r="F109" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$79,$A109&gt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B109,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$81,$A109&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B109,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G109" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$80),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C109,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C109,$A$15:$A$60,0))))</f>
         <v>102954.04623972709</v>
       </c>
       <c r="H109" s="14">
@@ -5600,7 +5634,7 @@
         <v>1809625.4704394301</v>
       </c>
       <c r="I109" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$79),0,Inputs!$B$50*(1+Inputs!$B$5)^($A109-Inputs!$B$78))</f>
+        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A109-Inputs!$B$80))</f>
         <v>202400.30595604848</v>
       </c>
       <c r="J109" s="14">
@@ -5624,77 +5658,77 @@
   <sheetData>
     <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="U3" s="19" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5710,19 +5744,19 @@
         <v>49</v>
       </c>
       <c r="D4" s="16">
-        <f>IF($A4&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A4-Inputs!$B$78),0)</f>
+        <f>IF($A4&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A4-Inputs!$B$80),0)</f>
         <v>1200000</v>
       </c>
       <c r="E4" s="16">
-        <f>IF($A4&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A4-Inputs!$B$78),0)</f>
+        <f>IF($A4&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A4-Inputs!$B$80),0)</f>
         <v>720000</v>
       </c>
       <c r="F4" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A4-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A4-Inputs!$B$80)</f>
         <v>395000</v>
       </c>
       <c r="G4" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A4-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A4-Inputs!$B$80)</f>
         <v>145000</v>
       </c>
       <c r="H4" s="16">
@@ -5738,15 +5772,15 @@
         <v>36000</v>
       </c>
       <c r="K4" s="16">
-        <f>IF($A4&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A4-Inputs!$B$78),0)</f>
+        <f>IF($A4&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A4-Inputs!$B$80),0)</f>
         <v>984000</v>
       </c>
       <c r="L4" s="16">
-        <f>IF(AND($A4&gt;=Inputs!$B$81,$A4&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A4-Inputs!$B$78),0)</f>
+        <f>IF(AND($A4&gt;=Inputs!$B$83,$A4&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A4-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M4" s="16">
-        <f>IF($A4&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A4-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A4&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A4&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A4-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A4&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N4" s="16">
@@ -5754,16 +5788,16 @@
         <v>0</v>
       </c>
       <c r="O4" s="16">
-        <f>IF($A4&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A4&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P4" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A4=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A4&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A4=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A4&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q4" s="16">
-        <f>D4+E4-H4-I4-J4-K4-L4-M4-N4+O4+P4-IF($A4&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>559230</v>
+        <f>D4+E4-H4-I4+J4-K4-L4-M4-N4+O4+P4-IF($A4&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>631230</v>
       </c>
       <c r="R4" s="16">
         <f>BalanceSheet!$B$37</f>
@@ -5774,12 +5808,12 @@
         <v>469920</v>
       </c>
       <c r="T4" s="16">
-        <f>IF($A4=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A4=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U4" s="16">
         <f t="shared" ref="U4:U50" si="2">MAX(R4+S4+Q4+T4,0)</f>
-        <v>10819150</v>
+        <v>10891150</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5795,19 +5829,19 @@
         <v>50</v>
       </c>
       <c r="D5" s="16">
-        <f>IF($A5&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A5-Inputs!$B$78),0)</f>
+        <f>IF($A5&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A5-Inputs!$B$80),0)</f>
         <v>1236000</v>
       </c>
       <c r="E5" s="16">
-        <f>IF($A5&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A5-Inputs!$B$78),0)</f>
+        <f>IF($A5&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A5-Inputs!$B$80),0)</f>
         <v>741600</v>
       </c>
       <c r="F5" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A5-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A5-Inputs!$B$80)</f>
         <v>404874.99999999994</v>
       </c>
       <c r="G5" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A5-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A5-Inputs!$B$80)</f>
         <v>148625</v>
       </c>
       <c r="H5" s="16">
@@ -5823,15 +5857,15 @@
         <v>36000</v>
       </c>
       <c r="K5" s="16">
-        <f>IF($A5&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A5-Inputs!$B$78),0)</f>
+        <f>IF($A5&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A5-Inputs!$B$80),0)</f>
         <v>1008599.9999999999</v>
       </c>
       <c r="L5" s="16">
-        <f>IF(AND($A5&gt;=Inputs!$B$81,$A5&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A5-Inputs!$B$78),0)</f>
+        <f>IF(AND($A5&gt;=Inputs!$B$83,$A5&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A5-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M5" s="16">
-        <f>IF($A5&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A5-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A5&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A5&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A5-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A5&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N5" s="16">
@@ -5839,32 +5873,32 @@
         <v>0</v>
       </c>
       <c r="O5" s="16">
-        <f>IF($A5&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A5&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P5" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A5=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A5&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A5=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A5&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q5" s="16">
-        <f>D5+E5-H5-I5-J5-K5-L5-M5-N5+O5+P5-IF($A5&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>584733.00000000012</v>
+        <f>D5+E5-H5-I5+J5-K5-L5-M5-N5+O5+P5-IF($A5&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>656733.00000000012</v>
       </c>
       <c r="R5" s="16">
         <f t="shared" ref="R5:R50" si="3">U4</f>
-        <v>10819150</v>
+        <v>10891150</v>
       </c>
       <c r="S5" s="16">
         <f>R5*Inputs!$B$35</f>
-        <v>519319.2</v>
+        <v>522775.2</v>
       </c>
       <c r="T5" s="16">
-        <f>IF($A5=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A5=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U5" s="16">
         <f t="shared" si="2"/>
-        <v>11923202.199999999</v>
+        <v>12070658.199999999</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -5880,19 +5914,19 @@
         <v>51</v>
       </c>
       <c r="D6" s="16">
-        <f>IF($A6&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A6-Inputs!$B$78),0)</f>
+        <f>IF($A6&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A6-Inputs!$B$80),0)</f>
         <v>1273080</v>
       </c>
       <c r="E6" s="16">
-        <f>IF($A6&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A6-Inputs!$B$78),0)</f>
+        <f>IF($A6&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A6-Inputs!$B$80),0)</f>
         <v>763848</v>
       </c>
       <c r="F6" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A6-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A6-Inputs!$B$80)</f>
         <v>414996.87499999994</v>
       </c>
       <c r="G6" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A6-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A6-Inputs!$B$80)</f>
         <v>152340.625</v>
       </c>
       <c r="H6" s="16">
@@ -5908,15 +5942,15 @@
         <v>36000</v>
       </c>
       <c r="K6" s="16">
-        <f>IF($A6&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A6-Inputs!$B$78),0)</f>
+        <f>IF($A6&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A6-Inputs!$B$80),0)</f>
         <v>1033814.9999999999</v>
       </c>
       <c r="L6" s="16">
-        <f>IF(AND($A6&gt;=Inputs!$B$81,$A6&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A6-Inputs!$B$78),0)</f>
+        <f>IF(AND($A6&gt;=Inputs!$B$83,$A6&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A6-Inputs!$B$80),0)</f>
         <v>661500</v>
       </c>
       <c r="M6" s="16">
-        <f>IF($A6&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A6-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A6&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A6&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A6-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A6&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N6" s="16">
@@ -5924,32 +5958,32 @@
         <v>0</v>
       </c>
       <c r="O6" s="16">
-        <f>IF($A6&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A6&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P6" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A6=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A6&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A6=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A6&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="16">
-        <f>D6+E6-H6-I6-J6-K6-L6-M6-N6+O6+P6-IF($A6&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>-50387.384999999893</v>
+        <f>D6+E6-H6-I6+J6-K6-L6-M6-N6+O6+P6-IF($A6&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>21612.615000000107</v>
       </c>
       <c r="R6" s="16">
         <f t="shared" si="3"/>
-        <v>11923202.199999999</v>
+        <v>12070658.199999999</v>
       </c>
       <c r="S6" s="16">
         <f>R6*Inputs!$B$35</f>
-        <v>572313.70559999999</v>
+        <v>579391.59360000002</v>
       </c>
       <c r="T6" s="16">
-        <f>IF($A6=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A6=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U6" s="16">
         <f t="shared" si="2"/>
-        <v>12445128.5206</v>
+        <v>12671662.408599999</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -5965,19 +5999,19 @@
         <v>52</v>
       </c>
       <c r="D7" s="16">
-        <f>IF($A7&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A7-Inputs!$B$78),0)</f>
+        <f>IF($A7&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A7-Inputs!$B$80),0)</f>
         <v>1311272.3999999999</v>
       </c>
       <c r="E7" s="16">
-        <f>IF($A7&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A7-Inputs!$B$78),0)</f>
+        <f>IF($A7&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A7-Inputs!$B$80),0)</f>
         <v>786763.44000000006</v>
       </c>
       <c r="F7" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A7-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A7-Inputs!$B$80)</f>
         <v>425371.79687499994</v>
       </c>
       <c r="G7" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A7-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A7-Inputs!$B$80)</f>
         <v>156149.14062499997</v>
       </c>
       <c r="H7" s="16">
@@ -5993,15 +6027,15 @@
         <v>36000</v>
       </c>
       <c r="K7" s="16">
-        <f>IF($A7&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A7-Inputs!$B$78),0)</f>
+        <f>IF($A7&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A7-Inputs!$B$80),0)</f>
         <v>1059660.3749999998</v>
       </c>
       <c r="L7" s="16">
-        <f>IF(AND($A7&gt;=Inputs!$B$81,$A7&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A7-Inputs!$B$78),0)</f>
+        <f>IF(AND($A7&gt;=Inputs!$B$83,$A7&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A7-Inputs!$B$80),0)</f>
         <v>694575.00000000012</v>
       </c>
       <c r="M7" s="16">
-        <f>IF($A7&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A7-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A7&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A7&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A7-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A7&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N7" s="16">
@@ -6009,32 +6043,32 @@
         <v>0</v>
       </c>
       <c r="O7" s="16">
-        <f>IF($A7&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A7&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A7=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A7&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A7=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A7&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="16">
-        <f>D7+E7-H7-I7-J7-K7-L7-M7-N7+O7+P7-IF($A7&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>-56177.068425000063</v>
+        <f>D7+E7-H7-I7+J7-K7-L7-M7-N7+O7+P7-IF($A7&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>15822.931574999937</v>
       </c>
       <c r="R7" s="16">
         <f t="shared" si="3"/>
-        <v>12445128.5206</v>
+        <v>12671662.408599999</v>
       </c>
       <c r="S7" s="16">
         <f>R7*Inputs!$B$35</f>
-        <v>597366.16898880003</v>
+        <v>608239.79561279994</v>
       </c>
       <c r="T7" s="16">
-        <f>IF($A7=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A7=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U7" s="16">
         <f t="shared" si="2"/>
-        <v>12986317.6211638</v>
+        <v>13295725.1357878</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6050,19 +6084,19 @@
         <v>53</v>
       </c>
       <c r="D8" s="16">
-        <f>IF($A8&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A8-Inputs!$B$78),0)</f>
+        <f>IF($A8&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A8-Inputs!$B$80),0)</f>
         <v>1350610.5719999999</v>
       </c>
       <c r="E8" s="16">
-        <f>IF($A8&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A8-Inputs!$B$78),0)</f>
+        <f>IF($A8&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A8-Inputs!$B$80),0)</f>
         <v>810366.34319999989</v>
       </c>
       <c r="F8" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A8-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A8-Inputs!$B$80)</f>
         <v>436006.09179687488</v>
       </c>
       <c r="G8" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A8-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A8-Inputs!$B$80)</f>
         <v>160052.86914062497</v>
       </c>
       <c r="H8" s="16">
@@ -6078,15 +6112,15 @@
         <v>36000</v>
       </c>
       <c r="K8" s="16">
-        <f>IF($A8&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A8-Inputs!$B$78),0)</f>
+        <f>IF($A8&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A8-Inputs!$B$80),0)</f>
         <v>1086151.8843749997</v>
       </c>
       <c r="L8" s="16">
-        <f>IF(AND($A8&gt;=Inputs!$B$81,$A8&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A8-Inputs!$B$78),0)</f>
+        <f>IF(AND($A8&gt;=Inputs!$B$83,$A8&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A8-Inputs!$B$80),0)</f>
         <v>729303.75</v>
       </c>
       <c r="M8" s="16">
-        <f>IF($A8&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A8-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A8&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A8&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A8-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A8&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="16">
@@ -6094,32 +6128,32 @@
         <v>0</v>
       </c>
       <c r="O8" s="16">
-        <f>IF($A8&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A8&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P8" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A8=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A8&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A8=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A8&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="16">
-        <f>D8+E8-H8-I8-J8-K8-L8-M8-N8+O8+P8-IF($A8&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>-62684.771399624879</v>
+        <f>D8+E8-H8-I8+J8-K8-L8-M8-N8+O8+P8-IF($A8&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>9315.2286003751215</v>
       </c>
       <c r="R8" s="16">
         <f t="shared" si="3"/>
-        <v>12986317.6211638</v>
+        <v>13295725.1357878</v>
       </c>
       <c r="S8" s="16">
         <f>R8*Inputs!$B$35</f>
-        <v>623343.24581586244</v>
+        <v>638194.8065178144</v>
       </c>
       <c r="T8" s="16">
-        <f>IF($A8=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A8=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U8" s="16">
         <f t="shared" si="2"/>
-        <v>13546976.095580038</v>
+        <v>13943235.170905991</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6135,19 +6169,19 @@
         <v>54</v>
       </c>
       <c r="D9" s="16">
-        <f>IF($A9&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A9-Inputs!$B$78),0)</f>
+        <f>IF($A9&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A9-Inputs!$B$80),0)</f>
         <v>1391128.8891599998</v>
       </c>
       <c r="E9" s="16">
-        <f>IF($A9&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A9-Inputs!$B$78),0)</f>
+        <f>IF($A9&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A9-Inputs!$B$80),0)</f>
         <v>834677.33349599992</v>
       </c>
       <c r="F9" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A9-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A9-Inputs!$B$80)</f>
         <v>446906.24409179675</v>
       </c>
       <c r="G9" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A9-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A9-Inputs!$B$80)</f>
         <v>164054.19086914058</v>
       </c>
       <c r="H9" s="16">
@@ -6163,15 +6197,15 @@
         <v>36000</v>
       </c>
       <c r="K9" s="16">
-        <f>IF($A9&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A9-Inputs!$B$78),0)</f>
+        <f>IF($A9&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A9-Inputs!$B$80),0)</f>
         <v>1113305.6814843747</v>
       </c>
       <c r="L9" s="16">
-        <f>IF(AND($A9&gt;=Inputs!$B$81,$A9&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A9-Inputs!$B$78),0)</f>
+        <f>IF(AND($A9&gt;=Inputs!$B$83,$A9&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A9-Inputs!$B$80),0)</f>
         <v>765768.93750000012</v>
       </c>
       <c r="M9" s="16">
-        <f>IF($A9&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A9-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A9&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A9&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A9-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A9&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="16">
@@ -6179,32 +6213,32 @@
         <v>0</v>
       </c>
       <c r="O9" s="16">
-        <f>IF($A9&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A9&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P9" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A9=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A9&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A9=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A9&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q9" s="16">
-        <f>D9+E9-H9-I9-J9-K9-L9-M9-N9+O9+P9-IF($A9&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>-69962.180236535962</v>
+        <f>D9+E9-H9-I9+J9-K9-L9-M9-N9+O9+P9-IF($A9&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>2037.8197634640383</v>
       </c>
       <c r="R9" s="16">
         <f t="shared" si="3"/>
-        <v>13546976.095580038</v>
+        <v>13943235.170905991</v>
       </c>
       <c r="S9" s="16">
         <f>R9*Inputs!$B$35</f>
-        <v>650254.8525878418</v>
+        <v>669275.28820348752</v>
       </c>
       <c r="T9" s="16">
-        <f>IF($A9=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A9=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U9" s="16">
         <f t="shared" si="2"/>
-        <v>14127268.767931344</v>
+        <v>14614548.278872943</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6220,19 +6254,19 @@
         <v>55</v>
       </c>
       <c r="D10" s="16">
-        <f>IF($A10&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A10-Inputs!$B$78),0)</f>
+        <f>IF($A10&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A10-Inputs!$B$80),0)</f>
         <v>1432862.7558348</v>
       </c>
       <c r="E10" s="16">
-        <f>IF($A10&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A10-Inputs!$B$78),0)</f>
+        <f>IF($A10&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A10-Inputs!$B$80),0)</f>
         <v>859717.65350087988</v>
       </c>
       <c r="F10" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A10-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A10-Inputs!$B$80)</f>
         <v>458078.90019409161</v>
       </c>
       <c r="G10" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A10-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A10-Inputs!$B$80)</f>
         <v>168155.54564086907</v>
       </c>
       <c r="H10" s="16">
@@ -6248,15 +6282,15 @@
         <v>36000</v>
       </c>
       <c r="K10" s="16">
-        <f>IF($A10&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A10-Inputs!$B$78),0)</f>
+        <f>IF($A10&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A10-Inputs!$B$80),0)</f>
         <v>1141138.3235214839</v>
       </c>
       <c r="L10" s="16">
-        <f>IF(AND($A10&gt;=Inputs!$B$81,$A10&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A10-Inputs!$B$78),0)</f>
+        <f>IF(AND($A10&gt;=Inputs!$B$83,$A10&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A10-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M10" s="16">
-        <f>IF($A10&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A10-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A10&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A10&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A10-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A10&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="16">
@@ -6264,32 +6298,32 @@
         <v>0</v>
       </c>
       <c r="O10" s="16">
-        <f>IF($A10&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A10&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P10" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A10=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A10&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A10=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A10&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q10" s="16">
-        <f>D10+E10-H10-I10-J10-K10-L10-M10-N10+O10+P10-IF($A10&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>725993.27201907383</v>
+        <f>D10+E10-H10-I10+J10-K10-L10-M10-N10+O10+P10-IF($A10&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>797993.27201907407</v>
       </c>
       <c r="R10" s="16">
         <f t="shared" si="3"/>
-        <v>14127268.767931344</v>
+        <v>14614548.278872943</v>
       </c>
       <c r="S10" s="16">
         <f>R10*Inputs!$B$35</f>
-        <v>678108.90086070448</v>
+        <v>701498.31738590123</v>
       </c>
       <c r="T10" s="16">
-        <f>IF($A10=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A10=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U10" s="16">
         <f t="shared" si="2"/>
-        <v>15531370.940811122</v>
+        <v>16114039.868277917</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6305,19 +6339,19 @@
         <v>56</v>
       </c>
       <c r="D11" s="16">
-        <f>IF($A11&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A11-Inputs!$B$78),0)</f>
+        <f>IF($A11&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A11-Inputs!$B$80),0)</f>
         <v>1475848.638509844</v>
       </c>
       <c r="E11" s="16">
-        <f>IF($A11&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A11-Inputs!$B$78),0)</f>
+        <f>IF($A11&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A11-Inputs!$B$80),0)</f>
         <v>885509.18310590636</v>
       </c>
       <c r="F11" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A11-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A11-Inputs!$B$80)</f>
         <v>469530.87269894395</v>
       </c>
       <c r="G11" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A11-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A11-Inputs!$B$80)</f>
         <v>172359.4342818908</v>
       </c>
       <c r="H11" s="16">
@@ -6333,15 +6367,15 @@
         <v>36000</v>
       </c>
       <c r="K11" s="16">
-        <f>IF($A11&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A11-Inputs!$B$78),0)</f>
+        <f>IF($A11&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A11-Inputs!$B$80),0)</f>
         <v>1169666.781609521</v>
       </c>
       <c r="L11" s="16">
-        <f>IF(AND($A11&gt;=Inputs!$B$81,$A11&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A11-Inputs!$B$78),0)</f>
+        <f>IF(AND($A11&gt;=Inputs!$B$83,$A11&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A11-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M11" s="16">
-        <f>IF($A11&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A11-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A11&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A11&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A11-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A11&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="16">
@@ -6349,32 +6383,32 @@
         <v>0</v>
       </c>
       <c r="O11" s="16">
-        <f>IF($A11&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A11&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P11" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A11=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A11&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A11=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A11&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="16">
-        <f>D11+E11-H11-I11-J11-K11-L11-M11-N11+O11+P11-IF($A11&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>757211.56251829374</v>
+        <f>D11+E11-H11-I11+J11-K11-L11-M11-N11+O11+P11-IF($A11&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>829211.56251829374</v>
       </c>
       <c r="R11" s="16">
         <f t="shared" si="3"/>
-        <v>15531370.940811122</v>
+        <v>16114039.868277917</v>
       </c>
       <c r="S11" s="16">
         <f>R11*Inputs!$B$35</f>
-        <v>745505.80515893386</v>
+        <v>773473.91367734002</v>
       </c>
       <c r="T11" s="16">
-        <f>IF($A11=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A11=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U11" s="16">
         <f t="shared" si="2"/>
-        <v>17034088.30848835</v>
+        <v>17716725.344473552</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6390,19 +6424,19 @@
         <v>57</v>
       </c>
       <c r="D12" s="16">
-        <f>IF($A12&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A12-Inputs!$B$78),0)</f>
+        <f>IF($A12&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A12-Inputs!$B$80),0)</f>
         <v>1520124.097665139</v>
       </c>
       <c r="E12" s="16">
-        <f>IF($A12&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A12-Inputs!$B$78),0)</f>
+        <f>IF($A12&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A12-Inputs!$B$80),0)</f>
         <v>912074.45859908347</v>
       </c>
       <c r="F12" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A12-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A12-Inputs!$B$80)</f>
         <v>481269.14451641747</v>
       </c>
       <c r="G12" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A12-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A12-Inputs!$B$80)</f>
         <v>176668.42013893806</v>
       </c>
       <c r="H12" s="16">
@@ -6418,15 +6452,15 @@
         <v>36000</v>
       </c>
       <c r="K12" s="16">
-        <f>IF($A12&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A12-Inputs!$B$78),0)</f>
+        <f>IF($A12&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A12-Inputs!$B$80),0)</f>
         <v>1198908.4511497591</v>
       </c>
       <c r="L12" s="16">
-        <f>IF(AND($A12&gt;=Inputs!$B$81,$A12&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A12-Inputs!$B$78),0)</f>
+        <f>IF(AND($A12&gt;=Inputs!$B$83,$A12&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A12-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M12" s="16">
-        <f>IF($A12&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A12-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A12&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A12&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A12-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A12&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N12" s="16">
@@ -6434,32 +6468,32 @@
         <v>0</v>
       </c>
       <c r="O12" s="16">
-        <f>IF($A12&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A12&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P12" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A12=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A12&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A12=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A12&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q12" s="16">
-        <f>D12+E12-H12-I12-J12-K12-L12-M12-N12+O12+P12-IF($A12&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>789495.73654095572</v>
+        <f>D12+E12-H12-I12+J12-K12-L12-M12-N12+O12+P12-IF($A12&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>861495.73654095572</v>
       </c>
       <c r="R12" s="16">
         <f t="shared" si="3"/>
-        <v>17034088.30848835</v>
+        <v>17716725.344473552</v>
       </c>
       <c r="S12" s="16">
         <f>R12*Inputs!$B$35</f>
-        <v>817636.23880744085</v>
+        <v>850402.81653473049</v>
       </c>
       <c r="T12" s="16">
-        <f>IF($A12=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A12=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U12" s="16">
         <f t="shared" si="2"/>
-        <v>18641220.283836745</v>
+        <v>19428623.897549238</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -6475,19 +6509,19 @@
         <v>58</v>
       </c>
       <c r="D13" s="16">
-        <f>IF($A13&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A13-Inputs!$B$78),0)</f>
+        <f>IF($A13&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A13-Inputs!$B$80),0)</f>
         <v>1565727.8205950933</v>
       </c>
       <c r="E13" s="16">
-        <f>IF($A13&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A13-Inputs!$B$78),0)</f>
+        <f>IF($A13&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A13-Inputs!$B$80),0)</f>
         <v>939436.69235705596</v>
       </c>
       <c r="F13" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A13-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A13-Inputs!$B$80)</f>
         <v>493300.87312932784</v>
       </c>
       <c r="G13" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A13-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A13-Inputs!$B$80)</f>
         <v>181085.13064241147</v>
       </c>
       <c r="H13" s="16">
@@ -6503,15 +6537,15 @@
         <v>36000</v>
       </c>
       <c r="K13" s="16">
-        <f>IF($A13&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A13-Inputs!$B$78),0)</f>
+        <f>IF($A13&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A13-Inputs!$B$80),0)</f>
         <v>1228881.1624285027</v>
       </c>
       <c r="L13" s="16">
-        <f>IF(AND($A13&gt;=Inputs!$B$81,$A13&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A13-Inputs!$B$78),0)</f>
+        <f>IF(AND($A13&gt;=Inputs!$B$83,$A13&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A13-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M13" s="16">
-        <f>IF($A13&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A13-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A13&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A13&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A13-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A13&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="16">
@@ -6519,32 +6553,32 @@
         <v>0</v>
       </c>
       <c r="O13" s="16">
-        <f>IF($A13&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A13&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P13" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A13=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A13&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A13=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A13&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q13" s="16">
-        <f>D13+E13-H13-I13-J13-K13-L13-M13-N13+O13+P13-IF($A13&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>822881.00396297663</v>
+        <f>D13+E13-H13-I13+J13-K13-L13-M13-N13+O13+P13-IF($A13&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>894881.00396297663</v>
       </c>
       <c r="R13" s="16">
         <f t="shared" si="3"/>
-        <v>18641220.283836745</v>
+        <v>19428623.897549238</v>
       </c>
       <c r="S13" s="16">
         <f>R13*Inputs!$B$35</f>
-        <v>894778.57362416375</v>
+        <v>932573.94708236342</v>
       </c>
       <c r="T13" s="16">
-        <f>IF($A13=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A13=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U13" s="16">
         <f t="shared" si="2"/>
-        <v>20358879.861423884</v>
+        <v>21256078.848594576</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -6560,19 +6594,19 @@
         <v>59</v>
       </c>
       <c r="D14" s="16">
-        <f>IF($A14&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A14-Inputs!$B$78),0)</f>
+        <f>IF($A14&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A14-Inputs!$B$80),0)</f>
         <v>1612699.6552129462</v>
       </c>
       <c r="E14" s="16">
-        <f>IF($A14&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A14-Inputs!$B$78),0)</f>
+        <f>IF($A14&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A14-Inputs!$B$80),0)</f>
         <v>967619.79312776763</v>
       </c>
       <c r="F14" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A14-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A14-Inputs!$B$80)</f>
         <v>505633.39495756105</v>
       </c>
       <c r="G14" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A14-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A14-Inputs!$B$80)</f>
         <v>185612.25890847179</v>
       </c>
       <c r="H14" s="16">
@@ -6588,15 +6622,15 @@
         <v>36000</v>
       </c>
       <c r="K14" s="16">
-        <f>IF($A14&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A14-Inputs!$B$78),0)</f>
+        <f>IF($A14&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A14-Inputs!$B$80),0)</f>
         <v>1259603.1914892155</v>
       </c>
       <c r="L14" s="16">
-        <f>IF(AND($A14&gt;=Inputs!$B$81,$A14&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A14-Inputs!$B$78),0)</f>
+        <f>IF(AND($A14&gt;=Inputs!$B$83,$A14&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A14-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M14" s="16">
-        <f>IF($A14&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A14-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A14&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A14&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A14-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A14&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="16">
@@ -6604,32 +6638,32 @@
         <v>0</v>
       </c>
       <c r="O14" s="16">
-        <f>IF($A14&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A14&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>0</v>
       </c>
       <c r="P14" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A14=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A14&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A14=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A14&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q14" s="16">
-        <f>D14+E14-H14-I14-J14-K14-L14-M14-N14+O14+P14-IF($A14&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>857403.71179080242</v>
+        <f>D14+E14-H14-I14+J14-K14-L14-M14-N14+O14+P14-IF($A14&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>929403.71179080242</v>
       </c>
       <c r="R14" s="16">
         <f t="shared" si="3"/>
-        <v>20358879.861423884</v>
+        <v>21256078.848594576</v>
       </c>
       <c r="S14" s="16">
         <f>R14*Inputs!$B$35</f>
-        <v>977226.23334834643</v>
+        <v>1020291.7847325397</v>
       </c>
       <c r="T14" s="16">
-        <f>IF($A14=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A14=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U14" s="16">
         <f t="shared" si="2"/>
-        <v>22193509.806563035</v>
+        <v>23205774.345117919</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -6645,19 +6679,19 @@
         <v>60</v>
       </c>
       <c r="D15" s="23">
-        <f>IF($A15&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A15-Inputs!$B$78),0)</f>
+        <f>IF($A15&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A15-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="23">
-        <f>IF($A15&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A15-Inputs!$B$78),0)</f>
+        <f>IF($A15&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A15-Inputs!$B$80),0)</f>
         <v>996648.38692160079</v>
       </c>
       <c r="F15" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A15-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A15-Inputs!$B$80)</f>
         <v>518274.22983150004</v>
       </c>
       <c r="G15" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A15-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A15-Inputs!$B$80)</f>
         <v>190252.56538118358</v>
       </c>
       <c r="H15" s="23">
@@ -6673,15 +6707,15 @@
         <v>18000</v>
       </c>
       <c r="K15" s="23">
-        <f>IF($A15&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A15-Inputs!$B$78),0)</f>
+        <f>IF($A15&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A15-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="23">
-        <f>IF(AND($A15&gt;=Inputs!$B$81,$A15&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A15-Inputs!$B$78),0)</f>
+        <f>IF(AND($A15&gt;=Inputs!$B$83,$A15&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A15-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="23">
-        <f>IF($A15&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A15-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A15&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A15&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A15-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A15&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1023427.5930849875</v>
       </c>
       <c r="N15" s="23">
@@ -6689,32 +6723,32 @@
         <v>0</v>
       </c>
       <c r="O15" s="23">
-        <f>IF($A15&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A15&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P15" s="23">
-        <f>IF(AND(Inputs!$B$56=1,$A15=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A15&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A15=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A15&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q15" s="23">
-        <f>D15+E15-H15-I15-J15-K15-L15-M15-N15+O15+P15-IF($A15&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>112548.50417474238</v>
+        <f>D15+E15-H15-I15+J15-K15-L15-M15-N15+O15+P15-IF($A15&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>148548.50417474238</v>
       </c>
       <c r="R15" s="23">
         <f t="shared" si="3"/>
-        <v>22193509.806563035</v>
+        <v>23205774.345117919</v>
       </c>
       <c r="S15" s="23">
         <f>R15*Inputs!$B$35</f>
-        <v>1065288.4707150257</v>
+        <v>1113877.1685656602</v>
       </c>
       <c r="T15" s="23">
-        <f>IF($A15=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A15=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>-4120000</v>
       </c>
       <c r="U15" s="23">
         <f t="shared" si="2"/>
-        <v>19251346.781452805</v>
+        <v>20348200.017858323</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -6730,19 +6764,19 @@
         <v>61</v>
       </c>
       <c r="D16" s="16">
-        <f>IF($A16&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A16-Inputs!$B$78),0)</f>
+        <f>IF($A16&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A16-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E16" s="16">
-        <f>IF($A16&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A16-Inputs!$B$78),0)</f>
+        <f>IF($A16&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A16-Inputs!$B$80),0)</f>
         <v>1026547.8385292486</v>
       </c>
       <c r="F16" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A16-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A16-Inputs!$B$80)</f>
         <v>531231.08557728748</v>
       </c>
       <c r="G16" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A16-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A16-Inputs!$B$80)</f>
         <v>195008.87951571314</v>
       </c>
       <c r="H16" s="16">
@@ -6758,15 +6792,15 @@
         <v>18000</v>
       </c>
       <c r="K16" s="16">
-        <f>IF($A16&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A16-Inputs!$B$78),0)</f>
+        <f>IF($A16&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A16-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L16" s="16">
-        <f>IF(AND($A16&gt;=Inputs!$B$81,$A16&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A16-Inputs!$B$78),0)</f>
+        <f>IF(AND($A16&gt;=Inputs!$B$83,$A16&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A16-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M16" s="16">
-        <f>IF($A16&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A16-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A16&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A16&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A16-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A16&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1049013.2829121121</v>
       </c>
       <c r="N16" s="16">
@@ -6774,32 +6808,32 @@
         <v>0</v>
       </c>
       <c r="O16" s="16">
-        <f>IF($A16&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A16&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P16" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A16=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A16&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A16=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A16&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q16" s="16">
-        <f>D16+E16-H16-I16-J16-K16-L16-M16-N16+O16+P16-IF($A16&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
-        <v>112587.93258483545</v>
+        <f>D16+E16-H16-I16+J16-K16-L16-M16-N16+O16+P16-IF($A16&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <v>148587.93258483545</v>
       </c>
       <c r="R16" s="16">
         <f t="shared" si="3"/>
-        <v>19251346.781452805</v>
+        <v>20348200.017858323</v>
       </c>
       <c r="S16" s="16">
         <f>R16*Inputs!$B$35</f>
-        <v>924064.64550973463</v>
+        <v>976713.60085719952</v>
       </c>
       <c r="T16" s="16">
-        <f>IF($A16=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A16=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U16" s="16">
         <f t="shared" si="2"/>
-        <v>20287999.359547377</v>
+        <v>21473501.551300358</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -6815,19 +6849,19 @@
         <v>62</v>
       </c>
       <c r="D17" s="23">
-        <f>IF($A17&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A17-Inputs!$B$78),0)</f>
+        <f>IF($A17&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A17-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="23">
-        <f>IF($A17&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A17-Inputs!$B$78),0)</f>
+        <f>IF($A17&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A17-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A17-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A17-Inputs!$B$80)</f>
         <v>544511.86271671974</v>
       </c>
       <c r="G17" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A17-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A17-Inputs!$B$80)</f>
         <v>199884.10150360595</v>
       </c>
       <c r="H17" s="23">
@@ -6843,15 +6877,15 @@
         <v>0</v>
       </c>
       <c r="K17" s="23">
-        <f>IF($A17&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A17-Inputs!$B$78),0)</f>
+        <f>IF($A17&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A17-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L17" s="23">
-        <f>IF(AND($A17&gt;=Inputs!$B$81,$A17&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A17-Inputs!$B$78),0)</f>
+        <f>IF(AND($A17&gt;=Inputs!$B$83,$A17&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A17-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M17" s="23">
-        <f>IF($A17&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A17-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A17&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A17&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A17-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A17&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1075238.6149849149</v>
       </c>
       <c r="N17" s="23">
@@ -6859,32 +6893,32 @@
         <v>69643.453498252085</v>
       </c>
       <c r="O17" s="23">
-        <f>IF($A17&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A17&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P17" s="23">
-        <f>IF(AND(Inputs!$B$56=1,$A17=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A17&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A17=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A17&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="23">
-        <f>D17+E17-H17-I17-J17-K17-L17-M17-N17+O17+P17-IF($A17&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D17+E17-H17-I17+J17-K17-L17-M17-N17+O17+P17-IF($A17&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-876882.06848316686</v>
       </c>
       <c r="R17" s="23">
         <f t="shared" si="3"/>
-        <v>20287999.359547377</v>
+        <v>21473501.551300358</v>
       </c>
       <c r="S17" s="23">
         <f>R17*Inputs!$B$35</f>
-        <v>973823.96925827407</v>
+        <v>1030728.0744624172</v>
       </c>
       <c r="T17" s="23">
-        <f>IF($A17=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A17=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U17" s="23">
         <f t="shared" si="2"/>
-        <v>20384941.260322485</v>
+        <v>21627347.557279609</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -6900,19 +6934,19 @@
         <v>63</v>
       </c>
       <c r="D18" s="16">
-        <f>IF($A18&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A18-Inputs!$B$78),0)</f>
+        <f>IF($A18&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A18-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E18" s="16">
-        <f>IF($A18&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A18-Inputs!$B$78),0)</f>
+        <f>IF($A18&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A18-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A18-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A18-Inputs!$B$80)</f>
         <v>558124.65928463766</v>
       </c>
       <c r="G18" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A18-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A18-Inputs!$B$80)</f>
         <v>204881.20404119609</v>
       </c>
       <c r="H18" s="16">
@@ -6928,15 +6962,15 @@
         <v>0</v>
       </c>
       <c r="K18" s="16">
-        <f>IF($A18&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A18-Inputs!$B$78),0)</f>
+        <f>IF($A18&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A18-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="16">
-        <f>IF(AND($A18&gt;=Inputs!$B$81,$A18&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A18-Inputs!$B$78),0)</f>
+        <f>IF(AND($A18&gt;=Inputs!$B$83,$A18&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A18-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="16">
-        <f>IF($A18&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A18-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A18&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A18&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A18-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A18&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1102119.5803595376</v>
       </c>
       <c r="N18" s="16">
@@ -6944,32 +6978,32 @@
         <v>87001.932886053866</v>
       </c>
       <c r="O18" s="16">
-        <f>IF($A18&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A18&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P18" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A18=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A18&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A18=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A18&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="16">
-        <f>D18+E18-H18-I18-J18-K18-L18-M18-N18+O18+P18-IF($A18&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D18+E18-H18-I18+J18-K18-L18-M18-N18+O18+P18-IF($A18&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-921121.51324559143</v>
       </c>
       <c r="R18" s="16">
         <f t="shared" si="3"/>
-        <v>20384941.260322485</v>
+        <v>21627347.557279609</v>
       </c>
       <c r="S18" s="16">
         <f>R18*Inputs!$B$35</f>
-        <v>978477.18049547926</v>
+        <v>1038112.6827494212</v>
       </c>
       <c r="T18" s="16">
-        <f>IF($A18=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A18=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U18" s="16">
         <f t="shared" si="2"/>
-        <v>20442296.927572373</v>
+        <v>21744338.72678344</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -6985,19 +7019,19 @@
         <v>64</v>
       </c>
       <c r="D19" s="16">
-        <f>IF($A19&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A19-Inputs!$B$78),0)</f>
+        <f>IF($A19&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A19-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E19" s="16">
-        <f>IF($A19&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A19-Inputs!$B$78),0)</f>
+        <f>IF($A19&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A19-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A19-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A19-Inputs!$B$80)</f>
         <v>572077.77576675359</v>
       </c>
       <c r="G19" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A19-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A19-Inputs!$B$80)</f>
         <v>210003.23414222602</v>
       </c>
       <c r="H19" s="16">
@@ -7013,15 +7047,15 @@
         <v>0</v>
       </c>
       <c r="K19" s="16">
-        <f>IF($A19&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A19-Inputs!$B$78),0)</f>
+        <f>IF($A19&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A19-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L19" s="16">
-        <f>IF(AND($A19&gt;=Inputs!$B$81,$A19&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A19-Inputs!$B$78),0)</f>
+        <f>IF(AND($A19&gt;=Inputs!$B$83,$A19&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A19-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="16">
-        <f>IF($A19&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A19-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A19&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A19&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A19-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A19&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1129672.5698685262</v>
       </c>
       <c r="N19" s="16">
@@ -7029,32 +7063,32 @@
         <v>106727.07007672689</v>
       </c>
       <c r="O19" s="16">
-        <f>IF($A19&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A19&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P19" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A19=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A19&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A19=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A19&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q19" s="16">
-        <f>D19+E19-H19-I19-J19-K19-L19-M19-N19+O19+P19-IF($A19&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D19+E19-H19-I19+J19-K19-L19-M19-N19+O19+P19-IF($A19&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-968399.63994525303</v>
       </c>
       <c r="R19" s="16">
         <f t="shared" si="3"/>
-        <v>20442296.927572373</v>
+        <v>21744338.72678344</v>
       </c>
       <c r="S19" s="16">
         <f>R19*Inputs!$B$35</f>
-        <v>981230.25252347393</v>
+        <v>1043728.2588856051</v>
       </c>
       <c r="T19" s="16">
-        <f>IF($A19=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A19=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U19" s="16">
         <f t="shared" si="2"/>
-        <v>20455127.540150594</v>
+        <v>21819667.345723789</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -7070,19 +7104,19 @@
         <v>65</v>
       </c>
       <c r="D20" s="16">
-        <f>IF($A20&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A20-Inputs!$B$78),0)</f>
+        <f>IF($A20&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A20-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="16">
-        <f>IF($A20&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A20-Inputs!$B$78),0)</f>
+        <f>IF($A20&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A20-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F20" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A20-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A20-Inputs!$B$80)</f>
         <v>586379.72016092238</v>
       </c>
       <c r="G20" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A20-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A20-Inputs!$B$80)</f>
         <v>215253.31499578166</v>
       </c>
       <c r="H20" s="16">
@@ -7098,15 +7132,15 @@
         <v>0</v>
       </c>
       <c r="K20" s="16">
-        <f>IF($A20&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A20-Inputs!$B$78),0)</f>
+        <f>IF($A20&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A20-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L20" s="16">
-        <f>IF(AND($A20&gt;=Inputs!$B$81,$A20&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A20-Inputs!$B$78),0)</f>
+        <f>IF(AND($A20&gt;=Inputs!$B$83,$A20&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A20-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M20" s="16">
-        <f>IF($A20&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A20-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A20&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A20&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A20-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A20&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1157914.3841152391</v>
       </c>
       <c r="N20" s="16">
@@ -7114,32 +7148,32 @@
         <v>129118.27483096196</v>
       </c>
       <c r="O20" s="16">
-        <f>IF($A20&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A20&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P20" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A20=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A20&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A20=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A20&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q20" s="16">
-        <f>D20+E20-H20-I20-J20-K20-L20-M20-N20+O20+P20-IF($A20&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D20+E20-H20-I20+J20-K20-L20-M20-N20+O20+P20-IF($A20&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1019032.6589462012</v>
       </c>
       <c r="R20" s="16">
         <f t="shared" si="3"/>
-        <v>20455127.540150594</v>
+        <v>21819667.345723789</v>
       </c>
       <c r="S20" s="16">
         <f>R20*Inputs!$B$35</f>
-        <v>981846.12192722852</v>
+        <v>1047344.0325947419</v>
       </c>
       <c r="T20" s="16">
-        <f>IF($A20=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A20=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U20" s="16">
         <f t="shared" si="2"/>
-        <v>20417941.003131621</v>
+        <v>21847978.719372328</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -7155,19 +7189,19 @@
         <v>66</v>
       </c>
       <c r="D21" s="16">
-        <f>IF($A21&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A21-Inputs!$B$78),0)</f>
+        <f>IF($A21&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A21-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="16">
-        <f>IF($A21&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A21-Inputs!$B$78),0)</f>
+        <f>IF($A21&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A21-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F21" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A21-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A21-Inputs!$B$80)</f>
         <v>601039.21316494537</v>
       </c>
       <c r="G21" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A21-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A21-Inputs!$B$80)</f>
         <v>220634.64787067616</v>
       </c>
       <c r="H21" s="16">
@@ -7183,15 +7217,15 @@
         <v>0</v>
       </c>
       <c r="K21" s="16">
-        <f>IF($A21&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A21-Inputs!$B$78),0)</f>
+        <f>IF($A21&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A21-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L21" s="16">
-        <f>IF(AND($A21&gt;=Inputs!$B$81,$A21&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A21-Inputs!$B$78),0)</f>
+        <f>IF(AND($A21&gt;=Inputs!$B$83,$A21&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A21-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M21" s="16">
-        <f>IF($A21&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A21-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A21&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A21&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A21-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A21&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1186862.24371812</v>
       </c>
       <c r="N21" s="16">
@@ -7199,32 +7233,32 @@
         <v>152618.39511465485</v>
       </c>
       <c r="O21" s="16">
-        <f>IF($A21&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A21&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P21" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A21=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A21&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A21=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A21&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q21" s="16">
-        <f>D21+E21-H21-I21-J21-K21-L21-M21-N21+O21+P21-IF($A21&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D21+E21-H21-I21+J21-K21-L21-M21-N21+O21+P21-IF($A21&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1071480.6388327749</v>
       </c>
       <c r="R21" s="16">
         <f t="shared" si="3"/>
-        <v>20417941.003131621</v>
+        <v>21847978.719372328</v>
       </c>
       <c r="S21" s="16">
         <f>R21*Inputs!$B$35</f>
-        <v>980061.16815031786</v>
+        <v>1048702.9785298717</v>
       </c>
       <c r="T21" s="16">
-        <f>IF($A21=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A21=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U21" s="16">
         <f t="shared" si="2"/>
-        <v>20326521.532449163</v>
+        <v>21825201.059069425</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -7240,19 +7274,19 @@
         <v>67</v>
       </c>
       <c r="D22" s="16">
-        <f>IF($A22&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A22-Inputs!$B$78),0)</f>
+        <f>IF($A22&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A22-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="16">
-        <f>IF($A22&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A22-Inputs!$B$78),0)</f>
+        <f>IF($A22&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A22-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A22-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A22-Inputs!$B$80)</f>
         <v>616065.19349406904</v>
       </c>
       <c r="G22" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A22-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A22-Inputs!$B$80)</f>
         <v>226150.51406744309</v>
       </c>
       <c r="H22" s="16">
@@ -7268,15 +7302,15 @@
         <v>0</v>
       </c>
       <c r="K22" s="16">
-        <f>IF($A22&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A22-Inputs!$B$78),0)</f>
+        <f>IF($A22&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A22-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L22" s="16">
-        <f>IF(AND($A22&gt;=Inputs!$B$81,$A22&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A22-Inputs!$B$78),0)</f>
+        <f>IF(AND($A22&gt;=Inputs!$B$83,$A22&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A22-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M22" s="16">
-        <f>IF($A22&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A22-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A22&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A22&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A22-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A22&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1216533.7998110731</v>
       </c>
       <c r="N22" s="16">
@@ -7284,32 +7318,32 @@
         <v>179034.89615033241</v>
       </c>
       <c r="O22" s="16">
-        <f>IF($A22&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A22&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P22" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A22=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A22&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A22=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A22&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q22" s="16">
-        <f>D22+E22-H22-I22-J22-K22-L22-M22-N22+O22+P22-IF($A22&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D22+E22-H22-I22+J22-K22-L22-M22-N22+O22+P22-IF($A22&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1127568.6959614055</v>
       </c>
       <c r="R22" s="16">
         <f t="shared" si="3"/>
-        <v>20326521.532449163</v>
+        <v>21825201.059069425</v>
       </c>
       <c r="S22" s="16">
         <f>R22*Inputs!$B$35</f>
-        <v>975673.03355755983</v>
+        <v>1047609.6508353325</v>
       </c>
       <c r="T22" s="16">
-        <f>IF($A22=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A22=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U22" s="16">
         <f t="shared" si="2"/>
-        <v>20174625.870045319</v>
+        <v>21745242.013943352</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -7325,19 +7359,19 @@
         <v>68</v>
       </c>
       <c r="D23" s="16">
-        <f>IF($A23&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A23-Inputs!$B$78),0)</f>
+        <f>IF($A23&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A23-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E23" s="16">
-        <f>IF($A23&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A23-Inputs!$B$78),0)</f>
+        <f>IF($A23&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A23-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F23" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A23-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A23-Inputs!$B$80)</f>
         <v>631466.82333142078</v>
       </c>
       <c r="G23" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A23-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A23-Inputs!$B$80)</f>
         <v>231804.27691912916</v>
       </c>
       <c r="H23" s="16">
@@ -7353,15 +7387,15 @@
         <v>0</v>
       </c>
       <c r="K23" s="16">
-        <f>IF($A23&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A23-Inputs!$B$78),0)</f>
+        <f>IF($A23&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A23-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L23" s="16">
-        <f>IF(AND($A23&gt;=Inputs!$B$81,$A23&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A23-Inputs!$B$78),0)</f>
+        <f>IF(AND($A23&gt;=Inputs!$B$83,$A23&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A23-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M23" s="16">
-        <f>IF($A23&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A23-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A23&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A23&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A23-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A23&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1246947.1448063499</v>
       </c>
       <c r="N23" s="16">
@@ -7369,32 +7403,32 @@
         <v>208708.27808234876</v>
       </c>
       <c r="O23" s="16">
-        <f>IF($A23&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A23&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P23" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A23=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A23&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A23=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A23&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q23" s="16">
-        <f>D23+E23-H23-I23-J23-K23-L23-M23-N23+O23+P23-IF($A23&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D23+E23-H23-I23+J23-K23-L23-M23-N23+O23+P23-IF($A23&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1187655.4228886985</v>
       </c>
       <c r="R23" s="16">
         <f t="shared" si="3"/>
-        <v>20174625.870045319</v>
+        <v>21745242.013943352</v>
       </c>
       <c r="S23" s="16">
         <f>R23*Inputs!$B$35</f>
-        <v>968382.04176217539</v>
+        <v>1043771.6166692809</v>
       </c>
       <c r="T23" s="16">
-        <f>IF($A23=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A23=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U23" s="16">
         <f t="shared" si="2"/>
-        <v>19955352.488918796</v>
+        <v>21601358.207723934</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -7410,19 +7444,19 @@
         <v>69</v>
       </c>
       <c r="D24" s="16">
-        <f>IF($A24&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A24-Inputs!$B$78),0)</f>
+        <f>IF($A24&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A24-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E24" s="16">
-        <f>IF($A24&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A24-Inputs!$B$78),0)</f>
+        <f>IF($A24&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A24-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F24" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A24-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A24-Inputs!$B$80)</f>
         <v>647253.49391470628</v>
       </c>
       <c r="G24" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A24-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A24-Inputs!$B$80)</f>
         <v>237599.38384210735</v>
       </c>
       <c r="H24" s="16">
@@ -7438,15 +7472,15 @@
         <v>0</v>
       </c>
       <c r="K24" s="16">
-        <f>IF($A24&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A24-Inputs!$B$78),0)</f>
+        <f>IF($A24&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A24-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="16">
-        <f>IF(AND($A24&gt;=Inputs!$B$81,$A24&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A24-Inputs!$B$78),0)</f>
+        <f>IF(AND($A24&gt;=Inputs!$B$83,$A24&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A24-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="16">
-        <f>IF($A24&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A24-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A24&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A24&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A24-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A24&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1278120.8234265086</v>
       </c>
       <c r="N24" s="16">
@@ -7454,32 +7488,32 @@
         <v>242018.30552795361</v>
       </c>
       <c r="O24" s="16">
-        <f>IF($A24&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A24&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P24" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A24=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A24&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A24=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A24&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q24" s="16">
-        <f>D24+E24-H24-I24-J24-K24-L24-M24-N24+O24+P24-IF($A24&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D24+E24-H24-I24+J24-K24-L24-M24-N24+O24+P24-IF($A24&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1252139.1289544622</v>
       </c>
       <c r="R24" s="16">
         <f t="shared" si="3"/>
-        <v>19955352.488918796</v>
+        <v>21601358.207723934</v>
       </c>
       <c r="S24" s="16">
         <f>R24*Inputs!$B$35</f>
-        <v>957856.91946810228</v>
+        <v>1036865.1939707488</v>
       </c>
       <c r="T24" s="16">
-        <f>IF($A24=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A24=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U24" s="16">
         <f t="shared" si="2"/>
-        <v>19661070.279432435</v>
+        <v>21386084.272740219</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -7495,19 +7529,19 @@
         <v>70</v>
       </c>
       <c r="D25" s="16">
-        <f>IF($A25&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A25-Inputs!$B$78),0)</f>
+        <f>IF($A25&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A25-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="16">
-        <f>IF($A25&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A25-Inputs!$B$78),0)</f>
+        <f>IF($A25&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A25-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F25" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A25-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A25-Inputs!$B$80)</f>
         <v>663434.83126257383</v>
       </c>
       <c r="G25" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A25-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A25-Inputs!$B$80)</f>
         <v>243539.36843816002</v>
       </c>
       <c r="H25" s="16">
@@ -7523,15 +7557,15 @@
         <v>0</v>
       </c>
       <c r="K25" s="16">
-        <f>IF($A25&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A25-Inputs!$B$78),0)</f>
+        <f>IF($A25&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A25-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L25" s="16">
-        <f>IF(AND($A25&gt;=Inputs!$B$81,$A25&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A25-Inputs!$B$78),0)</f>
+        <f>IF(AND($A25&gt;=Inputs!$B$83,$A25&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A25-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M25" s="16">
-        <f>IF($A25&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A25-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A25&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A25&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A25-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A25&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1310073.844012171</v>
       </c>
       <c r="N25" s="16">
@@ -7539,32 +7573,32 @@
         <v>279388.52389267285</v>
       </c>
       <c r="O25" s="16">
-        <f>IF($A25&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A25&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P25" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A25=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A25&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A25=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A25&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q25" s="16">
-        <f>D25+E25-H25-I25-J25-K25-L25-M25-N25+O25+P25-IF($A25&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D25+E25-H25-I25+J25-K25-L25-M25-N25+O25+P25-IF($A25&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1321462.3679048438</v>
       </c>
       <c r="R25" s="16">
         <f t="shared" si="3"/>
-        <v>19661070.279432435</v>
+        <v>21386084.272740219</v>
       </c>
       <c r="S25" s="16">
         <f>R25*Inputs!$B$35</f>
-        <v>943731.37341275683</v>
+        <v>1026532.0450915305</v>
       </c>
       <c r="T25" s="16">
-        <f>IF($A25=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A25=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U25" s="16">
         <f t="shared" si="2"/>
-        <v>19283339.284940347</v>
+        <v>21091153.949926905</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -7580,19 +7614,19 @@
         <v>71</v>
       </c>
       <c r="D26" s="16">
-        <f>IF($A26&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A26-Inputs!$B$78),0)</f>
+        <f>IF($A26&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A26-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="16">
-        <f>IF($A26&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A26-Inputs!$B$78),0)</f>
+        <f>IF($A26&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A26-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F26" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A26-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A26-Inputs!$B$80)</f>
         <v>680020.7020441381</v>
       </c>
       <c r="G26" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A26-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A26-Inputs!$B$80)</f>
         <v>249627.85264911401</v>
       </c>
       <c r="H26" s="16">
@@ -7608,15 +7642,15 @@
         <v>0</v>
       </c>
       <c r="K26" s="16">
-        <f>IF($A26&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A26-Inputs!$B$78),0)</f>
+        <f>IF($A26&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A26-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L26" s="16">
-        <f>IF(AND($A26&gt;=Inputs!$B$81,$A26&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A26-Inputs!$B$78),0)</f>
+        <f>IF(AND($A26&gt;=Inputs!$B$83,$A26&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A26-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M26" s="16">
-        <f>IF($A26&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A26-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A26&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A26&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A26-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A26&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1342825.6901124753</v>
       </c>
       <c r="N26" s="16">
@@ -7624,32 +7658,32 @@
         <v>317434.86122545542</v>
       </c>
       <c r="O26" s="16">
-        <f>IF($A26&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A26&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P26" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A26=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A26&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A26=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A26&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q26" s="16">
-        <f>D26+E26-H26-I26-J26-K26-L26-M26-N26+O26+P26-IF($A26&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D26+E26-H26-I26+J26-K26-L26-M26-N26+O26+P26-IF($A26&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1392260.5513379308</v>
       </c>
       <c r="R26" s="16">
         <f t="shared" si="3"/>
-        <v>19283339.284940347</v>
+        <v>21091153.949926905</v>
       </c>
       <c r="S26" s="16">
         <f>R26*Inputs!$B$35</f>
-        <v>925600.28567713674</v>
+        <v>1012375.3895964915</v>
       </c>
       <c r="T26" s="16">
-        <f>IF($A26=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A26=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U26" s="16">
         <f t="shared" si="2"/>
-        <v>18816679.019279551</v>
+        <v>20711268.788185466</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -7665,19 +7699,19 @@
         <v>72</v>
       </c>
       <c r="D27" s="16">
-        <f>IF($A27&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A27-Inputs!$B$78),0)</f>
+        <f>IF($A27&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A27-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E27" s="16">
-        <f>IF($A27&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A27-Inputs!$B$78),0)</f>
+        <f>IF($A27&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A27-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F27" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A27-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A27-Inputs!$B$80)</f>
         <v>697021.21959524159</v>
       </c>
       <c r="G27" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A27-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A27-Inputs!$B$80)</f>
         <v>255868.54896534188</v>
       </c>
       <c r="H27" s="16">
@@ -7693,15 +7727,15 @@
         <v>0</v>
       </c>
       <c r="K27" s="16">
-        <f>IF($A27&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A27-Inputs!$B$78),0)</f>
+        <f>IF($A27&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A27-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L27" s="16">
-        <f>IF(AND($A27&gt;=Inputs!$B$81,$A27&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A27-Inputs!$B$78),0)</f>
+        <f>IF(AND($A27&gt;=Inputs!$B$83,$A27&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A27-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M27" s="16">
-        <f>IF($A27&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A27-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A27&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A27&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A27-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A27&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1376396.3323652872</v>
       </c>
       <c r="N27" s="16">
@@ -7709,32 +7743,32 @@
         <v>359733.95381528605</v>
       </c>
       <c r="O27" s="16">
-        <f>IF($A27&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A27&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P27" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A27=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A27&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A27=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A27&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q27" s="16">
-        <f>D27+E27-H27-I27-J27-K27-L27-M27-N27+O27+P27-IF($A27&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D27+E27-H27-I27+J27-K27-L27-M27-N27+O27+P27-IF($A27&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1468130.2861805733</v>
       </c>
       <c r="R27" s="16">
         <f t="shared" si="3"/>
-        <v>18816679.019279551</v>
+        <v>20711268.788185466</v>
       </c>
       <c r="S27" s="16">
         <f>R27*Inputs!$B$35</f>
-        <v>903200.5929254184</v>
+        <v>994140.90183290234</v>
       </c>
       <c r="T27" s="16">
-        <f>IF($A27=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A27=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U27" s="16">
         <f t="shared" si="2"/>
-        <v>18251749.326024394</v>
+        <v>20237279.403837793</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -7750,19 +7784,19 @@
         <v>73</v>
       </c>
       <c r="D28" s="16">
-        <f>IF($A28&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A28-Inputs!$B$78),0)</f>
+        <f>IF($A28&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A28-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E28" s="16">
-        <f>IF($A28&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A28-Inputs!$B$78),0)</f>
+        <f>IF($A28&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A28-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F28" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A28-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A28-Inputs!$B$80)</f>
         <v>714446.75008512265</v>
       </c>
       <c r="G28" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A28-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A28-Inputs!$B$80)</f>
         <v>262265.26268947538</v>
       </c>
       <c r="H28" s="16">
@@ -7778,15 +7812,15 @@
         <v>0</v>
       </c>
       <c r="K28" s="16">
-        <f>IF($A28&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A28-Inputs!$B$78),0)</f>
+        <f>IF($A28&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A28-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L28" s="16">
-        <f>IF(AND($A28&gt;=Inputs!$B$81,$A28&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A28-Inputs!$B$78),0)</f>
+        <f>IF(AND($A28&gt;=Inputs!$B$83,$A28&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A28-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M28" s="16">
-        <f>IF($A28&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A28-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A28&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A28&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A28-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A28&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1410806.2406744193</v>
       </c>
       <c r="N28" s="16">
@@ -7794,32 +7828,32 @@
         <v>406746.4728097815</v>
       </c>
       <c r="O28" s="16">
-        <f>IF($A28&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A28&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P28" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A28=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A28&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A28=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A28&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q28" s="16">
-        <f>D28+E28-H28-I28-J28-K28-L28-M28-N28+O28+P28-IF($A28&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D28+E28-H28-I28+J28-K28-L28-M28-N28+O28+P28-IF($A28&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1549552.7134842009</v>
       </c>
       <c r="R28" s="16">
         <f t="shared" si="3"/>
-        <v>18251749.326024394</v>
+        <v>20237279.403837793</v>
       </c>
       <c r="S28" s="16">
         <f>R28*Inputs!$B$35</f>
-        <v>876083.9676491709</v>
+        <v>971389.41138421407</v>
       </c>
       <c r="T28" s="16">
-        <f>IF($A28=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A28=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U28" s="16">
         <f t="shared" si="2"/>
-        <v>17578280.580189362</v>
+        <v>19659116.101737805</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -7835,19 +7869,19 @@
         <v>74</v>
       </c>
       <c r="D29" s="16">
-        <f>IF($A29&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A29-Inputs!$B$78),0)</f>
+        <f>IF($A29&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A29-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E29" s="16">
-        <f>IF($A29&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A29-Inputs!$B$78),0)</f>
+        <f>IF($A29&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A29-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F29" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A29-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A29-Inputs!$B$80)</f>
         <v>732307.91883725056</v>
       </c>
       <c r="G29" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A29-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A29-Inputs!$B$80)</f>
         <v>268821.89425671223</v>
       </c>
       <c r="H29" s="16">
@@ -7863,15 +7897,15 @@
         <v>0</v>
       </c>
       <c r="K29" s="16">
-        <f>IF($A29&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A29-Inputs!$B$78),0)</f>
+        <f>IF($A29&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A29-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L29" s="16">
-        <f>IF(AND($A29&gt;=Inputs!$B$81,$A29&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A29-Inputs!$B$78),0)</f>
+        <f>IF(AND($A29&gt;=Inputs!$B$83,$A29&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A29-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M29" s="16">
-        <f>IF($A29&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A29-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A29&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A29&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A29-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A29&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1446076.3966912797</v>
       </c>
       <c r="N29" s="16">
@@ -7879,32 +7913,32 @@
         <v>458982.99832589674</v>
       </c>
       <c r="O29" s="16">
-        <f>IF($A29&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A29&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P29" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A29=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A29&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A29=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A29&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q29" s="16">
-        <f>D29+E29-H29-I29-J29-K29-L29-M29-N29+O29+P29-IF($A29&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D29+E29-H29-I29+J29-K29-L29-M29-N29+O29+P29-IF($A29&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1637059.3950171764</v>
       </c>
       <c r="R29" s="16">
         <f t="shared" si="3"/>
-        <v>17578280.580189362</v>
+        <v>19659116.101737805</v>
       </c>
       <c r="S29" s="16">
         <f>R29*Inputs!$B$35</f>
-        <v>843757.46784908941</v>
+        <v>943637.57288341469</v>
       </c>
       <c r="T29" s="16">
-        <f>IF($A29=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A29=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U29" s="16">
         <f t="shared" si="2"/>
-        <v>16784978.653021276</v>
+        <v>18965694.279604044</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -7920,19 +7954,19 @@
         <v>75</v>
       </c>
       <c r="D30" s="16">
-        <f>IF($A30&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A30-Inputs!$B$78),0)</f>
+        <f>IF($A30&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A30-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E30" s="16">
-        <f>IF($A30&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A30-Inputs!$B$78),0)</f>
+        <f>IF($A30&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A30-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F30" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A30-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A30-Inputs!$B$80)</f>
         <v>750615.61680818175</v>
       </c>
       <c r="G30" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A30-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A30-Inputs!$B$80)</f>
         <v>275542.44161313004</v>
       </c>
       <c r="H30" s="16">
@@ -7948,15 +7982,15 @@
         <v>0</v>
       </c>
       <c r="K30" s="16">
-        <f>IF($A30&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A30-Inputs!$B$78),0)</f>
+        <f>IF($A30&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A30-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="16">
-        <f>IF(AND($A30&gt;=Inputs!$B$81,$A30&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A30-Inputs!$B$78),0)</f>
+        <f>IF(AND($A30&gt;=Inputs!$B$83,$A30&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A30-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="16">
-        <f>IF($A30&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A30-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A30&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A30&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A30-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A30&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1482228.3066085614</v>
       </c>
       <c r="N30" s="16">
@@ -7964,32 +7998,32 @@
         <v>517009.46438955533</v>
       </c>
       <c r="O30" s="16">
-        <f>IF($A30&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A30&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P30" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A30=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A30&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A30=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A30&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q30" s="16">
-        <f>D30+E30-H30-I30-J30-K30-L30-M30-N30+O30+P30-IF($A30&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D30+E30-H30-I30+J30-K30-L30-M30-N30+O30+P30-IF($A30&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1731237.7709981168</v>
       </c>
       <c r="R30" s="16">
         <f t="shared" si="3"/>
-        <v>16784978.653021276</v>
+        <v>18965694.279604044</v>
       </c>
       <c r="S30" s="16">
         <f>R30*Inputs!$B$35</f>
-        <v>805678.97534502123</v>
+        <v>910353.32542099408</v>
       </c>
       <c r="T30" s="16">
-        <f>IF($A30=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A30=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U30" s="16">
         <f t="shared" si="2"/>
-        <v>15859419.857368182</v>
+        <v>18144809.834026922</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -8005,19 +8039,19 @@
         <v>76</v>
       </c>
       <c r="D31" s="16">
-        <f>IF($A31&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A31-Inputs!$B$78),0)</f>
+        <f>IF($A31&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A31-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E31" s="16">
-        <f>IF($A31&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A31-Inputs!$B$78),0)</f>
+        <f>IF($A31&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A31-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F31" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A31-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A31-Inputs!$B$80)</f>
         <v>769381.00722838636</v>
       </c>
       <c r="G31" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A31-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A31-Inputs!$B$80)</f>
         <v>282431.00265345827</v>
       </c>
       <c r="H31" s="16">
@@ -8033,15 +8067,15 @@
         <v>0</v>
       </c>
       <c r="K31" s="16">
-        <f>IF($A31&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A31-Inputs!$B$78),0)</f>
+        <f>IF($A31&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A31-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="16">
-        <f>IF(AND($A31&gt;=Inputs!$B$81,$A31&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A31-Inputs!$B$78),0)</f>
+        <f>IF(AND($A31&gt;=Inputs!$B$83,$A31&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A31-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="16">
-        <f>IF($A31&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A31-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A31&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A31&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A31-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A31&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1519284.0142737755</v>
       </c>
       <c r="N31" s="16">
@@ -8049,32 +8083,32 @@
         <v>575236.07736100326</v>
       </c>
       <c r="O31" s="16">
-        <f>IF($A31&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A31&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P31" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A31=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A31&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A31=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A31&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="16">
-        <f>D31+E31-H31-I31-J31-K31-L31-M31-N31+O31+P31-IF($A31&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D31+E31-H31-I31+J31-K31-L31-M31-N31+O31+P31-IF($A31&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1826520.0916347788</v>
       </c>
       <c r="R31" s="16">
         <f t="shared" si="3"/>
-        <v>15859419.857368182</v>
+        <v>18144809.834026922</v>
       </c>
       <c r="S31" s="16">
         <f>R31*Inputs!$B$35</f>
-        <v>761252.15315367281</v>
+        <v>870950.87203329219</v>
       </c>
       <c r="T31" s="16">
-        <f>IF($A31=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A31=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U31" s="16">
         <f t="shared" si="2"/>
-        <v>14794151.918887077</v>
+        <v>17189240.614425432</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -8090,19 +8124,19 @@
         <v>77</v>
       </c>
       <c r="D32" s="16">
-        <f>IF($A32&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A32-Inputs!$B$78),0)</f>
+        <f>IF($A32&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A32-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E32" s="16">
-        <f>IF($A32&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A32-Inputs!$B$78),0)</f>
+        <f>IF($A32&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A32-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F32" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A32-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A32-Inputs!$B$80)</f>
         <v>788615.5324090959</v>
       </c>
       <c r="G32" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A32-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A32-Inputs!$B$80)</f>
         <v>289491.77771979471</v>
       </c>
       <c r="H32" s="16">
@@ -8118,15 +8152,15 @@
         <v>0</v>
       </c>
       <c r="K32" s="16">
-        <f>IF($A32&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A32-Inputs!$B$78),0)</f>
+        <f>IF($A32&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A32-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="16">
-        <f>IF(AND($A32&gt;=Inputs!$B$81,$A32&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A32-Inputs!$B$78),0)</f>
+        <f>IF(AND($A32&gt;=Inputs!$B$83,$A32&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A32-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="16">
-        <f>IF($A32&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A32-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A32&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A32&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A32-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A32&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1557266.1146306198</v>
       </c>
       <c r="N32" s="16">
@@ -8134,32 +8168,32 @@
         <v>639254.84679752751</v>
       </c>
       <c r="O32" s="16">
-        <f>IF($A32&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A32&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P32" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A32=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A32&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A32=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A32&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q32" s="16">
-        <f>D32+E32-H32-I32-J32-K32-L32-M32-N32+O32+P32-IF($A32&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D32+E32-H32-I32+J32-K32-L32-M32-N32+O32+P32-IF($A32&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1928520.9614281473</v>
       </c>
       <c r="R32" s="16">
         <f t="shared" si="3"/>
-        <v>14794151.918887077</v>
+        <v>17189240.614425432</v>
       </c>
       <c r="S32" s="16">
         <f>R32*Inputs!$B$35</f>
-        <v>710119.29210657976</v>
+        <v>825083.54949242075</v>
       </c>
       <c r="T32" s="16">
-        <f>IF($A32=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A32=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U32" s="16">
         <f t="shared" si="2"/>
-        <v>13575750.24956551</v>
+        <v>16085803.202489708</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -8175,19 +8209,19 @@
         <v>78</v>
       </c>
       <c r="D33" s="16">
-        <f>IF($A33&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A33-Inputs!$B$78),0)</f>
+        <f>IF($A33&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A33-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E33" s="16">
-        <f>IF($A33&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A33-Inputs!$B$78),0)</f>
+        <f>IF($A33&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A33-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F33" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A33-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A33-Inputs!$B$80)</f>
         <v>808330.92071932333</v>
       </c>
       <c r="G33" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A33-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A33-Inputs!$B$80)</f>
         <v>296729.07216278958</v>
       </c>
       <c r="H33" s="16">
@@ -8203,15 +8237,15 @@
         <v>0</v>
       </c>
       <c r="K33" s="16">
-        <f>IF($A33&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A33-Inputs!$B$78),0)</f>
+        <f>IF($A33&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A33-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="16">
-        <f>IF(AND($A33&gt;=Inputs!$B$81,$A33&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A33-Inputs!$B$78),0)</f>
+        <f>IF(AND($A33&gt;=Inputs!$B$83,$A33&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A33-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="16">
-        <f>IF($A33&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A33-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A33&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A33&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A33-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A33&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1596197.7674963854</v>
       </c>
       <c r="N33" s="16">
@@ -8219,32 +8253,32 @@
         <v>709625.69004126394</v>
       </c>
       <c r="O33" s="16">
-        <f>IF($A33&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A33&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P33" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A33=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A33&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A33=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A33&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q33" s="16">
-        <f>D33+E33-H33-I33-J33-K33-L33-M33-N33+O33+P33-IF($A33&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D33+E33-H33-I33+J33-K33-L33-M33-N33+O33+P33-IF($A33&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2037823.4575376492</v>
       </c>
       <c r="R33" s="16">
         <f t="shared" si="3"/>
-        <v>13575750.24956551</v>
+        <v>16085803.202489708</v>
       </c>
       <c r="S33" s="16">
         <f>R33*Inputs!$B$35</f>
-        <v>651636.01197914453</v>
+        <v>772118.55371950602</v>
       </c>
       <c r="T33" s="16">
-        <f>IF($A33=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A33=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U33" s="16">
         <f t="shared" si="2"/>
-        <v>12189562.804007005</v>
+        <v>14820098.298671564</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -8260,19 +8294,19 @@
         <v>79</v>
       </c>
       <c r="D34" s="23">
-        <f>IF($A34&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A34-Inputs!$B$78),0)</f>
+        <f>IF($A34&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A34-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E34" s="23">
-        <f>IF($A34&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A34-Inputs!$B$78),0)</f>
+        <f>IF($A34&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A34-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F34" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A34-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A34-Inputs!$B$80)</f>
         <v>828539.19373730628</v>
       </c>
       <c r="G34" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A34-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A34-Inputs!$B$80)</f>
         <v>304147.29896685929</v>
       </c>
       <c r="H34" s="23">
@@ -8288,15 +8322,15 @@
         <v>0</v>
       </c>
       <c r="K34" s="23">
-        <f>IF($A34&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A34-Inputs!$B$78),0)</f>
+        <f>IF($A34&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A34-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="23">
-        <f>IF(AND($A34&gt;=Inputs!$B$81,$A34&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A34-Inputs!$B$78),0)</f>
+        <f>IF(AND($A34&gt;=Inputs!$B$83,$A34&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A34-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="23">
-        <f>IF($A34&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A34-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A34&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A34&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A34-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A34&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1636102.7116837946</v>
       </c>
       <c r="N34" s="23">
@@ -8304,32 +8338,32 @@
         <v>786962.25948538142</v>
       </c>
       <c r="O34" s="23">
-        <f>IF($A34&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A34&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P34" s="23">
-        <f>IF(AND(Inputs!$B$56=1,$A34=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A34&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A34=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A34&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q34" s="23">
-        <f>D34+E34-H34-I34-J34-K34-L34-M34-N34+O34+P34-IF($A34&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D34+E34-H34-I34+J34-K34-L34-M34-N34+O34+P34-IF($A34&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2155064.971169176</v>
       </c>
       <c r="R34" s="23">
         <f t="shared" si="3"/>
-        <v>12189562.804007005</v>
+        <v>14820098.298671564</v>
       </c>
       <c r="S34" s="23">
         <f>R34*Inputs!$B$35</f>
-        <v>585099.01459233626</v>
+        <v>711364.71833623503</v>
       </c>
       <c r="T34" s="23">
-        <f>IF($A34=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A34=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U34" s="23">
         <f t="shared" si="2"/>
-        <v>10619596.847430166</v>
+        <v>13376398.045838624</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -8345,19 +8379,19 @@
         <v>80</v>
       </c>
       <c r="D35" s="16">
-        <f>IF($A35&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A35-Inputs!$B$78),0)</f>
+        <f>IF($A35&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A35-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E35" s="16">
-        <f>IF($A35&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A35-Inputs!$B$78),0)</f>
+        <f>IF($A35&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A35-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F35" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A35-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A35-Inputs!$B$80)</f>
         <v>849252.67358073918</v>
       </c>
       <c r="G35" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A35-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A35-Inputs!$B$80)</f>
         <v>311750.98144103086</v>
       </c>
       <c r="H35" s="16">
@@ -8373,15 +8407,15 @@
         <v>0</v>
       </c>
       <c r="K35" s="16">
-        <f>IF($A35&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A35-Inputs!$B$78),0)</f>
+        <f>IF($A35&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A35-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L35" s="16">
-        <f>IF(AND($A35&gt;=Inputs!$B$81,$A35&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A35-Inputs!$B$78),0)</f>
+        <f>IF(AND($A35&gt;=Inputs!$B$83,$A35&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A35-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M35" s="16">
-        <f>IF($A35&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A35-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A35&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A35&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A35-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A35&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1677005.2794758901</v>
       </c>
       <c r="N35" s="16">
@@ -8389,32 +8423,32 @@
         <v>320636.7888385402</v>
       </c>
       <c r="O35" s="16">
-        <f>IF($A35&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A35&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P35" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A35=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A35&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A35=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A35&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q35" s="16">
-        <f>D35+E35-H35-I35-J35-K35-L35-M35-N35+O35+P35-IF($A35&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D35+E35-H35-I35+J35-K35-L35-M35-N35+O35+P35-IF($A35&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1729642.0683144303</v>
       </c>
       <c r="R35" s="16">
         <f t="shared" si="3"/>
-        <v>10619596.847430166</v>
+        <v>13376398.045838624</v>
       </c>
       <c r="S35" s="16">
         <f>R35*Inputs!$B$35</f>
-        <v>509740.64867664798</v>
+        <v>642067.10620025394</v>
       </c>
       <c r="T35" s="16">
-        <f>IF($A35=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A35=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U35" s="16">
         <f t="shared" si="2"/>
-        <v>9399695.4277923852</v>
+        <v>12288823.083724447</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -8430,19 +8464,19 @@
         <v>81</v>
       </c>
       <c r="D36" s="16">
-        <f>IF($A36&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A36-Inputs!$B$78),0)</f>
+        <f>IF($A36&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A36-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E36" s="16">
-        <f>IF($A36&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A36-Inputs!$B$78),0)</f>
+        <f>IF($A36&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A36-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F36" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A36-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A36-Inputs!$B$80)</f>
         <v>870483.99042025744</v>
       </c>
       <c r="G36" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A36-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A36-Inputs!$B$80)</f>
         <v>319544.75597705651</v>
       </c>
       <c r="H36" s="16">
@@ -8458,15 +8492,15 @@
         <v>0</v>
       </c>
       <c r="K36" s="16">
-        <f>IF($A36&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A36-Inputs!$B$78),0)</f>
+        <f>IF($A36&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A36-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L36" s="16">
-        <f>IF(AND($A36&gt;=Inputs!$B$81,$A36&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A36-Inputs!$B$78),0)</f>
+        <f>IF(AND($A36&gt;=Inputs!$B$83,$A36&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A36-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M36" s="16">
-        <f>IF($A36&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A36-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A36&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A36&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A36-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A36&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1718930.4114627868</v>
       </c>
       <c r="N36" s="16">
@@ -8474,32 +8508,32 @@
         <v>361131.66369229648</v>
       </c>
       <c r="O36" s="16">
-        <f>IF($A36&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A36&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P36" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A36=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A36&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A36=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A36&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q36" s="16">
-        <f>D36+E36-H36-I36-J36-K36-L36-M36-N36+O36+P36-IF($A36&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D36+E36-H36-I36+J36-K36-L36-M36-N36+O36+P36-IF($A36&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1812062.0751550833</v>
       </c>
       <c r="R36" s="16">
         <f t="shared" si="3"/>
-        <v>9399695.4277923852</v>
+        <v>12288823.083724447</v>
       </c>
       <c r="S36" s="16">
         <f>R36*Inputs!$B$35</f>
-        <v>451185.38053403451</v>
+        <v>589863.5080187734</v>
       </c>
       <c r="T36" s="16">
-        <f>IF($A36=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A36=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U36" s="16">
         <f t="shared" si="2"/>
-        <v>8038818.7331713364</v>
+        <v>11066624.516588137</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -8515,19 +8549,19 @@
         <v>82</v>
       </c>
       <c r="D37" s="16">
-        <f>IF($A37&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A37-Inputs!$B$78),0)</f>
+        <f>IF($A37&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A37-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E37" s="16">
-        <f>IF($A37&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A37-Inputs!$B$78),0)</f>
+        <f>IF($A37&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A37-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F37" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A37-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A37-Inputs!$B$80)</f>
         <v>892246.09018076386</v>
       </c>
       <c r="G37" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A37-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A37-Inputs!$B$80)</f>
         <v>327533.37487648294</v>
       </c>
       <c r="H37" s="16">
@@ -8543,15 +8577,15 @@
         <v>0</v>
       </c>
       <c r="K37" s="16">
-        <f>IF($A37&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A37-Inputs!$B$78),0)</f>
+        <f>IF($A37&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A37-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L37" s="16">
-        <f>IF(AND($A37&gt;=Inputs!$B$81,$A37&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A37-Inputs!$B$78),0)</f>
+        <f>IF(AND($A37&gt;=Inputs!$B$83,$A37&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A37-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M37" s="16">
-        <f>IF($A37&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A37-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A37&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A37&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A37-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A37&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1761903.6717493564</v>
       </c>
       <c r="N37" s="16">
@@ -8559,32 +8593,32 @@
         <v>405742.17836414505</v>
       </c>
       <c r="O37" s="16">
-        <f>IF($A37&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A37&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P37" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A37=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A37&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A37=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A37&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q37" s="16">
-        <f>D37+E37-H37-I37-J37-K37-L37-M37-N37+O37+P37-IF($A37&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D37+E37-H37-I37+J37-K37-L37-M37-N37+O37+P37-IF($A37&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1899645.8501135013</v>
       </c>
       <c r="R37" s="16">
         <f t="shared" si="3"/>
-        <v>8038818.7331713364</v>
+        <v>11066624.516588137</v>
       </c>
       <c r="S37" s="16">
         <f>R37*Inputs!$B$35</f>
-        <v>385863.29919222416</v>
+        <v>531197.97679623053</v>
       </c>
       <c r="T37" s="16">
-        <f>IF($A37=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A37=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U37" s="16">
         <f t="shared" si="2"/>
-        <v>6525036.1822500583</v>
+        <v>9698176.6432708651</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -8600,19 +8634,19 @@
         <v>83</v>
       </c>
       <c r="D38" s="16">
-        <f>IF($A38&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A38-Inputs!$B$78),0)</f>
+        <f>IF($A38&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A38-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E38" s="16">
-        <f>IF($A38&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A38-Inputs!$B$78),0)</f>
+        <f>IF($A38&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A38-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F38" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A38-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A38-Inputs!$B$80)</f>
         <v>914552.24243528291</v>
       </c>
       <c r="G38" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A38-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A38-Inputs!$B$80)</f>
         <v>335721.709248395</v>
       </c>
       <c r="H38" s="16">
@@ -8628,15 +8662,15 @@
         <v>0</v>
       </c>
       <c r="K38" s="16">
-        <f>IF($A38&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A38-Inputs!$B$78),0)</f>
+        <f>IF($A38&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A38-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L38" s="16">
-        <f>IF(AND($A38&gt;=Inputs!$B$81,$A38&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A38-Inputs!$B$78),0)</f>
+        <f>IF(AND($A38&gt;=Inputs!$B$83,$A38&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A38-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M38" s="16">
-        <f>IF($A38&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A38-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A38&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A38&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A38-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A38&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1805951.2635430903</v>
       </c>
       <c r="N38" s="16">
@@ -8644,32 +8678,32 @@
         <v>454867.73190867808</v>
       </c>
       <c r="O38" s="16">
-        <f>IF($A38&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A38&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P38" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A38=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A38&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A38=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A38&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q38" s="16">
-        <f>D38+E38-H38-I38-J38-K38-L38-M38-N38+O38+P38-IF($A38&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D38+E38-H38-I38+J38-K38-L38-M38-N38+O38+P38-IF($A38&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-1992818.9954517684</v>
       </c>
       <c r="R38" s="16">
         <f t="shared" si="3"/>
-        <v>6525036.1822500583</v>
+        <v>9698176.6432708651</v>
       </c>
       <c r="S38" s="16">
         <f>R38*Inputs!$B$35</f>
-        <v>313201.73674800282</v>
+        <v>465512.47887700156</v>
       </c>
       <c r="T38" s="16">
-        <f>IF($A38=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A38=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U38" s="16">
         <f t="shared" si="2"/>
-        <v>4845418.9235462919</v>
+        <v>8170870.1266960986</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -8685,19 +8719,19 @@
         <v>84</v>
       </c>
       <c r="D39" s="16">
-        <f>IF($A39&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A39-Inputs!$B$78),0)</f>
+        <f>IF($A39&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A39-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E39" s="16">
-        <f>IF($A39&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A39-Inputs!$B$78),0)</f>
+        <f>IF($A39&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A39-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F39" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A39-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A39-Inputs!$B$80)</f>
         <v>937416.04849616485</v>
       </c>
       <c r="G39" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A39-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A39-Inputs!$B$80)</f>
         <v>344114.75197960483</v>
       </c>
       <c r="H39" s="16">
@@ -8713,15 +8747,15 @@
         <v>0</v>
       </c>
       <c r="K39" s="16">
-        <f>IF($A39&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A39-Inputs!$B$78),0)</f>
+        <f>IF($A39&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A39-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="16">
-        <f>IF(AND($A39&gt;=Inputs!$B$81,$A39&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A39-Inputs!$B$78),0)</f>
+        <f>IF(AND($A39&gt;=Inputs!$B$83,$A39&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A39-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="16">
-        <f>IF($A39&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A39-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A39&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A39&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A39-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A39&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1851100.0451316673</v>
       </c>
       <c r="N39" s="16">
@@ -8729,32 +8763,32 @@
         <v>508946.03882352327</v>
       </c>
       <c r="O39" s="16">
-        <f>IF($A39&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A39&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P39" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A39=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A39&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A39=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A39&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q39" s="16">
-        <f>D39+E39-H39-I39-J39-K39-L39-M39-N39+O39+P39-IF($A39&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D39+E39-H39-I39+J39-K39-L39-M39-N39+O39+P39-IF($A39&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2092046.0839551906</v>
       </c>
       <c r="R39" s="16">
         <f t="shared" si="3"/>
-        <v>4845418.9235462919</v>
+        <v>8170870.1266960986</v>
       </c>
       <c r="S39" s="16">
         <f>R39*Inputs!$B$35</f>
-        <v>232580.10833022202</v>
+        <v>392201.76608141273</v>
       </c>
       <c r="T39" s="16">
-        <f>IF($A39=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A39=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U39" s="16">
         <f t="shared" si="2"/>
-        <v>2985952.9479213231</v>
+        <v>6471025.8088223208</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -8770,19 +8804,19 @@
         <v>85</v>
       </c>
       <c r="D40" s="16">
-        <f>IF($A40&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A40-Inputs!$B$78),0)</f>
+        <f>IF($A40&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A40-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E40" s="16">
-        <f>IF($A40&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A40-Inputs!$B$78),0)</f>
+        <f>IF($A40&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A40-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F40" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A40-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A40-Inputs!$B$80)</f>
         <v>960851.4497085691</v>
       </c>
       <c r="G40" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A40-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A40-Inputs!$B$80)</f>
         <v>352717.62077909498</v>
       </c>
       <c r="H40" s="16">
@@ -8798,15 +8832,15 @@
         <v>0</v>
       </c>
       <c r="K40" s="16">
-        <f>IF($A40&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A40-Inputs!$B$78),0)</f>
+        <f>IF($A40&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A40-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="16">
-        <f>IF(AND($A40&gt;=Inputs!$B$81,$A40&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A40-Inputs!$B$78),0)</f>
+        <f>IF(AND($A40&gt;=Inputs!$B$83,$A40&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A40-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="16">
-        <f>IF($A40&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A40-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A40&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A40&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A40-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A40&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1897377.5462599592</v>
       </c>
       <c r="N40" s="16">
@@ -8814,32 +8848,32 @@
         <v>568456.79382758285</v>
       </c>
       <c r="O40" s="16">
-        <f>IF($A40&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A40&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P40" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A40=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A40&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A40=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A40&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q40" s="16">
-        <f>D40+E40-H40-I40-J40-K40-L40-M40-N40+O40+P40-IF($A40&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D40+E40-H40-I40+J40-K40-L40-M40-N40+O40+P40-IF($A40&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2197834.3400875423</v>
       </c>
       <c r="R40" s="16">
         <f t="shared" si="3"/>
-        <v>2985952.9479213231</v>
+        <v>6471025.8088223208</v>
       </c>
       <c r="S40" s="16">
         <f>R40*Inputs!$B$35</f>
-        <v>143325.74150022352</v>
+        <v>310609.23882347142</v>
       </c>
       <c r="T40" s="16">
-        <f>IF($A40=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A40=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U40" s="16">
         <f t="shared" si="2"/>
-        <v>931444.34933400434</v>
+        <v>4583800.7075582501</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -8855,19 +8889,19 @@
         <v>86</v>
       </c>
       <c r="D41" s="16">
-        <f>IF($A41&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A41-Inputs!$B$78),0)</f>
+        <f>IF($A41&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A41-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E41" s="16">
-        <f>IF($A41&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A41-Inputs!$B$78),0)</f>
+        <f>IF($A41&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A41-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F41" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A41-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A41-Inputs!$B$80)</f>
         <v>984872.73595128313</v>
       </c>
       <c r="G41" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A41-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A41-Inputs!$B$80)</f>
         <v>361535.56129857228</v>
       </c>
       <c r="H41" s="16">
@@ -8883,15 +8917,15 @@
         <v>0</v>
       </c>
       <c r="K41" s="16">
-        <f>IF($A41&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A41-Inputs!$B$78),0)</f>
+        <f>IF($A41&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A41-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L41" s="16">
-        <f>IF(AND($A41&gt;=Inputs!$B$81,$A41&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A41-Inputs!$B$78),0)</f>
+        <f>IF(AND($A41&gt;=Inputs!$B$83,$A41&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A41-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M41" s="16">
-        <f>IF($A41&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A41-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A41&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A41&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A41-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A41&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1944811.9849164579</v>
       </c>
       <c r="N41" s="16">
@@ -8899,32 +8933,32 @@
         <v>633925.68689425697</v>
       </c>
       <c r="O41" s="16">
-        <f>IF($A41&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A41&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P41" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A41=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A41&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A41=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A41&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q41" s="16">
-        <f>D41+E41-H41-I41-J41-K41-L41-M41-N41+O41+P41-IF($A41&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D41+E41-H41-I41+J41-K41-L41-M41-N41+O41+P41-IF($A41&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2310737.671810715</v>
       </c>
       <c r="R41" s="16">
         <f t="shared" si="3"/>
-        <v>931444.34933400434</v>
+        <v>4583800.7075582501</v>
       </c>
       <c r="S41" s="16">
         <f>R41*Inputs!$B$35</f>
-        <v>44709.32876803221</v>
+        <v>220022.433962796</v>
       </c>
       <c r="T41" s="16">
-        <f>IF($A41=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A41=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U41" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2493085.4697103309</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -8940,19 +8974,19 @@
         <v>87</v>
       </c>
       <c r="D42" s="16">
-        <f>IF($A42&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A42-Inputs!$B$78),0)</f>
+        <f>IF($A42&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A42-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E42" s="16">
-        <f>IF($A42&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A42-Inputs!$B$78),0)</f>
+        <f>IF($A42&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A42-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F42" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A42-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A42-Inputs!$B$80)</f>
         <v>1009494.5543500651</v>
       </c>
       <c r="G42" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A42-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A42-Inputs!$B$80)</f>
         <v>370573.95033103653</v>
       </c>
       <c r="H42" s="16">
@@ -8968,15 +9002,15 @@
         <v>0</v>
       </c>
       <c r="K42" s="16">
-        <f>IF($A42&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A42-Inputs!$B$78),0)</f>
+        <f>IF($A42&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A42-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L42" s="16">
-        <f>IF(AND($A42&gt;=Inputs!$B$81,$A42&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A42-Inputs!$B$78),0)</f>
+        <f>IF(AND($A42&gt;=Inputs!$B$83,$A42&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A42-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M42" s="16">
-        <f>IF($A42&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A42-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A42&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A42&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A42-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A42&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>1993432.2845393689</v>
       </c>
       <c r="N42" s="16">
@@ -8984,32 +9018,32 @@
         <v>705928.80200788286</v>
       </c>
       <c r="O42" s="16">
-        <f>IF($A42&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A42&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P42" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A42=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A42&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A42=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A42&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q42" s="16">
-        <f>D42+E42-H42-I42-J42-K42-L42-M42-N42+O42+P42-IF($A42&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D42+E42-H42-I42+J42-K42-L42-M42-N42+O42+P42-IF($A42&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2431361.0865472518</v>
       </c>
       <c r="R42" s="16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2493085.4697103309</v>
       </c>
       <c r="S42" s="16">
         <f>R42*Inputs!$B$35</f>
-        <v>0</v>
+        <v>119668.10254609589</v>
       </c>
       <c r="T42" s="16">
-        <f>IF($A42=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A42=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U42" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>181392.485709175</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -9025,19 +9059,19 @@
         <v>88</v>
       </c>
       <c r="D43" s="16">
-        <f>IF($A43&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A43-Inputs!$B$78),0)</f>
+        <f>IF($A43&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A43-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E43" s="16">
-        <f>IF($A43&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A43-Inputs!$B$78),0)</f>
+        <f>IF($A43&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A43-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F43" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A43-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A43-Inputs!$B$80)</f>
         <v>1034731.9182088168</v>
       </c>
       <c r="G43" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A43-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A43-Inputs!$B$80)</f>
         <v>379838.2990893125</v>
       </c>
       <c r="H43" s="16">
@@ -9053,15 +9087,15 @@
         <v>0</v>
       </c>
       <c r="K43" s="16">
-        <f>IF($A43&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A43-Inputs!$B$78),0)</f>
+        <f>IF($A43&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A43-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="16">
-        <f>IF(AND($A43&gt;=Inputs!$B$81,$A43&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A43-Inputs!$B$78),0)</f>
+        <f>IF(AND($A43&gt;=Inputs!$B$83,$A43&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A43-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="16">
-        <f>IF($A43&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A43-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A43&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A43&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A43-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A43&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2043268.0916528534</v>
       </c>
       <c r="N43" s="16">
@@ -9069,27 +9103,27 @@
         <v>785097.43630947405</v>
       </c>
       <c r="O43" s="16">
-        <f>IF($A43&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A43&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P43" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A43=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A43&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A43=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A43&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q43" s="16">
-        <f>D43+E43-H43-I43-J43-K43-L43-M43-N43+O43+P43-IF($A43&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D43+E43-H43-I43+J43-K43-L43-M43-N43+O43+P43-IF($A43&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2560365.5279623275</v>
       </c>
       <c r="R43" s="16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>181392.485709175</v>
       </c>
       <c r="S43" s="16">
         <f>R43*Inputs!$B$35</f>
-        <v>0</v>
+        <v>8706.8393140404005</v>
       </c>
       <c r="T43" s="16">
-        <f>IF($A43=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A43=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U43" s="16">
@@ -9110,19 +9144,19 @@
         <v>89</v>
       </c>
       <c r="D44" s="23">
-        <f>IF($A44&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A44-Inputs!$B$78),0)</f>
+        <f>IF($A44&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A44-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E44" s="23">
-        <f>IF($A44&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A44-Inputs!$B$78),0)</f>
+        <f>IF($A44&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A44-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F44" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A44-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A44-Inputs!$B$80)</f>
         <v>1060600.2161640371</v>
       </c>
       <c r="G44" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A44-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A44-Inputs!$B$80)</f>
         <v>389334.25656654523</v>
       </c>
       <c r="H44" s="23">
@@ -9138,15 +9172,15 @@
         <v>0</v>
       </c>
       <c r="K44" s="23">
-        <f>IF($A44&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A44-Inputs!$B$78),0)</f>
+        <f>IF($A44&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A44-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L44" s="23">
-        <f>IF(AND($A44&gt;=Inputs!$B$81,$A44&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A44-Inputs!$B$78),0)</f>
+        <f>IF(AND($A44&gt;=Inputs!$B$83,$A44&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A44-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M44" s="23">
-        <f>IF($A44&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A44-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A44&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A44&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A44-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A44&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2094349.7939441744</v>
       </c>
       <c r="N44" s="23">
@@ -9154,15 +9188,15 @@
         <v>872123.3798012404</v>
       </c>
       <c r="O44" s="23">
-        <f>IF($A44&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A44&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P44" s="23">
-        <f>IF(AND(Inputs!$B$56=1,$A44=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A44&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A44=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A44&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q44" s="23">
-        <f>D44+E44-H44-I44-J44-K44-L44-M44-N44+O44+P44-IF($A44&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D44+E44-H44-I44+J44-K44-L44-M44-N44+O44+P44-IF($A44&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2698473.1737454147</v>
       </c>
       <c r="R44" s="23">
@@ -9174,7 +9208,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="23">
-        <f>IF($A44=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A44=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U44" s="23">
@@ -9195,19 +9229,19 @@
         <v>90</v>
       </c>
       <c r="D45" s="16">
-        <f>IF($A45&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A45-Inputs!$B$78),0)</f>
+        <f>IF($A45&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A45-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E45" s="16">
-        <f>IF($A45&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A45-Inputs!$B$78),0)</f>
+        <f>IF($A45&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A45-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F45" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A45-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A45-Inputs!$B$80)</f>
         <v>1087115.2215681379</v>
       </c>
       <c r="G45" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A45-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A45-Inputs!$B$80)</f>
         <v>399067.61298070889</v>
       </c>
       <c r="H45" s="16">
@@ -9223,15 +9257,15 @@
         <v>0</v>
       </c>
       <c r="K45" s="16">
-        <f>IF($A45&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A45-Inputs!$B$78),0)</f>
+        <f>IF($A45&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A45-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L45" s="16">
-        <f>IF(AND($A45&gt;=Inputs!$B$81,$A45&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A45-Inputs!$B$78),0)</f>
+        <f>IF(AND($A45&gt;=Inputs!$B$83,$A45&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A45-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M45" s="16">
-        <f>IF($A45&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A45-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A45&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A45&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A45-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A45&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2146708.5387927787</v>
       </c>
       <c r="N45" s="16">
@@ -9239,15 +9273,15 @@
         <v>967764.69961750961</v>
       </c>
       <c r="O45" s="16">
-        <f>IF($A45&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A45&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P45" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A45=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A45&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A45=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A45&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q45" s="16">
-        <f>D45+E45-H45-I45-J45-K45-L45-M45-N45+O45+P45-IF($A45&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D45+E45-H45-I45+J45-K45-L45-M45-N45+O45+P45-IF($A45&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-2846473.2384102885</v>
       </c>
       <c r="R45" s="16">
@@ -9259,7 +9293,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="16">
-        <f>IF($A45=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A45=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U45" s="16">
@@ -9280,19 +9314,19 @@
         <v>91</v>
       </c>
       <c r="D46" s="16">
-        <f>IF($A46&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A46-Inputs!$B$78),0)</f>
+        <f>IF($A46&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A46-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E46" s="16">
-        <f>IF($A46&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A46-Inputs!$B$78),0)</f>
+        <f>IF($A46&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A46-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F46" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A46-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A46-Inputs!$B$80)</f>
         <v>1114293.1021073414</v>
       </c>
       <c r="G46" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A46-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A46-Inputs!$B$80)</f>
         <v>409044.30330522655</v>
       </c>
       <c r="H46" s="16">
@@ -9308,15 +9342,15 @@
         <v>0</v>
       </c>
       <c r="K46" s="16">
-        <f>IF($A46&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A46-Inputs!$B$78),0)</f>
+        <f>IF($A46&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A46-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="16">
-        <f>IF(AND($A46&gt;=Inputs!$B$81,$A46&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A46-Inputs!$B$78),0)</f>
+        <f>IF(AND($A46&gt;=Inputs!$B$83,$A46&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A46-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="16">
-        <f>IF($A46&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A46-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A46&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A46&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A46-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A46&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2200376.2522625979</v>
       </c>
       <c r="N46" s="16">
@@ -9324,15 +9358,15 @@
         <v>1072852.0770745291</v>
       </c>
       <c r="O46" s="16">
-        <f>IF($A46&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A46&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P46" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A46=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A46&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A46=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A46&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q46" s="16">
-        <f>D46+E46-H46-I46-J46-K46-L46-M46-N46+O46+P46-IF($A46&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D46+E46-H46-I46+J46-K46-L46-M46-N46+O46+P46-IF($A46&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-3005228.329337127</v>
       </c>
       <c r="R46" s="16">
@@ -9344,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="16">
-        <f>IF($A46=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A46=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U46" s="16">
@@ -9365,19 +9399,19 @@
         <v>92</v>
       </c>
       <c r="D47" s="16">
-        <f>IF($A47&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A47-Inputs!$B$78),0)</f>
+        <f>IF($A47&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A47-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E47" s="16">
-        <f>IF($A47&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A47-Inputs!$B$78),0)</f>
+        <f>IF($A47&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A47-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F47" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A47-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A47-Inputs!$B$80)</f>
         <v>1142150.4296600248</v>
       </c>
       <c r="G47" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A47-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A47-Inputs!$B$80)</f>
         <v>419270.41088785726</v>
       </c>
       <c r="H47" s="16">
@@ -9393,15 +9427,15 @@
         <v>0</v>
       </c>
       <c r="K47" s="16">
-        <f>IF($A47&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A47-Inputs!$B$78),0)</f>
+        <f>IF($A47&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A47-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="16">
-        <f>IF(AND($A47&gt;=Inputs!$B$81,$A47&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A47-Inputs!$B$78),0)</f>
+        <f>IF(AND($A47&gt;=Inputs!$B$83,$A47&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A47-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="16">
-        <f>IF($A47&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A47-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A47&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A47&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A47-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A47&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2255385.6585691632</v>
       </c>
       <c r="N47" s="16">
@@ -9409,15 +9443,15 @@
         <v>1188295.7503182599</v>
       </c>
       <c r="O47" s="16">
-        <f>IF($A47&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A47&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P47" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A47=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A47&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A47=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A47&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q47" s="16">
-        <f>D47+E47-H47-I47-J47-K47-L47-M47-N47+O47+P47-IF($A47&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D47+E47-H47-I47+J47-K47-L47-M47-N47+O47+P47-IF($A47&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-3175681.4088874231</v>
       </c>
       <c r="R47" s="16">
@@ -9429,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="16">
-        <f>IF($A47=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A47=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U47" s="16">
@@ -9450,19 +9484,19 @@
         <v>93</v>
       </c>
       <c r="D48" s="16">
-        <f>IF($A48&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A48-Inputs!$B$78),0)</f>
+        <f>IF($A48&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A48-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E48" s="16">
-        <f>IF($A48&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A48-Inputs!$B$78),0)</f>
+        <f>IF($A48&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A48-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F48" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A48-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A48-Inputs!$B$80)</f>
         <v>1170704.1904015252</v>
       </c>
       <c r="G48" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A48-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A48-Inputs!$B$80)</f>
         <v>429752.17116005358</v>
       </c>
       <c r="H48" s="16">
@@ -9478,15 +9512,15 @@
         <v>0</v>
       </c>
       <c r="K48" s="16">
-        <f>IF($A48&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A48-Inputs!$B$78),0)</f>
+        <f>IF($A48&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A48-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L48" s="16">
-        <f>IF(AND($A48&gt;=Inputs!$B$81,$A48&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A48-Inputs!$B$78),0)</f>
+        <f>IF(AND($A48&gt;=Inputs!$B$83,$A48&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A48-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M48" s="16">
-        <f>IF($A48&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A48-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A48&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A48&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A48-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A48&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2311770.3000333915</v>
       </c>
       <c r="N48" s="16">
@@ -9494,15 +9528,15 @@
         <v>1315093.1204360425</v>
       </c>
       <c r="O48" s="16">
-        <f>IF($A48&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A48&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P48" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A48=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A48&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A48=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A48&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q48" s="16">
-        <f>D48+E48-H48-I48-J48-K48-L48-M48-N48+O48+P48-IF($A48&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D48+E48-H48-I48+J48-K48-L48-M48-N48+O48+P48-IF($A48&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-3358863.420469434</v>
       </c>
       <c r="R48" s="16">
@@ -9514,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="16">
-        <f>IF($A48=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A48=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U48" s="16">
@@ -9535,19 +9569,19 @@
         <v>94</v>
       </c>
       <c r="D49" s="16">
-        <f>IF($A49&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A49-Inputs!$B$78),0)</f>
+        <f>IF($A49&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A49-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E49" s="16">
-        <f>IF($A49&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A49-Inputs!$B$78),0)</f>
+        <f>IF($A49&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A49-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F49" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A49-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A49-Inputs!$B$80)</f>
         <v>1199971.7951615634</v>
       </c>
       <c r="G49" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A49-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A49-Inputs!$B$80)</f>
         <v>440495.97543905495</v>
       </c>
       <c r="H49" s="16">
@@ -9563,15 +9597,15 @@
         <v>0</v>
       </c>
       <c r="K49" s="16">
-        <f>IF($A49&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A49-Inputs!$B$78),0)</f>
+        <f>IF($A49&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A49-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L49" s="16">
-        <f>IF(AND($A49&gt;=Inputs!$B$81,$A49&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A49-Inputs!$B$78),0)</f>
+        <f>IF(AND($A49&gt;=Inputs!$B$83,$A49&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A49-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M49" s="16">
-        <f>IF($A49&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A49-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A49&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A49&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A49-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A49&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2369564.5575342267</v>
       </c>
       <c r="N49" s="16">
@@ -9579,15 +9613,15 @@
         <v>1454337.0844270117</v>
       </c>
       <c r="O49" s="16">
-        <f>IF($A49&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A49&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P49" s="16">
-        <f>IF(AND(Inputs!$B$56=1,$A49=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A49&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A49=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A49&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q49" s="16">
-        <f>D49+E49-H49-I49-J49-K49-L49-M49-N49+O49+P49-IF($A49&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D49+E49-H49-I49+J49-K49-L49-M49-N49+O49+P49-IF($A49&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-3555901.6419612383</v>
       </c>
       <c r="R49" s="16">
@@ -9599,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="16">
-        <f>IF($A49=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A49=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U49" s="16">
@@ -9620,19 +9654,19 @@
         <v>95</v>
       </c>
       <c r="D50" s="23">
-        <f>IF($A50&lt;Inputs!$B$79,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A50-Inputs!$B$78),0)</f>
+        <f>IF($A50&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A50-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="E50" s="23">
-        <f>IF($A50&lt;Inputs!$B$80,Inputs!$B$29*(1+Inputs!$B$7)^($A50-Inputs!$B$78),0)</f>
+        <f>IF($A50&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A50-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="F50" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A50-Inputs!$B$78)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A50-Inputs!$B$80)</f>
         <v>1229971.0900406023</v>
       </c>
       <c r="G50" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A50-Inputs!$B$78)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A50-Inputs!$B$80)</f>
         <v>451508.37482503121</v>
       </c>
       <c r="H50" s="23">
@@ -9648,15 +9682,15 @@
         <v>0</v>
       </c>
       <c r="K50" s="23">
-        <f>IF($A50&lt;Inputs!$B$79,Inputs!$B$31*(1+Inputs!$B$5)^($A50-Inputs!$B$78),0)</f>
+        <f>IF($A50&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A50-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="L50" s="23">
-        <f>IF(AND($A50&gt;=Inputs!$B$81,$A50&lt;Inputs!$B$81+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A50-Inputs!$B$78),0)</f>
+        <f>IF(AND($A50&gt;=Inputs!$B$83,$A50&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A50-Inputs!$B$80),0)</f>
         <v>0</v>
       </c>
       <c r="M50" s="23">
-        <f>IF($A50&gt;=Inputs!$B$79,Inputs!$B$32*(1+Inputs!$B$5)^($A50-Inputs!$B$78)*IF(AND(Inputs!$B$53=1,$A50&gt;Inputs!$B$82),Inputs!$B$52,1),0)</f>
+        <f>IF($A50&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A50-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A50&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
         <v>2428803.6714725816</v>
       </c>
       <c r="N50" s="23">
@@ -9664,15 +9698,15 @@
         <v>1607225.1644833817</v>
       </c>
       <c r="O50" s="23">
-        <f>IF($A50&gt;=Inputs!$B$79,Inputs!$B$39,0)</f>
+        <f>IF($A50&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
         <v>268000</v>
       </c>
       <c r="P50" s="23">
-        <f>IF(AND(Inputs!$B$56=1,$A50=Inputs!$B$55),Inputs!$B$54,0)+IF(AND(Inputs!$B$59=1,$A50&gt;=Inputs!$B$58),Inputs!$B$57,0)</f>
+        <f>IF(AND(Inputs!$B$58=1,$A50=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A50&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
         <v>0</v>
       </c>
       <c r="Q50" s="23">
-        <f>D50+E50-H50-I50-J50-K50-L50-M50-N50+O50+P50-IF($A50&lt;Inputs!$B$79,Inputs!$B$42,0)</f>
+        <f>D50+E50-H50-I50+J50-K50-L50-M50-N50+O50+P50-IF($A50&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
         <v>-3768028.8359559635</v>
       </c>
       <c r="R50" s="23">
@@ -9684,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="23">
-        <f>IF($A50=Inputs!$B$79,-Inputs!$B$38,0)</f>
+        <f>IF($A50=Inputs!$B$81,-Inputs!$B$38,0)</f>
         <v>0</v>
       </c>
       <c r="U50" s="23">
@@ -9708,23 +9742,23 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B5" s="24">
         <f>BalanceSheet!B33</f>
@@ -9733,7 +9767,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B6" s="24">
         <f>BalanceSheet!$B$37</f>
@@ -9742,7 +9776,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B7" s="24">
         <f>Tax!B27-Inputs!$B$42</f>
@@ -9751,7 +9785,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B8" s="25">
         <f>BalanceSheet!B7/(Inputs!$B$31/12)</f>
@@ -9760,13 +9794,13 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B10" s="24">
         <f>Tax!B15</f>
@@ -9775,7 +9809,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B11" s="24">
         <f>Tax!B16</f>
@@ -9784,7 +9818,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B12" s="24">
         <f>Tax!B17</f>
@@ -9793,49 +9827,49 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B14" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$79,Projection!A:A,0))</f>
-        <v>19251346.781452805</v>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$81,Projection!A:A,0))</f>
+        <v>20348200.017858323</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B15" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$83,Projection!A:A,0))</f>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$85,Projection!A:A,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B16" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$84,Projection!A:A,0))</f>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$86,Projection!A:A,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B17" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$79,Projection!A:A,0))/(1+Inputs!$B$5)^(Inputs!$B$79-Inputs!$B$78)</f>
-        <v>14672313.499257222</v>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$81,Projection!A:A,0))/(1+Inputs!$B$5)^(Inputs!$B$81-Inputs!$B$80)</f>
+        <v>15508274.470191544</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B18" s="24">
         <f>Inputs!$B$32*(1-(1+0.02)^-29)/0.02</f>
@@ -9844,49 +9878,49 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B19" s="26">
         <f>IFERROR(INDEX(Projection!A4:A50,MATCH(0,Projection!U4:U50,0)),0)</f>
-        <v>2063</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B20" s="26">
         <f>IF(B19=0,"lasts",B19-1977)</f>
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B21" s="27" t="str">
-        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$83,Projection!A:A,0))&gt;0,"YES","NO")</f>
+        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$85,Projection!A:A,0))&gt;0,"YES","NO")</f>
         <v>NO</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B22" s="27" t="str">
-        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$84,Projection!A:A,0))&gt;0,"YES","NO")</f>
+        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$86,Projection!A:A,0))&gt;0,"YES","NO")</f>
         <v>NO</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B23" s="4"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B24" s="24">
         <f>SUM(Projection!L4:L50)</f>
@@ -9895,28 +9929,28 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B25" s="24">
-        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$79,Projection!A:A,0))</f>
+        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$81,Projection!A:A,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B26" s="24">
-        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$83,Projection!A:A,0))</f>
+        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$85,Projection!A:A,0))</f>
         <v>872123.3798012404</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B27" s="24">
-        <f>SUMPRODUCT((Projection!A4:A50&lt;=Inputs!$B$83)*Projection!N4:N50)</f>
+        <f>SUMPRODUCT((Projection!A4:A50&lt;=Inputs!$B$85)*Projection!N4:N50)</f>
         <v>11842102.254778726</v>
       </c>
     </row>

--- a/model/wong_model.xlsx
+++ b/model/wong_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\finplan\finplan\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECFA40C-1A85-43A1-8458-488055C4C821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8E23D6-C4E4-4BE9-9ED1-5271BC2B6A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -235,7 +235,7 @@
     <t>Insurance premiums (Lookbua, TBC)</t>
   </si>
   <si>
-    <t>parents' new cover, avg a year to 2036: DI 37K, term life 7K, CI 2.75M each ~96K avg (Bowtie Aug 2026), VHIS 15K. Paid until Adrian retires</t>
+    <t>parents' new cover, avg a year to 2036: DI 37K, term life 7K, CI 1.5M each ~55K avg (needs-based, Bowtie Aug 2026), VHIS 15K. Paid until Adrian retires</t>
   </si>
   <si>
     <t>MEDICAL (methodology §1)</t>
@@ -1693,7 +1693,7 @@
         <v>64</v>
       </c>
       <c r="B42" s="8">
-        <v>159000</v>
+        <v>113600</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>65</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="Q4" s="16">
         <f>D4+E4-H4-I4+J4-K4-L4-M4-N4+O4+P4-IF($A4&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>631230</v>
+        <v>676630</v>
       </c>
       <c r="R4" s="16">
         <f>BalanceSheet!$B$37</f>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="U4" s="16">
         <f t="shared" ref="U4:U50" si="2">MAX(R4+S4+Q4+T4,0)</f>
-        <v>10891150</v>
+        <v>10936550</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -5882,15 +5882,15 @@
       </c>
       <c r="Q5" s="16">
         <f>D5+E5-H5-I5+J5-K5-L5-M5-N5+O5+P5-IF($A5&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>656733.00000000012</v>
+        <v>702133.00000000012</v>
       </c>
       <c r="R5" s="16">
         <f t="shared" ref="R5:R50" si="3">U4</f>
-        <v>10891150</v>
+        <v>10936550</v>
       </c>
       <c r="S5" s="16">
         <f>R5*Inputs!$B$35</f>
-        <v>522775.2</v>
+        <v>524954.4</v>
       </c>
       <c r="T5" s="16">
         <f>IF($A5=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="U5" s="16">
         <f t="shared" si="2"/>
-        <v>12070658.199999999</v>
+        <v>12163637.4</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -5967,15 +5967,15 @@
       </c>
       <c r="Q6" s="16">
         <f>D6+E6-H6-I6+J6-K6-L6-M6-N6+O6+P6-IF($A6&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>21612.615000000107</v>
+        <v>67012.615000000107</v>
       </c>
       <c r="R6" s="16">
         <f t="shared" si="3"/>
-        <v>12070658.199999999</v>
+        <v>12163637.4</v>
       </c>
       <c r="S6" s="16">
         <f>R6*Inputs!$B$35</f>
-        <v>579391.59360000002</v>
+        <v>583854.59519999998</v>
       </c>
       <c r="T6" s="16">
         <f>IF($A6=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="U6" s="16">
         <f t="shared" si="2"/>
-        <v>12671662.408599999</v>
+        <v>12814504.610200001</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -6052,15 +6052,15 @@
       </c>
       <c r="Q7" s="16">
         <f>D7+E7-H7-I7+J7-K7-L7-M7-N7+O7+P7-IF($A7&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>15822.931574999937</v>
+        <v>61222.931574999937</v>
       </c>
       <c r="R7" s="16">
         <f t="shared" si="3"/>
-        <v>12671662.408599999</v>
+        <v>12814504.610200001</v>
       </c>
       <c r="S7" s="16">
         <f>R7*Inputs!$B$35</f>
-        <v>608239.79561279994</v>
+        <v>615096.22128960001</v>
       </c>
       <c r="T7" s="16">
         <f>IF($A7=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="U7" s="16">
         <f t="shared" si="2"/>
-        <v>13295725.1357878</v>
+        <v>13490823.763064601</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -6137,15 +6137,15 @@
       </c>
       <c r="Q8" s="16">
         <f>D8+E8-H8-I8+J8-K8-L8-M8-N8+O8+P8-IF($A8&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>9315.2286003751215</v>
+        <v>54715.228600375121</v>
       </c>
       <c r="R8" s="16">
         <f t="shared" si="3"/>
-        <v>13295725.1357878</v>
+        <v>13490823.763064601</v>
       </c>
       <c r="S8" s="16">
         <f>R8*Inputs!$B$35</f>
-        <v>638194.8065178144</v>
+        <v>647559.54062710085</v>
       </c>
       <c r="T8" s="16">
         <f>IF($A8=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="U8" s="16">
         <f t="shared" si="2"/>
-        <v>13943235.170905991</v>
+        <v>14193098.532292077</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -6222,15 +6222,15 @@
       </c>
       <c r="Q9" s="16">
         <f>D9+E9-H9-I9+J9-K9-L9-M9-N9+O9+P9-IF($A9&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>2037.8197634640383</v>
+        <v>47437.819763464038</v>
       </c>
       <c r="R9" s="16">
         <f t="shared" si="3"/>
-        <v>13943235.170905991</v>
+        <v>14193098.532292077</v>
       </c>
       <c r="S9" s="16">
         <f>R9*Inputs!$B$35</f>
-        <v>669275.28820348752</v>
+        <v>681268.72955001972</v>
       </c>
       <c r="T9" s="16">
         <f>IF($A9=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="U9" s="16">
         <f t="shared" si="2"/>
-        <v>14614548.278872943</v>
+        <v>14921805.081605561</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -6307,15 +6307,15 @@
       </c>
       <c r="Q10" s="16">
         <f>D10+E10-H10-I10+J10-K10-L10-M10-N10+O10+P10-IF($A10&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>797993.27201907407</v>
+        <v>843393.27201907407</v>
       </c>
       <c r="R10" s="16">
         <f t="shared" si="3"/>
-        <v>14614548.278872943</v>
+        <v>14921805.081605561</v>
       </c>
       <c r="S10" s="16">
         <f>R10*Inputs!$B$35</f>
-        <v>701498.31738590123</v>
+        <v>716246.64391706698</v>
       </c>
       <c r="T10" s="16">
         <f>IF($A10=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="U10" s="16">
         <f t="shared" si="2"/>
-        <v>16114039.868277917</v>
+        <v>16481444.997541701</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -6392,15 +6392,15 @@
       </c>
       <c r="Q11" s="16">
         <f>D11+E11-H11-I11+J11-K11-L11-M11-N11+O11+P11-IF($A11&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>829211.56251829374</v>
+        <v>874611.56251829374</v>
       </c>
       <c r="R11" s="16">
         <f t="shared" si="3"/>
-        <v>16114039.868277917</v>
+        <v>16481444.997541701</v>
       </c>
       <c r="S11" s="16">
         <f>R11*Inputs!$B$35</f>
-        <v>773473.91367734002</v>
+        <v>791109.35988200165</v>
       </c>
       <c r="T11" s="16">
         <f>IF($A11=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="U11" s="16">
         <f t="shared" si="2"/>
-        <v>17716725.344473552</v>
+        <v>18147165.919941999</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -6477,15 +6477,15 @@
       </c>
       <c r="Q12" s="16">
         <f>D12+E12-H12-I12+J12-K12-L12-M12-N12+O12+P12-IF($A12&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>861495.73654095572</v>
+        <v>906895.73654095572</v>
       </c>
       <c r="R12" s="16">
         <f t="shared" si="3"/>
-        <v>17716725.344473552</v>
+        <v>18147165.919941999</v>
       </c>
       <c r="S12" s="16">
         <f>R12*Inputs!$B$35</f>
-        <v>850402.81653473049</v>
+        <v>871063.96415721602</v>
       </c>
       <c r="T12" s="16">
         <f>IF($A12=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="U12" s="16">
         <f t="shared" si="2"/>
-        <v>19428623.897549238</v>
+        <v>19925125.62064017</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -6562,15 +6562,15 @@
       </c>
       <c r="Q13" s="16">
         <f>D13+E13-H13-I13+J13-K13-L13-M13-N13+O13+P13-IF($A13&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>894881.00396297663</v>
+        <v>940281.00396297663</v>
       </c>
       <c r="R13" s="16">
         <f t="shared" si="3"/>
-        <v>19428623.897549238</v>
+        <v>19925125.62064017</v>
       </c>
       <c r="S13" s="16">
         <f>R13*Inputs!$B$35</f>
-        <v>932573.94708236342</v>
+        <v>956406.02979072812</v>
       </c>
       <c r="T13" s="16">
         <f>IF($A13=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="U13" s="16">
         <f t="shared" si="2"/>
-        <v>21256078.848594576</v>
+        <v>21821812.654393874</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -6647,15 +6647,15 @@
       </c>
       <c r="Q14" s="16">
         <f>D14+E14-H14-I14+J14-K14-L14-M14-N14+O14+P14-IF($A14&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>929403.71179080242</v>
+        <v>974803.71179080242</v>
       </c>
       <c r="R14" s="16">
         <f t="shared" si="3"/>
-        <v>21256078.848594576</v>
+        <v>21821812.654393874</v>
       </c>
       <c r="S14" s="16">
         <f>R14*Inputs!$B$35</f>
-        <v>1020291.7847325397</v>
+        <v>1047447.007410906</v>
       </c>
       <c r="T14" s="16">
         <f>IF($A14=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="U14" s="16">
         <f t="shared" si="2"/>
-        <v>23205774.345117919</v>
+        <v>23844063.373595584</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -6736,11 +6736,11 @@
       </c>
       <c r="R15" s="23">
         <f t="shared" si="3"/>
-        <v>23205774.345117919</v>
+        <v>23844063.373595584</v>
       </c>
       <c r="S15" s="23">
         <f>R15*Inputs!$B$35</f>
-        <v>1113877.1685656602</v>
+        <v>1144515.041932588</v>
       </c>
       <c r="T15" s="23">
         <f>IF($A15=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="U15" s="23">
         <f t="shared" si="2"/>
-        <v>20348200.017858323</v>
+        <v>21017126.919702914</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -6821,11 +6821,11 @@
       </c>
       <c r="R16" s="16">
         <f t="shared" si="3"/>
-        <v>20348200.017858323</v>
+        <v>21017126.919702914</v>
       </c>
       <c r="S16" s="16">
         <f>R16*Inputs!$B$35</f>
-        <v>976713.60085719952</v>
+        <v>1008822.0921457398</v>
       </c>
       <c r="T16" s="16">
         <f>IF($A16=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="U16" s="16">
         <f t="shared" si="2"/>
-        <v>21473501.551300358</v>
+        <v>22174536.944433492</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="R17" s="23">
         <f t="shared" si="3"/>
-        <v>21473501.551300358</v>
+        <v>22174536.944433492</v>
       </c>
       <c r="S17" s="23">
         <f>R17*Inputs!$B$35</f>
-        <v>1030728.0744624172</v>
+        <v>1064377.7733328077</v>
       </c>
       <c r="T17" s="23">
         <f>IF($A17=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="U17" s="23">
         <f t="shared" si="2"/>
-        <v>21627347.557279609</v>
+        <v>22362032.649283133</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -6991,11 +6991,11 @@
       </c>
       <c r="R18" s="16">
         <f t="shared" si="3"/>
-        <v>21627347.557279609</v>
+        <v>22362032.649283133</v>
       </c>
       <c r="S18" s="16">
         <f>R18*Inputs!$B$35</f>
-        <v>1038112.6827494212</v>
+        <v>1073377.5671655904</v>
       </c>
       <c r="T18" s="16">
         <f>IF($A18=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="U18" s="16">
         <f t="shared" si="2"/>
-        <v>21744338.72678344</v>
+        <v>22514288.703203134</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -7076,11 +7076,11 @@
       </c>
       <c r="R19" s="16">
         <f t="shared" si="3"/>
-        <v>21744338.72678344</v>
+        <v>22514288.703203134</v>
       </c>
       <c r="S19" s="16">
         <f>R19*Inputs!$B$35</f>
-        <v>1043728.2588856051</v>
+        <v>1080685.8577537504</v>
       </c>
       <c r="T19" s="16">
         <f>IF($A19=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="U19" s="16">
         <f t="shared" si="2"/>
-        <v>21819667.345723789</v>
+        <v>22626574.92101163</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -7161,11 +7161,11 @@
       </c>
       <c r="R20" s="16">
         <f t="shared" si="3"/>
-        <v>21819667.345723789</v>
+        <v>22626574.92101163</v>
       </c>
       <c r="S20" s="16">
         <f>R20*Inputs!$B$35</f>
-        <v>1047344.0325947419</v>
+        <v>1086075.5962085582</v>
       </c>
       <c r="T20" s="16">
         <f>IF($A20=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="U20" s="16">
         <f t="shared" si="2"/>
-        <v>21847978.719372328</v>
+        <v>22693617.858273987</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -7246,11 +7246,11 @@
       </c>
       <c r="R21" s="16">
         <f t="shared" si="3"/>
-        <v>21847978.719372328</v>
+        <v>22693617.858273987</v>
       </c>
       <c r="S21" s="16">
         <f>R21*Inputs!$B$35</f>
-        <v>1048702.9785298717</v>
+        <v>1089293.6571971513</v>
       </c>
       <c r="T21" s="16">
         <f>IF($A21=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="U21" s="16">
         <f t="shared" si="2"/>
-        <v>21825201.059069425</v>
+        <v>22711430.876638364</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="R22" s="16">
         <f t="shared" si="3"/>
-        <v>21825201.059069425</v>
+        <v>22711430.876638364</v>
       </c>
       <c r="S22" s="16">
         <f>R22*Inputs!$B$35</f>
-        <v>1047609.6508353325</v>
+        <v>1090148.6820786416</v>
       </c>
       <c r="T22" s="16">
         <f>IF($A22=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="U22" s="16">
         <f t="shared" si="2"/>
-        <v>21745242.013943352</v>
+        <v>22674010.8627556</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -7416,11 +7416,11 @@
       </c>
       <c r="R23" s="16">
         <f t="shared" si="3"/>
-        <v>21745242.013943352</v>
+        <v>22674010.8627556</v>
       </c>
       <c r="S23" s="16">
         <f>R23*Inputs!$B$35</f>
-        <v>1043771.6166692809</v>
+        <v>1088352.5214122687</v>
       </c>
       <c r="T23" s="16">
         <f>IF($A23=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="U23" s="16">
         <f t="shared" si="2"/>
-        <v>21601358.207723934</v>
+        <v>22574707.961279169</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -7501,11 +7501,11 @@
       </c>
       <c r="R24" s="16">
         <f t="shared" si="3"/>
-        <v>21601358.207723934</v>
+        <v>22574707.961279169</v>
       </c>
       <c r="S24" s="16">
         <f>R24*Inputs!$B$35</f>
-        <v>1036865.1939707488</v>
+        <v>1083585.9821414002</v>
       </c>
       <c r="T24" s="16">
         <f>IF($A24=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="U24" s="16">
         <f t="shared" si="2"/>
-        <v>21386084.272740219</v>
+        <v>22406154.814466108</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -7586,11 +7586,11 @@
       </c>
       <c r="R25" s="16">
         <f t="shared" si="3"/>
-        <v>21386084.272740219</v>
+        <v>22406154.814466108</v>
       </c>
       <c r="S25" s="16">
         <f>R25*Inputs!$B$35</f>
-        <v>1026532.0450915305</v>
+        <v>1075495.4310943731</v>
       </c>
       <c r="T25" s="16">
         <f>IF($A25=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="U25" s="16">
         <f t="shared" si="2"/>
-        <v>21091153.949926905</v>
+        <v>22160187.87765564</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -7671,11 +7671,11 @@
       </c>
       <c r="R26" s="16">
         <f t="shared" si="3"/>
-        <v>21091153.949926905</v>
+        <v>22160187.87765564</v>
       </c>
       <c r="S26" s="16">
         <f>R26*Inputs!$B$35</f>
-        <v>1012375.3895964915</v>
+        <v>1063689.0181274707</v>
       </c>
       <c r="T26" s="16">
         <f>IF($A26=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="U26" s="16">
         <f t="shared" si="2"/>
-        <v>20711268.788185466</v>
+        <v>21831616.34444518</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -7756,11 +7756,11 @@
       </c>
       <c r="R27" s="16">
         <f t="shared" si="3"/>
-        <v>20711268.788185466</v>
+        <v>21831616.34444518</v>
       </c>
       <c r="S27" s="16">
         <f>R27*Inputs!$B$35</f>
-        <v>994140.90183290234</v>
+        <v>1047917.5845333687</v>
       </c>
       <c r="T27" s="16">
         <f>IF($A27=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="U27" s="16">
         <f t="shared" si="2"/>
-        <v>20237279.403837793</v>
+        <v>21411403.642797973</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -7841,11 +7841,11 @@
       </c>
       <c r="R28" s="16">
         <f t="shared" si="3"/>
-        <v>20237279.403837793</v>
+        <v>21411403.642797973</v>
       </c>
       <c r="S28" s="16">
         <f>R28*Inputs!$B$35</f>
-        <v>971389.41138421407</v>
+        <v>1027747.3748543027</v>
       </c>
       <c r="T28" s="16">
         <f>IF($A28=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="U28" s="16">
         <f t="shared" si="2"/>
-        <v>19659116.101737805</v>
+        <v>20889598.304168075</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -7926,11 +7926,11 @@
       </c>
       <c r="R29" s="16">
         <f t="shared" si="3"/>
-        <v>19659116.101737805</v>
+        <v>20889598.304168075</v>
       </c>
       <c r="S29" s="16">
         <f>R29*Inputs!$B$35</f>
-        <v>943637.57288341469</v>
+        <v>1002700.7186000677</v>
       </c>
       <c r="T29" s="16">
         <f>IF($A29=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="U29" s="16">
         <f t="shared" si="2"/>
-        <v>18965694.279604044</v>
+        <v>20255239.627750967</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="R30" s="16">
         <f t="shared" si="3"/>
-        <v>18965694.279604044</v>
+        <v>20255239.627750967</v>
       </c>
       <c r="S30" s="16">
         <f>R30*Inputs!$B$35</f>
-        <v>910353.32542099408</v>
+        <v>972251.50213204639</v>
       </c>
       <c r="T30" s="16">
         <f>IF($A30=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="U30" s="16">
         <f t="shared" si="2"/>
-        <v>18144809.834026922</v>
+        <v>19496253.358884897</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -8096,11 +8096,11 @@
       </c>
       <c r="R31" s="16">
         <f t="shared" si="3"/>
-        <v>18144809.834026922</v>
+        <v>19496253.358884897</v>
       </c>
       <c r="S31" s="16">
         <f>R31*Inputs!$B$35</f>
-        <v>870950.87203329219</v>
+        <v>935820.16122647503</v>
       </c>
       <c r="T31" s="16">
         <f>IF($A31=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="U31" s="16">
         <f t="shared" si="2"/>
-        <v>17189240.614425432</v>
+        <v>18605553.428476591</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="R32" s="16">
         <f t="shared" si="3"/>
-        <v>17189240.614425432</v>
+        <v>18605553.428476591</v>
       </c>
       <c r="S32" s="16">
         <f>R32*Inputs!$B$35</f>
-        <v>825083.54949242075</v>
+        <v>893066.56456687639</v>
       </c>
       <c r="T32" s="16">
         <f>IF($A32=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="U32" s="16">
         <f t="shared" si="2"/>
-        <v>16085803.202489708</v>
+        <v>17570099.031615321</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -8266,11 +8266,11 @@
       </c>
       <c r="R33" s="16">
         <f t="shared" si="3"/>
-        <v>16085803.202489708</v>
+        <v>17570099.031615321</v>
       </c>
       <c r="S33" s="16">
         <f>R33*Inputs!$B$35</f>
-        <v>772118.55371950602</v>
+        <v>843364.7535175354</v>
       </c>
       <c r="T33" s="16">
         <f>IF($A33=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="U33" s="16">
         <f t="shared" si="2"/>
-        <v>14820098.298671564</v>
+        <v>16375640.327595206</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -8351,11 +8351,11 @@
       </c>
       <c r="R34" s="23">
         <f t="shared" si="3"/>
-        <v>14820098.298671564</v>
+        <v>16375640.327595206</v>
       </c>
       <c r="S34" s="23">
         <f>R34*Inputs!$B$35</f>
-        <v>711364.71833623503</v>
+        <v>786030.73572456988</v>
       </c>
       <c r="T34" s="23">
         <f>IF($A34=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="U34" s="23">
         <f t="shared" si="2"/>
-        <v>13376398.045838624</v>
+        <v>15006606.092150601</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -8436,11 +8436,11 @@
       </c>
       <c r="R35" s="16">
         <f t="shared" si="3"/>
-        <v>13376398.045838624</v>
+        <v>15006606.092150601</v>
       </c>
       <c r="S35" s="16">
         <f>R35*Inputs!$B$35</f>
-        <v>642067.10620025394</v>
+        <v>720317.0924232289</v>
       </c>
       <c r="T35" s="16">
         <f>IF($A35=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="U35" s="16">
         <f t="shared" si="2"/>
-        <v>12288823.083724447</v>
+        <v>13997281.1162594</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="R36" s="16">
         <f t="shared" si="3"/>
-        <v>12288823.083724447</v>
+        <v>13997281.1162594</v>
       </c>
       <c r="S36" s="16">
         <f>R36*Inputs!$B$35</f>
-        <v>589863.5080187734</v>
+        <v>671869.49358045124</v>
       </c>
       <c r="T36" s="16">
         <f>IF($A36=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="U36" s="16">
         <f t="shared" si="2"/>
-        <v>11066624.516588137</v>
+        <v>12857088.534684768</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="R37" s="16">
         <f t="shared" si="3"/>
-        <v>11066624.516588137</v>
+        <v>12857088.534684768</v>
       </c>
       <c r="S37" s="16">
         <f>R37*Inputs!$B$35</f>
-        <v>531197.97679623053</v>
+        <v>617140.24966486893</v>
       </c>
       <c r="T37" s="16">
         <f>IF($A37=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="U37" s="16">
         <f t="shared" si="2"/>
-        <v>9698176.6432708651</v>
+        <v>11574582.934236135</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -8691,11 +8691,11 @@
       </c>
       <c r="R38" s="16">
         <f t="shared" si="3"/>
-        <v>9698176.6432708651</v>
+        <v>11574582.934236135</v>
       </c>
       <c r="S38" s="16">
         <f>R38*Inputs!$B$35</f>
-        <v>465512.47887700156</v>
+        <v>555579.98084333446</v>
       </c>
       <c r="T38" s="16">
         <f>IF($A38=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="U38" s="16">
         <f t="shared" si="2"/>
-        <v>8170870.1266960986</v>
+        <v>10137343.919627702</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -8776,11 +8776,11 @@
       </c>
       <c r="R39" s="16">
         <f t="shared" si="3"/>
-        <v>8170870.1266960986</v>
+        <v>10137343.919627702</v>
       </c>
       <c r="S39" s="16">
         <f>R39*Inputs!$B$35</f>
-        <v>392201.76608141273</v>
+        <v>486592.50814212969</v>
       </c>
       <c r="T39" s="16">
         <f>IF($A39=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="U39" s="16">
         <f t="shared" si="2"/>
-        <v>6471025.8088223208</v>
+        <v>8531890.3438146412</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -8861,11 +8861,11 @@
       </c>
       <c r="R40" s="16">
         <f t="shared" si="3"/>
-        <v>6471025.8088223208</v>
+        <v>8531890.3438146412</v>
       </c>
       <c r="S40" s="16">
         <f>R40*Inputs!$B$35</f>
-        <v>310609.23882347142</v>
+        <v>409530.73650310282</v>
       </c>
       <c r="T40" s="16">
         <f>IF($A40=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="U40" s="16">
         <f t="shared" si="2"/>
-        <v>4583800.7075582501</v>
+        <v>6743586.7402302008</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -8946,11 +8946,11 @@
       </c>
       <c r="R41" s="16">
         <f t="shared" si="3"/>
-        <v>4583800.7075582501</v>
+        <v>6743586.7402302008</v>
       </c>
       <c r="S41" s="16">
         <f>R41*Inputs!$B$35</f>
-        <v>220022.433962796</v>
+        <v>323692.16353104962</v>
       </c>
       <c r="T41" s="16">
         <f>IF($A41=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="U41" s="16">
         <f t="shared" si="2"/>
-        <v>2493085.4697103309</v>
+        <v>4756541.2319505364</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -9031,11 +9031,11 @@
       </c>
       <c r="R42" s="16">
         <f t="shared" si="3"/>
-        <v>2493085.4697103309</v>
+        <v>4756541.2319505364</v>
       </c>
       <c r="S42" s="16">
         <f>R42*Inputs!$B$35</f>
-        <v>119668.10254609589</v>
+        <v>228313.97913362575</v>
       </c>
       <c r="T42" s="16">
         <f>IF($A42=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="U42" s="16">
         <f t="shared" si="2"/>
-        <v>181392.485709175</v>
+        <v>2553494.1245369101</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -9116,11 +9116,11 @@
       </c>
       <c r="R43" s="16">
         <f t="shared" si="3"/>
-        <v>181392.485709175</v>
+        <v>2553494.1245369101</v>
       </c>
       <c r="S43" s="16">
         <f>R43*Inputs!$B$35</f>
-        <v>8706.8393140404005</v>
+        <v>122567.71797777168</v>
       </c>
       <c r="T43" s="16">
         <f>IF($A43=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="U43" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>115696.31455235416</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -9201,11 +9201,11 @@
       </c>
       <c r="R44" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>115696.31455235416</v>
       </c>
       <c r="S44" s="23">
         <f>R44*Inputs!$B$35</f>
-        <v>0</v>
+        <v>5553.4230985129998</v>
       </c>
       <c r="T44" s="23">
         <f>IF($A44=Inputs!$B$81,-Inputs!$B$38,0)</f>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B7" s="24">
         <f>Tax!B27-Inputs!$B$42</f>
-        <v>559230</v>
+        <v>604630</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="B14" s="24">
         <f>INDEX(Projection!U:U,MATCH(Inputs!$B$81,Projection!A:A,0))</f>
-        <v>20348200.017858323</v>
+        <v>21017126.919702914</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="B17" s="24">
         <f>INDEX(Projection!U:U,MATCH(Inputs!$B$81,Projection!A:A,0))/(1+Inputs!$B$5)^(Inputs!$B$81-Inputs!$B$80)</f>
-        <v>15508274.470191544</v>
+        <v>16018093.618086508</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="B19" s="26">
         <f>IFERROR(INDEX(Projection!A4:A50,MATCH(0,Projection!U4:U50,0)),0)</f>
-        <v>2065</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B20" s="26">
         <f>IF(B19=0,"lasts",B19-1977)</f>
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">

--- a/model/wong_model.xlsx
+++ b/model/wong_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\finplan\finplan\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8E23D6-C4E4-4BE9-9ED1-5271BC2B6A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B9C359-618B-42FA-BA71-895939315759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="272">
   <si>
     <t>Wong Family model — INPUTS</t>
   </si>
@@ -208,16 +208,34 @@
     <t>vs 30.5 today</t>
   </si>
   <si>
-    <t>Annuity purchase cost at 2037</t>
-  </si>
-  <si>
-    <t>Pete: MPF 2.31M (A) + 1.81M (C)</t>
-  </si>
-  <si>
-    <t>Annuity income (HKMC, annual)</t>
-  </si>
-  <si>
-    <t>Pete: HKMC payout at 65</t>
+    <t>Annuity: Adrian premium (MPF at 65, 2037)</t>
+  </si>
+  <si>
+    <t>Pete: projected MPF at 65</t>
+  </si>
+  <si>
+    <t>Annuity: Adrian income a year</t>
+  </si>
+  <si>
+    <t>HKMC male at 65: 5,800 a month per HK$1M. Single life: stops at death</t>
+  </si>
+  <si>
+    <t>Annuity: Carmen premium (MPF at 62, 2039)</t>
+  </si>
+  <si>
+    <t>Pete: projected MPF at 62; bought when she stops work</t>
+  </si>
+  <si>
+    <t>Mortgage: balance repaid at Adrian's retirement (2037)</t>
+  </si>
+  <si>
+    <t>HK$1.8M at 3.5%, ~14 years left at HK$13.6K a month: 36 months left in 2037 (PV). Outside the HK$780K; must be cleared before a reverse mortgage</t>
+  </si>
+  <si>
+    <t>Annuity: Carmen income a year</t>
+  </si>
+  <si>
+    <t>HKMC female, ~4,940 a month per HK$1M at 62 (between 4,700 at 60 and 5,300 at 65)</t>
   </si>
   <si>
     <t>Education — overseas annual (today)</t>
@@ -754,7 +772,7 @@
     <t>Investment return</t>
   </si>
   <si>
-    <t>Annuity purchase</t>
+    <t>Lump sums out (annuities, mortgage)</t>
   </si>
   <si>
     <t>Portfolio close</t>
@@ -1267,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1649,7 +1667,7 @@
         <v>56</v>
       </c>
       <c r="B38" s="8">
-        <v>4120000</v>
+        <v>2310000</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>57</v>
@@ -1660,7 +1678,7 @@
         <v>58</v>
       </c>
       <c r="B39" s="8">
-        <v>268000</v>
+        <v>160800</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>59</v>
@@ -1671,7 +1689,7 @@
         <v>60</v>
       </c>
       <c r="B40" s="8">
-        <v>600000</v>
+        <v>1810000</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>61</v>
@@ -1681,8 +1699,8 @@
       <c r="A41" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="9">
-        <v>4</v>
+      <c r="B41" s="8">
+        <v>460000</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>63</v>
@@ -1693,59 +1711,59 @@
         <v>64</v>
       </c>
       <c r="B42" s="8">
-        <v>113600</v>
+        <v>107300</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="B43" s="8">
+        <v>600000</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B44" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="6">
-        <v>0.1</v>
+        <v>70</v>
+      </c>
+      <c r="B45" s="8">
+        <v>113600</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="A46" s="3" t="s">
         <v>72</v>
       </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B47" s="9">
-        <v>2036</v>
+        <v>1</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>74</v>
@@ -1756,7 +1774,7 @@
         <v>75</v>
       </c>
       <c r="B48" s="6">
-        <v>8.5400000000000004E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>76</v>
@@ -1766,8 +1784,8 @@
       <c r="A49" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="9">
-        <v>0</v>
+      <c r="B49" s="6">
+        <v>0.06</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>78</v>
@@ -1777,8 +1795,8 @@
       <c r="A50" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="8">
-        <v>65000</v>
+      <c r="B50" s="9">
+        <v>2036</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>80</v>
@@ -1788,8 +1806,8 @@
       <c r="A51" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B51" s="9">
-        <v>2047</v>
+      <c r="B51" s="6">
+        <v>8.5400000000000004E-2</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>82</v>
@@ -1799,60 +1817,60 @@
       <c r="A52" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B52" s="6">
-        <v>0.5</v>
+      <c r="B52" s="9">
+        <v>0</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="8">
+        <v>65000</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B54" s="6">
-        <v>0.7</v>
+        <v>87</v>
+      </c>
+      <c r="B54" s="9">
+        <v>2047</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B55" s="9">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="B55" s="6">
+        <v>0.5</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="8">
-        <v>3000000</v>
-      </c>
-      <c r="D56" s="7" t="s">
+      <c r="A56" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="9">
-        <v>2039</v>
+      <c r="B57" s="6">
+        <v>0.7</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>93</v>
@@ -1874,7 +1892,7 @@
         <v>96</v>
       </c>
       <c r="B59" s="8">
-        <v>230000</v>
+        <v>3000000</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>97</v>
@@ -1885,7 +1903,7 @@
         <v>98</v>
       </c>
       <c r="B60" s="9">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>99</v>
@@ -1903,115 +1921,115 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
+      <c r="B62" s="8">
+        <v>230000</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B63" s="6">
-        <v>0.04</v>
+        <v>104</v>
+      </c>
+      <c r="B63" s="9">
+        <v>2037</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B64" s="6">
-        <v>2.5000000000000001E-2</v>
+        <v>106</v>
+      </c>
+      <c r="B64" s="9">
+        <v>0</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B65" s="6">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>107</v>
-      </c>
+      <c r="A65" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
+      <c r="A66" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B66" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B67" s="8">
-        <v>11500000</v>
+        <v>110</v>
+      </c>
+      <c r="B67" s="6">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B68" s="6">
-        <v>1.4999999999999999E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B69" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>112</v>
-      </c>
+      <c r="A69" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="6">
-        <v>1.2500000000000001E-2</v>
+        <v>115</v>
+      </c>
+      <c r="B70" s="8">
+        <v>11500000</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B71" s="6">
-        <v>1.9599999999999999E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>116</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B72" s="8">
-        <v>8000000</v>
+      <c r="B72" s="6">
+        <v>0.04</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>118</v>
@@ -2022,43 +2040,43 @@
         <v>119</v>
       </c>
       <c r="B73" s="6">
-        <v>0.5</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B74" s="8">
-        <v>7000000</v>
+        <v>121</v>
+      </c>
+      <c r="B74" s="6">
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B75" s="6">
-        <v>3.7499999999999999E-2</v>
+        <v>123</v>
+      </c>
+      <c r="B75" s="8">
+        <v>8000000</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B76" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="B76" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2066,7 +2084,7 @@
         <v>126</v>
       </c>
       <c r="B77" s="8">
-        <v>200000</v>
+        <v>7000000</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>127</v>
@@ -2076,85 +2094,85 @@
       <c r="A78" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B78" s="9">
-        <v>2037</v>
+      <c r="B78" s="6">
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
+      <c r="B79" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="9">
-        <v>2026</v>
+        <v>132</v>
+      </c>
+      <c r="B80" s="8">
+        <v>200000</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B81" s="9">
         <v>2037</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B82" s="9">
-        <v>2039</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="A82" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B83" s="9">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B84" s="9">
-        <v>2056</v>
+        <v>2037</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B85" s="9">
-        <v>2066</v>
+        <v>2039</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2162,10 +2180,43 @@
         <v>141</v>
       </c>
       <c r="B86" s="9">
-        <v>2072</v>
+        <v>2028</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B87" s="9">
+        <v>2056</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B88" s="9">
+        <v>2066</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" s="9">
+        <v>2072</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2184,18 +2235,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B4" s="8">
         <v>620000</v>
@@ -2203,7 +2254,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B5" s="8">
         <v>1480000</v>
@@ -2211,7 +2262,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B6" s="8">
         <v>400000</v>
@@ -2219,7 +2270,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B7" s="11">
         <f>SUM(B4:B6)</f>
@@ -2228,13 +2279,13 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B9" s="8">
         <v>1000000</v>
@@ -2242,7 +2293,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B10" s="8">
         <v>1350000</v>
@@ -2250,7 +2301,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B11" s="8">
         <v>900000</v>
@@ -2258,7 +2309,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B12" s="8">
         <v>700000</v>
@@ -2266,7 +2317,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B13" s="8">
         <v>450000</v>
@@ -2274,7 +2325,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B14" s="8">
         <v>800000</v>
@@ -2282,7 +2333,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B15" s="8">
         <v>1050000</v>
@@ -2290,7 +2341,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B16" s="8">
         <v>620000</v>
@@ -2298,7 +2349,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B17" s="8">
         <v>180000</v>
@@ -2306,7 +2357,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B18" s="8">
         <v>500000</v>
@@ -2314,7 +2365,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B19" s="8">
         <v>420000</v>
@@ -2322,7 +2373,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B20" s="11">
         <f>SUM(B9:B19)</f>
@@ -2331,13 +2382,13 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B21" s="4"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B22" s="8">
         <v>11500000</v>
@@ -2345,7 +2396,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B23" s="8">
         <v>5000000</v>
@@ -2353,7 +2404,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B24" s="8">
         <v>220000</v>
@@ -2361,7 +2412,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B25" s="11">
         <f>SUM(B22:B24)</f>
@@ -2370,13 +2421,13 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B27" s="8">
         <v>1800000</v>
@@ -2384,7 +2435,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B28" s="8">
         <v>900000</v>
@@ -2392,7 +2443,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B29" s="8">
         <v>85000</v>
@@ -2400,7 +2451,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B30" s="11">
         <f>SUM(B27:B29)</f>
@@ -2409,7 +2460,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B32" s="12">
         <f>B7+B20+B25</f>
@@ -2418,7 +2469,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B33" s="12">
         <f>B32-B30</f>
@@ -2427,7 +2478,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B35" s="13">
         <f>B33-24405000</f>
@@ -2436,7 +2487,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B37" s="12">
         <f>B7+B20-B17-B18</f>
@@ -2459,17 +2510,17 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B4" s="14">
         <f>BalanceSheet!B27*Inputs!$B$25</f>
@@ -2479,21 +2530,21 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="15" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B7" s="16">
         <f>Inputs!$B$27+Inputs!$B$28</f>
@@ -2514,7 +2565,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B8" s="16">
         <f>-Inputs!$B$22</f>
@@ -2535,7 +2586,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B9" s="16">
         <f>-$B$4/2</f>
@@ -2555,7 +2606,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B10" s="16">
         <f>SUM(B7:B9)</f>
@@ -2576,7 +2627,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B11" s="16">
         <f>-(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)</f>
@@ -2597,7 +2648,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B12" s="16">
         <f>MAX(B10+B11,0)</f>
@@ -2618,7 +2669,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B13" s="11">
         <f>IF(B12&gt;200000,Inputs!$B$24+(B12-200000)*Inputs!$B$23,IF(B12&gt;150000,9000+(B12-150000)*0.14,IF(B12&gt;100000,4000+(B12-100000)*0.1,IF(B12&gt;50000,1000+(B12-50000)*0.06,B12*0.02))))</f>
@@ -2639,7 +2690,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B15" s="17">
         <f>B13+C13</f>
@@ -2648,7 +2699,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B16" s="12">
         <f>D13</f>
@@ -2657,7 +2708,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B17" s="12">
         <f>B16-B15</f>
@@ -2666,7 +2717,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B19" s="13">
         <f>B15-181770</f>
@@ -2675,7 +2726,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B20" s="13">
         <f>B16-199770</f>
@@ -2684,12 +2735,12 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B23" s="14">
         <f>D7</f>
@@ -2698,7 +2749,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B24" s="14">
         <f>-B15</f>
@@ -2707,7 +2758,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B25" s="14">
         <f>D8</f>
@@ -2716,7 +2767,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B26" s="14">
         <f>-Inputs!$B$31</f>
@@ -2725,7 +2776,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B27" s="17">
         <f>SUM(B23:B26)</f>
@@ -2748,29 +2799,29 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,7 +2924,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B12" s="18">
         <f>(B11/B10)^(1/5)-1</f>
@@ -2890,16 +2941,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3686,34 +3737,34 @@
     </row>
     <row r="62" spans="1:10" ht="39" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3729,18 +3780,18 @@
         <v>49</v>
       </c>
       <c r="D63" s="18">
-        <f>IF($A63=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A63&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A63-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A63=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A63&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A63-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0</v>
       </c>
       <c r="E63" s="21">
         <v>1</v>
       </c>
       <c r="F63" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$81,$A63&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B63,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A63&lt;Inputs!$B$84,$A63&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B63,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G63" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C63,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A63&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C63,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C63,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H63" s="14">
@@ -3748,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A63&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A63-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A63&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A63-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J63" s="14">
@@ -3769,7 +3820,7 @@
         <v>50</v>
       </c>
       <c r="D64" s="18">
-        <f>IF($A64=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A64&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A64-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A64=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A64&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A64-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.1</v>
       </c>
       <c r="E64" s="21">
@@ -3777,11 +3828,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F64" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$81,$A64&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B64,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A64&lt;Inputs!$B$84,$A64&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B64,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G64" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C64,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A64&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C64,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C64,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H64" s="14">
@@ -3789,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A64&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A64-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A64&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A64-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J64" s="14">
@@ -3810,7 +3861,7 @@
         <v>51</v>
       </c>
       <c r="D65" s="18">
-        <f>IF($A65=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A65&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A65-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A65=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A65&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A65-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>9.555555555555556E-2</v>
       </c>
       <c r="E65" s="21">
@@ -3818,11 +3869,11 @@
         <v>1.2051111111111112</v>
       </c>
       <c r="F65" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$81,$A65&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B65,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A65&lt;Inputs!$B$84,$A65&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B65,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G65" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C65,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A65&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C65,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C65,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H65" s="14">
@@ -3830,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A65&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A65-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A65&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A65-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J65" s="14">
@@ -3851,7 +3902,7 @@
         <v>52</v>
       </c>
       <c r="D66" s="18">
-        <f>IF($A66=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A66&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A66-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A66=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A66&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A66-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>9.1111111111111115E-2</v>
       </c>
       <c r="E66" s="21">
@@ -3859,11 +3910,11 @@
         <v>1.3149101234567904</v>
       </c>
       <c r="F66" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$81,$A66&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B66,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A66&lt;Inputs!$B$84,$A66&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B66,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G66" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C66,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A66&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C66,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C66,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H66" s="14">
@@ -3871,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A66&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A66-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A66&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A66-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J66" s="14">
@@ -3892,7 +3943,7 @@
         <v>53</v>
       </c>
       <c r="D67" s="18">
-        <f>IF($A67=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A67&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A67-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A67=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A67&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A67-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>8.666666666666667E-2</v>
       </c>
       <c r="E67" s="21">
@@ -3900,11 +3951,11 @@
         <v>1.4288690008230456</v>
       </c>
       <c r="F67" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$81,$A67&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B67,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A67&lt;Inputs!$B$84,$A67&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B67,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G67" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C67,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A67&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C67,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C67,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H67" s="14">
@@ -3912,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A67&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A67-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A67&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A67-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J67" s="14">
@@ -3933,7 +3984,7 @@
         <v>54</v>
       </c>
       <c r="D68" s="18">
-        <f>IF($A68=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A68&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A68-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A68=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A68&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A68-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>8.2222222222222224E-2</v>
       </c>
       <c r="E68" s="21">
@@ -3941,11 +3992,11 @@
         <v>1.5463537853351625</v>
       </c>
       <c r="F68" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$81,$A68&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B68,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A68&lt;Inputs!$B$84,$A68&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B68,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G68" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C68,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A68&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C68,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C68,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H68" s="14">
@@ -3953,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A68&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A68-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A68&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A68-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J68" s="14">
@@ -3974,7 +4025,7 @@
         <v>55</v>
       </c>
       <c r="D69" s="18">
-        <f>IF($A69=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A69&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A69-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A69=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A69&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A69-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="E69" s="21">
@@ -3982,11 +4033,11 @@
         <v>1.6666257464167862</v>
       </c>
       <c r="F69" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$81,$A69&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B69,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A69&lt;Inputs!$B$84,$A69&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B69,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G69" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C69,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A69&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C69,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C69,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H69" s="14">
@@ -3994,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A69&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A69-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A69&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A69-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J69" s="14">
@@ -4015,7 +4066,7 @@
         <v>56</v>
       </c>
       <c r="D70" s="18">
-        <f>IF($A70=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A70&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A70-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A70=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A70&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A70-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>7.3333333333333334E-2</v>
       </c>
       <c r="E70" s="21">
@@ -4023,11 +4074,11 @@
         <v>1.7888449678206837</v>
       </c>
       <c r="F70" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$81,$A70&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B70,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A70&lt;Inputs!$B$84,$A70&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B70,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G70" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C70,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A70&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C70,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C70,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H70" s="14">
@@ -4035,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A70&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A70-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A70&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A70-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J70" s="14">
@@ -4056,7 +4107,7 @@
         <v>57</v>
       </c>
       <c r="D71" s="18">
-        <f>IF($A71=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A71&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A71-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A71=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A71&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A71-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>6.8888888888888888E-2</v>
       </c>
       <c r="E71" s="21">
@@ -4064,11 +4115,11 @@
         <v>1.912076510048331</v>
       </c>
       <c r="F71" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$81,$A71&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B71,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A71&lt;Inputs!$B$84,$A71&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B71,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G71" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C71,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A71&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C71,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C71,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H71" s="14">
@@ -4076,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A71&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A71-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A71&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A71-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J71" s="14">
@@ -4097,7 +4148,7 @@
         <v>58</v>
       </c>
       <c r="D72" s="18">
-        <f>IF($A72=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A72&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A72-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A72=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A72&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A72-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>6.4444444444444443E-2</v>
       </c>
       <c r="E72" s="21">
@@ -4105,11 +4156,11 @@
         <v>2.0352992184736682</v>
       </c>
       <c r="F72" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$81,$A72&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B72,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A72&lt;Inputs!$B$84,$A72&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B72,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G72" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C72,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A72&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C72,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C72,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H72" s="14">
@@ -4117,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A72&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A72-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A72&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A72-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J72" s="14">
@@ -4138,7 +4189,7 @@
         <v>59</v>
       </c>
       <c r="D73" s="18">
-        <f>IF($A73=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A73&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A73-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A73=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A73&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A73-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E73" s="21">
@@ -4146,11 +4197,11 @@
         <v>2.1574171715820882</v>
       </c>
       <c r="F73" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$81,$A73&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B73,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A73&lt;Inputs!$B$84,$A73&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B73,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G73" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C73,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A73&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C73,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C73,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H73" s="14">
@@ -4158,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A73&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A73-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A73&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A73-Inputs!$B$83))</f>
         <v>0</v>
       </c>
       <c r="J73" s="14">
@@ -4179,7 +4230,7 @@
         <v>60</v>
       </c>
       <c r="D74" s="18">
-        <f>IF($A74=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A74&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A74-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A74=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A74&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A74-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E74" s="21">
@@ -4187,11 +4238,11 @@
         <v>2.2868622018770135</v>
       </c>
       <c r="F74" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$81,$A74&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B74,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A74&lt;Inputs!$B$84,$A74&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B74,$A$15:$A$60,0))))</f>
         <v>32542</v>
       </c>
       <c r="G74" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C74,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A74&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C74,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C74,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H74" s="14">
@@ -4199,7 +4250,7 @@
         <v>74419.06977348178</v>
       </c>
       <c r="I74" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A74&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A74-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A74&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A74-Inputs!$B$83))</f>
         <v>85285.63275708229</v>
       </c>
       <c r="J74" s="14">
@@ -4220,7 +4271,7 @@
         <v>61</v>
       </c>
       <c r="D75" s="18">
-        <f>IF($A75=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A75&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A75-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A75=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A75&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A75-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E75" s="21">
@@ -4228,11 +4279,11 @@
         <v>2.4240739339896344</v>
       </c>
       <c r="F75" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$81,$A75&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B75,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A75&lt;Inputs!$B$84,$A75&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B75,$A$15:$A$60,0))))</f>
         <v>34265.509148780548</v>
       </c>
       <c r="G75" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C75,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A75&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C75,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C75,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="H75" s="14">
@@ -4240,7 +4291,7 @@
         <v>83062.127562442271</v>
       </c>
       <c r="I75" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A75&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A75-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A75&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A75-Inputs!$B$83))</f>
         <v>87417.773576009335</v>
       </c>
       <c r="J75" s="14">
@@ -4261,7 +4312,7 @@
         <v>62</v>
       </c>
       <c r="D76" s="18">
-        <f>IF($A76=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A76&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A76-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A76=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A76&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A76-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E76" s="21">
@@ -4269,11 +4320,11 @@
         <v>2.5695183700290127</v>
       </c>
       <c r="F76" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$81,$A76&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B76,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A76&lt;Inputs!$B$84,$A76&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B76,$A$15:$A$60,0))))</f>
         <v>36080.299834833859</v>
       </c>
       <c r="G76" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C76,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A76&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C76,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C76,$A$15:$A$60,0))))</f>
         <v>25895</v>
       </c>
       <c r="H76" s="14">
@@ -4281,7 +4332,7 @@
         <v>159246.67141366165</v>
       </c>
       <c r="I76" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A76&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A76-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A76&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A76-Inputs!$B$83))</f>
         <v>89603.217915409565</v>
       </c>
       <c r="J76" s="14">
@@ -4302,7 +4353,7 @@
         <v>63</v>
       </c>
       <c r="D77" s="18">
-        <f>IF($A77=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A77&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A77-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A77=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A77&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A77-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E77" s="21">
@@ -4310,11 +4361,11 @@
         <v>2.7236894722307534</v>
       </c>
       <c r="F77" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$81,$A77&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B77,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A77&lt;Inputs!$B$84,$A77&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B77,$A$15:$A$60,0))))</f>
         <v>37991.206566321816</v>
       </c>
       <c r="G77" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C77,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A77&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C77,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C77,$A$15:$A$60,0))))</f>
         <v>27671.650037838353</v>
       </c>
       <c r="H77" s="14">
@@ -4322,7 +4373,7 @@
         <v>178845.23124934867</v>
       </c>
       <c r="I77" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A77&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A77-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A77&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A77-Inputs!$B$83))</f>
         <v>91843.298363294802</v>
       </c>
       <c r="J77" s="14">
@@ -4343,7 +4394,7 @@
         <v>64</v>
       </c>
       <c r="D78" s="18">
-        <f>IF($A78=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A78&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A78-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A78=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A78&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A78-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E78" s="21">
@@ -4351,11 +4402,11 @@
         <v>2.8871108405645987</v>
       </c>
       <c r="F78" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$81,$A78&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B78,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A78&lt;Inputs!$B$84,$A78&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B78,$A$15:$A$60,0))))</f>
         <v>40003.319899560935</v>
       </c>
       <c r="G78" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C78,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A78&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C78,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C78,$A$15:$A$60,0))))</f>
         <v>29570.19562914074</v>
       </c>
       <c r="H78" s="14">
@@ -4363,7 +4414,7 @@
         <v>200866.45089910406</v>
       </c>
       <c r="I78" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A78&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A78-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A78&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A78-Inputs!$B$83))</f>
         <v>94139.380822377178</v>
       </c>
       <c r="J78" s="14">
@@ -4384,7 +4435,7 @@
         <v>65</v>
       </c>
       <c r="D79" s="18">
-        <f>IF($A79=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A79&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A79-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A79=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A79&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A79-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E79" s="21">
@@ -4392,11 +4443,11 @@
         <v>3.0603374909984749</v>
       </c>
       <c r="F79" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$81,$A79&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B79,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A79&lt;Inputs!$B$84,$A79&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B79,$A$15:$A$60,0))))</f>
         <v>42122</v>
       </c>
       <c r="G79" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C79,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A79&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C79,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C79,$A$15:$A$60,0))))</f>
         <v>31599</v>
       </c>
       <c r="H79" s="14">
@@ -4404,7 +4455,7 @@
         <v>225611.14017389857</v>
       </c>
       <c r="I79" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A79&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A79-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A79&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A79-Inputs!$B$83))</f>
         <v>96492.86534293661</v>
       </c>
       <c r="J79" s="14">
@@ -4425,7 +4476,7 @@
         <v>66</v>
       </c>
       <c r="D80" s="18">
-        <f>IF($A80=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A80&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A80-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A80=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A80&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A80-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E80" s="21">
@@ -4433,11 +4484,11 @@
         <v>3.2439577404583835</v>
       </c>
       <c r="F80" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$81,$A80&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B80,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A80&lt;Inputs!$B$84,$A80&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B80,$A$15:$A$60,0))))</f>
         <v>44249.053788011741</v>
       </c>
       <c r="G80" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C80,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A80&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C80,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C80,$A$15:$A$60,0))))</f>
         <v>33286.969247733367</v>
       </c>
       <c r="H80" s="14">
@@ -4445,7 +4496,7 @@
         <v>251523.58209116486</v>
       </c>
       <c r="I80" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A80&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A80-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A80&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A80-Inputs!$B$83))</f>
         <v>98905.186976509998</v>
       </c>
       <c r="J80" s="14">
@@ -4466,7 +4517,7 @@
         <v>67</v>
       </c>
       <c r="D81" s="18">
-        <f>IF($A81=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A81&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A81-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A81=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A81&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A81-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E81" s="21">
@@ -4474,11 +4525,11 @@
         <v>3.4385952048858868</v>
       </c>
       <c r="F81" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$81,$A81&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B81,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A81&lt;Inputs!$B$84,$A81&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B81,$A$15:$A$60,0))))</f>
         <v>46483.518378385568</v>
       </c>
       <c r="G81" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C81,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A81&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C81,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C81,$A$15:$A$60,0))))</f>
         <v>35065.107177427992</v>
       </c>
       <c r="H81" s="14">
@@ -4486,7 +4537,7 @@
         <v>280412.71280125517</v>
       </c>
       <c r="I81" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A81&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A81-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A81&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A81-Inputs!$B$83))</f>
         <v>101377.81665092276</v>
       </c>
       <c r="J81" s="14">
@@ -4507,7 +4558,7 @@
         <v>68</v>
       </c>
       <c r="D82" s="18">
-        <f>IF($A82=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A82&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A82-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A82=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A82&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A82-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E82" s="21">
@@ -4515,11 +4566,11 @@
         <v>3.6449109171790401</v>
       </c>
       <c r="F82" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$81,$A82&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B82,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A82&lt;Inputs!$B$84,$A82&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B82,$A$15:$A$60,0))))</f>
         <v>48830.817743250918</v>
       </c>
       <c r="G82" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C82,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A82&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C82,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C82,$A$15:$A$60,0))))</f>
         <v>36938.230459303144</v>
       </c>
       <c r="H82" s="14">
@@ -4527,7 +4578,7 @@
         <v>312620.5401495446</v>
       </c>
       <c r="I82" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A82&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A82-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A82&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A82-Inputs!$B$83))</f>
         <v>103912.26206719583</v>
       </c>
       <c r="J82" s="14">
@@ -4548,7 +4599,7 @@
         <v>69</v>
       </c>
       <c r="D83" s="18">
-        <f>IF($A83=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A83&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A83-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A83=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A83&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A83-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E83" s="21">
@@ -4556,11 +4607,11 @@
         <v>3.8636055722097828</v>
       </c>
       <c r="F83" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$81,$A83&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B83,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A83&lt;Inputs!$B$84,$A83&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B83,$A$15:$A$60,0))))</f>
         <v>51296.649751524339</v>
       </c>
       <c r="G83" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C83,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A83&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C83,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C83,$A$15:$A$60,0))))</f>
         <v>38911.413062581472</v>
       </c>
       <c r="H83" s="14">
@@ -4568,7 +4619,7 @@
         <v>348528.3741468293</v>
       </c>
       <c r="I83" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A83&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A83-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A83&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A83-Inputs!$B$83))</f>
         <v>106510.06861887571</v>
       </c>
       <c r="J83" s="14">
@@ -4589,7 +4640,7 @@
         <v>70</v>
       </c>
       <c r="D84" s="18">
-        <f>IF($A84=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A84&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A84-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A84=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A84&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A84-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E84" s="21">
@@ -4597,11 +4648,11 @@
         <v>4.09542190654237</v>
       </c>
       <c r="F84" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$81,$A84&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B84,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A84&lt;Inputs!$B$84,$A84&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B84,$A$15:$A$60,0))))</f>
         <v>53887</v>
       </c>
       <c r="G84" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C84,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A84&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C84,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C84,$A$15:$A$60,0))))</f>
         <v>40990</v>
       </c>
       <c r="H84" s="14">
@@ -4609,7 +4660,7 @@
         <v>388561.34422702045</v>
       </c>
       <c r="I84" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A84&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A84-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A84&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A84-Inputs!$B$83))</f>
         <v>109172.82033434759</v>
       </c>
       <c r="J84" s="14">
@@ -4630,7 +4681,7 @@
         <v>71</v>
       </c>
       <c r="D85" s="18">
-        <f>IF($A85=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A85&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A85-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A85=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A85&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A85-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E85" s="21">
@@ -4638,11 +4689,11 @@
         <v>4.3411472209349125</v>
       </c>
       <c r="F85" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$81,$A85&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B85,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A85&lt;Inputs!$B$84,$A85&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B85,$A$15:$A$60,0))))</f>
         <v>55710.710648470209</v>
       </c>
       <c r="G85" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C85,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A85&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C85,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C85,$A$15:$A$60,0))))</f>
         <v>43188.72312279437</v>
       </c>
       <c r="H85" s="14">
@@ -4650,7 +4701,7 @@
         <v>429337.00206816167</v>
       </c>
       <c r="I85" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A85&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A85-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A85&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A85-Inputs!$B$83))</f>
         <v>111902.14084270629</v>
       </c>
       <c r="J85" s="14">
@@ -4671,7 +4722,7 @@
         <v>72</v>
       </c>
       <c r="D86" s="18">
-        <f>IF($A86=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A86&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A86-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A86=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A86&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A86-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E86" s="21">
@@ -4679,11 +4730,11 @@
         <v>4.6016160541910072</v>
       </c>
       <c r="F86" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$81,$A86&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B86,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A86&lt;Inputs!$B$84,$A86&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B86,$A$15:$A$60,0))))</f>
         <v>57596.141573247209</v>
       </c>
       <c r="G86" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C86,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A86&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C86,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C86,$A$15:$A$60,0))))</f>
         <v>45505.38680110743</v>
       </c>
       <c r="H86" s="14">
@@ -4691,7 +4742,7 @@
         <v>474433.64817905996</v>
       </c>
       <c r="I86" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A86&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A86-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A86&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A86-Inputs!$B$83))</f>
         <v>114699.69436377395</v>
       </c>
       <c r="J86" s="14">
@@ -4712,7 +4763,7 @@
         <v>73</v>
       </c>
       <c r="D87" s="18">
-        <f>IF($A87=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A87&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A87-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A87=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A87&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A87-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E87" s="21">
@@ -4720,11 +4771,11 @@
         <v>4.8777130174424679</v>
       </c>
       <c r="F87" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$81,$A87&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B87,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A87&lt;Inputs!$B$84,$A87&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B87,$A$15:$A$60,0))))</f>
         <v>59545.381588425793</v>
       </c>
       <c r="G87" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C87,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A87&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C87,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C87,$A$15:$A$60,0))))</f>
         <v>47946.317422510139</v>
       </c>
       <c r="H87" s="14">
@@ -4732,7 +4783,7 @@
         <v>524313.65953264979</v>
       </c>
       <c r="I87" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A87&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A87-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A87&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A87-Inputs!$B$83))</f>
         <v>117567.18672286828</v>
       </c>
       <c r="J87" s="14">
@@ -4753,7 +4804,7 @@
         <v>74</v>
       </c>
       <c r="D88" s="18">
-        <f>IF($A88=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A88&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A88-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A88=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A88&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A88-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E88" s="21">
@@ -4761,11 +4812,11 @@
         <v>5.1703757984890162</v>
       </c>
       <c r="F88" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$81,$A88&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B88,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A88&lt;Inputs!$B$84,$A88&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B88,$A$15:$A$60,0))))</f>
         <v>61560.590200336541</v>
       </c>
       <c r="G88" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C88,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A88&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C88,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C88,$A$15:$A$60,0))))</f>
         <v>50518.180725015911</v>
       </c>
       <c r="H88" s="14">
@@ -4773,7 +4824,7 @@
         <v>579489.36471683672</v>
       </c>
       <c r="I88" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A88&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A88-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A88&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A88-Inputs!$B$83))</f>
         <v>120506.36639093996</v>
       </c>
       <c r="J88" s="14">
@@ -4794,7 +4845,7 @@
         <v>75</v>
       </c>
       <c r="D89" s="18">
-        <f>IF($A89=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A89&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A89-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A89=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A89&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A89-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E89" s="21">
@@ -4802,11 +4853,11 @@
         <v>5.4805983463983576</v>
       </c>
       <c r="F89" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$81,$A89&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B89,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A89&lt;Inputs!$B$84,$A89&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B89,$A$15:$A$60,0))))</f>
         <v>63644</v>
       </c>
       <c r="G89" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C89,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A89&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C89,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C89,$A$15:$A$60,0))))</f>
         <v>53228</v>
       </c>
       <c r="H89" s="14">
@@ -4814,7 +4865,7 @@
         <v>640528.4899402688</v>
       </c>
       <c r="I89" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A89&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A89-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A89&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A89-Inputs!$B$83))</f>
         <v>123519.02555071346</v>
       </c>
       <c r="J89" s="14">
@@ -4835,7 +4886,7 @@
         <v>76</v>
       </c>
       <c r="D90" s="18">
-        <f>IF($A90=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A90&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A90-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A90=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A90&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A90-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E90" s="21">
@@ -4843,11 +4894,11 @@
         <v>5.8094342471822591</v>
       </c>
       <c r="F90" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$81,$A90&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B90,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A90&lt;Inputs!$B$84,$A90&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B90,$A$15:$A$60,0))))</f>
         <v>65797.919136549404</v>
       </c>
       <c r="G90" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C90,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A90&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C90,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C90,$A$15:$A$60,0))))</f>
         <v>55012.997845753707</v>
       </c>
       <c r="H90" s="14">
@@ -4855,7 +4906,7 @@
         <v>701843.0785504845</v>
       </c>
       <c r="I90" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A90&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A90-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A90&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A90-Inputs!$B$83))</f>
         <v>126607.00118948129</v>
       </c>
       <c r="J90" s="14">
@@ -4876,7 +4927,7 @@
         <v>77</v>
       </c>
       <c r="D91" s="18">
-        <f>IF($A91=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A91&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A91-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A91=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A91&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A91-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E91" s="21">
@@ -4884,11 +4935,11 @@
         <v>6.1580003020131953</v>
       </c>
       <c r="F91" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$81,$A91&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B91,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A91&lt;Inputs!$B$84,$A91&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B91,$A$15:$A$60,0))))</f>
         <v>68024.733874361991</v>
       </c>
       <c r="G91" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C91,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A91&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C91,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C91,$A$15:$A$60,0))))</f>
         <v>56857.855489157992</v>
       </c>
       <c r="H91" s="14">
@@ -4896,7 +4947,7 @@
         <v>769027.02301674581</v>
       </c>
       <c r="I91" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A91&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A91-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A91&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A91-Inputs!$B$83))</f>
         <v>129772.17621921831</v>
       </c>
       <c r="J91" s="14">
@@ -4917,7 +4968,7 @@
         <v>78</v>
       </c>
       <c r="D92" s="18">
-        <f>IF($A92=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A92&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A92-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A92=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A92&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A92-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E92" s="21">
@@ -4925,11 +4976,11 @@
         <v>6.5274803201339875</v>
       </c>
       <c r="F92" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$81,$A92&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B92,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A92&lt;Inputs!$B$84,$A92&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B92,$A$15:$A$60,0))))</f>
         <v>70326.911236731874</v>
       </c>
       <c r="G92" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C92,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A92&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C92,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C92,$A$15:$A$60,0))))</f>
         <v>58764.580325002338</v>
       </c>
       <c r="H92" s="14">
@@ -4937,7 +4988,7 @@
         <v>842642.17066596274</v>
       </c>
       <c r="I92" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A92&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A92-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A92&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A92-Inputs!$B$83))</f>
         <v>133016.48062469877</v>
       </c>
       <c r="J92" s="14">
@@ -4958,7 +5009,7 @@
         <v>79</v>
       </c>
       <c r="D93" s="18">
-        <f>IF($A93=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A93&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A93-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A93=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A93&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A93-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E93" s="21">
@@ -4966,11 +5017,11 @@
         <v>6.9191291393420267</v>
       </c>
       <c r="F93" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$81,$A93&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B93,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A93&lt;Inputs!$B$84,$A93&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B93,$A$15:$A$60,0))))</f>
         <v>72707.001739013445</v>
       </c>
       <c r="G93" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C93,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A93&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C93,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C93,$A$15:$A$60,0))))</f>
         <v>60735.247065942247</v>
       </c>
       <c r="H93" s="14">
@@ -4978,7 +5029,7 @@
         <v>923304.15212569758</v>
       </c>
       <c r="I93" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A93&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A93-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A93&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A93-Inputs!$B$83))</f>
         <v>136341.89264031622</v>
       </c>
       <c r="J93" s="14">
@@ -4999,7 +5050,7 @@
         <v>80</v>
       </c>
       <c r="D94" s="18">
-        <f>IF($A94=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A94&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A94-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A94=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A94&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A94-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E94" s="21">
@@ -5007,11 +5058,11 @@
         <v>7.3342768877025488</v>
       </c>
       <c r="F94" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$81,$A94&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B94,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A94&lt;Inputs!$B$84,$A94&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B94,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G94" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C94,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A94&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C94,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C94,$A$15:$A$60,0))))</f>
         <v>62772</v>
       </c>
       <c r="H94" s="14">
@@ -5019,7 +5070,7 @@
         <v>460387.22879486438</v>
       </c>
       <c r="I94" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A94&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A94-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A94&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A94-Inputs!$B$83))</f>
         <v>139750.43995632418</v>
       </c>
       <c r="J94" s="14">
@@ -5040,7 +5091,7 @@
         <v>81</v>
       </c>
       <c r="D95" s="18">
-        <f>IF($A95=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A95&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A95-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A95=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A95&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A95-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E95" s="21">
@@ -5048,11 +5099,11 @@
         <v>7.7743335009647021</v>
       </c>
       <c r="F95" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$81,$A95&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B95,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A95&lt;Inputs!$B$84,$A95&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B95,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G95" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C95,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A95&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C95,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C95,$A$15:$A$60,0))))</f>
         <v>64877.055323770415</v>
       </c>
       <c r="H95" s="14">
@@ -5060,7 +5111,7 @@
         <v>504375.86464752874</v>
       </c>
       <c r="I95" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A95&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A95-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A95&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A95-Inputs!$B$83))</f>
         <v>143244.20095523223</v>
       </c>
       <c r="J95" s="14">
@@ -5081,7 +5132,7 @@
         <v>82</v>
       </c>
       <c r="D96" s="18">
-        <f>IF($A96=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A96&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A96-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A96=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A96&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A96-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E96" s="21">
@@ -5089,11 +5140,11 @@
         <v>8.2407935110225843</v>
       </c>
       <c r="F96" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$81,$A96&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B96,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A96&lt;Inputs!$B$84,$A96&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B96,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G96" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C96,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A96&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C96,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C96,$A$15:$A$60,0))))</f>
         <v>67052.703553870626</v>
       </c>
       <c r="H96" s="14">
@@ -5101,7 +5152,7 @@
         <v>552567.48434325808</v>
       </c>
       <c r="I96" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A96&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A96-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A96&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A96-Inputs!$B$83))</f>
         <v>146825.30597911304</v>
       </c>
       <c r="J96" s="14">
@@ -5122,7 +5173,7 @@
         <v>83</v>
       </c>
       <c r="D97" s="18">
-        <f>IF($A97=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A97&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A97-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A97=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A97&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A97-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E97" s="21">
@@ -5130,11 +5181,11 @@
         <v>8.7352411216839396</v>
       </c>
       <c r="F97" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$81,$A97&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B97,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A97&lt;Inputs!$B$84,$A97&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B97,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G97" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C97,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A97&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C97,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C97,$A$15:$A$60,0))))</f>
         <v>69301.312019257661</v>
       </c>
       <c r="H97" s="14">
@@ -5142,7 +5193,7 @@
         <v>605363.67053726898</v>
       </c>
       <c r="I97" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A97&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A97-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A97&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A97-Inputs!$B$83))</f>
         <v>150495.93862859087</v>
       </c>
       <c r="J97" s="14">
@@ -5163,7 +5214,7 @@
         <v>84</v>
       </c>
       <c r="D98" s="18">
-        <f>IF($A98=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A98&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A98-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A98=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A98&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A98-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E98" s="21">
@@ -5171,11 +5222,11 @@
         <v>9.2593555889849757</v>
       </c>
       <c r="F98" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$81,$A98&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B98,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A98&lt;Inputs!$B$84,$A98&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B98,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G98" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C98,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A98&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C98,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C98,$A$15:$A$60,0))))</f>
         <v>71625.327437125714</v>
       </c>
       <c r="H98" s="14">
@@ -5183,7 +5234,7 @@
         <v>663204.37591782887</v>
       </c>
       <c r="I98" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A98&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A98-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A98&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A98-Inputs!$B$83))</f>
         <v>154258.33709430561</v>
       </c>
       <c r="J98" s="14">
@@ -5204,7 +5255,7 @@
         <v>85</v>
       </c>
       <c r="D99" s="18">
-        <f>IF($A99=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A99&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A99-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A99=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A99&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A99-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E99" s="21">
@@ -5212,11 +5263,11 @@
         <v>9.8149169243240753</v>
       </c>
       <c r="F99" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$81,$A99&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B99,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A99&lt;Inputs!$B$84,$A99&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B99,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G99" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C99,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A99&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C99,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C99,$A$15:$A$60,0))))</f>
         <v>74027.278575186006</v>
       </c>
       <c r="H99" s="14">
@@ -5224,7 +5275,7 @@
         <v>726571.58934924612</v>
       </c>
       <c r="I99" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A99&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A99-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A99&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A99-Inputs!$B$83))</f>
         <v>158114.79552166327</v>
       </c>
       <c r="J99" s="14">
@@ -5245,7 +5296,7 @@
         <v>86</v>
       </c>
       <c r="D100" s="18">
-        <f>IF($A100=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A100&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A100-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A100=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A100&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A100-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E100" s="21">
@@ -5253,11 +5304,11 @@
         <v>10.40381193978352</v>
       </c>
       <c r="F100" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$81,$A100&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B100,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A100&lt;Inputs!$B$84,$A100&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B100,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G100" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C100,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A100&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C100,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C100,$A$15:$A$60,0))))</f>
         <v>76509.779003226067</v>
       </c>
       <c r="H100" s="14">
@@ -5265,7 +5316,7 @@
         <v>795993.35230396176</v>
       </c>
       <c r="I100" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A100&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A100-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A100&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A100-Inputs!$B$83))</f>
         <v>162067.66540970482</v>
       </c>
       <c r="J100" s="14">
@@ -5286,7 +5337,7 @@
         <v>87</v>
       </c>
       <c r="D101" s="18">
-        <f>IF($A101=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A101&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A101-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A101=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A101&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A101-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E101" s="21">
@@ -5294,11 +5345,11 @@
         <v>11.028040656170532</v>
       </c>
       <c r="F101" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$81,$A101&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B101,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A101&lt;Inputs!$B$84,$A101&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B101,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G101" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C101,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A101&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C101,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C101,$A$15:$A$60,0))))</f>
         <v>79075.529936942359</v>
       </c>
       <c r="H101" s="14">
@@ -5306,7 +5357,7 @@
         <v>872048.15905283031</v>
       </c>
       <c r="I101" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A101&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A101-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A101&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A101-Inputs!$B$83))</f>
         <v>166119.35704494742</v>
       </c>
       <c r="J101" s="14">
@@ -5327,7 +5378,7 @@
         <v>88</v>
       </c>
       <c r="D102" s="18">
-        <f>IF($A102=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A102&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A102-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A102=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A102&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A102-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E102" s="21">
@@ -5335,11 +5386,11 @@
         <v>11.689723095540764</v>
       </c>
       <c r="F102" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$81,$A102&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B102,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A102&lt;Inputs!$B$84,$A102&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B102,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G102" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C102,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A102&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C102,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C102,$A$15:$A$60,0))))</f>
         <v>81727.323177140657</v>
       </c>
       <c r="H102" s="14">
@@ -5347,7 +5398,7 @@
         <v>955369.77728054509</v>
       </c>
       <c r="I102" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A102&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A102-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A102&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A102-Inputs!$B$83))</f>
         <v>170272.3409710711</v>
       </c>
       <c r="J102" s="14">
@@ -5368,7 +5419,7 @@
         <v>89</v>
       </c>
       <c r="D103" s="18">
-        <f>IF($A103=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A103&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A103-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A103=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A103&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A103-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E103" s="21">
@@ -5376,11 +5427,11 @@
         <v>12.39110648127321</v>
       </c>
       <c r="F103" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$81,$A103&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B103,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A103&lt;Inputs!$B$84,$A103&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B103,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G103" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C103,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A103&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C103,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C103,$A$15:$A$60,0))))</f>
         <v>84468.044147502369</v>
       </c>
       <c r="H103" s="14">
@@ -5388,7 +5439,7 @@
         <v>1046652.5292965883</v>
       </c>
       <c r="I103" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A103&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A103-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A103&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A103-Inputs!$B$83))</f>
         <v>174529.14949534787</v>
       </c>
       <c r="J103" s="14">
@@ -5409,7 +5460,7 @@
         <v>90</v>
       </c>
       <c r="D104" s="18">
-        <f>IF($A104=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A104&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A104-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A104=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A104&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A104-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E104" s="21">
@@ -5417,11 +5468,11 @@
         <v>13.134572870149604</v>
       </c>
       <c r="F104" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$81,$A104&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B104,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A104&lt;Inputs!$B$84,$A104&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B104,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G104" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C104,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A104&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C104,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C104,$A$15:$A$60,0))))</f>
         <v>87300.675034222149</v>
       </c>
       <c r="H104" s="14">
@@ -5429,7 +5480,7 @@
         <v>1146657.0778502412</v>
       </c>
       <c r="I104" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A104&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A104-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A104&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A104-Inputs!$B$83))</f>
         <v>178892.37823273157</v>
       </c>
       <c r="J104" s="14">
@@ -5450,7 +5501,7 @@
         <v>91</v>
       </c>
       <c r="D105" s="18">
-        <f>IF($A105=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A105&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A105-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A105=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A105&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A105-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E105" s="21">
@@ -5458,11 +5509,11 @@
         <v>13.922647242358581</v>
       </c>
       <c r="F105" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$81,$A105&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B105,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A105&lt;Inputs!$B$84,$A105&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B105,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G105" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C105,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A105&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C105,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C105,$A$15:$A$60,0))))</f>
         <v>90228.298030933103</v>
       </c>
       <c r="H105" s="14">
@@ -5470,7 +5521,7 @@
         <v>1256216.7647630789</v>
       </c>
       <c r="I105" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A105&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A105-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A105&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A105-Inputs!$B$83))</f>
         <v>183364.68768854984</v>
       </c>
       <c r="J105" s="14">
@@ -5491,7 +5542,7 @@
         <v>92</v>
       </c>
       <c r="D106" s="18">
-        <f>IF($A106=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A106&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A106-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A106=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A106&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A106-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E106" s="21">
@@ -5499,11 +5550,11 @@
         <v>14.758006076900097</v>
       </c>
       <c r="F106" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$81,$A106&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B106,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A106&lt;Inputs!$B$84,$A106&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B106,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G106" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C106,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A106&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C106,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C106,$A$15:$A$60,0))))</f>
         <v>93254.098692450338</v>
       </c>
       <c r="H106" s="14">
@@ -5511,7 +5562,7 @@
         <v>1376244.5551990236</v>
       </c>
       <c r="I106" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A106&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A106-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A106&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A106-Inputs!$B$83))</f>
         <v>187948.80488076361</v>
       </c>
       <c r="J106" s="14">
@@ -5532,7 +5583,7 @@
         <v>93</v>
       </c>
       <c r="D107" s="18">
-        <f>IF($A107=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A107&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A107-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A107=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A107&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A107-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E107" s="21">
@@ -5540,11 +5591,11 @@
         <v>15.643486441514103</v>
       </c>
       <c r="F107" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$81,$A107&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B107,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A107&lt;Inputs!$B$84,$A107&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B107,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G107" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C107,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A107&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C107,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C107,$A$15:$A$60,0))))</f>
         <v>96381.369400982076</v>
       </c>
       <c r="H107" s="14">
@@ -5552,7 +5603,7 @@
         <v>1507740.6454388252</v>
       </c>
       <c r="I107" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A107&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A107-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A107&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A107-Inputs!$B$83))</f>
         <v>192647.52500278264</v>
       </c>
       <c r="J107" s="14">
@@ -5573,7 +5624,7 @@
         <v>94</v>
       </c>
       <c r="D108" s="18">
-        <f>IF($A108=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A108&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A108-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A108=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A108&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A108-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E108" s="21">
@@ -5581,11 +5632,11 @@
         <v>16.58209562800495</v>
       </c>
       <c r="F108" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$81,$A108&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B108,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A108&lt;Inputs!$B$84,$A108&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B108,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G108" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C108,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A108&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C108,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C108,$A$15:$A$60,0))))</f>
         <v>99613.512948580057</v>
       </c>
       <c r="H108" s="14">
@@ -5593,7 +5644,7 @@
         <v>1651800.7975548638</v>
       </c>
       <c r="I108" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A108&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A108-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A108&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A108-Inputs!$B$83))</f>
         <v>197463.71312785221</v>
       </c>
       <c r="J108" s="14">
@@ -5614,7 +5665,7 @@
         <v>95</v>
       </c>
       <c r="D109" s="18">
-        <f>IF($A109=Inputs!$B$80,0,IF(Inputs!$B$49=1,Inputs!$B$48,IF($A109&gt;=Inputs!$B$47,Inputs!$B$46,Inputs!$B$45-(Inputs!$B$45-Inputs!$B$46)*($A109-(Inputs!$B$80+1))/(Inputs!$B$47-(Inputs!$B$80+1)))))</f>
+        <f>IF($A109=Inputs!$B$83,0,IF(Inputs!$B$52=1,Inputs!$B$51,IF($A109&gt;=Inputs!$B$50,Inputs!$B$49,Inputs!$B$48-(Inputs!$B$48-Inputs!$B$49)*($A109-(Inputs!$B$83+1))/(Inputs!$B$50-(Inputs!$B$83+1)))))</f>
         <v>0.06</v>
       </c>
       <c r="E109" s="21">
@@ -5622,11 +5673,11 @@
         <v>17.577021365685248</v>
       </c>
       <c r="F109" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$81,$A109&gt;Inputs!$B$84),0,IF(Inputs!$B$44=1,INDEX($B$15:$B$60,MATCH(B109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B109,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A109&lt;Inputs!$B$84,$A109&gt;Inputs!$B$87),0,IF(Inputs!$B$47=1,INDEX($B$15:$B$60,MATCH(B109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(B109,$A$15:$A$60,0))))</f>
         <v>0</v>
       </c>
       <c r="G109" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$82),0,IF(Inputs!$B$44=1,INDEX($C$15:$C$60,MATCH(C109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C109,$A$15:$A$60,0))))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A109&lt;Inputs!$B$85),0,IF(Inputs!$B$47=1,INDEX($C$15:$C$60,MATCH(C109,$A$15:$A$60,0)),INDEX($D$15:$D$60,MATCH(C109,$A$15:$A$60,0))))</f>
         <v>102954.04623972709</v>
       </c>
       <c r="H109" s="14">
@@ -5634,7 +5685,7 @@
         <v>1809625.4704394301</v>
       </c>
       <c r="I109" s="14">
-        <f>IF(OR(Inputs!$B$44=0,$A109&lt;Inputs!$B$81),0,Inputs!$B$50*(1+Inputs!$B$5)^($A109-Inputs!$B$80))</f>
+        <f>IF(OR(Inputs!$B$47=0,$A109&lt;Inputs!$B$84),0,Inputs!$B$53*(1+Inputs!$B$5)^($A109-Inputs!$B$83))</f>
         <v>202400.30595604848</v>
       </c>
       <c r="J109" s="14">
@@ -5658,77 +5709,77 @@
   <sheetData>
     <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="U3" s="19" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -5744,19 +5795,19 @@
         <v>49</v>
       </c>
       <c r="D4" s="16">
-        <f>IF($A4&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A4-Inputs!$B$80),0)</f>
+        <f>IF($A4&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A4-Inputs!$B$83),0)</f>
         <v>1200000</v>
       </c>
       <c r="E4" s="16">
-        <f>IF($A4&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A4-Inputs!$B$80),0)</f>
+        <f>IF($A4&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A4-Inputs!$B$83),0)</f>
         <v>720000</v>
       </c>
       <c r="F4" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A4-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A4-Inputs!$B$83)</f>
         <v>395000</v>
       </c>
       <c r="G4" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A4-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A4-Inputs!$B$83)</f>
         <v>145000</v>
       </c>
       <c r="H4" s="16">
@@ -5772,15 +5823,15 @@
         <v>36000</v>
       </c>
       <c r="K4" s="16">
-        <f>IF($A4&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A4-Inputs!$B$80),0)</f>
+        <f>IF($A4&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A4-Inputs!$B$83),0)</f>
         <v>984000</v>
       </c>
       <c r="L4" s="16">
-        <f>IF(AND($A4&gt;=Inputs!$B$83,$A4&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A4-Inputs!$B$80),0)</f>
+        <f>IF(AND($A4&gt;=Inputs!$B$86,$A4&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A4-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M4" s="16">
-        <f>IF($A4&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A4-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A4&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A4&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A4-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A4&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N4" s="16">
@@ -5788,15 +5839,15 @@
         <v>0</v>
       </c>
       <c r="O4" s="16">
-        <f>IF($A4&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A4&gt;=Inputs!$B$84,$A4&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A4&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P4" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A4=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A4&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A4=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A4&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q4" s="16">
-        <f>D4+E4-H4-I4+J4-K4-L4-M4-N4+O4+P4-IF($A4&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D4+E4-H4-I4+J4-K4-L4-M4-N4+O4+P4-IF($A4&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>676630</v>
       </c>
       <c r="R4" s="16">
@@ -5808,7 +5859,7 @@
         <v>469920</v>
       </c>
       <c r="T4" s="16">
-        <f>IF($A4=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A4=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A4=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U4" s="16">
@@ -5829,19 +5880,19 @@
         <v>50</v>
       </c>
       <c r="D5" s="16">
-        <f>IF($A5&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A5-Inputs!$B$80),0)</f>
+        <f>IF($A5&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A5-Inputs!$B$83),0)</f>
         <v>1236000</v>
       </c>
       <c r="E5" s="16">
-        <f>IF($A5&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A5-Inputs!$B$80),0)</f>
+        <f>IF($A5&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A5-Inputs!$B$83),0)</f>
         <v>741600</v>
       </c>
       <c r="F5" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A5-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A5-Inputs!$B$83)</f>
         <v>404874.99999999994</v>
       </c>
       <c r="G5" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A5-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A5-Inputs!$B$83)</f>
         <v>148625</v>
       </c>
       <c r="H5" s="16">
@@ -5857,15 +5908,15 @@
         <v>36000</v>
       </c>
       <c r="K5" s="16">
-        <f>IF($A5&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A5-Inputs!$B$80),0)</f>
+        <f>IF($A5&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A5-Inputs!$B$83),0)</f>
         <v>1008599.9999999999</v>
       </c>
       <c r="L5" s="16">
-        <f>IF(AND($A5&gt;=Inputs!$B$83,$A5&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A5-Inputs!$B$80),0)</f>
+        <f>IF(AND($A5&gt;=Inputs!$B$86,$A5&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A5-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M5" s="16">
-        <f>IF($A5&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A5-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A5&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A5&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A5-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A5&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N5" s="16">
@@ -5873,15 +5924,15 @@
         <v>0</v>
       </c>
       <c r="O5" s="16">
-        <f>IF($A5&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A5&gt;=Inputs!$B$84,$A5&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A5&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P5" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A5=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A5&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A5=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A5&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q5" s="16">
-        <f>D5+E5-H5-I5+J5-K5-L5-M5-N5+O5+P5-IF($A5&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D5+E5-H5-I5+J5-K5-L5-M5-N5+O5+P5-IF($A5&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>702133.00000000012</v>
       </c>
       <c r="R5" s="16">
@@ -5893,7 +5944,7 @@
         <v>524954.4</v>
       </c>
       <c r="T5" s="16">
-        <f>IF($A5=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A5=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A5=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U5" s="16">
@@ -5914,19 +5965,19 @@
         <v>51</v>
       </c>
       <c r="D6" s="16">
-        <f>IF($A6&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A6-Inputs!$B$80),0)</f>
+        <f>IF($A6&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A6-Inputs!$B$83),0)</f>
         <v>1273080</v>
       </c>
       <c r="E6" s="16">
-        <f>IF($A6&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A6-Inputs!$B$80),0)</f>
+        <f>IF($A6&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A6-Inputs!$B$83),0)</f>
         <v>763848</v>
       </c>
       <c r="F6" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A6-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A6-Inputs!$B$83)</f>
         <v>414996.87499999994</v>
       </c>
       <c r="G6" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A6-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A6-Inputs!$B$83)</f>
         <v>152340.625</v>
       </c>
       <c r="H6" s="16">
@@ -5942,15 +5993,15 @@
         <v>36000</v>
       </c>
       <c r="K6" s="16">
-        <f>IF($A6&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A6-Inputs!$B$80),0)</f>
+        <f>IF($A6&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A6-Inputs!$B$83),0)</f>
         <v>1033814.9999999999</v>
       </c>
       <c r="L6" s="16">
-        <f>IF(AND($A6&gt;=Inputs!$B$83,$A6&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A6-Inputs!$B$80),0)</f>
+        <f>IF(AND($A6&gt;=Inputs!$B$86,$A6&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A6-Inputs!$B$83),0)</f>
         <v>661500</v>
       </c>
       <c r="M6" s="16">
-        <f>IF($A6&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A6-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A6&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A6&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A6-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A6&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N6" s="16">
@@ -5958,15 +6009,15 @@
         <v>0</v>
       </c>
       <c r="O6" s="16">
-        <f>IF($A6&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A6&gt;=Inputs!$B$84,$A6&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A6&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P6" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A6=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A6&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A6=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A6&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="16">
-        <f>D6+E6-H6-I6+J6-K6-L6-M6-N6+O6+P6-IF($A6&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D6+E6-H6-I6+J6-K6-L6-M6-N6+O6+P6-IF($A6&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>67012.615000000107</v>
       </c>
       <c r="R6" s="16">
@@ -5978,7 +6029,7 @@
         <v>583854.59519999998</v>
       </c>
       <c r="T6" s="16">
-        <f>IF($A6=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A6=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A6=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U6" s="16">
@@ -5999,19 +6050,19 @@
         <v>52</v>
       </c>
       <c r="D7" s="16">
-        <f>IF($A7&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A7-Inputs!$B$80),0)</f>
+        <f>IF($A7&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A7-Inputs!$B$83),0)</f>
         <v>1311272.3999999999</v>
       </c>
       <c r="E7" s="16">
-        <f>IF($A7&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A7-Inputs!$B$80),0)</f>
+        <f>IF($A7&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A7-Inputs!$B$83),0)</f>
         <v>786763.44000000006</v>
       </c>
       <c r="F7" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A7-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A7-Inputs!$B$83)</f>
         <v>425371.79687499994</v>
       </c>
       <c r="G7" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A7-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A7-Inputs!$B$83)</f>
         <v>156149.14062499997</v>
       </c>
       <c r="H7" s="16">
@@ -6027,15 +6078,15 @@
         <v>36000</v>
       </c>
       <c r="K7" s="16">
-        <f>IF($A7&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A7-Inputs!$B$80),0)</f>
+        <f>IF($A7&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A7-Inputs!$B$83),0)</f>
         <v>1059660.3749999998</v>
       </c>
       <c r="L7" s="16">
-        <f>IF(AND($A7&gt;=Inputs!$B$83,$A7&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A7-Inputs!$B$80),0)</f>
+        <f>IF(AND($A7&gt;=Inputs!$B$86,$A7&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A7-Inputs!$B$83),0)</f>
         <v>694575.00000000012</v>
       </c>
       <c r="M7" s="16">
-        <f>IF($A7&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A7-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A7&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A7&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A7-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A7&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N7" s="16">
@@ -6043,15 +6094,15 @@
         <v>0</v>
       </c>
       <c r="O7" s="16">
-        <f>IF($A7&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A7&gt;=Inputs!$B$84,$A7&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A7&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A7=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A7&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A7=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A7&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="16">
-        <f>D7+E7-H7-I7+J7-K7-L7-M7-N7+O7+P7-IF($A7&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D7+E7-H7-I7+J7-K7-L7-M7-N7+O7+P7-IF($A7&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>61222.931574999937</v>
       </c>
       <c r="R7" s="16">
@@ -6063,7 +6114,7 @@
         <v>615096.22128960001</v>
       </c>
       <c r="T7" s="16">
-        <f>IF($A7=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A7=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A7=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U7" s="16">
@@ -6084,19 +6135,19 @@
         <v>53</v>
       </c>
       <c r="D8" s="16">
-        <f>IF($A8&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A8-Inputs!$B$80),0)</f>
+        <f>IF($A8&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A8-Inputs!$B$83),0)</f>
         <v>1350610.5719999999</v>
       </c>
       <c r="E8" s="16">
-        <f>IF($A8&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A8-Inputs!$B$80),0)</f>
+        <f>IF($A8&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A8-Inputs!$B$83),0)</f>
         <v>810366.34319999989</v>
       </c>
       <c r="F8" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A8-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A8-Inputs!$B$83)</f>
         <v>436006.09179687488</v>
       </c>
       <c r="G8" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A8-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A8-Inputs!$B$83)</f>
         <v>160052.86914062497</v>
       </c>
       <c r="H8" s="16">
@@ -6112,15 +6163,15 @@
         <v>36000</v>
       </c>
       <c r="K8" s="16">
-        <f>IF($A8&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A8-Inputs!$B$80),0)</f>
+        <f>IF($A8&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A8-Inputs!$B$83),0)</f>
         <v>1086151.8843749997</v>
       </c>
       <c r="L8" s="16">
-        <f>IF(AND($A8&gt;=Inputs!$B$83,$A8&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A8-Inputs!$B$80),0)</f>
+        <f>IF(AND($A8&gt;=Inputs!$B$86,$A8&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A8-Inputs!$B$83),0)</f>
         <v>729303.75</v>
       </c>
       <c r="M8" s="16">
-        <f>IF($A8&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A8-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A8&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A8&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A8-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A8&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="16">
@@ -6128,15 +6179,15 @@
         <v>0</v>
       </c>
       <c r="O8" s="16">
-        <f>IF($A8&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A8&gt;=Inputs!$B$84,$A8&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A8&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P8" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A8=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A8&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A8=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A8&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="16">
-        <f>D8+E8-H8-I8+J8-K8-L8-M8-N8+O8+P8-IF($A8&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D8+E8-H8-I8+J8-K8-L8-M8-N8+O8+P8-IF($A8&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>54715.228600375121</v>
       </c>
       <c r="R8" s="16">
@@ -6148,7 +6199,7 @@
         <v>647559.54062710085</v>
       </c>
       <c r="T8" s="16">
-        <f>IF($A8=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A8=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A8=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U8" s="16">
@@ -6169,19 +6220,19 @@
         <v>54</v>
       </c>
       <c r="D9" s="16">
-        <f>IF($A9&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A9-Inputs!$B$80),0)</f>
+        <f>IF($A9&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A9-Inputs!$B$83),0)</f>
         <v>1391128.8891599998</v>
       </c>
       <c r="E9" s="16">
-        <f>IF($A9&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A9-Inputs!$B$80),0)</f>
+        <f>IF($A9&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A9-Inputs!$B$83),0)</f>
         <v>834677.33349599992</v>
       </c>
       <c r="F9" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A9-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A9-Inputs!$B$83)</f>
         <v>446906.24409179675</v>
       </c>
       <c r="G9" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A9-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A9-Inputs!$B$83)</f>
         <v>164054.19086914058</v>
       </c>
       <c r="H9" s="16">
@@ -6197,15 +6248,15 @@
         <v>36000</v>
       </c>
       <c r="K9" s="16">
-        <f>IF($A9&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A9-Inputs!$B$80),0)</f>
+        <f>IF($A9&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A9-Inputs!$B$83),0)</f>
         <v>1113305.6814843747</v>
       </c>
       <c r="L9" s="16">
-        <f>IF(AND($A9&gt;=Inputs!$B$83,$A9&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A9-Inputs!$B$80),0)</f>
+        <f>IF(AND($A9&gt;=Inputs!$B$86,$A9&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A9-Inputs!$B$83),0)</f>
         <v>765768.93750000012</v>
       </c>
       <c r="M9" s="16">
-        <f>IF($A9&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A9-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A9&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A9&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A9-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A9&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="16">
@@ -6213,15 +6264,15 @@
         <v>0</v>
       </c>
       <c r="O9" s="16">
-        <f>IF($A9&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A9&gt;=Inputs!$B$84,$A9&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A9&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P9" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A9=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A9&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A9=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A9&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q9" s="16">
-        <f>D9+E9-H9-I9+J9-K9-L9-M9-N9+O9+P9-IF($A9&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D9+E9-H9-I9+J9-K9-L9-M9-N9+O9+P9-IF($A9&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>47437.819763464038</v>
       </c>
       <c r="R9" s="16">
@@ -6233,7 +6284,7 @@
         <v>681268.72955001972</v>
       </c>
       <c r="T9" s="16">
-        <f>IF($A9=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A9=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A9=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U9" s="16">
@@ -6254,19 +6305,19 @@
         <v>55</v>
       </c>
       <c r="D10" s="16">
-        <f>IF($A10&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A10-Inputs!$B$80),0)</f>
+        <f>IF($A10&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A10-Inputs!$B$83),0)</f>
         <v>1432862.7558348</v>
       </c>
       <c r="E10" s="16">
-        <f>IF($A10&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A10-Inputs!$B$80),0)</f>
+        <f>IF($A10&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A10-Inputs!$B$83),0)</f>
         <v>859717.65350087988</v>
       </c>
       <c r="F10" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A10-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A10-Inputs!$B$83)</f>
         <v>458078.90019409161</v>
       </c>
       <c r="G10" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A10-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A10-Inputs!$B$83)</f>
         <v>168155.54564086907</v>
       </c>
       <c r="H10" s="16">
@@ -6282,15 +6333,15 @@
         <v>36000</v>
       </c>
       <c r="K10" s="16">
-        <f>IF($A10&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A10-Inputs!$B$80),0)</f>
+        <f>IF($A10&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A10-Inputs!$B$83),0)</f>
         <v>1141138.3235214839</v>
       </c>
       <c r="L10" s="16">
-        <f>IF(AND($A10&gt;=Inputs!$B$83,$A10&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A10-Inputs!$B$80),0)</f>
+        <f>IF(AND($A10&gt;=Inputs!$B$86,$A10&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A10-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M10" s="16">
-        <f>IF($A10&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A10-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A10&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A10&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A10-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A10&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="16">
@@ -6298,15 +6349,15 @@
         <v>0</v>
       </c>
       <c r="O10" s="16">
-        <f>IF($A10&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A10&gt;=Inputs!$B$84,$A10&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A10&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P10" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A10=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A10&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A10=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A10&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q10" s="16">
-        <f>D10+E10-H10-I10+J10-K10-L10-M10-N10+O10+P10-IF($A10&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D10+E10-H10-I10+J10-K10-L10-M10-N10+O10+P10-IF($A10&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>843393.27201907407</v>
       </c>
       <c r="R10" s="16">
@@ -6318,7 +6369,7 @@
         <v>716246.64391706698</v>
       </c>
       <c r="T10" s="16">
-        <f>IF($A10=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A10=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A10=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U10" s="16">
@@ -6339,19 +6390,19 @@
         <v>56</v>
       </c>
       <c r="D11" s="16">
-        <f>IF($A11&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A11-Inputs!$B$80),0)</f>
+        <f>IF($A11&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A11-Inputs!$B$83),0)</f>
         <v>1475848.638509844</v>
       </c>
       <c r="E11" s="16">
-        <f>IF($A11&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A11-Inputs!$B$80),0)</f>
+        <f>IF($A11&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A11-Inputs!$B$83),0)</f>
         <v>885509.18310590636</v>
       </c>
       <c r="F11" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A11-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A11-Inputs!$B$83)</f>
         <v>469530.87269894395</v>
       </c>
       <c r="G11" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A11-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A11-Inputs!$B$83)</f>
         <v>172359.4342818908</v>
       </c>
       <c r="H11" s="16">
@@ -6367,15 +6418,15 @@
         <v>36000</v>
       </c>
       <c r="K11" s="16">
-        <f>IF($A11&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A11-Inputs!$B$80),0)</f>
+        <f>IF($A11&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A11-Inputs!$B$83),0)</f>
         <v>1169666.781609521</v>
       </c>
       <c r="L11" s="16">
-        <f>IF(AND($A11&gt;=Inputs!$B$83,$A11&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A11-Inputs!$B$80),0)</f>
+        <f>IF(AND($A11&gt;=Inputs!$B$86,$A11&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A11-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M11" s="16">
-        <f>IF($A11&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A11-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A11&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A11&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A11-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A11&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="16">
@@ -6383,15 +6434,15 @@
         <v>0</v>
       </c>
       <c r="O11" s="16">
-        <f>IF($A11&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A11&gt;=Inputs!$B$84,$A11&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A11&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P11" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A11=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A11&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A11=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A11&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="16">
-        <f>D11+E11-H11-I11+J11-K11-L11-M11-N11+O11+P11-IF($A11&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D11+E11-H11-I11+J11-K11-L11-M11-N11+O11+P11-IF($A11&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>874611.56251829374</v>
       </c>
       <c r="R11" s="16">
@@ -6403,7 +6454,7 @@
         <v>791109.35988200165</v>
       </c>
       <c r="T11" s="16">
-        <f>IF($A11=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A11=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A11=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U11" s="16">
@@ -6424,19 +6475,19 @@
         <v>57</v>
       </c>
       <c r="D12" s="16">
-        <f>IF($A12&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A12-Inputs!$B$80),0)</f>
+        <f>IF($A12&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A12-Inputs!$B$83),0)</f>
         <v>1520124.097665139</v>
       </c>
       <c r="E12" s="16">
-        <f>IF($A12&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A12-Inputs!$B$80),0)</f>
+        <f>IF($A12&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A12-Inputs!$B$83),0)</f>
         <v>912074.45859908347</v>
       </c>
       <c r="F12" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A12-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A12-Inputs!$B$83)</f>
         <v>481269.14451641747</v>
       </c>
       <c r="G12" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A12-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A12-Inputs!$B$83)</f>
         <v>176668.42013893806</v>
       </c>
       <c r="H12" s="16">
@@ -6452,15 +6503,15 @@
         <v>36000</v>
       </c>
       <c r="K12" s="16">
-        <f>IF($A12&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A12-Inputs!$B$80),0)</f>
+        <f>IF($A12&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A12-Inputs!$B$83),0)</f>
         <v>1198908.4511497591</v>
       </c>
       <c r="L12" s="16">
-        <f>IF(AND($A12&gt;=Inputs!$B$83,$A12&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A12-Inputs!$B$80),0)</f>
+        <f>IF(AND($A12&gt;=Inputs!$B$86,$A12&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A12-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M12" s="16">
-        <f>IF($A12&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A12-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A12&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A12&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A12-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A12&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N12" s="16">
@@ -6468,15 +6519,15 @@
         <v>0</v>
       </c>
       <c r="O12" s="16">
-        <f>IF($A12&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A12&gt;=Inputs!$B$84,$A12&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A12&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P12" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A12=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A12&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A12=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A12&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q12" s="16">
-        <f>D12+E12-H12-I12+J12-K12-L12-M12-N12+O12+P12-IF($A12&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D12+E12-H12-I12+J12-K12-L12-M12-N12+O12+P12-IF($A12&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>906895.73654095572</v>
       </c>
       <c r="R12" s="16">
@@ -6488,7 +6539,7 @@
         <v>871063.96415721602</v>
       </c>
       <c r="T12" s="16">
-        <f>IF($A12=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A12=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A12=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U12" s="16">
@@ -6509,19 +6560,19 @@
         <v>58</v>
       </c>
       <c r="D13" s="16">
-        <f>IF($A13&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A13-Inputs!$B$80),0)</f>
+        <f>IF($A13&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A13-Inputs!$B$83),0)</f>
         <v>1565727.8205950933</v>
       </c>
       <c r="E13" s="16">
-        <f>IF($A13&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A13-Inputs!$B$80),0)</f>
+        <f>IF($A13&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A13-Inputs!$B$83),0)</f>
         <v>939436.69235705596</v>
       </c>
       <c r="F13" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A13-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A13-Inputs!$B$83)</f>
         <v>493300.87312932784</v>
       </c>
       <c r="G13" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A13-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A13-Inputs!$B$83)</f>
         <v>181085.13064241147</v>
       </c>
       <c r="H13" s="16">
@@ -6537,15 +6588,15 @@
         <v>36000</v>
       </c>
       <c r="K13" s="16">
-        <f>IF($A13&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A13-Inputs!$B$80),0)</f>
+        <f>IF($A13&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A13-Inputs!$B$83),0)</f>
         <v>1228881.1624285027</v>
       </c>
       <c r="L13" s="16">
-        <f>IF(AND($A13&gt;=Inputs!$B$83,$A13&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A13-Inputs!$B$80),0)</f>
+        <f>IF(AND($A13&gt;=Inputs!$B$86,$A13&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A13-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M13" s="16">
-        <f>IF($A13&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A13-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A13&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A13&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A13-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A13&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="16">
@@ -6553,15 +6604,15 @@
         <v>0</v>
       </c>
       <c r="O13" s="16">
-        <f>IF($A13&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A13&gt;=Inputs!$B$84,$A13&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A13&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P13" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A13=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A13&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A13=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A13&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q13" s="16">
-        <f>D13+E13-H13-I13+J13-K13-L13-M13-N13+O13+P13-IF($A13&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D13+E13-H13-I13+J13-K13-L13-M13-N13+O13+P13-IF($A13&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>940281.00396297663</v>
       </c>
       <c r="R13" s="16">
@@ -6573,7 +6624,7 @@
         <v>956406.02979072812</v>
       </c>
       <c r="T13" s="16">
-        <f>IF($A13=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A13=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A13=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U13" s="16">
@@ -6594,19 +6645,19 @@
         <v>59</v>
       </c>
       <c r="D14" s="16">
-        <f>IF($A14&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A14-Inputs!$B$80),0)</f>
+        <f>IF($A14&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A14-Inputs!$B$83),0)</f>
         <v>1612699.6552129462</v>
       </c>
       <c r="E14" s="16">
-        <f>IF($A14&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A14-Inputs!$B$80),0)</f>
+        <f>IF($A14&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A14-Inputs!$B$83),0)</f>
         <v>967619.79312776763</v>
       </c>
       <c r="F14" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A14-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A14-Inputs!$B$83)</f>
         <v>505633.39495756105</v>
       </c>
       <c r="G14" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A14-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A14-Inputs!$B$83)</f>
         <v>185612.25890847179</v>
       </c>
       <c r="H14" s="16">
@@ -6622,15 +6673,15 @@
         <v>36000</v>
       </c>
       <c r="K14" s="16">
-        <f>IF($A14&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A14-Inputs!$B$80),0)</f>
+        <f>IF($A14&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A14-Inputs!$B$83),0)</f>
         <v>1259603.1914892155</v>
       </c>
       <c r="L14" s="16">
-        <f>IF(AND($A14&gt;=Inputs!$B$83,$A14&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A14-Inputs!$B$80),0)</f>
+        <f>IF(AND($A14&gt;=Inputs!$B$86,$A14&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A14-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M14" s="16">
-        <f>IF($A14&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A14-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A14&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A14&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A14-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A14&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="16">
@@ -6638,15 +6689,15 @@
         <v>0</v>
       </c>
       <c r="O14" s="16">
-        <f>IF($A14&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
+        <f>IF(AND($A14&gt;=Inputs!$B$84,$A14&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A14&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
         <v>0</v>
       </c>
       <c r="P14" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A14=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A14&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A14=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A14&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q14" s="16">
-        <f>D14+E14-H14-I14+J14-K14-L14-M14-N14+O14+P14-IF($A14&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
+        <f>D14+E14-H14-I14+J14-K14-L14-M14-N14+O14+P14-IF($A14&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
         <v>974803.71179080242</v>
       </c>
       <c r="R14" s="16">
@@ -6658,7 +6709,7 @@
         <v>1047447.007410906</v>
       </c>
       <c r="T14" s="16">
-        <f>IF($A14=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A14=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A14=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U14" s="16">
@@ -6679,19 +6730,19 @@
         <v>60</v>
       </c>
       <c r="D15" s="23">
-        <f>IF($A15&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A15-Inputs!$B$80),0)</f>
+        <f>IF($A15&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A15-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="23">
-        <f>IF($A15&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A15-Inputs!$B$80),0)</f>
+        <f>IF($A15&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A15-Inputs!$B$83),0)</f>
         <v>996648.38692160079</v>
       </c>
       <c r="F15" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A15-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A15-Inputs!$B$83)</f>
         <v>518274.22983150004</v>
       </c>
       <c r="G15" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A15-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A15-Inputs!$B$83)</f>
         <v>190252.56538118358</v>
       </c>
       <c r="H15" s="23">
@@ -6707,15 +6758,15 @@
         <v>18000</v>
       </c>
       <c r="K15" s="23">
-        <f>IF($A15&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A15-Inputs!$B$80),0)</f>
+        <f>IF($A15&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A15-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="23">
-        <f>IF(AND($A15&gt;=Inputs!$B$83,$A15&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A15-Inputs!$B$80),0)</f>
+        <f>IF(AND($A15&gt;=Inputs!$B$86,$A15&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A15-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="23">
-        <f>IF($A15&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A15-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A15&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A15&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A15-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A15&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1023427.5930849875</v>
       </c>
       <c r="N15" s="23">
@@ -6723,16 +6774,16 @@
         <v>0</v>
       </c>
       <c r="O15" s="23">
-        <f>IF($A15&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A15&gt;=Inputs!$B$84,$A15&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A15&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>160800</v>
       </c>
       <c r="P15" s="23">
-        <f>IF(AND(Inputs!$B$58=1,$A15=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A15&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A15=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A15&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q15" s="23">
-        <f>D15+E15-H15-I15+J15-K15-L15-M15-N15+O15+P15-IF($A15&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>148548.50417474238</v>
+        <f>D15+E15-H15-I15+J15-K15-L15-M15-N15+O15+P15-IF($A15&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>41348.504174742382</v>
       </c>
       <c r="R15" s="23">
         <f t="shared" si="3"/>
@@ -6743,12 +6794,12 @@
         <v>1144515.041932588</v>
       </c>
       <c r="T15" s="23">
-        <f>IF($A15=Inputs!$B$81,-Inputs!$B$38,0)</f>
-        <v>-4120000</v>
+        <f>IF($A15=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A15=Inputs!$B$85,-Inputs!$B$40,0)</f>
+        <v>-2770000</v>
       </c>
       <c r="U15" s="23">
         <f t="shared" si="2"/>
-        <v>21017126.919702914</v>
+        <v>22259926.919702914</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -6764,19 +6815,19 @@
         <v>61</v>
       </c>
       <c r="D16" s="16">
-        <f>IF($A16&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A16-Inputs!$B$80),0)</f>
+        <f>IF($A16&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A16-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E16" s="16">
-        <f>IF($A16&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A16-Inputs!$B$80),0)</f>
+        <f>IF($A16&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A16-Inputs!$B$83),0)</f>
         <v>1026547.8385292486</v>
       </c>
       <c r="F16" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A16-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A16-Inputs!$B$83)</f>
         <v>531231.08557728748</v>
       </c>
       <c r="G16" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A16-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A16-Inputs!$B$83)</f>
         <v>195008.87951571314</v>
       </c>
       <c r="H16" s="16">
@@ -6792,15 +6843,15 @@
         <v>18000</v>
       </c>
       <c r="K16" s="16">
-        <f>IF($A16&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A16-Inputs!$B$80),0)</f>
+        <f>IF($A16&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A16-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L16" s="16">
-        <f>IF(AND($A16&gt;=Inputs!$B$83,$A16&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A16-Inputs!$B$80),0)</f>
+        <f>IF(AND($A16&gt;=Inputs!$B$86,$A16&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A16-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M16" s="16">
-        <f>IF($A16&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A16-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A16&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A16&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A16-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A16&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1049013.2829121121</v>
       </c>
       <c r="N16" s="16">
@@ -6808,32 +6859,32 @@
         <v>0</v>
       </c>
       <c r="O16" s="16">
-        <f>IF($A16&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A16&gt;=Inputs!$B$84,$A16&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A16&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>160800</v>
       </c>
       <c r="P16" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A16=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A16&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A16=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A16&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q16" s="16">
-        <f>D16+E16-H16-I16+J16-K16-L16-M16-N16+O16+P16-IF($A16&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>148587.93258483545</v>
+        <f>D16+E16-H16-I16+J16-K16-L16-M16-N16+O16+P16-IF($A16&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>41387.932584835449</v>
       </c>
       <c r="R16" s="16">
         <f t="shared" si="3"/>
-        <v>21017126.919702914</v>
+        <v>22259926.919702914</v>
       </c>
       <c r="S16" s="16">
         <f>R16*Inputs!$B$35</f>
-        <v>1008822.0921457398</v>
+        <v>1068476.49214574</v>
       </c>
       <c r="T16" s="16">
-        <f>IF($A16=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A16=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A16=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U16" s="16">
         <f t="shared" si="2"/>
-        <v>22174536.944433492</v>
+        <v>23369791.34443349</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -6849,19 +6900,19 @@
         <v>62</v>
       </c>
       <c r="D17" s="23">
-        <f>IF($A17&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A17-Inputs!$B$80),0)</f>
+        <f>IF($A17&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A17-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="23">
-        <f>IF($A17&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A17-Inputs!$B$80),0)</f>
+        <f>IF($A17&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A17-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A17-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A17-Inputs!$B$83)</f>
         <v>544511.86271671974</v>
       </c>
       <c r="G17" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A17-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A17-Inputs!$B$83)</f>
         <v>199884.10150360595</v>
       </c>
       <c r="H17" s="23">
@@ -6877,15 +6928,15 @@
         <v>0</v>
       </c>
       <c r="K17" s="23">
-        <f>IF($A17&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A17-Inputs!$B$80),0)</f>
+        <f>IF($A17&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A17-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L17" s="23">
-        <f>IF(AND($A17&gt;=Inputs!$B$83,$A17&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A17-Inputs!$B$80),0)</f>
+        <f>IF(AND($A17&gt;=Inputs!$B$86,$A17&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A17-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M17" s="23">
-        <f>IF($A17&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A17-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A17&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A17&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A17-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A17&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1075238.6149849149</v>
       </c>
       <c r="N17" s="23">
@@ -6893,32 +6944,32 @@
         <v>69643.453498252085</v>
       </c>
       <c r="O17" s="23">
-        <f>IF($A17&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A17&gt;=Inputs!$B$84,$A17&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A17&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P17" s="23">
-        <f>IF(AND(Inputs!$B$58=1,$A17=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A17&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A17=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A17&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="23">
-        <f>D17+E17-H17-I17+J17-K17-L17-M17-N17+O17+P17-IF($A17&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-876882.06848316686</v>
+        <f>D17+E17-H17-I17+J17-K17-L17-M17-N17+O17+P17-IF($A17&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-876782.06848316686</v>
       </c>
       <c r="R17" s="23">
         <f t="shared" si="3"/>
-        <v>22174536.944433492</v>
+        <v>23369791.34443349</v>
       </c>
       <c r="S17" s="23">
         <f>R17*Inputs!$B$35</f>
-        <v>1064377.7733328077</v>
+        <v>1121749.9845328075</v>
       </c>
       <c r="T17" s="23">
-        <f>IF($A17=Inputs!$B$81,-Inputs!$B$38,0)</f>
-        <v>0</v>
+        <f>IF($A17=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A17=Inputs!$B$85,-Inputs!$B$40,0)</f>
+        <v>-1810000</v>
       </c>
       <c r="U17" s="23">
         <f t="shared" si="2"/>
-        <v>22362032.649283133</v>
+        <v>21804759.260483131</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -6934,19 +6985,19 @@
         <v>63</v>
       </c>
       <c r="D18" s="16">
-        <f>IF($A18&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A18-Inputs!$B$80),0)</f>
+        <f>IF($A18&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A18-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E18" s="16">
-        <f>IF($A18&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A18-Inputs!$B$80),0)</f>
+        <f>IF($A18&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A18-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A18-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A18-Inputs!$B$83)</f>
         <v>558124.65928463766</v>
       </c>
       <c r="G18" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A18-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A18-Inputs!$B$83)</f>
         <v>204881.20404119609</v>
       </c>
       <c r="H18" s="16">
@@ -6962,15 +7013,15 @@
         <v>0</v>
       </c>
       <c r="K18" s="16">
-        <f>IF($A18&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A18-Inputs!$B$80),0)</f>
+        <f>IF($A18&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A18-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="16">
-        <f>IF(AND($A18&gt;=Inputs!$B$83,$A18&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A18-Inputs!$B$80),0)</f>
+        <f>IF(AND($A18&gt;=Inputs!$B$86,$A18&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A18-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="16">
-        <f>IF($A18&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A18-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A18&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A18&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A18-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A18&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1102119.5803595376</v>
       </c>
       <c r="N18" s="16">
@@ -6978,32 +7029,32 @@
         <v>87001.932886053866</v>
       </c>
       <c r="O18" s="16">
-        <f>IF($A18&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A18&gt;=Inputs!$B$84,$A18&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A18&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P18" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A18=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A18&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A18=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A18&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="16">
-        <f>D18+E18-H18-I18+J18-K18-L18-M18-N18+O18+P18-IF($A18&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-921121.51324559143</v>
+        <f>D18+E18-H18-I18+J18-K18-L18-M18-N18+O18+P18-IF($A18&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-921021.51324559143</v>
       </c>
       <c r="R18" s="16">
         <f t="shared" si="3"/>
-        <v>22362032.649283133</v>
+        <v>21804759.260483131</v>
       </c>
       <c r="S18" s="16">
         <f>R18*Inputs!$B$35</f>
-        <v>1073377.5671655904</v>
+        <v>1046628.4445031903</v>
       </c>
       <c r="T18" s="16">
-        <f>IF($A18=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A18=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A18=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U18" s="16">
         <f t="shared" si="2"/>
-        <v>22514288.703203134</v>
+        <v>21930366.191740733</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -7019,19 +7070,19 @@
         <v>64</v>
       </c>
       <c r="D19" s="16">
-        <f>IF($A19&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A19-Inputs!$B$80),0)</f>
+        <f>IF($A19&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A19-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E19" s="16">
-        <f>IF($A19&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A19-Inputs!$B$80),0)</f>
+        <f>IF($A19&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A19-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A19-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A19-Inputs!$B$83)</f>
         <v>572077.77576675359</v>
       </c>
       <c r="G19" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A19-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A19-Inputs!$B$83)</f>
         <v>210003.23414222602</v>
       </c>
       <c r="H19" s="16">
@@ -7047,15 +7098,15 @@
         <v>0</v>
       </c>
       <c r="K19" s="16">
-        <f>IF($A19&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A19-Inputs!$B$80),0)</f>
+        <f>IF($A19&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A19-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L19" s="16">
-        <f>IF(AND($A19&gt;=Inputs!$B$83,$A19&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A19-Inputs!$B$80),0)</f>
+        <f>IF(AND($A19&gt;=Inputs!$B$86,$A19&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A19-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M19" s="16">
-        <f>IF($A19&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A19-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A19&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A19&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A19-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A19&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1129672.5698685262</v>
       </c>
       <c r="N19" s="16">
@@ -7063,32 +7114,32 @@
         <v>106727.07007672689</v>
       </c>
       <c r="O19" s="16">
-        <f>IF($A19&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A19&gt;=Inputs!$B$84,$A19&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A19&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P19" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A19=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A19&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A19=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A19&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q19" s="16">
-        <f>D19+E19-H19-I19+J19-K19-L19-M19-N19+O19+P19-IF($A19&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-968399.63994525303</v>
+        <f>D19+E19-H19-I19+J19-K19-L19-M19-N19+O19+P19-IF($A19&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-968299.63994525303</v>
       </c>
       <c r="R19" s="16">
         <f t="shared" si="3"/>
-        <v>22514288.703203134</v>
+        <v>21930366.191740733</v>
       </c>
       <c r="S19" s="16">
         <f>R19*Inputs!$B$35</f>
-        <v>1080685.8577537504</v>
+        <v>1052657.5772035553</v>
       </c>
       <c r="T19" s="16">
-        <f>IF($A19=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A19=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A19=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U19" s="16">
         <f t="shared" si="2"/>
-        <v>22626574.92101163</v>
+        <v>22014724.128999036</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -7104,19 +7155,19 @@
         <v>65</v>
       </c>
       <c r="D20" s="16">
-        <f>IF($A20&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A20-Inputs!$B$80),0)</f>
+        <f>IF($A20&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A20-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="16">
-        <f>IF($A20&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A20-Inputs!$B$80),0)</f>
+        <f>IF($A20&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A20-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F20" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A20-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A20-Inputs!$B$83)</f>
         <v>586379.72016092238</v>
       </c>
       <c r="G20" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A20-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A20-Inputs!$B$83)</f>
         <v>215253.31499578166</v>
       </c>
       <c r="H20" s="16">
@@ -7132,15 +7183,15 @@
         <v>0</v>
       </c>
       <c r="K20" s="16">
-        <f>IF($A20&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A20-Inputs!$B$80),0)</f>
+        <f>IF($A20&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A20-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L20" s="16">
-        <f>IF(AND($A20&gt;=Inputs!$B$83,$A20&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A20-Inputs!$B$80),0)</f>
+        <f>IF(AND($A20&gt;=Inputs!$B$86,$A20&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A20-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M20" s="16">
-        <f>IF($A20&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A20-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A20&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A20&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A20-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A20&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1157914.3841152391</v>
       </c>
       <c r="N20" s="16">
@@ -7148,32 +7199,32 @@
         <v>129118.27483096196</v>
       </c>
       <c r="O20" s="16">
-        <f>IF($A20&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A20&gt;=Inputs!$B$84,$A20&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A20&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P20" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A20=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A20&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A20=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A20&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q20" s="16">
-        <f>D20+E20-H20-I20+J20-K20-L20-M20-N20+O20+P20-IF($A20&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1019032.6589462012</v>
+        <f>D20+E20-H20-I20+J20-K20-L20-M20-N20+O20+P20-IF($A20&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1018932.6589462012</v>
       </c>
       <c r="R20" s="16">
         <f t="shared" si="3"/>
-        <v>22626574.92101163</v>
+        <v>22014724.128999036</v>
       </c>
       <c r="S20" s="16">
         <f>R20*Inputs!$B$35</f>
-        <v>1086075.5962085582</v>
+        <v>1056706.7581919536</v>
       </c>
       <c r="T20" s="16">
-        <f>IF($A20=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A20=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A20=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U20" s="16">
         <f t="shared" si="2"/>
-        <v>22693617.858273987</v>
+        <v>22052498.228244789</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -7189,19 +7240,19 @@
         <v>66</v>
       </c>
       <c r="D21" s="16">
-        <f>IF($A21&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A21-Inputs!$B$80),0)</f>
+        <f>IF($A21&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A21-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="16">
-        <f>IF($A21&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A21-Inputs!$B$80),0)</f>
+        <f>IF($A21&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A21-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F21" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A21-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A21-Inputs!$B$83)</f>
         <v>601039.21316494537</v>
       </c>
       <c r="G21" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A21-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A21-Inputs!$B$83)</f>
         <v>220634.64787067616</v>
       </c>
       <c r="H21" s="16">
@@ -7217,15 +7268,15 @@
         <v>0</v>
       </c>
       <c r="K21" s="16">
-        <f>IF($A21&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A21-Inputs!$B$80),0)</f>
+        <f>IF($A21&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A21-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L21" s="16">
-        <f>IF(AND($A21&gt;=Inputs!$B$83,$A21&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A21-Inputs!$B$80),0)</f>
+        <f>IF(AND($A21&gt;=Inputs!$B$86,$A21&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A21-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M21" s="16">
-        <f>IF($A21&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A21-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A21&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A21&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A21-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A21&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1186862.24371812</v>
       </c>
       <c r="N21" s="16">
@@ -7233,32 +7284,32 @@
         <v>152618.39511465485</v>
       </c>
       <c r="O21" s="16">
-        <f>IF($A21&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A21&gt;=Inputs!$B$84,$A21&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A21&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P21" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A21=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A21&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A21=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A21&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q21" s="16">
-        <f>D21+E21-H21-I21+J21-K21-L21-M21-N21+O21+P21-IF($A21&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1071480.6388327749</v>
+        <f>D21+E21-H21-I21+J21-K21-L21-M21-N21+O21+P21-IF($A21&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1071380.6388327749</v>
       </c>
       <c r="R21" s="16">
         <f t="shared" si="3"/>
-        <v>22693617.858273987</v>
+        <v>22052498.228244789</v>
       </c>
       <c r="S21" s="16">
         <f>R21*Inputs!$B$35</f>
-        <v>1089293.6571971513</v>
+        <v>1058519.9149557499</v>
       </c>
       <c r="T21" s="16">
-        <f>IF($A21=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A21=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A21=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U21" s="16">
         <f t="shared" si="2"/>
-        <v>22711430.876638364</v>
+        <v>22039637.504367765</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -7274,19 +7325,19 @@
         <v>67</v>
       </c>
       <c r="D22" s="16">
-        <f>IF($A22&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A22-Inputs!$B$80),0)</f>
+        <f>IF($A22&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A22-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="16">
-        <f>IF($A22&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A22-Inputs!$B$80),0)</f>
+        <f>IF($A22&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A22-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A22-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A22-Inputs!$B$83)</f>
         <v>616065.19349406904</v>
       </c>
       <c r="G22" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A22-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A22-Inputs!$B$83)</f>
         <v>226150.51406744309</v>
       </c>
       <c r="H22" s="16">
@@ -7302,15 +7353,15 @@
         <v>0</v>
       </c>
       <c r="K22" s="16">
-        <f>IF($A22&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A22-Inputs!$B$80),0)</f>
+        <f>IF($A22&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A22-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L22" s="16">
-        <f>IF(AND($A22&gt;=Inputs!$B$83,$A22&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A22-Inputs!$B$80),0)</f>
+        <f>IF(AND($A22&gt;=Inputs!$B$86,$A22&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A22-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M22" s="16">
-        <f>IF($A22&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A22-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A22&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A22&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A22-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A22&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1216533.7998110731</v>
       </c>
       <c r="N22" s="16">
@@ -7318,32 +7369,32 @@
         <v>179034.89615033241</v>
       </c>
       <c r="O22" s="16">
-        <f>IF($A22&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A22&gt;=Inputs!$B$84,$A22&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A22&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P22" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A22=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A22&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A22=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A22&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q22" s="16">
-        <f>D22+E22-H22-I22+J22-K22-L22-M22-N22+O22+P22-IF($A22&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1127568.6959614055</v>
+        <f>D22+E22-H22-I22+J22-K22-L22-M22-N22+O22+P22-IF($A22&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1127468.6959614055</v>
       </c>
       <c r="R22" s="16">
         <f t="shared" si="3"/>
-        <v>22711430.876638364</v>
+        <v>22039637.504367765</v>
       </c>
       <c r="S22" s="16">
         <f>R22*Inputs!$B$35</f>
-        <v>1090148.6820786416</v>
+        <v>1057902.6002096527</v>
       </c>
       <c r="T22" s="16">
-        <f>IF($A22=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A22=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A22=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U22" s="16">
         <f t="shared" si="2"/>
-        <v>22674010.8627556</v>
+        <v>21970071.408616014</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -7359,19 +7410,19 @@
         <v>68</v>
       </c>
       <c r="D23" s="16">
-        <f>IF($A23&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A23-Inputs!$B$80),0)</f>
+        <f>IF($A23&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A23-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E23" s="16">
-        <f>IF($A23&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A23-Inputs!$B$80),0)</f>
+        <f>IF($A23&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A23-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F23" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A23-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A23-Inputs!$B$83)</f>
         <v>631466.82333142078</v>
       </c>
       <c r="G23" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A23-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A23-Inputs!$B$83)</f>
         <v>231804.27691912916</v>
       </c>
       <c r="H23" s="16">
@@ -7387,15 +7438,15 @@
         <v>0</v>
       </c>
       <c r="K23" s="16">
-        <f>IF($A23&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A23-Inputs!$B$80),0)</f>
+        <f>IF($A23&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A23-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L23" s="16">
-        <f>IF(AND($A23&gt;=Inputs!$B$83,$A23&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A23-Inputs!$B$80),0)</f>
+        <f>IF(AND($A23&gt;=Inputs!$B$86,$A23&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A23-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M23" s="16">
-        <f>IF($A23&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A23-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A23&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A23&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A23-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A23&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1246947.1448063499</v>
       </c>
       <c r="N23" s="16">
@@ -7403,32 +7454,32 @@
         <v>208708.27808234876</v>
       </c>
       <c r="O23" s="16">
-        <f>IF($A23&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A23&gt;=Inputs!$B$84,$A23&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A23&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P23" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A23=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A23&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A23=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A23&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q23" s="16">
-        <f>D23+E23-H23-I23+J23-K23-L23-M23-N23+O23+P23-IF($A23&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1187655.4228886985</v>
+        <f>D23+E23-H23-I23+J23-K23-L23-M23-N23+O23+P23-IF($A23&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1187555.4228886985</v>
       </c>
       <c r="R23" s="16">
         <f t="shared" si="3"/>
-        <v>22674010.8627556</v>
+        <v>21970071.408616014</v>
       </c>
       <c r="S23" s="16">
         <f>R23*Inputs!$B$35</f>
-        <v>1088352.5214122687</v>
+        <v>1054563.4276135687</v>
       </c>
       <c r="T23" s="16">
-        <f>IF($A23=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A23=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A23=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U23" s="16">
         <f t="shared" si="2"/>
-        <v>22574707.961279169</v>
+        <v>21837079.413340881</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -7444,19 +7495,19 @@
         <v>69</v>
       </c>
       <c r="D24" s="16">
-        <f>IF($A24&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A24-Inputs!$B$80),0)</f>
+        <f>IF($A24&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A24-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E24" s="16">
-        <f>IF($A24&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A24-Inputs!$B$80),0)</f>
+        <f>IF($A24&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A24-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F24" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A24-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A24-Inputs!$B$83)</f>
         <v>647253.49391470628</v>
       </c>
       <c r="G24" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A24-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A24-Inputs!$B$83)</f>
         <v>237599.38384210735</v>
       </c>
       <c r="H24" s="16">
@@ -7472,15 +7523,15 @@
         <v>0</v>
       </c>
       <c r="K24" s="16">
-        <f>IF($A24&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A24-Inputs!$B$80),0)</f>
+        <f>IF($A24&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A24-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="16">
-        <f>IF(AND($A24&gt;=Inputs!$B$83,$A24&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A24-Inputs!$B$80),0)</f>
+        <f>IF(AND($A24&gt;=Inputs!$B$86,$A24&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A24-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="16">
-        <f>IF($A24&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A24-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A24&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A24&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A24-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A24&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1278120.8234265086</v>
       </c>
       <c r="N24" s="16">
@@ -7488,32 +7539,32 @@
         <v>242018.30552795361</v>
       </c>
       <c r="O24" s="16">
-        <f>IF($A24&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A24&gt;=Inputs!$B$84,$A24&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A24&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P24" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A24=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A24&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A24=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A24&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q24" s="16">
-        <f>D24+E24-H24-I24+J24-K24-L24-M24-N24+O24+P24-IF($A24&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1252139.1289544622</v>
+        <f>D24+E24-H24-I24+J24-K24-L24-M24-N24+O24+P24-IF($A24&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1252039.1289544622</v>
       </c>
       <c r="R24" s="16">
         <f t="shared" si="3"/>
-        <v>22574707.961279169</v>
+        <v>21837079.413340881</v>
       </c>
       <c r="S24" s="16">
         <f>R24*Inputs!$B$35</f>
-        <v>1083585.9821414002</v>
+        <v>1048179.8118403624</v>
       </c>
       <c r="T24" s="16">
-        <f>IF($A24=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A24=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A24=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U24" s="16">
         <f t="shared" si="2"/>
-        <v>22406154.814466108</v>
+        <v>21633220.096226782</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -7529,19 +7580,19 @@
         <v>70</v>
       </c>
       <c r="D25" s="16">
-        <f>IF($A25&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A25-Inputs!$B$80),0)</f>
+        <f>IF($A25&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A25-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="16">
-        <f>IF($A25&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A25-Inputs!$B$80),0)</f>
+        <f>IF($A25&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A25-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F25" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A25-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A25-Inputs!$B$83)</f>
         <v>663434.83126257383</v>
       </c>
       <c r="G25" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A25-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A25-Inputs!$B$83)</f>
         <v>243539.36843816002</v>
       </c>
       <c r="H25" s="16">
@@ -7557,15 +7608,15 @@
         <v>0</v>
       </c>
       <c r="K25" s="16">
-        <f>IF($A25&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A25-Inputs!$B$80),0)</f>
+        <f>IF($A25&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A25-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L25" s="16">
-        <f>IF(AND($A25&gt;=Inputs!$B$83,$A25&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A25-Inputs!$B$80),0)</f>
+        <f>IF(AND($A25&gt;=Inputs!$B$86,$A25&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A25-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M25" s="16">
-        <f>IF($A25&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A25-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A25&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A25&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A25-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A25&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1310073.844012171</v>
       </c>
       <c r="N25" s="16">
@@ -7573,32 +7624,32 @@
         <v>279388.52389267285</v>
       </c>
       <c r="O25" s="16">
-        <f>IF($A25&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A25&gt;=Inputs!$B$84,$A25&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A25&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P25" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A25=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A25&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A25=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A25&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q25" s="16">
-        <f>D25+E25-H25-I25+J25-K25-L25-M25-N25+O25+P25-IF($A25&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1321462.3679048438</v>
+        <f>D25+E25-H25-I25+J25-K25-L25-M25-N25+O25+P25-IF($A25&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1321362.3679048438</v>
       </c>
       <c r="R25" s="16">
         <f t="shared" si="3"/>
-        <v>22406154.814466108</v>
+        <v>21633220.096226782</v>
       </c>
       <c r="S25" s="16">
         <f>R25*Inputs!$B$35</f>
-        <v>1075495.4310943731</v>
+        <v>1038394.5646188855</v>
       </c>
       <c r="T25" s="16">
-        <f>IF($A25=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A25=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A25=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U25" s="16">
         <f t="shared" si="2"/>
-        <v>22160187.87765564</v>
+        <v>21350252.292940825</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -7614,19 +7665,19 @@
         <v>71</v>
       </c>
       <c r="D26" s="16">
-        <f>IF($A26&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A26-Inputs!$B$80),0)</f>
+        <f>IF($A26&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A26-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="16">
-        <f>IF($A26&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A26-Inputs!$B$80),0)</f>
+        <f>IF($A26&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A26-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F26" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A26-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A26-Inputs!$B$83)</f>
         <v>680020.7020441381</v>
       </c>
       <c r="G26" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A26-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A26-Inputs!$B$83)</f>
         <v>249627.85264911401</v>
       </c>
       <c r="H26" s="16">
@@ -7642,15 +7693,15 @@
         <v>0</v>
       </c>
       <c r="K26" s="16">
-        <f>IF($A26&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A26-Inputs!$B$80),0)</f>
+        <f>IF($A26&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A26-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L26" s="16">
-        <f>IF(AND($A26&gt;=Inputs!$B$83,$A26&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A26-Inputs!$B$80),0)</f>
+        <f>IF(AND($A26&gt;=Inputs!$B$86,$A26&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A26-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M26" s="16">
-        <f>IF($A26&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A26-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A26&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A26&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A26-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A26&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1342825.6901124753</v>
       </c>
       <c r="N26" s="16">
@@ -7658,32 +7709,32 @@
         <v>317434.86122545542</v>
       </c>
       <c r="O26" s="16">
-        <f>IF($A26&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A26&gt;=Inputs!$B$84,$A26&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A26&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P26" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A26=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A26&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A26=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A26&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q26" s="16">
-        <f>D26+E26-H26-I26+J26-K26-L26-M26-N26+O26+P26-IF($A26&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1392260.5513379308</v>
+        <f>D26+E26-H26-I26+J26-K26-L26-M26-N26+O26+P26-IF($A26&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1392160.5513379308</v>
       </c>
       <c r="R26" s="16">
         <f t="shared" si="3"/>
-        <v>22160187.87765564</v>
+        <v>21350252.292940825</v>
       </c>
       <c r="S26" s="16">
         <f>R26*Inputs!$B$35</f>
-        <v>1063689.0181274707</v>
+        <v>1024812.1100611596</v>
       </c>
       <c r="T26" s="16">
-        <f>IF($A26=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A26=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A26=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U26" s="16">
         <f t="shared" si="2"/>
-        <v>21831616.34444518</v>
+        <v>20982903.851664055</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -7699,19 +7750,19 @@
         <v>72</v>
       </c>
       <c r="D27" s="16">
-        <f>IF($A27&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A27-Inputs!$B$80),0)</f>
+        <f>IF($A27&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A27-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E27" s="16">
-        <f>IF($A27&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A27-Inputs!$B$80),0)</f>
+        <f>IF($A27&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A27-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F27" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A27-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A27-Inputs!$B$83)</f>
         <v>697021.21959524159</v>
       </c>
       <c r="G27" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A27-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A27-Inputs!$B$83)</f>
         <v>255868.54896534188</v>
       </c>
       <c r="H27" s="16">
@@ -7727,15 +7778,15 @@
         <v>0</v>
       </c>
       <c r="K27" s="16">
-        <f>IF($A27&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A27-Inputs!$B$80),0)</f>
+        <f>IF($A27&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A27-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L27" s="16">
-        <f>IF(AND($A27&gt;=Inputs!$B$83,$A27&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A27-Inputs!$B$80),0)</f>
+        <f>IF(AND($A27&gt;=Inputs!$B$86,$A27&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A27-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M27" s="16">
-        <f>IF($A27&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A27-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A27&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A27&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A27-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A27&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1376396.3323652872</v>
       </c>
       <c r="N27" s="16">
@@ -7743,32 +7794,32 @@
         <v>359733.95381528605</v>
       </c>
       <c r="O27" s="16">
-        <f>IF($A27&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A27&gt;=Inputs!$B$84,$A27&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A27&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P27" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A27=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A27&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A27=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A27&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q27" s="16">
-        <f>D27+E27-H27-I27+J27-K27-L27-M27-N27+O27+P27-IF($A27&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1468130.2861805733</v>
+        <f>D27+E27-H27-I27+J27-K27-L27-M27-N27+O27+P27-IF($A27&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1468030.2861805733</v>
       </c>
       <c r="R27" s="16">
         <f t="shared" si="3"/>
-        <v>21831616.34444518</v>
+        <v>20982903.851664055</v>
       </c>
       <c r="S27" s="16">
         <f>R27*Inputs!$B$35</f>
-        <v>1047917.5845333687</v>
+        <v>1007179.3848798746</v>
       </c>
       <c r="T27" s="16">
-        <f>IF($A27=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A27=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A27=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U27" s="16">
         <f t="shared" si="2"/>
-        <v>21411403.642797973</v>
+        <v>20522052.950363357</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -7784,19 +7835,19 @@
         <v>73</v>
       </c>
       <c r="D28" s="16">
-        <f>IF($A28&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A28-Inputs!$B$80),0)</f>
+        <f>IF($A28&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A28-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E28" s="16">
-        <f>IF($A28&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A28-Inputs!$B$80),0)</f>
+        <f>IF($A28&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A28-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F28" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A28-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A28-Inputs!$B$83)</f>
         <v>714446.75008512265</v>
       </c>
       <c r="G28" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A28-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A28-Inputs!$B$83)</f>
         <v>262265.26268947538</v>
       </c>
       <c r="H28" s="16">
@@ -7812,15 +7863,15 @@
         <v>0</v>
       </c>
       <c r="K28" s="16">
-        <f>IF($A28&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A28-Inputs!$B$80),0)</f>
+        <f>IF($A28&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A28-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L28" s="16">
-        <f>IF(AND($A28&gt;=Inputs!$B$83,$A28&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A28-Inputs!$B$80),0)</f>
+        <f>IF(AND($A28&gt;=Inputs!$B$86,$A28&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A28-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M28" s="16">
-        <f>IF($A28&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A28-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A28&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A28&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A28-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A28&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1410806.2406744193</v>
       </c>
       <c r="N28" s="16">
@@ -7828,32 +7879,32 @@
         <v>406746.4728097815</v>
       </c>
       <c r="O28" s="16">
-        <f>IF($A28&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A28&gt;=Inputs!$B$84,$A28&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A28&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P28" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A28=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A28&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A28=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A28&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q28" s="16">
-        <f>D28+E28-H28-I28+J28-K28-L28-M28-N28+O28+P28-IF($A28&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1549552.7134842009</v>
+        <f>D28+E28-H28-I28+J28-K28-L28-M28-N28+O28+P28-IF($A28&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1549452.7134842009</v>
       </c>
       <c r="R28" s="16">
         <f t="shared" si="3"/>
-        <v>21411403.642797973</v>
+        <v>20522052.950363357</v>
       </c>
       <c r="S28" s="16">
         <f>R28*Inputs!$B$35</f>
-        <v>1027747.3748543027</v>
+        <v>985058.54161744111</v>
       </c>
       <c r="T28" s="16">
-        <f>IF($A28=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A28=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A28=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U28" s="16">
         <f t="shared" si="2"/>
-        <v>20889598.304168075</v>
+        <v>19957658.778496597</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -7869,19 +7920,19 @@
         <v>74</v>
       </c>
       <c r="D29" s="16">
-        <f>IF($A29&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A29-Inputs!$B$80),0)</f>
+        <f>IF($A29&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A29-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E29" s="16">
-        <f>IF($A29&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A29-Inputs!$B$80),0)</f>
+        <f>IF($A29&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A29-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F29" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A29-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A29-Inputs!$B$83)</f>
         <v>732307.91883725056</v>
       </c>
       <c r="G29" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A29-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A29-Inputs!$B$83)</f>
         <v>268821.89425671223</v>
       </c>
       <c r="H29" s="16">
@@ -7897,15 +7948,15 @@
         <v>0</v>
       </c>
       <c r="K29" s="16">
-        <f>IF($A29&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A29-Inputs!$B$80),0)</f>
+        <f>IF($A29&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A29-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L29" s="16">
-        <f>IF(AND($A29&gt;=Inputs!$B$83,$A29&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A29-Inputs!$B$80),0)</f>
+        <f>IF(AND($A29&gt;=Inputs!$B$86,$A29&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A29-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M29" s="16">
-        <f>IF($A29&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A29-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A29&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A29&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A29-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A29&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1446076.3966912797</v>
       </c>
       <c r="N29" s="16">
@@ -7913,32 +7964,32 @@
         <v>458982.99832589674</v>
       </c>
       <c r="O29" s="16">
-        <f>IF($A29&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A29&gt;=Inputs!$B$84,$A29&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A29&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P29" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A29=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A29&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A29=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A29&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q29" s="16">
-        <f>D29+E29-H29-I29+J29-K29-L29-M29-N29+O29+P29-IF($A29&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1637059.3950171764</v>
+        <f>D29+E29-H29-I29+J29-K29-L29-M29-N29+O29+P29-IF($A29&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1636959.3950171764</v>
       </c>
       <c r="R29" s="16">
         <f t="shared" si="3"/>
-        <v>20889598.304168075</v>
+        <v>19957658.778496597</v>
       </c>
       <c r="S29" s="16">
         <f>R29*Inputs!$B$35</f>
-        <v>1002700.7186000677</v>
+        <v>957967.62136783672</v>
       </c>
       <c r="T29" s="16">
-        <f>IF($A29=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A29=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A29=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U29" s="16">
         <f t="shared" si="2"/>
-        <v>20255239.627750967</v>
+        <v>19278667.004847258</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -7954,19 +8005,19 @@
         <v>75</v>
       </c>
       <c r="D30" s="16">
-        <f>IF($A30&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A30-Inputs!$B$80),0)</f>
+        <f>IF($A30&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A30-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E30" s="16">
-        <f>IF($A30&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A30-Inputs!$B$80),0)</f>
+        <f>IF($A30&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A30-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F30" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A30-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A30-Inputs!$B$83)</f>
         <v>750615.61680818175</v>
       </c>
       <c r="G30" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A30-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A30-Inputs!$B$83)</f>
         <v>275542.44161313004</v>
       </c>
       <c r="H30" s="16">
@@ -7982,15 +8033,15 @@
         <v>0</v>
       </c>
       <c r="K30" s="16">
-        <f>IF($A30&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A30-Inputs!$B$80),0)</f>
+        <f>IF($A30&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A30-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="16">
-        <f>IF(AND($A30&gt;=Inputs!$B$83,$A30&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A30-Inputs!$B$80),0)</f>
+        <f>IF(AND($A30&gt;=Inputs!$B$86,$A30&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A30-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="16">
-        <f>IF($A30&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A30-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A30&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A30&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A30-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A30&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1482228.3066085614</v>
       </c>
       <c r="N30" s="16">
@@ -7998,32 +8049,32 @@
         <v>517009.46438955533</v>
       </c>
       <c r="O30" s="16">
-        <f>IF($A30&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A30&gt;=Inputs!$B$84,$A30&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A30&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P30" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A30=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A30&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A30=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A30&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q30" s="16">
-        <f>D30+E30-H30-I30+J30-K30-L30-M30-N30+O30+P30-IF($A30&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1731237.7709981168</v>
+        <f>D30+E30-H30-I30+J30-K30-L30-M30-N30+O30+P30-IF($A30&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1731137.7709981168</v>
       </c>
       <c r="R30" s="16">
         <f t="shared" si="3"/>
-        <v>20255239.627750967</v>
+        <v>19278667.004847258</v>
       </c>
       <c r="S30" s="16">
         <f>R30*Inputs!$B$35</f>
-        <v>972251.50213204639</v>
+        <v>925376.01623266842</v>
       </c>
       <c r="T30" s="16">
-        <f>IF($A30=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A30=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A30=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U30" s="16">
         <f t="shared" si="2"/>
-        <v>19496253.358884897</v>
+        <v>18472905.250081811</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -8039,19 +8090,19 @@
         <v>76</v>
       </c>
       <c r="D31" s="16">
-        <f>IF($A31&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A31-Inputs!$B$80),0)</f>
+        <f>IF($A31&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A31-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E31" s="16">
-        <f>IF($A31&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A31-Inputs!$B$80),0)</f>
+        <f>IF($A31&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A31-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F31" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A31-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A31-Inputs!$B$83)</f>
         <v>769381.00722838636</v>
       </c>
       <c r="G31" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A31-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A31-Inputs!$B$83)</f>
         <v>282431.00265345827</v>
       </c>
       <c r="H31" s="16">
@@ -8067,15 +8118,15 @@
         <v>0</v>
       </c>
       <c r="K31" s="16">
-        <f>IF($A31&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A31-Inputs!$B$80),0)</f>
+        <f>IF($A31&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A31-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="16">
-        <f>IF(AND($A31&gt;=Inputs!$B$83,$A31&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A31-Inputs!$B$80),0)</f>
+        <f>IF(AND($A31&gt;=Inputs!$B$86,$A31&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A31-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="16">
-        <f>IF($A31&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A31-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A31&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A31&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A31-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A31&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1519284.0142737755</v>
       </c>
       <c r="N31" s="16">
@@ -8083,32 +8134,32 @@
         <v>575236.07736100326</v>
       </c>
       <c r="O31" s="16">
-        <f>IF($A31&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A31&gt;=Inputs!$B$84,$A31&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A31&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P31" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A31=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A31&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A31=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A31&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="16">
-        <f>D31+E31-H31-I31+J31-K31-L31-M31-N31+O31+P31-IF($A31&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1826520.0916347788</v>
+        <f>D31+E31-H31-I31+J31-K31-L31-M31-N31+O31+P31-IF($A31&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1826420.0916347788</v>
       </c>
       <c r="R31" s="16">
         <f t="shared" si="3"/>
-        <v>19496253.358884897</v>
+        <v>18472905.250081811</v>
       </c>
       <c r="S31" s="16">
         <f>R31*Inputs!$B$35</f>
-        <v>935820.16122647503</v>
+        <v>886699.45200392697</v>
       </c>
       <c r="T31" s="16">
-        <f>IF($A31=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A31=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A31=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U31" s="16">
         <f t="shared" si="2"/>
-        <v>18605553.428476591</v>
+        <v>17533184.610450957</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -8124,19 +8175,19 @@
         <v>77</v>
       </c>
       <c r="D32" s="16">
-        <f>IF($A32&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A32-Inputs!$B$80),0)</f>
+        <f>IF($A32&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A32-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E32" s="16">
-        <f>IF($A32&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A32-Inputs!$B$80),0)</f>
+        <f>IF($A32&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A32-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F32" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A32-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A32-Inputs!$B$83)</f>
         <v>788615.5324090959</v>
       </c>
       <c r="G32" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A32-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A32-Inputs!$B$83)</f>
         <v>289491.77771979471</v>
       </c>
       <c r="H32" s="16">
@@ -8152,15 +8203,15 @@
         <v>0</v>
       </c>
       <c r="K32" s="16">
-        <f>IF($A32&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A32-Inputs!$B$80),0)</f>
+        <f>IF($A32&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A32-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="16">
-        <f>IF(AND($A32&gt;=Inputs!$B$83,$A32&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A32-Inputs!$B$80),0)</f>
+        <f>IF(AND($A32&gt;=Inputs!$B$86,$A32&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A32-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="16">
-        <f>IF($A32&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A32-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A32&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A32&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A32-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A32&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1557266.1146306198</v>
       </c>
       <c r="N32" s="16">
@@ -8168,32 +8219,32 @@
         <v>639254.84679752751</v>
       </c>
       <c r="O32" s="16">
-        <f>IF($A32&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A32&gt;=Inputs!$B$84,$A32&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A32&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P32" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A32=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A32&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A32=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A32&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q32" s="16">
-        <f>D32+E32-H32-I32+J32-K32-L32-M32-N32+O32+P32-IF($A32&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1928520.9614281473</v>
+        <f>D32+E32-H32-I32+J32-K32-L32-M32-N32+O32+P32-IF($A32&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1928420.9614281473</v>
       </c>
       <c r="R32" s="16">
         <f t="shared" si="3"/>
-        <v>18605553.428476591</v>
+        <v>17533184.610450957</v>
       </c>
       <c r="S32" s="16">
         <f>R32*Inputs!$B$35</f>
-        <v>893066.56456687639</v>
+        <v>841592.86130164599</v>
       </c>
       <c r="T32" s="16">
-        <f>IF($A32=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A32=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A32=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U32" s="16">
         <f t="shared" si="2"/>
-        <v>17570099.031615321</v>
+        <v>16446356.510324456</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -8209,19 +8260,19 @@
         <v>78</v>
       </c>
       <c r="D33" s="16">
-        <f>IF($A33&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A33-Inputs!$B$80),0)</f>
+        <f>IF($A33&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A33-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E33" s="16">
-        <f>IF($A33&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A33-Inputs!$B$80),0)</f>
+        <f>IF($A33&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A33-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F33" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A33-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A33-Inputs!$B$83)</f>
         <v>808330.92071932333</v>
       </c>
       <c r="G33" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A33-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A33-Inputs!$B$83)</f>
         <v>296729.07216278958</v>
       </c>
       <c r="H33" s="16">
@@ -8237,15 +8288,15 @@
         <v>0</v>
       </c>
       <c r="K33" s="16">
-        <f>IF($A33&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A33-Inputs!$B$80),0)</f>
+        <f>IF($A33&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A33-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="16">
-        <f>IF(AND($A33&gt;=Inputs!$B$83,$A33&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A33-Inputs!$B$80),0)</f>
+        <f>IF(AND($A33&gt;=Inputs!$B$86,$A33&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A33-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="16">
-        <f>IF($A33&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A33-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A33&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A33&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A33-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A33&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1596197.7674963854</v>
       </c>
       <c r="N33" s="16">
@@ -8253,32 +8304,32 @@
         <v>709625.69004126394</v>
       </c>
       <c r="O33" s="16">
-        <f>IF($A33&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A33&gt;=Inputs!$B$84,$A33&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A33&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P33" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A33=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A33&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A33=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A33&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q33" s="16">
-        <f>D33+E33-H33-I33+J33-K33-L33-M33-N33+O33+P33-IF($A33&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2037823.4575376492</v>
+        <f>D33+E33-H33-I33+J33-K33-L33-M33-N33+O33+P33-IF($A33&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2037723.4575376492</v>
       </c>
       <c r="R33" s="16">
         <f t="shared" si="3"/>
-        <v>17570099.031615321</v>
+        <v>16446356.510324456</v>
       </c>
       <c r="S33" s="16">
         <f>R33*Inputs!$B$35</f>
-        <v>843364.7535175354</v>
+        <v>789425.11249557394</v>
       </c>
       <c r="T33" s="16">
-        <f>IF($A33=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A33=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A33=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U33" s="16">
         <f t="shared" si="2"/>
-        <v>16375640.327595206</v>
+        <v>15198058.165282382</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -8294,19 +8345,19 @@
         <v>79</v>
       </c>
       <c r="D34" s="23">
-        <f>IF($A34&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A34-Inputs!$B$80),0)</f>
+        <f>IF($A34&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A34-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E34" s="23">
-        <f>IF($A34&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A34-Inputs!$B$80),0)</f>
+        <f>IF($A34&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A34-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F34" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A34-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A34-Inputs!$B$83)</f>
         <v>828539.19373730628</v>
       </c>
       <c r="G34" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A34-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A34-Inputs!$B$83)</f>
         <v>304147.29896685929</v>
       </c>
       <c r="H34" s="23">
@@ -8322,15 +8373,15 @@
         <v>0</v>
       </c>
       <c r="K34" s="23">
-        <f>IF($A34&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A34-Inputs!$B$80),0)</f>
+        <f>IF($A34&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A34-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="23">
-        <f>IF(AND($A34&gt;=Inputs!$B$83,$A34&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A34-Inputs!$B$80),0)</f>
+        <f>IF(AND($A34&gt;=Inputs!$B$86,$A34&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A34-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="23">
-        <f>IF($A34&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A34-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A34&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A34&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A34-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A34&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1636102.7116837946</v>
       </c>
       <c r="N34" s="23">
@@ -8338,32 +8389,32 @@
         <v>786962.25948538142</v>
       </c>
       <c r="O34" s="23">
-        <f>IF($A34&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A34&gt;=Inputs!$B$84,$A34&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A34&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>268100</v>
       </c>
       <c r="P34" s="23">
-        <f>IF(AND(Inputs!$B$58=1,$A34=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A34&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A34=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A34&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q34" s="23">
-        <f>D34+E34-H34-I34+J34-K34-L34-M34-N34+O34+P34-IF($A34&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2155064.971169176</v>
+        <f>D34+E34-H34-I34+J34-K34-L34-M34-N34+O34+P34-IF($A34&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2154964.971169176</v>
       </c>
       <c r="R34" s="23">
         <f t="shared" si="3"/>
-        <v>16375640.327595206</v>
+        <v>15198058.165282382</v>
       </c>
       <c r="S34" s="23">
         <f>R34*Inputs!$B$35</f>
-        <v>786030.73572456988</v>
+        <v>729506.79193355434</v>
       </c>
       <c r="T34" s="23">
-        <f>IF($A34=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A34=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A34=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U34" s="23">
         <f t="shared" si="2"/>
-        <v>15006606.092150601</v>
+        <v>13772599.986046761</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -8379,19 +8430,19 @@
         <v>80</v>
       </c>
       <c r="D35" s="16">
-        <f>IF($A35&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A35-Inputs!$B$80),0)</f>
+        <f>IF($A35&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A35-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E35" s="16">
-        <f>IF($A35&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A35-Inputs!$B$80),0)</f>
+        <f>IF($A35&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A35-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F35" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A35-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A35-Inputs!$B$83)</f>
         <v>849252.67358073918</v>
       </c>
       <c r="G35" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A35-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A35-Inputs!$B$83)</f>
         <v>311750.98144103086</v>
       </c>
       <c r="H35" s="16">
@@ -8407,15 +8458,15 @@
         <v>0</v>
       </c>
       <c r="K35" s="16">
-        <f>IF($A35&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A35-Inputs!$B$80),0)</f>
+        <f>IF($A35&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A35-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L35" s="16">
-        <f>IF(AND($A35&gt;=Inputs!$B$83,$A35&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A35-Inputs!$B$80),0)</f>
+        <f>IF(AND($A35&gt;=Inputs!$B$86,$A35&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A35-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M35" s="16">
-        <f>IF($A35&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A35-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A35&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A35&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A35-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A35&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1677005.2794758901</v>
       </c>
       <c r="N35" s="16">
@@ -8423,32 +8474,32 @@
         <v>320636.7888385402</v>
       </c>
       <c r="O35" s="16">
-        <f>IF($A35&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A35&gt;=Inputs!$B$84,$A35&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A35&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P35" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A35=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A35&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A35=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A35&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q35" s="16">
-        <f>D35+E35-H35-I35+J35-K35-L35-M35-N35+O35+P35-IF($A35&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1729642.0683144303</v>
+        <f>D35+E35-H35-I35+J35-K35-L35-M35-N35+O35+P35-IF($A35&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1890342.0683144303</v>
       </c>
       <c r="R35" s="16">
         <f t="shared" si="3"/>
-        <v>15006606.092150601</v>
+        <v>13772599.986046761</v>
       </c>
       <c r="S35" s="16">
         <f>R35*Inputs!$B$35</f>
-        <v>720317.0924232289</v>
+        <v>661084.79933024454</v>
       </c>
       <c r="T35" s="16">
-        <f>IF($A35=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A35=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A35=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U35" s="16">
         <f t="shared" si="2"/>
-        <v>13997281.1162594</v>
+        <v>12543342.717062574</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -8464,19 +8515,19 @@
         <v>81</v>
       </c>
       <c r="D36" s="16">
-        <f>IF($A36&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A36-Inputs!$B$80),0)</f>
+        <f>IF($A36&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A36-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E36" s="16">
-        <f>IF($A36&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A36-Inputs!$B$80),0)</f>
+        <f>IF($A36&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A36-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F36" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A36-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A36-Inputs!$B$83)</f>
         <v>870483.99042025744</v>
       </c>
       <c r="G36" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A36-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A36-Inputs!$B$83)</f>
         <v>319544.75597705651</v>
       </c>
       <c r="H36" s="16">
@@ -8492,15 +8543,15 @@
         <v>0</v>
       </c>
       <c r="K36" s="16">
-        <f>IF($A36&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A36-Inputs!$B$80),0)</f>
+        <f>IF($A36&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A36-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L36" s="16">
-        <f>IF(AND($A36&gt;=Inputs!$B$83,$A36&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A36-Inputs!$B$80),0)</f>
+        <f>IF(AND($A36&gt;=Inputs!$B$86,$A36&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A36-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M36" s="16">
-        <f>IF($A36&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A36-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A36&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A36&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A36-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A36&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1718930.4114627868</v>
       </c>
       <c r="N36" s="16">
@@ -8508,32 +8559,32 @@
         <v>361131.66369229648</v>
       </c>
       <c r="O36" s="16">
-        <f>IF($A36&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A36&gt;=Inputs!$B$84,$A36&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A36&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P36" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A36=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A36&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A36=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A36&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q36" s="16">
-        <f>D36+E36-H36-I36+J36-K36-L36-M36-N36+O36+P36-IF($A36&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1812062.0751550833</v>
+        <f>D36+E36-H36-I36+J36-K36-L36-M36-N36+O36+P36-IF($A36&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-1972762.0751550833</v>
       </c>
       <c r="R36" s="16">
         <f t="shared" si="3"/>
-        <v>13997281.1162594</v>
+        <v>12543342.717062574</v>
       </c>
       <c r="S36" s="16">
         <f>R36*Inputs!$B$35</f>
-        <v>671869.49358045124</v>
+        <v>602080.45041900361</v>
       </c>
       <c r="T36" s="16">
-        <f>IF($A36=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A36=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A36=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U36" s="16">
         <f t="shared" si="2"/>
-        <v>12857088.534684768</v>
+        <v>11172661.092326494</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -8549,19 +8600,19 @@
         <v>82</v>
       </c>
       <c r="D37" s="16">
-        <f>IF($A37&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A37-Inputs!$B$80),0)</f>
+        <f>IF($A37&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A37-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E37" s="16">
-        <f>IF($A37&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A37-Inputs!$B$80),0)</f>
+        <f>IF($A37&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A37-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F37" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A37-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A37-Inputs!$B$83)</f>
         <v>892246.09018076386</v>
       </c>
       <c r="G37" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A37-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A37-Inputs!$B$83)</f>
         <v>327533.37487648294</v>
       </c>
       <c r="H37" s="16">
@@ -8577,15 +8628,15 @@
         <v>0</v>
       </c>
       <c r="K37" s="16">
-        <f>IF($A37&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A37-Inputs!$B$80),0)</f>
+        <f>IF($A37&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A37-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L37" s="16">
-        <f>IF(AND($A37&gt;=Inputs!$B$83,$A37&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A37-Inputs!$B$80),0)</f>
+        <f>IF(AND($A37&gt;=Inputs!$B$86,$A37&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A37-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M37" s="16">
-        <f>IF($A37&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A37-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A37&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A37&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A37-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A37&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1761903.6717493564</v>
       </c>
       <c r="N37" s="16">
@@ -8593,32 +8644,32 @@
         <v>405742.17836414505</v>
       </c>
       <c r="O37" s="16">
-        <f>IF($A37&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A37&gt;=Inputs!$B$84,$A37&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A37&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P37" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A37=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A37&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A37=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A37&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q37" s="16">
-        <f>D37+E37-H37-I37+J37-K37-L37-M37-N37+O37+P37-IF($A37&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1899645.8501135013</v>
+        <f>D37+E37-H37-I37+J37-K37-L37-M37-N37+O37+P37-IF($A37&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2060345.8501135013</v>
       </c>
       <c r="R37" s="16">
         <f t="shared" si="3"/>
-        <v>12857088.534684768</v>
+        <v>11172661.092326494</v>
       </c>
       <c r="S37" s="16">
         <f>R37*Inputs!$B$35</f>
-        <v>617140.24966486893</v>
+        <v>536287.7324316717</v>
       </c>
       <c r="T37" s="16">
-        <f>IF($A37=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A37=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A37=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U37" s="16">
         <f t="shared" si="2"/>
-        <v>11574582.934236135</v>
+        <v>9648602.9746446647</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -8634,19 +8685,19 @@
         <v>83</v>
       </c>
       <c r="D38" s="16">
-        <f>IF($A38&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A38-Inputs!$B$80),0)</f>
+        <f>IF($A38&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A38-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E38" s="16">
-        <f>IF($A38&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A38-Inputs!$B$80),0)</f>
+        <f>IF($A38&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A38-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F38" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A38-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A38-Inputs!$B$83)</f>
         <v>914552.24243528291</v>
       </c>
       <c r="G38" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A38-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A38-Inputs!$B$83)</f>
         <v>335721.709248395</v>
       </c>
       <c r="H38" s="16">
@@ -8662,15 +8713,15 @@
         <v>0</v>
       </c>
       <c r="K38" s="16">
-        <f>IF($A38&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A38-Inputs!$B$80),0)</f>
+        <f>IF($A38&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A38-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L38" s="16">
-        <f>IF(AND($A38&gt;=Inputs!$B$83,$A38&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A38-Inputs!$B$80),0)</f>
+        <f>IF(AND($A38&gt;=Inputs!$B$86,$A38&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A38-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M38" s="16">
-        <f>IF($A38&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A38-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A38&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A38&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A38-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A38&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1805951.2635430903</v>
       </c>
       <c r="N38" s="16">
@@ -8678,32 +8729,32 @@
         <v>454867.73190867808</v>
       </c>
       <c r="O38" s="16">
-        <f>IF($A38&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A38&gt;=Inputs!$B$84,$A38&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A38&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P38" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A38=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A38&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A38=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A38&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q38" s="16">
-        <f>D38+E38-H38-I38+J38-K38-L38-M38-N38+O38+P38-IF($A38&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-1992818.9954517684</v>
+        <f>D38+E38-H38-I38+J38-K38-L38-M38-N38+O38+P38-IF($A38&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2153518.9954517684</v>
       </c>
       <c r="R38" s="16">
         <f t="shared" si="3"/>
-        <v>11574582.934236135</v>
+        <v>9648602.9746446647</v>
       </c>
       <c r="S38" s="16">
         <f>R38*Inputs!$B$35</f>
-        <v>555579.98084333446</v>
+        <v>463132.94278294389</v>
       </c>
       <c r="T38" s="16">
-        <f>IF($A38=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A38=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A38=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U38" s="16">
         <f t="shared" si="2"/>
-        <v>10137343.919627702</v>
+        <v>7958216.9219758399</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -8719,19 +8770,19 @@
         <v>84</v>
       </c>
       <c r="D39" s="16">
-        <f>IF($A39&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A39-Inputs!$B$80),0)</f>
+        <f>IF($A39&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A39-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E39" s="16">
-        <f>IF($A39&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A39-Inputs!$B$80),0)</f>
+        <f>IF($A39&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A39-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F39" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A39-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A39-Inputs!$B$83)</f>
         <v>937416.04849616485</v>
       </c>
       <c r="G39" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A39-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A39-Inputs!$B$83)</f>
         <v>344114.75197960483</v>
       </c>
       <c r="H39" s="16">
@@ -8747,15 +8798,15 @@
         <v>0</v>
       </c>
       <c r="K39" s="16">
-        <f>IF($A39&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A39-Inputs!$B$80),0)</f>
+        <f>IF($A39&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A39-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="16">
-        <f>IF(AND($A39&gt;=Inputs!$B$83,$A39&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A39-Inputs!$B$80),0)</f>
+        <f>IF(AND($A39&gt;=Inputs!$B$86,$A39&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A39-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="16">
-        <f>IF($A39&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A39-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A39&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A39&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A39-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A39&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1851100.0451316673</v>
       </c>
       <c r="N39" s="16">
@@ -8763,32 +8814,32 @@
         <v>508946.03882352327</v>
       </c>
       <c r="O39" s="16">
-        <f>IF($A39&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A39&gt;=Inputs!$B$84,$A39&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A39&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P39" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A39=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A39&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A39=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A39&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q39" s="16">
-        <f>D39+E39-H39-I39+J39-K39-L39-M39-N39+O39+P39-IF($A39&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2092046.0839551906</v>
+        <f>D39+E39-H39-I39+J39-K39-L39-M39-N39+O39+P39-IF($A39&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2252746.0839551906</v>
       </c>
       <c r="R39" s="16">
         <f t="shared" si="3"/>
-        <v>10137343.919627702</v>
+        <v>7958216.9219758399</v>
       </c>
       <c r="S39" s="16">
         <f>R39*Inputs!$B$35</f>
-        <v>486592.50814212969</v>
+        <v>381994.41225484031</v>
       </c>
       <c r="T39" s="16">
-        <f>IF($A39=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A39=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A39=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U39" s="16">
         <f t="shared" si="2"/>
-        <v>8531890.3438146412</v>
+        <v>6087465.2502754889</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -8804,19 +8855,19 @@
         <v>85</v>
       </c>
       <c r="D40" s="16">
-        <f>IF($A40&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A40-Inputs!$B$80),0)</f>
+        <f>IF($A40&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A40-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E40" s="16">
-        <f>IF($A40&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A40-Inputs!$B$80),0)</f>
+        <f>IF($A40&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A40-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F40" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A40-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A40-Inputs!$B$83)</f>
         <v>960851.4497085691</v>
       </c>
       <c r="G40" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A40-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A40-Inputs!$B$83)</f>
         <v>352717.62077909498</v>
       </c>
       <c r="H40" s="16">
@@ -8832,15 +8883,15 @@
         <v>0</v>
       </c>
       <c r="K40" s="16">
-        <f>IF($A40&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A40-Inputs!$B$80),0)</f>
+        <f>IF($A40&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A40-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="16">
-        <f>IF(AND($A40&gt;=Inputs!$B$83,$A40&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A40-Inputs!$B$80),0)</f>
+        <f>IF(AND($A40&gt;=Inputs!$B$86,$A40&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A40-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="16">
-        <f>IF($A40&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A40-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A40&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A40&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A40-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A40&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1897377.5462599592</v>
       </c>
       <c r="N40" s="16">
@@ -8848,32 +8899,32 @@
         <v>568456.79382758285</v>
       </c>
       <c r="O40" s="16">
-        <f>IF($A40&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A40&gt;=Inputs!$B$84,$A40&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A40&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P40" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A40=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A40&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A40=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A40&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q40" s="16">
-        <f>D40+E40-H40-I40+J40-K40-L40-M40-N40+O40+P40-IF($A40&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2197834.3400875423</v>
+        <f>D40+E40-H40-I40+J40-K40-L40-M40-N40+O40+P40-IF($A40&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2358534.3400875423</v>
       </c>
       <c r="R40" s="16">
         <f t="shared" si="3"/>
-        <v>8531890.3438146412</v>
+        <v>6087465.2502754889</v>
       </c>
       <c r="S40" s="16">
         <f>R40*Inputs!$B$35</f>
-        <v>409530.73650310282</v>
+        <v>292198.33201322349</v>
       </c>
       <c r="T40" s="16">
-        <f>IF($A40=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A40=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A40=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U40" s="16">
         <f t="shared" si="2"/>
-        <v>6743586.7402302008</v>
+        <v>4021129.24220117</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -8889,19 +8940,19 @@
         <v>86</v>
       </c>
       <c r="D41" s="16">
-        <f>IF($A41&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A41-Inputs!$B$80),0)</f>
+        <f>IF($A41&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A41-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E41" s="16">
-        <f>IF($A41&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A41-Inputs!$B$80),0)</f>
+        <f>IF($A41&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A41-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F41" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A41-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A41-Inputs!$B$83)</f>
         <v>984872.73595128313</v>
       </c>
       <c r="G41" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A41-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A41-Inputs!$B$83)</f>
         <v>361535.56129857228</v>
       </c>
       <c r="H41" s="16">
@@ -8917,15 +8968,15 @@
         <v>0</v>
       </c>
       <c r="K41" s="16">
-        <f>IF($A41&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A41-Inputs!$B$80),0)</f>
+        <f>IF($A41&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A41-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L41" s="16">
-        <f>IF(AND($A41&gt;=Inputs!$B$83,$A41&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A41-Inputs!$B$80),0)</f>
+        <f>IF(AND($A41&gt;=Inputs!$B$86,$A41&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A41-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M41" s="16">
-        <f>IF($A41&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A41-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A41&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A41&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A41-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A41&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1944811.9849164579</v>
       </c>
       <c r="N41" s="16">
@@ -8933,32 +8984,32 @@
         <v>633925.68689425697</v>
       </c>
       <c r="O41" s="16">
-        <f>IF($A41&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A41&gt;=Inputs!$B$84,$A41&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A41&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P41" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A41=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A41&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A41=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A41&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q41" s="16">
-        <f>D41+E41-H41-I41+J41-K41-L41-M41-N41+O41+P41-IF($A41&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2310737.671810715</v>
+        <f>D41+E41-H41-I41+J41-K41-L41-M41-N41+O41+P41-IF($A41&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2471437.671810715</v>
       </c>
       <c r="R41" s="16">
         <f t="shared" si="3"/>
-        <v>6743586.7402302008</v>
+        <v>4021129.24220117</v>
       </c>
       <c r="S41" s="16">
         <f>R41*Inputs!$B$35</f>
-        <v>323692.16353104962</v>
+        <v>193014.20362565617</v>
       </c>
       <c r="T41" s="16">
-        <f>IF($A41=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A41=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A41=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U41" s="16">
         <f t="shared" si="2"/>
-        <v>4756541.2319505364</v>
+        <v>1742705.7740161107</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -8974,19 +9025,19 @@
         <v>87</v>
       </c>
       <c r="D42" s="16">
-        <f>IF($A42&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A42-Inputs!$B$80),0)</f>
+        <f>IF($A42&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A42-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E42" s="16">
-        <f>IF($A42&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A42-Inputs!$B$80),0)</f>
+        <f>IF($A42&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A42-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F42" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A42-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A42-Inputs!$B$83)</f>
         <v>1009494.5543500651</v>
       </c>
       <c r="G42" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A42-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A42-Inputs!$B$83)</f>
         <v>370573.95033103653</v>
       </c>
       <c r="H42" s="16">
@@ -9002,15 +9053,15 @@
         <v>0</v>
       </c>
       <c r="K42" s="16">
-        <f>IF($A42&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A42-Inputs!$B$80),0)</f>
+        <f>IF($A42&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A42-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L42" s="16">
-        <f>IF(AND($A42&gt;=Inputs!$B$83,$A42&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A42-Inputs!$B$80),0)</f>
+        <f>IF(AND($A42&gt;=Inputs!$B$86,$A42&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A42-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M42" s="16">
-        <f>IF($A42&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A42-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A42&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A42&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A42-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A42&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>1993432.2845393689</v>
       </c>
       <c r="N42" s="16">
@@ -9018,32 +9069,32 @@
         <v>705928.80200788286</v>
       </c>
       <c r="O42" s="16">
-        <f>IF($A42&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A42&gt;=Inputs!$B$84,$A42&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A42&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P42" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A42=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A42&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A42=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A42&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q42" s="16">
-        <f>D42+E42-H42-I42+J42-K42-L42-M42-N42+O42+P42-IF($A42&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2431361.0865472518</v>
+        <f>D42+E42-H42-I42+J42-K42-L42-M42-N42+O42+P42-IF($A42&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2592061.0865472518</v>
       </c>
       <c r="R42" s="16">
         <f t="shared" si="3"/>
-        <v>4756541.2319505364</v>
+        <v>1742705.7740161107</v>
       </c>
       <c r="S42" s="16">
         <f>R42*Inputs!$B$35</f>
-        <v>228313.97913362575</v>
+        <v>83649.877152773319</v>
       </c>
       <c r="T42" s="16">
-        <f>IF($A42=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A42=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A42=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U42" s="16">
         <f t="shared" si="2"/>
-        <v>2553494.1245369101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -9059,19 +9110,19 @@
         <v>88</v>
       </c>
       <c r="D43" s="16">
-        <f>IF($A43&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A43-Inputs!$B$80),0)</f>
+        <f>IF($A43&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A43-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E43" s="16">
-        <f>IF($A43&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A43-Inputs!$B$80),0)</f>
+        <f>IF($A43&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A43-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F43" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A43-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A43-Inputs!$B$83)</f>
         <v>1034731.9182088168</v>
       </c>
       <c r="G43" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A43-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A43-Inputs!$B$83)</f>
         <v>379838.2990893125</v>
       </c>
       <c r="H43" s="16">
@@ -9087,15 +9138,15 @@
         <v>0</v>
       </c>
       <c r="K43" s="16">
-        <f>IF($A43&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A43-Inputs!$B$80),0)</f>
+        <f>IF($A43&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A43-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="16">
-        <f>IF(AND($A43&gt;=Inputs!$B$83,$A43&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A43-Inputs!$B$80),0)</f>
+        <f>IF(AND($A43&gt;=Inputs!$B$86,$A43&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A43-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="16">
-        <f>IF($A43&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A43-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A43&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A43&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A43-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A43&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2043268.0916528534</v>
       </c>
       <c r="N43" s="16">
@@ -9103,32 +9154,32 @@
         <v>785097.43630947405</v>
       </c>
       <c r="O43" s="16">
-        <f>IF($A43&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A43&gt;=Inputs!$B$84,$A43&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A43&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P43" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A43=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A43&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A43=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A43&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q43" s="16">
-        <f>D43+E43-H43-I43+J43-K43-L43-M43-N43+O43+P43-IF($A43&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2560365.5279623275</v>
+        <f>D43+E43-H43-I43+J43-K43-L43-M43-N43+O43+P43-IF($A43&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2721065.5279623275</v>
       </c>
       <c r="R43" s="16">
         <f t="shared" si="3"/>
-        <v>2553494.1245369101</v>
+        <v>0</v>
       </c>
       <c r="S43" s="16">
         <f>R43*Inputs!$B$35</f>
-        <v>122567.71797777168</v>
+        <v>0</v>
       </c>
       <c r="T43" s="16">
-        <f>IF($A43=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A43=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A43=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U43" s="16">
         <f t="shared" si="2"/>
-        <v>115696.31455235416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -9144,19 +9195,19 @@
         <v>89</v>
       </c>
       <c r="D44" s="23">
-        <f>IF($A44&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A44-Inputs!$B$80),0)</f>
+        <f>IF($A44&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A44-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E44" s="23">
-        <f>IF($A44&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A44-Inputs!$B$80),0)</f>
+        <f>IF($A44&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A44-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F44" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A44-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A44-Inputs!$B$83)</f>
         <v>1060600.2161640371</v>
       </c>
       <c r="G44" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A44-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A44-Inputs!$B$83)</f>
         <v>389334.25656654523</v>
       </c>
       <c r="H44" s="23">
@@ -9172,15 +9223,15 @@
         <v>0</v>
       </c>
       <c r="K44" s="23">
-        <f>IF($A44&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A44-Inputs!$B$80),0)</f>
+        <f>IF($A44&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A44-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L44" s="23">
-        <f>IF(AND($A44&gt;=Inputs!$B$83,$A44&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A44-Inputs!$B$80),0)</f>
+        <f>IF(AND($A44&gt;=Inputs!$B$86,$A44&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A44-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M44" s="23">
-        <f>IF($A44&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A44-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A44&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A44&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A44-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A44&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2094349.7939441744</v>
       </c>
       <c r="N44" s="23">
@@ -9188,27 +9239,27 @@
         <v>872123.3798012404</v>
       </c>
       <c r="O44" s="23">
-        <f>IF($A44&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A44&gt;=Inputs!$B$84,$A44&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A44&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P44" s="23">
-        <f>IF(AND(Inputs!$B$58=1,$A44=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A44&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A44=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A44&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q44" s="23">
-        <f>D44+E44-H44-I44+J44-K44-L44-M44-N44+O44+P44-IF($A44&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2698473.1737454147</v>
+        <f>D44+E44-H44-I44+J44-K44-L44-M44-N44+O44+P44-IF($A44&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-2859173.1737454147</v>
       </c>
       <c r="R44" s="23">
         <f t="shared" si="3"/>
-        <v>115696.31455235416</v>
+        <v>0</v>
       </c>
       <c r="S44" s="23">
         <f>R44*Inputs!$B$35</f>
-        <v>5553.4230985129998</v>
+        <v>0</v>
       </c>
       <c r="T44" s="23">
-        <f>IF($A44=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A44=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A44=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U44" s="23">
@@ -9229,19 +9280,19 @@
         <v>90</v>
       </c>
       <c r="D45" s="16">
-        <f>IF($A45&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A45-Inputs!$B$80),0)</f>
+        <f>IF($A45&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A45-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E45" s="16">
-        <f>IF($A45&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A45-Inputs!$B$80),0)</f>
+        <f>IF($A45&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A45-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F45" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A45-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A45-Inputs!$B$83)</f>
         <v>1087115.2215681379</v>
       </c>
       <c r="G45" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A45-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A45-Inputs!$B$83)</f>
         <v>399067.61298070889</v>
       </c>
       <c r="H45" s="16">
@@ -9257,15 +9308,15 @@
         <v>0</v>
       </c>
       <c r="K45" s="16">
-        <f>IF($A45&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A45-Inputs!$B$80),0)</f>
+        <f>IF($A45&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A45-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L45" s="16">
-        <f>IF(AND($A45&gt;=Inputs!$B$83,$A45&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A45-Inputs!$B$80),0)</f>
+        <f>IF(AND($A45&gt;=Inputs!$B$86,$A45&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A45-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M45" s="16">
-        <f>IF($A45&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A45-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A45&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A45&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A45-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A45&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2146708.5387927787</v>
       </c>
       <c r="N45" s="16">
@@ -9273,16 +9324,16 @@
         <v>967764.69961750961</v>
       </c>
       <c r="O45" s="16">
-        <f>IF($A45&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A45&gt;=Inputs!$B$84,$A45&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A45&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P45" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A45=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A45&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A45=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A45&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q45" s="16">
-        <f>D45+E45-H45-I45+J45-K45-L45-M45-N45+O45+P45-IF($A45&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-2846473.2384102885</v>
+        <f>D45+E45-H45-I45+J45-K45-L45-M45-N45+O45+P45-IF($A45&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-3007173.2384102885</v>
       </c>
       <c r="R45" s="16">
         <f t="shared" si="3"/>
@@ -9293,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="16">
-        <f>IF($A45=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A45=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A45=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U45" s="16">
@@ -9314,19 +9365,19 @@
         <v>91</v>
       </c>
       <c r="D46" s="16">
-        <f>IF($A46&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A46-Inputs!$B$80),0)</f>
+        <f>IF($A46&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A46-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E46" s="16">
-        <f>IF($A46&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A46-Inputs!$B$80),0)</f>
+        <f>IF($A46&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A46-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F46" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A46-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A46-Inputs!$B$83)</f>
         <v>1114293.1021073414</v>
       </c>
       <c r="G46" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A46-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A46-Inputs!$B$83)</f>
         <v>409044.30330522655</v>
       </c>
       <c r="H46" s="16">
@@ -9342,15 +9393,15 @@
         <v>0</v>
       </c>
       <c r="K46" s="16">
-        <f>IF($A46&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A46-Inputs!$B$80),0)</f>
+        <f>IF($A46&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A46-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="16">
-        <f>IF(AND($A46&gt;=Inputs!$B$83,$A46&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A46-Inputs!$B$80),0)</f>
+        <f>IF(AND($A46&gt;=Inputs!$B$86,$A46&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A46-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="16">
-        <f>IF($A46&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A46-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A46&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A46&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A46-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A46&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2200376.2522625979</v>
       </c>
       <c r="N46" s="16">
@@ -9358,16 +9409,16 @@
         <v>1072852.0770745291</v>
       </c>
       <c r="O46" s="16">
-        <f>IF($A46&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A46&gt;=Inputs!$B$84,$A46&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A46&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P46" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A46=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A46&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A46=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A46&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q46" s="16">
-        <f>D46+E46-H46-I46+J46-K46-L46-M46-N46+O46+P46-IF($A46&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-3005228.329337127</v>
+        <f>D46+E46-H46-I46+J46-K46-L46-M46-N46+O46+P46-IF($A46&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-3165928.329337127</v>
       </c>
       <c r="R46" s="16">
         <f t="shared" si="3"/>
@@ -9378,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="16">
-        <f>IF($A46=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A46=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A46=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U46" s="16">
@@ -9399,19 +9450,19 @@
         <v>92</v>
       </c>
       <c r="D47" s="16">
-        <f>IF($A47&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A47-Inputs!$B$80),0)</f>
+        <f>IF($A47&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A47-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E47" s="16">
-        <f>IF($A47&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A47-Inputs!$B$80),0)</f>
+        <f>IF($A47&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A47-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F47" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A47-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A47-Inputs!$B$83)</f>
         <v>1142150.4296600248</v>
       </c>
       <c r="G47" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A47-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A47-Inputs!$B$83)</f>
         <v>419270.41088785726</v>
       </c>
       <c r="H47" s="16">
@@ -9427,15 +9478,15 @@
         <v>0</v>
       </c>
       <c r="K47" s="16">
-        <f>IF($A47&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A47-Inputs!$B$80),0)</f>
+        <f>IF($A47&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A47-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="16">
-        <f>IF(AND($A47&gt;=Inputs!$B$83,$A47&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A47-Inputs!$B$80),0)</f>
+        <f>IF(AND($A47&gt;=Inputs!$B$86,$A47&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A47-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="16">
-        <f>IF($A47&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A47-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A47&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A47&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A47-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A47&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2255385.6585691632</v>
       </c>
       <c r="N47" s="16">
@@ -9443,16 +9494,16 @@
         <v>1188295.7503182599</v>
       </c>
       <c r="O47" s="16">
-        <f>IF($A47&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A47&gt;=Inputs!$B$84,$A47&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A47&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P47" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A47=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A47&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A47=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A47&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q47" s="16">
-        <f>D47+E47-H47-I47+J47-K47-L47-M47-N47+O47+P47-IF($A47&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-3175681.4088874231</v>
+        <f>D47+E47-H47-I47+J47-K47-L47-M47-N47+O47+P47-IF($A47&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-3336381.4088874231</v>
       </c>
       <c r="R47" s="16">
         <f t="shared" si="3"/>
@@ -9463,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="16">
-        <f>IF($A47=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A47=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A47=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U47" s="16">
@@ -9484,19 +9535,19 @@
         <v>93</v>
       </c>
       <c r="D48" s="16">
-        <f>IF($A48&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A48-Inputs!$B$80),0)</f>
+        <f>IF($A48&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A48-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E48" s="16">
-        <f>IF($A48&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A48-Inputs!$B$80),0)</f>
+        <f>IF($A48&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A48-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F48" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A48-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A48-Inputs!$B$83)</f>
         <v>1170704.1904015252</v>
       </c>
       <c r="G48" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A48-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A48-Inputs!$B$83)</f>
         <v>429752.17116005358</v>
       </c>
       <c r="H48" s="16">
@@ -9512,15 +9563,15 @@
         <v>0</v>
       </c>
       <c r="K48" s="16">
-        <f>IF($A48&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A48-Inputs!$B$80),0)</f>
+        <f>IF($A48&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A48-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L48" s="16">
-        <f>IF(AND($A48&gt;=Inputs!$B$83,$A48&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A48-Inputs!$B$80),0)</f>
+        <f>IF(AND($A48&gt;=Inputs!$B$86,$A48&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A48-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M48" s="16">
-        <f>IF($A48&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A48-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A48&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A48&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A48-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A48&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2311770.3000333915</v>
       </c>
       <c r="N48" s="16">
@@ -9528,16 +9579,16 @@
         <v>1315093.1204360425</v>
       </c>
       <c r="O48" s="16">
-        <f>IF($A48&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A48&gt;=Inputs!$B$84,$A48&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A48&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P48" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A48=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A48&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A48=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A48&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q48" s="16">
-        <f>D48+E48-H48-I48+J48-K48-L48-M48-N48+O48+P48-IF($A48&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-3358863.420469434</v>
+        <f>D48+E48-H48-I48+J48-K48-L48-M48-N48+O48+P48-IF($A48&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-3519563.420469434</v>
       </c>
       <c r="R48" s="16">
         <f t="shared" si="3"/>
@@ -9548,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="16">
-        <f>IF($A48=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A48=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A48=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U48" s="16">
@@ -9569,19 +9620,19 @@
         <v>94</v>
       </c>
       <c r="D49" s="16">
-        <f>IF($A49&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A49-Inputs!$B$80),0)</f>
+        <f>IF($A49&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A49-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E49" s="16">
-        <f>IF($A49&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A49-Inputs!$B$80),0)</f>
+        <f>IF($A49&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A49-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F49" s="16">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A49-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A49-Inputs!$B$83)</f>
         <v>1199971.7951615634</v>
       </c>
       <c r="G49" s="16">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A49-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A49-Inputs!$B$83)</f>
         <v>440495.97543905495</v>
       </c>
       <c r="H49" s="16">
@@ -9597,15 +9648,15 @@
         <v>0</v>
       </c>
       <c r="K49" s="16">
-        <f>IF($A49&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A49-Inputs!$B$80),0)</f>
+        <f>IF($A49&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A49-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L49" s="16">
-        <f>IF(AND($A49&gt;=Inputs!$B$83,$A49&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A49-Inputs!$B$80),0)</f>
+        <f>IF(AND($A49&gt;=Inputs!$B$86,$A49&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A49-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M49" s="16">
-        <f>IF($A49&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A49-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A49&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A49&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A49-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A49&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2369564.5575342267</v>
       </c>
       <c r="N49" s="16">
@@ -9613,16 +9664,16 @@
         <v>1454337.0844270117</v>
       </c>
       <c r="O49" s="16">
-        <f>IF($A49&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A49&gt;=Inputs!$B$84,$A49&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A49&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P49" s="16">
-        <f>IF(AND(Inputs!$B$58=1,$A49=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A49&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A49=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A49&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q49" s="16">
-        <f>D49+E49-H49-I49+J49-K49-L49-M49-N49+O49+P49-IF($A49&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-3555901.6419612383</v>
+        <f>D49+E49-H49-I49+J49-K49-L49-M49-N49+O49+P49-IF($A49&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-3716601.6419612383</v>
       </c>
       <c r="R49" s="16">
         <f t="shared" si="3"/>
@@ -9633,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="16">
-        <f>IF($A49=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A49=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A49=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U49" s="16">
@@ -9654,19 +9705,19 @@
         <v>95</v>
       </c>
       <c r="D50" s="23">
-        <f>IF($A50&lt;Inputs!$B$81,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A50-Inputs!$B$80),0)</f>
+        <f>IF($A50&lt;Inputs!$B$84,(Inputs!$B$27+Inputs!$B$28)*(1+Inputs!$B$6)^($A50-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="E50" s="23">
-        <f>IF($A50&lt;Inputs!$B$82,Inputs!$B$29*(1+Inputs!$B$7)^($A50-Inputs!$B$80),0)</f>
+        <f>IF($A50&lt;Inputs!$B$85,Inputs!$B$29*(1+Inputs!$B$7)^($A50-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="F50" s="23">
-        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A50-Inputs!$B$80)</f>
+        <f>(Inputs!$B$18+Inputs!$B$20+2*Inputs!$B$21)*(1+Inputs!$B$5)^($A50-Inputs!$B$83)</f>
         <v>1229971.0900406023</v>
       </c>
       <c r="G50" s="23">
-        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A50-Inputs!$B$80)</f>
+        <f>Inputs!$B$18*(1+Inputs!$B$5)^($A50-Inputs!$B$83)</f>
         <v>451508.37482503121</v>
       </c>
       <c r="H50" s="23">
@@ -9682,15 +9733,15 @@
         <v>0</v>
       </c>
       <c r="K50" s="23">
-        <f>IF($A50&lt;Inputs!$B$81,Inputs!$B$31*(1+Inputs!$B$5)^($A50-Inputs!$B$80),0)</f>
+        <f>IF($A50&lt;Inputs!$B$84,Inputs!$B$31*(1+Inputs!$B$5)^($A50-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="L50" s="23">
-        <f>IF(AND($A50&gt;=Inputs!$B$83,$A50&lt;Inputs!$B$83+Inputs!$B$41),Inputs!$B$40*(1+Inputs!$B$8)^($A50-Inputs!$B$80),0)</f>
+        <f>IF(AND($A50&gt;=Inputs!$B$86,$A50&lt;Inputs!$B$86+Inputs!$B$44),Inputs!$B$43*(1+Inputs!$B$8)^($A50-Inputs!$B$83),0)</f>
         <v>0</v>
       </c>
       <c r="M50" s="23">
-        <f>IF($A50&gt;=Inputs!$B$81,Inputs!$B$32*(1+Inputs!$B$5)^($A50-Inputs!$B$80)*IF(AND(Inputs!$B$55=1,$A50&gt;Inputs!$B$84),Inputs!$B$54,1),0)</f>
+        <f>IF($A50&gt;=Inputs!$B$84,Inputs!$B$32*(1+Inputs!$B$5)^($A50-Inputs!$B$83)*IF(AND(Inputs!$B$58=1,$A50&gt;Inputs!$B$87),Inputs!$B$57,1),0)</f>
         <v>2428803.6714725816</v>
       </c>
       <c r="N50" s="23">
@@ -9698,16 +9749,16 @@
         <v>1607225.1644833817</v>
       </c>
       <c r="O50" s="23">
-        <f>IF($A50&gt;=Inputs!$B$81,Inputs!$B$39,0)</f>
-        <v>268000</v>
+        <f>IF(AND($A50&gt;=Inputs!$B$84,$A50&lt;=Inputs!$B$87),Inputs!$B$39,0)+IF($A50&gt;=Inputs!$B$85,Inputs!$B$42,0)</f>
+        <v>107300</v>
       </c>
       <c r="P50" s="23">
-        <f>IF(AND(Inputs!$B$58=1,$A50=Inputs!$B$57),Inputs!$B$56,0)+IF(AND(Inputs!$B$61=1,$A50&gt;=Inputs!$B$60),Inputs!$B$59,0)</f>
+        <f>IF(AND(Inputs!$B$61=1,$A50=Inputs!$B$60),Inputs!$B$59,0)+IF(AND(Inputs!$B$64=1,$A50&gt;=Inputs!$B$63),Inputs!$B$62,0)</f>
         <v>0</v>
       </c>
       <c r="Q50" s="23">
-        <f>D50+E50-H50-I50+J50-K50-L50-M50-N50+O50+P50-IF($A50&lt;Inputs!$B$81,Inputs!$B$42,0)</f>
-        <v>-3768028.8359559635</v>
+        <f>D50+E50-H50-I50+J50-K50-L50-M50-N50+O50+P50-IF($A50&lt;Inputs!$B$84,Inputs!$B$45,0)</f>
+        <v>-3928728.8359559635</v>
       </c>
       <c r="R50" s="23">
         <f t="shared" si="3"/>
@@ -9718,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="23">
-        <f>IF($A50=Inputs!$B$81,-Inputs!$B$38,0)</f>
+        <f>IF($A50=Inputs!$B$84,-Inputs!$B$38-Inputs!$B$41,0)+IF($A50=Inputs!$B$85,-Inputs!$B$40,0)</f>
         <v>0</v>
       </c>
       <c r="U50" s="23">
@@ -9742,23 +9793,23 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B5" s="24">
         <f>BalanceSheet!B33</f>
@@ -9767,7 +9818,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B6" s="24">
         <f>BalanceSheet!$B$37</f>
@@ -9776,16 +9827,16 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B7" s="24">
-        <f>Tax!B27-Inputs!$B$42</f>
+        <f>Tax!B27-Inputs!$B$45</f>
         <v>604630</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B8" s="25">
         <f>BalanceSheet!B7/(Inputs!$B$31/12)</f>
@@ -9794,13 +9845,13 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B10" s="24">
         <f>Tax!B15</f>
@@ -9809,7 +9860,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B11" s="24">
         <f>Tax!B16</f>
@@ -9818,7 +9869,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B12" s="24">
         <f>Tax!B17</f>
@@ -9827,49 +9878,49 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B14" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$81,Projection!A:A,0))</f>
-        <v>21017126.919702914</v>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$84,Projection!A:A,0))</f>
+        <v>22259926.919702914</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B15" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$85,Projection!A:A,0))</f>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$88,Projection!A:A,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B16" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$86,Projection!A:A,0))</f>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$89,Projection!A:A,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B17" s="24">
-        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$81,Projection!A:A,0))/(1+Inputs!$B$5)^(Inputs!$B$81-Inputs!$B$80)</f>
-        <v>16018093.618086508</v>
+        <f>INDEX(Projection!U:U,MATCH(Inputs!$B$84,Projection!A:A,0))/(1+Inputs!$B$5)^(Inputs!$B$84-Inputs!$B$83)</f>
+        <v>16965287.153369173</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B18" s="24">
         <f>Inputs!$B$32*(1-(1+0.02)^-29)/0.02</f>
@@ -9878,49 +9929,49 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B19" s="26">
         <f>IFERROR(INDEX(Projection!A4:A50,MATCH(0,Projection!U4:U50,0)),0)</f>
-        <v>2066</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B20" s="26">
         <f>IF(B19=0,"lasts",B19-1977)</f>
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B21" s="27" t="str">
-        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$85,Projection!A:A,0))&gt;0,"YES","NO")</f>
+        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$88,Projection!A:A,0))&gt;0,"YES","NO")</f>
         <v>NO</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B22" s="27" t="str">
-        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$86,Projection!A:A,0))&gt;0,"YES","NO")</f>
+        <f>IF(INDEX(Projection!U:U,MATCH(Inputs!$B$89,Projection!A:A,0))&gt;0,"YES","NO")</f>
         <v>NO</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B23" s="4"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B24" s="24">
         <f>SUM(Projection!L4:L50)</f>
@@ -9929,28 +9980,28 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B25" s="24">
-        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$81,Projection!A:A,0))</f>
+        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$84,Projection!A:A,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B26" s="24">
-        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$85,Projection!A:A,0))</f>
+        <f>INDEX(Projection!N:N,MATCH(Inputs!$B$88,Projection!A:A,0))</f>
         <v>872123.3798012404</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B27" s="24">
-        <f>SUMPRODUCT((Projection!A4:A50&lt;=Inputs!$B$85)*Projection!N4:N50)</f>
+        <f>SUMPRODUCT((Projection!A4:A50&lt;=Inputs!$B$88)*Projection!N4:N50)</f>
         <v>11842102.254778726</v>
       </c>
     </row>
